--- a/Part2_PlatformBenchmarks_Results.xlsx
+++ b/Part2_PlatformBenchmarks_Results.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="503">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 2: Platform Benchmarks</t>
   </si>
@@ -1309,25 +1309,49 @@
     <t xml:space="preserve">Temperature Gain (°C)</t>
   </si>
   <si>
+    <t xml:space="preserve">n/a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advanced Math</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exp (ops/ms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log (ops/ms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log10 (ops/ms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pow (ops/ms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">atan2 (ops/ms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">asin (ops/ms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acos (ops/ms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tan (ops/ms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fmod (ops/ms)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Serial</t>
   </si>
   <si>
+    <t xml:space="preserve">Enqueue (B/ms)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Throughput (B/ms)</t>
   </si>
   <si>
-    <t xml:space="preserve">Advanced Math</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exp (ops/ms)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log (ops/ms)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pow (ops/ms)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">atan2 (ops/ms)</t>
+    <t xml:space="preserve">Ratio (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Timing</t>
@@ -1339,13 +1363,16 @@
     <t xml:space="preserve">micros() resolution (μs)</t>
   </si>
   <si>
+    <t xml:space="preserve">micros() error (μs)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Delay Accuracy</t>
   </si>
   <si>
-    <t xml:space="preserve">delay() deviation (ms)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">delayMicroseconds() deviation (μs)</t>
+    <t xml:space="preserve">average delay() deviation (ms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">average delayMicroseconds() deviation (μs)</t>
   </si>
   <si>
     <t xml:space="preserve">Stack</t>
@@ -1357,6 +1384,18 @@
     <t xml:space="preserve">Per-frame cost (bytes)</t>
   </si>
   <si>
+    <t xml:space="preserve">Per-level time (μs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I2C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 kHz speed (txn/ms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">400 kHz speed (txn/ms)</t>
+  </si>
+  <si>
     <t xml:space="preserve">WiFi</t>
   </si>
   <si>
@@ -1375,6 +1414,15 @@
     <t xml:space="preserve">Crypto</t>
   </si>
   <si>
+    <t xml:space="preserve">Public Key Generation (keys/sec)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Config write (bytes/sec)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC signing (ops/sec)</t>
+  </si>
+  <si>
     <t xml:space="preserve">SHA1 String (ops/ms)</t>
   </si>
   <si>
@@ -1396,7 +1444,7 @@
     <t xml:space="preserve">Hardware AES Decrypt (ops/ms)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hardware RNG (values/ms)</t>
+    <t xml:space="preserve">Hardware RNG (bytes/sec)</t>
   </si>
   <si>
     <t xml:space="preserve">Multi-Core</t>
@@ -1417,10 +1465,28 @@
     <t xml:space="preserve">Pattern switching (ops/ms)</t>
   </si>
   <si>
+    <t xml:space="preserve">Bitmap rendering (ops/ms)</t>
+  </si>
+  <si>
     <t xml:space="preserve">DAC</t>
   </si>
   <si>
-    <t xml:space="preserve">Write speed (ops/ms)</t>
+    <t xml:space="preserve">analogWrite() speed (ops/ms)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effective sample rate (kHz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read speed (ops/sec)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write speed (ops/sec)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accuracy (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Touch</t>
@@ -1442,15 +1508,6 @@
   </si>
   <si>
     <t xml:space="preserve">Speedup vs CPU (x)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I2C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100 kHz overhead (μs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">400 kHz overhead (μs)</t>
   </si>
   <si>
     <t xml:space="preserve">Watchdog</t>
@@ -1593,23 +1650,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1865,12 +1922,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:PI43"/>
+  <dimension ref="A1:PI60"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.06"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="425" min="3" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="38.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.87"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="425" min="4" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3586,8 +3644,12 @@
       <c r="B4" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
+      <c r="C4" s="5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>75.81</v>
+      </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
@@ -4017,8 +4079,12 @@
       <c r="B5" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -4443,13 +4509,17 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+        <v>431</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>36.86</v>
+      </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -4874,13 +4944,17 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
+      <c r="C7" s="5" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>37.79</v>
+      </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
@@ -5305,13 +5379,17 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>433</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
+      <c r="C8" s="5" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>37.71</v>
+      </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
@@ -5736,13 +5814,17 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>434</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+      <c r="C9" s="5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>17.41</v>
+      </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
@@ -6167,13 +6249,17 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
+      <c r="C10" s="5" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>173.91</v>
+      </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
@@ -6598,13 +6684,17 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="5" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>199.2</v>
+      </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
@@ -7029,13 +7119,17 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+        <v>437</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>205.76</v>
+      </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
@@ -7460,13 +7554,17 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+        <v>438</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>214.59</v>
+      </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
@@ -7891,13 +7989,17 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="C14" s="5" t="n">
+        <v>35.47</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>210.97</v>
+      </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -8322,13 +8424,17 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
+        <v>441</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>11.56</v>
+      </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
@@ -8753,13 +8859,17 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>442</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
+      <c r="C16" s="5" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>11.52</v>
+      </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -9184,13 +9294,17 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
+        <v>443</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>64.85</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>99.63</v>
+      </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -9615,13 +9729,17 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -10046,13 +10164,17 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
+        <v>446</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -10477,13 +10599,17 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
+      <c r="C20" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>51</v>
+      </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -10908,13 +11034,17 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
+        <v>449</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0.006</v>
+      </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -11339,13 +11469,17 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
+      <c r="C22" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.5</v>
+      </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -11770,13 +11904,17 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
+        <v>452</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>325</v>
+      </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -12201,13 +12339,17 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
+        <v>453</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>56</v>
+      </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -12632,13 +12774,17 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+        <v>454</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>0.61</v>
+      </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -13063,13 +13209,17 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="5" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>0.99</v>
+      </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -13494,13 +13644,17 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>457</v>
       </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
+      <c r="C27" s="5" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0.99</v>
+      </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
@@ -13925,13 +14079,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
+        <v>459</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -14356,13 +14514,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
+      <c r="C29" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -14787,13 +14949,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>461</v>
-      </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
+        <v>462</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>6</v>
+      </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -15218,13 +15384,17 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>462</v>
-      </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
+        <v>460</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>5068.28</v>
+      </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -15654,8 +15824,12 @@
       <c r="B32" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
+      <c r="C32" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>5.155</v>
+      </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -16080,13 +16254,17 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>465</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
+      <c r="C33" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>128000000</v>
+      </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
@@ -16511,13 +16689,17 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>468</v>
-      </c>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
+        <v>466</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>5.16</v>
+      </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
@@ -16942,13 +17124,17 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
+        <v>467</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
@@ -17373,13 +17559,17 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
+        <v>468</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -17804,13 +17994,17 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>473</v>
-      </c>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
+        <v>469</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -18235,13 +18429,17 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
+        <v>470</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -18666,13 +18864,17 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>476</v>
-      </c>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
+        <v>471</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
@@ -19097,13 +19299,17 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>477</v>
+        <v>463</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
+        <v>472</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -19528,13 +19734,17 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
+        <v>473</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -19959,13 +20169,17 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>479</v>
+        <v>463</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
+        <v>474</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>9142.04</v>
+      </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
@@ -20390,13 +20604,17 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>483</v>
-      </c>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
+        <v>476</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
@@ -20819,6 +21037,7401 @@
       <c r="PH43" s="5"/>
       <c r="PI43" s="5"/>
     </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="5"/>
+      <c r="R44" s="5"/>
+      <c r="S44" s="5"/>
+      <c r="T44" s="5"/>
+      <c r="U44" s="5"/>
+      <c r="V44" s="5"/>
+      <c r="W44" s="5"/>
+      <c r="X44" s="5"/>
+      <c r="Y44" s="5"/>
+      <c r="Z44" s="5"/>
+      <c r="AA44" s="5"/>
+      <c r="AB44" s="5"/>
+      <c r="AC44" s="5"/>
+      <c r="AD44" s="5"/>
+      <c r="AE44" s="5"/>
+      <c r="AF44" s="5"/>
+      <c r="AG44" s="5"/>
+      <c r="AH44" s="5"/>
+      <c r="AI44" s="5"/>
+      <c r="AJ44" s="5"/>
+      <c r="AK44" s="5"/>
+      <c r="AL44" s="5"/>
+      <c r="AM44" s="5"/>
+      <c r="AN44" s="5"/>
+      <c r="AO44" s="5"/>
+      <c r="AP44" s="5"/>
+      <c r="AQ44" s="5"/>
+      <c r="AR44" s="5"/>
+      <c r="AS44" s="5"/>
+      <c r="AT44" s="5"/>
+      <c r="AU44" s="5"/>
+      <c r="AV44" s="5"/>
+      <c r="AW44" s="5"/>
+      <c r="AX44" s="5"/>
+      <c r="AY44" s="5"/>
+      <c r="AZ44" s="5"/>
+      <c r="BA44" s="5"/>
+      <c r="BB44" s="5"/>
+      <c r="BC44" s="5"/>
+      <c r="BD44" s="5"/>
+      <c r="BE44" s="5"/>
+      <c r="BF44" s="5"/>
+      <c r="BG44" s="5"/>
+      <c r="BH44" s="5"/>
+      <c r="BI44" s="5"/>
+      <c r="BJ44" s="5"/>
+      <c r="BK44" s="5"/>
+      <c r="BL44" s="5"/>
+      <c r="BM44" s="5"/>
+      <c r="BN44" s="5"/>
+      <c r="BO44" s="5"/>
+      <c r="BP44" s="5"/>
+      <c r="BQ44" s="5"/>
+      <c r="BR44" s="5"/>
+      <c r="BS44" s="5"/>
+      <c r="BT44" s="5"/>
+      <c r="BU44" s="5"/>
+      <c r="BV44" s="5"/>
+      <c r="BW44" s="5"/>
+      <c r="BX44" s="5"/>
+      <c r="BY44" s="5"/>
+      <c r="BZ44" s="5"/>
+      <c r="CA44" s="5"/>
+      <c r="CB44" s="5"/>
+      <c r="CC44" s="5"/>
+      <c r="CD44" s="5"/>
+      <c r="CE44" s="5"/>
+      <c r="CF44" s="5"/>
+      <c r="CG44" s="5"/>
+      <c r="CH44" s="5"/>
+      <c r="CI44" s="5"/>
+      <c r="CJ44" s="5"/>
+      <c r="CK44" s="5"/>
+      <c r="CL44" s="5"/>
+      <c r="CM44" s="5"/>
+      <c r="CN44" s="5"/>
+      <c r="CO44" s="5"/>
+      <c r="CP44" s="5"/>
+      <c r="CQ44" s="5"/>
+      <c r="CR44" s="5"/>
+      <c r="CS44" s="5"/>
+      <c r="CT44" s="5"/>
+      <c r="CU44" s="5"/>
+      <c r="CV44" s="5"/>
+      <c r="CW44" s="5"/>
+      <c r="CX44" s="5"/>
+      <c r="CY44" s="5"/>
+      <c r="CZ44" s="5"/>
+      <c r="DA44" s="5"/>
+      <c r="DB44" s="5"/>
+      <c r="DC44" s="5"/>
+      <c r="DD44" s="5"/>
+      <c r="DE44" s="5"/>
+      <c r="DF44" s="5"/>
+      <c r="DG44" s="5"/>
+      <c r="DH44" s="5"/>
+      <c r="DI44" s="5"/>
+      <c r="DJ44" s="5"/>
+      <c r="DK44" s="5"/>
+      <c r="DL44" s="5"/>
+      <c r="DM44" s="5"/>
+      <c r="DN44" s="5"/>
+      <c r="DO44" s="5"/>
+      <c r="DP44" s="5"/>
+      <c r="DQ44" s="5"/>
+      <c r="DR44" s="5"/>
+      <c r="DS44" s="5"/>
+      <c r="DT44" s="5"/>
+      <c r="DU44" s="5"/>
+      <c r="DV44" s="5"/>
+      <c r="DW44" s="5"/>
+      <c r="DX44" s="5"/>
+      <c r="DY44" s="5"/>
+      <c r="DZ44" s="5"/>
+      <c r="EA44" s="5"/>
+      <c r="EB44" s="5"/>
+      <c r="EC44" s="5"/>
+      <c r="ED44" s="5"/>
+      <c r="EE44" s="5"/>
+      <c r="EF44" s="5"/>
+      <c r="EG44" s="5"/>
+      <c r="EH44" s="5"/>
+      <c r="EI44" s="5"/>
+      <c r="EJ44" s="5"/>
+      <c r="EK44" s="5"/>
+      <c r="EL44" s="5"/>
+      <c r="EM44" s="5"/>
+      <c r="EN44" s="5"/>
+      <c r="EO44" s="5"/>
+      <c r="EP44" s="5"/>
+      <c r="EQ44" s="5"/>
+      <c r="ER44" s="5"/>
+      <c r="ES44" s="5"/>
+      <c r="ET44" s="5"/>
+      <c r="EU44" s="5"/>
+      <c r="EV44" s="5"/>
+      <c r="EW44" s="5"/>
+      <c r="EX44" s="5"/>
+      <c r="EY44" s="5"/>
+      <c r="EZ44" s="5"/>
+      <c r="FA44" s="5"/>
+      <c r="FB44" s="5"/>
+      <c r="FC44" s="5"/>
+      <c r="FD44" s="5"/>
+      <c r="FE44" s="5"/>
+      <c r="FF44" s="5"/>
+      <c r="FG44" s="5"/>
+      <c r="FH44" s="5"/>
+      <c r="FI44" s="5"/>
+      <c r="FJ44" s="5"/>
+      <c r="FK44" s="5"/>
+      <c r="FL44" s="5"/>
+      <c r="FM44" s="5"/>
+      <c r="FN44" s="5"/>
+      <c r="FO44" s="5"/>
+      <c r="FP44" s="5"/>
+      <c r="FQ44" s="5"/>
+      <c r="FR44" s="5"/>
+      <c r="FS44" s="5"/>
+      <c r="FT44" s="5"/>
+      <c r="FU44" s="5"/>
+      <c r="FV44" s="5"/>
+      <c r="FW44" s="5"/>
+      <c r="FX44" s="5"/>
+      <c r="FY44" s="5"/>
+      <c r="FZ44" s="5"/>
+      <c r="GA44" s="5"/>
+      <c r="GB44" s="5"/>
+      <c r="GC44" s="5"/>
+      <c r="GD44" s="5"/>
+      <c r="GE44" s="5"/>
+      <c r="GF44" s="5"/>
+      <c r="GG44" s="5"/>
+      <c r="GH44" s="5"/>
+      <c r="GI44" s="5"/>
+      <c r="GJ44" s="5"/>
+      <c r="GK44" s="5"/>
+      <c r="GL44" s="5"/>
+      <c r="GM44" s="5"/>
+      <c r="GN44" s="5"/>
+      <c r="GO44" s="5"/>
+      <c r="GP44" s="5"/>
+      <c r="GQ44" s="5"/>
+      <c r="GR44" s="5"/>
+      <c r="GS44" s="5"/>
+      <c r="GT44" s="5"/>
+      <c r="GU44" s="5"/>
+      <c r="GV44" s="5"/>
+      <c r="GW44" s="5"/>
+      <c r="GX44" s="5"/>
+      <c r="GY44" s="5"/>
+      <c r="GZ44" s="5"/>
+      <c r="HA44" s="5"/>
+      <c r="HB44" s="5"/>
+      <c r="HC44" s="5"/>
+      <c r="HD44" s="5"/>
+      <c r="HE44" s="5"/>
+      <c r="HF44" s="5"/>
+      <c r="HG44" s="5"/>
+      <c r="HH44" s="5"/>
+      <c r="HI44" s="5"/>
+      <c r="HJ44" s="5"/>
+      <c r="HK44" s="5"/>
+      <c r="HL44" s="5"/>
+      <c r="HM44" s="5"/>
+      <c r="HN44" s="5"/>
+      <c r="HO44" s="5"/>
+      <c r="HP44" s="5"/>
+      <c r="HQ44" s="5"/>
+      <c r="HR44" s="5"/>
+      <c r="HS44" s="5"/>
+      <c r="HT44" s="5"/>
+      <c r="HU44" s="5"/>
+      <c r="HV44" s="5"/>
+      <c r="HW44" s="5"/>
+      <c r="HX44" s="5"/>
+      <c r="HY44" s="5"/>
+      <c r="HZ44" s="5"/>
+      <c r="IA44" s="5"/>
+      <c r="IB44" s="5"/>
+      <c r="IC44" s="5"/>
+      <c r="ID44" s="5"/>
+      <c r="IE44" s="5"/>
+      <c r="IF44" s="5"/>
+      <c r="IG44" s="5"/>
+      <c r="IH44" s="5"/>
+      <c r="II44" s="5"/>
+      <c r="IJ44" s="5"/>
+      <c r="IK44" s="5"/>
+      <c r="IL44" s="5"/>
+      <c r="IM44" s="5"/>
+      <c r="IN44" s="5"/>
+      <c r="IO44" s="5"/>
+      <c r="IP44" s="5"/>
+      <c r="IQ44" s="5"/>
+      <c r="IR44" s="5"/>
+      <c r="IS44" s="5"/>
+      <c r="IT44" s="5"/>
+      <c r="IU44" s="5"/>
+      <c r="IV44" s="5"/>
+      <c r="IW44" s="5"/>
+      <c r="IX44" s="5"/>
+      <c r="IY44" s="5"/>
+      <c r="IZ44" s="5"/>
+      <c r="JA44" s="5"/>
+      <c r="JB44" s="5"/>
+      <c r="JC44" s="5"/>
+      <c r="JD44" s="5"/>
+      <c r="JE44" s="5"/>
+      <c r="JF44" s="5"/>
+      <c r="JG44" s="5"/>
+      <c r="JH44" s="5"/>
+      <c r="JI44" s="5"/>
+      <c r="JJ44" s="5"/>
+      <c r="JK44" s="5"/>
+      <c r="JL44" s="5"/>
+      <c r="JM44" s="5"/>
+      <c r="JN44" s="5"/>
+      <c r="JO44" s="5"/>
+      <c r="JP44" s="5"/>
+      <c r="JQ44" s="5"/>
+      <c r="JR44" s="5"/>
+      <c r="JS44" s="5"/>
+      <c r="JT44" s="5"/>
+      <c r="JU44" s="5"/>
+      <c r="JV44" s="5"/>
+      <c r="JW44" s="5"/>
+      <c r="JX44" s="5"/>
+      <c r="JY44" s="5"/>
+      <c r="JZ44" s="5"/>
+      <c r="KA44" s="5"/>
+      <c r="KB44" s="5"/>
+      <c r="KC44" s="5"/>
+      <c r="KD44" s="5"/>
+      <c r="KE44" s="5"/>
+      <c r="KF44" s="5"/>
+      <c r="KG44" s="5"/>
+      <c r="KH44" s="5"/>
+      <c r="KI44" s="5"/>
+      <c r="KJ44" s="5"/>
+      <c r="KK44" s="5"/>
+      <c r="KL44" s="5"/>
+      <c r="KM44" s="5"/>
+      <c r="KN44" s="5"/>
+      <c r="KO44" s="5"/>
+      <c r="KP44" s="5"/>
+      <c r="KQ44" s="5"/>
+      <c r="KR44" s="5"/>
+      <c r="KS44" s="5"/>
+      <c r="KT44" s="5"/>
+      <c r="KU44" s="5"/>
+      <c r="KV44" s="5"/>
+      <c r="KW44" s="5"/>
+      <c r="KX44" s="5"/>
+      <c r="KY44" s="5"/>
+      <c r="KZ44" s="5"/>
+      <c r="LA44" s="5"/>
+      <c r="LB44" s="5"/>
+      <c r="LC44" s="5"/>
+      <c r="LD44" s="5"/>
+      <c r="LE44" s="5"/>
+      <c r="LF44" s="5"/>
+      <c r="LG44" s="5"/>
+      <c r="LH44" s="5"/>
+      <c r="LI44" s="5"/>
+      <c r="LJ44" s="5"/>
+      <c r="LK44" s="5"/>
+      <c r="LL44" s="5"/>
+      <c r="LM44" s="5"/>
+      <c r="LN44" s="5"/>
+      <c r="LO44" s="5"/>
+      <c r="LP44" s="5"/>
+      <c r="LQ44" s="5"/>
+      <c r="LR44" s="5"/>
+      <c r="LS44" s="5"/>
+      <c r="LT44" s="5"/>
+      <c r="LU44" s="5"/>
+      <c r="LV44" s="5"/>
+      <c r="LW44" s="5"/>
+      <c r="LX44" s="5"/>
+      <c r="LY44" s="5"/>
+      <c r="LZ44" s="5"/>
+      <c r="MA44" s="5"/>
+      <c r="MB44" s="5"/>
+      <c r="MC44" s="5"/>
+      <c r="MD44" s="5"/>
+      <c r="ME44" s="5"/>
+      <c r="MF44" s="5"/>
+      <c r="MG44" s="5"/>
+      <c r="MH44" s="5"/>
+      <c r="MI44" s="5"/>
+      <c r="MJ44" s="5"/>
+      <c r="MK44" s="5"/>
+      <c r="ML44" s="5"/>
+      <c r="MM44" s="5"/>
+      <c r="MN44" s="5"/>
+      <c r="MO44" s="5"/>
+      <c r="MP44" s="5"/>
+      <c r="MQ44" s="5"/>
+      <c r="MR44" s="5"/>
+      <c r="MS44" s="5"/>
+      <c r="MT44" s="5"/>
+      <c r="MU44" s="5"/>
+      <c r="MV44" s="5"/>
+      <c r="MW44" s="5"/>
+      <c r="MX44" s="5"/>
+      <c r="MY44" s="5"/>
+      <c r="MZ44" s="5"/>
+      <c r="NA44" s="5"/>
+      <c r="NB44" s="5"/>
+      <c r="NC44" s="5"/>
+      <c r="ND44" s="5"/>
+      <c r="NE44" s="5"/>
+      <c r="NF44" s="5"/>
+      <c r="NG44" s="5"/>
+      <c r="NH44" s="5"/>
+      <c r="NI44" s="5"/>
+      <c r="NJ44" s="5"/>
+      <c r="NK44" s="5"/>
+      <c r="NL44" s="5"/>
+      <c r="NM44" s="5"/>
+      <c r="NN44" s="5"/>
+      <c r="NO44" s="5"/>
+      <c r="NP44" s="5"/>
+      <c r="NQ44" s="5"/>
+      <c r="NR44" s="5"/>
+      <c r="NS44" s="5"/>
+      <c r="NT44" s="5"/>
+      <c r="NU44" s="5"/>
+      <c r="NV44" s="5"/>
+      <c r="NW44" s="5"/>
+      <c r="NX44" s="5"/>
+      <c r="NY44" s="5"/>
+      <c r="NZ44" s="5"/>
+      <c r="OA44" s="5"/>
+      <c r="OB44" s="5"/>
+      <c r="OC44" s="5"/>
+      <c r="OD44" s="5"/>
+      <c r="OE44" s="5"/>
+      <c r="OF44" s="5"/>
+      <c r="OG44" s="5"/>
+      <c r="OH44" s="5"/>
+      <c r="OI44" s="5"/>
+      <c r="OJ44" s="5"/>
+      <c r="OK44" s="5"/>
+      <c r="OL44" s="5"/>
+      <c r="OM44" s="5"/>
+      <c r="ON44" s="5"/>
+      <c r="OO44" s="5"/>
+      <c r="OP44" s="5"/>
+      <c r="OQ44" s="5"/>
+      <c r="OR44" s="5"/>
+      <c r="OS44" s="5"/>
+      <c r="OT44" s="5"/>
+      <c r="OU44" s="5"/>
+      <c r="OV44" s="5"/>
+      <c r="OW44" s="5"/>
+      <c r="OX44" s="5"/>
+      <c r="OY44" s="5"/>
+      <c r="OZ44" s="5"/>
+      <c r="PA44" s="5"/>
+      <c r="PB44" s="5"/>
+      <c r="PC44" s="5"/>
+      <c r="PD44" s="5"/>
+      <c r="PE44" s="5"/>
+      <c r="PF44" s="5"/>
+      <c r="PG44" s="5"/>
+      <c r="PH44" s="5"/>
+      <c r="PI44" s="5"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="5"/>
+      <c r="R45" s="5"/>
+      <c r="S45" s="5"/>
+      <c r="T45" s="5"/>
+      <c r="U45" s="5"/>
+      <c r="V45" s="5"/>
+      <c r="W45" s="5"/>
+      <c r="X45" s="5"/>
+      <c r="Y45" s="5"/>
+      <c r="Z45" s="5"/>
+      <c r="AA45" s="5"/>
+      <c r="AB45" s="5"/>
+      <c r="AC45" s="5"/>
+      <c r="AD45" s="5"/>
+      <c r="AE45" s="5"/>
+      <c r="AF45" s="5"/>
+      <c r="AG45" s="5"/>
+      <c r="AH45" s="5"/>
+      <c r="AI45" s="5"/>
+      <c r="AJ45" s="5"/>
+      <c r="AK45" s="5"/>
+      <c r="AL45" s="5"/>
+      <c r="AM45" s="5"/>
+      <c r="AN45" s="5"/>
+      <c r="AO45" s="5"/>
+      <c r="AP45" s="5"/>
+      <c r="AQ45" s="5"/>
+      <c r="AR45" s="5"/>
+      <c r="AS45" s="5"/>
+      <c r="AT45" s="5"/>
+      <c r="AU45" s="5"/>
+      <c r="AV45" s="5"/>
+      <c r="AW45" s="5"/>
+      <c r="AX45" s="5"/>
+      <c r="AY45" s="5"/>
+      <c r="AZ45" s="5"/>
+      <c r="BA45" s="5"/>
+      <c r="BB45" s="5"/>
+      <c r="BC45" s="5"/>
+      <c r="BD45" s="5"/>
+      <c r="BE45" s="5"/>
+      <c r="BF45" s="5"/>
+      <c r="BG45" s="5"/>
+      <c r="BH45" s="5"/>
+      <c r="BI45" s="5"/>
+      <c r="BJ45" s="5"/>
+      <c r="BK45" s="5"/>
+      <c r="BL45" s="5"/>
+      <c r="BM45" s="5"/>
+      <c r="BN45" s="5"/>
+      <c r="BO45" s="5"/>
+      <c r="BP45" s="5"/>
+      <c r="BQ45" s="5"/>
+      <c r="BR45" s="5"/>
+      <c r="BS45" s="5"/>
+      <c r="BT45" s="5"/>
+      <c r="BU45" s="5"/>
+      <c r="BV45" s="5"/>
+      <c r="BW45" s="5"/>
+      <c r="BX45" s="5"/>
+      <c r="BY45" s="5"/>
+      <c r="BZ45" s="5"/>
+      <c r="CA45" s="5"/>
+      <c r="CB45" s="5"/>
+      <c r="CC45" s="5"/>
+      <c r="CD45" s="5"/>
+      <c r="CE45" s="5"/>
+      <c r="CF45" s="5"/>
+      <c r="CG45" s="5"/>
+      <c r="CH45" s="5"/>
+      <c r="CI45" s="5"/>
+      <c r="CJ45" s="5"/>
+      <c r="CK45" s="5"/>
+      <c r="CL45" s="5"/>
+      <c r="CM45" s="5"/>
+      <c r="CN45" s="5"/>
+      <c r="CO45" s="5"/>
+      <c r="CP45" s="5"/>
+      <c r="CQ45" s="5"/>
+      <c r="CR45" s="5"/>
+      <c r="CS45" s="5"/>
+      <c r="CT45" s="5"/>
+      <c r="CU45" s="5"/>
+      <c r="CV45" s="5"/>
+      <c r="CW45" s="5"/>
+      <c r="CX45" s="5"/>
+      <c r="CY45" s="5"/>
+      <c r="CZ45" s="5"/>
+      <c r="DA45" s="5"/>
+      <c r="DB45" s="5"/>
+      <c r="DC45" s="5"/>
+      <c r="DD45" s="5"/>
+      <c r="DE45" s="5"/>
+      <c r="DF45" s="5"/>
+      <c r="DG45" s="5"/>
+      <c r="DH45" s="5"/>
+      <c r="DI45" s="5"/>
+      <c r="DJ45" s="5"/>
+      <c r="DK45" s="5"/>
+      <c r="DL45" s="5"/>
+      <c r="DM45" s="5"/>
+      <c r="DN45" s="5"/>
+      <c r="DO45" s="5"/>
+      <c r="DP45" s="5"/>
+      <c r="DQ45" s="5"/>
+      <c r="DR45" s="5"/>
+      <c r="DS45" s="5"/>
+      <c r="DT45" s="5"/>
+      <c r="DU45" s="5"/>
+      <c r="DV45" s="5"/>
+      <c r="DW45" s="5"/>
+      <c r="DX45" s="5"/>
+      <c r="DY45" s="5"/>
+      <c r="DZ45" s="5"/>
+      <c r="EA45" s="5"/>
+      <c r="EB45" s="5"/>
+      <c r="EC45" s="5"/>
+      <c r="ED45" s="5"/>
+      <c r="EE45" s="5"/>
+      <c r="EF45" s="5"/>
+      <c r="EG45" s="5"/>
+      <c r="EH45" s="5"/>
+      <c r="EI45" s="5"/>
+      <c r="EJ45" s="5"/>
+      <c r="EK45" s="5"/>
+      <c r="EL45" s="5"/>
+      <c r="EM45" s="5"/>
+      <c r="EN45" s="5"/>
+      <c r="EO45" s="5"/>
+      <c r="EP45" s="5"/>
+      <c r="EQ45" s="5"/>
+      <c r="ER45" s="5"/>
+      <c r="ES45" s="5"/>
+      <c r="ET45" s="5"/>
+      <c r="EU45" s="5"/>
+      <c r="EV45" s="5"/>
+      <c r="EW45" s="5"/>
+      <c r="EX45" s="5"/>
+      <c r="EY45" s="5"/>
+      <c r="EZ45" s="5"/>
+      <c r="FA45" s="5"/>
+      <c r="FB45" s="5"/>
+      <c r="FC45" s="5"/>
+      <c r="FD45" s="5"/>
+      <c r="FE45" s="5"/>
+      <c r="FF45" s="5"/>
+      <c r="FG45" s="5"/>
+      <c r="FH45" s="5"/>
+      <c r="FI45" s="5"/>
+      <c r="FJ45" s="5"/>
+      <c r="FK45" s="5"/>
+      <c r="FL45" s="5"/>
+      <c r="FM45" s="5"/>
+      <c r="FN45" s="5"/>
+      <c r="FO45" s="5"/>
+      <c r="FP45" s="5"/>
+      <c r="FQ45" s="5"/>
+      <c r="FR45" s="5"/>
+      <c r="FS45" s="5"/>
+      <c r="FT45" s="5"/>
+      <c r="FU45" s="5"/>
+      <c r="FV45" s="5"/>
+      <c r="FW45" s="5"/>
+      <c r="FX45" s="5"/>
+      <c r="FY45" s="5"/>
+      <c r="FZ45" s="5"/>
+      <c r="GA45" s="5"/>
+      <c r="GB45" s="5"/>
+      <c r="GC45" s="5"/>
+      <c r="GD45" s="5"/>
+      <c r="GE45" s="5"/>
+      <c r="GF45" s="5"/>
+      <c r="GG45" s="5"/>
+      <c r="GH45" s="5"/>
+      <c r="GI45" s="5"/>
+      <c r="GJ45" s="5"/>
+      <c r="GK45" s="5"/>
+      <c r="GL45" s="5"/>
+      <c r="GM45" s="5"/>
+      <c r="GN45" s="5"/>
+      <c r="GO45" s="5"/>
+      <c r="GP45" s="5"/>
+      <c r="GQ45" s="5"/>
+      <c r="GR45" s="5"/>
+      <c r="GS45" s="5"/>
+      <c r="GT45" s="5"/>
+      <c r="GU45" s="5"/>
+      <c r="GV45" s="5"/>
+      <c r="GW45" s="5"/>
+      <c r="GX45" s="5"/>
+      <c r="GY45" s="5"/>
+      <c r="GZ45" s="5"/>
+      <c r="HA45" s="5"/>
+      <c r="HB45" s="5"/>
+      <c r="HC45" s="5"/>
+      <c r="HD45" s="5"/>
+      <c r="HE45" s="5"/>
+      <c r="HF45" s="5"/>
+      <c r="HG45" s="5"/>
+      <c r="HH45" s="5"/>
+      <c r="HI45" s="5"/>
+      <c r="HJ45" s="5"/>
+      <c r="HK45" s="5"/>
+      <c r="HL45" s="5"/>
+      <c r="HM45" s="5"/>
+      <c r="HN45" s="5"/>
+      <c r="HO45" s="5"/>
+      <c r="HP45" s="5"/>
+      <c r="HQ45" s="5"/>
+      <c r="HR45" s="5"/>
+      <c r="HS45" s="5"/>
+      <c r="HT45" s="5"/>
+      <c r="HU45" s="5"/>
+      <c r="HV45" s="5"/>
+      <c r="HW45" s="5"/>
+      <c r="HX45" s="5"/>
+      <c r="HY45" s="5"/>
+      <c r="HZ45" s="5"/>
+      <c r="IA45" s="5"/>
+      <c r="IB45" s="5"/>
+      <c r="IC45" s="5"/>
+      <c r="ID45" s="5"/>
+      <c r="IE45" s="5"/>
+      <c r="IF45" s="5"/>
+      <c r="IG45" s="5"/>
+      <c r="IH45" s="5"/>
+      <c r="II45" s="5"/>
+      <c r="IJ45" s="5"/>
+      <c r="IK45" s="5"/>
+      <c r="IL45" s="5"/>
+      <c r="IM45" s="5"/>
+      <c r="IN45" s="5"/>
+      <c r="IO45" s="5"/>
+      <c r="IP45" s="5"/>
+      <c r="IQ45" s="5"/>
+      <c r="IR45" s="5"/>
+      <c r="IS45" s="5"/>
+      <c r="IT45" s="5"/>
+      <c r="IU45" s="5"/>
+      <c r="IV45" s="5"/>
+      <c r="IW45" s="5"/>
+      <c r="IX45" s="5"/>
+      <c r="IY45" s="5"/>
+      <c r="IZ45" s="5"/>
+      <c r="JA45" s="5"/>
+      <c r="JB45" s="5"/>
+      <c r="JC45" s="5"/>
+      <c r="JD45" s="5"/>
+      <c r="JE45" s="5"/>
+      <c r="JF45" s="5"/>
+      <c r="JG45" s="5"/>
+      <c r="JH45" s="5"/>
+      <c r="JI45" s="5"/>
+      <c r="JJ45" s="5"/>
+      <c r="JK45" s="5"/>
+      <c r="JL45" s="5"/>
+      <c r="JM45" s="5"/>
+      <c r="JN45" s="5"/>
+      <c r="JO45" s="5"/>
+      <c r="JP45" s="5"/>
+      <c r="JQ45" s="5"/>
+      <c r="JR45" s="5"/>
+      <c r="JS45" s="5"/>
+      <c r="JT45" s="5"/>
+      <c r="JU45" s="5"/>
+      <c r="JV45" s="5"/>
+      <c r="JW45" s="5"/>
+      <c r="JX45" s="5"/>
+      <c r="JY45" s="5"/>
+      <c r="JZ45" s="5"/>
+      <c r="KA45" s="5"/>
+      <c r="KB45" s="5"/>
+      <c r="KC45" s="5"/>
+      <c r="KD45" s="5"/>
+      <c r="KE45" s="5"/>
+      <c r="KF45" s="5"/>
+      <c r="KG45" s="5"/>
+      <c r="KH45" s="5"/>
+      <c r="KI45" s="5"/>
+      <c r="KJ45" s="5"/>
+      <c r="KK45" s="5"/>
+      <c r="KL45" s="5"/>
+      <c r="KM45" s="5"/>
+      <c r="KN45" s="5"/>
+      <c r="KO45" s="5"/>
+      <c r="KP45" s="5"/>
+      <c r="KQ45" s="5"/>
+      <c r="KR45" s="5"/>
+      <c r="KS45" s="5"/>
+      <c r="KT45" s="5"/>
+      <c r="KU45" s="5"/>
+      <c r="KV45" s="5"/>
+      <c r="KW45" s="5"/>
+      <c r="KX45" s="5"/>
+      <c r="KY45" s="5"/>
+      <c r="KZ45" s="5"/>
+      <c r="LA45" s="5"/>
+      <c r="LB45" s="5"/>
+      <c r="LC45" s="5"/>
+      <c r="LD45" s="5"/>
+      <c r="LE45" s="5"/>
+      <c r="LF45" s="5"/>
+      <c r="LG45" s="5"/>
+      <c r="LH45" s="5"/>
+      <c r="LI45" s="5"/>
+      <c r="LJ45" s="5"/>
+      <c r="LK45" s="5"/>
+      <c r="LL45" s="5"/>
+      <c r="LM45" s="5"/>
+      <c r="LN45" s="5"/>
+      <c r="LO45" s="5"/>
+      <c r="LP45" s="5"/>
+      <c r="LQ45" s="5"/>
+      <c r="LR45" s="5"/>
+      <c r="LS45" s="5"/>
+      <c r="LT45" s="5"/>
+      <c r="LU45" s="5"/>
+      <c r="LV45" s="5"/>
+      <c r="LW45" s="5"/>
+      <c r="LX45" s="5"/>
+      <c r="LY45" s="5"/>
+      <c r="LZ45" s="5"/>
+      <c r="MA45" s="5"/>
+      <c r="MB45" s="5"/>
+      <c r="MC45" s="5"/>
+      <c r="MD45" s="5"/>
+      <c r="ME45" s="5"/>
+      <c r="MF45" s="5"/>
+      <c r="MG45" s="5"/>
+      <c r="MH45" s="5"/>
+      <c r="MI45" s="5"/>
+      <c r="MJ45" s="5"/>
+      <c r="MK45" s="5"/>
+      <c r="ML45" s="5"/>
+      <c r="MM45" s="5"/>
+      <c r="MN45" s="5"/>
+      <c r="MO45" s="5"/>
+      <c r="MP45" s="5"/>
+      <c r="MQ45" s="5"/>
+      <c r="MR45" s="5"/>
+      <c r="MS45" s="5"/>
+      <c r="MT45" s="5"/>
+      <c r="MU45" s="5"/>
+      <c r="MV45" s="5"/>
+      <c r="MW45" s="5"/>
+      <c r="MX45" s="5"/>
+      <c r="MY45" s="5"/>
+      <c r="MZ45" s="5"/>
+      <c r="NA45" s="5"/>
+      <c r="NB45" s="5"/>
+      <c r="NC45" s="5"/>
+      <c r="ND45" s="5"/>
+      <c r="NE45" s="5"/>
+      <c r="NF45" s="5"/>
+      <c r="NG45" s="5"/>
+      <c r="NH45" s="5"/>
+      <c r="NI45" s="5"/>
+      <c r="NJ45" s="5"/>
+      <c r="NK45" s="5"/>
+      <c r="NL45" s="5"/>
+      <c r="NM45" s="5"/>
+      <c r="NN45" s="5"/>
+      <c r="NO45" s="5"/>
+      <c r="NP45" s="5"/>
+      <c r="NQ45" s="5"/>
+      <c r="NR45" s="5"/>
+      <c r="NS45" s="5"/>
+      <c r="NT45" s="5"/>
+      <c r="NU45" s="5"/>
+      <c r="NV45" s="5"/>
+      <c r="NW45" s="5"/>
+      <c r="NX45" s="5"/>
+      <c r="NY45" s="5"/>
+      <c r="NZ45" s="5"/>
+      <c r="OA45" s="5"/>
+      <c r="OB45" s="5"/>
+      <c r="OC45" s="5"/>
+      <c r="OD45" s="5"/>
+      <c r="OE45" s="5"/>
+      <c r="OF45" s="5"/>
+      <c r="OG45" s="5"/>
+      <c r="OH45" s="5"/>
+      <c r="OI45" s="5"/>
+      <c r="OJ45" s="5"/>
+      <c r="OK45" s="5"/>
+      <c r="OL45" s="5"/>
+      <c r="OM45" s="5"/>
+      <c r="ON45" s="5"/>
+      <c r="OO45" s="5"/>
+      <c r="OP45" s="5"/>
+      <c r="OQ45" s="5"/>
+      <c r="OR45" s="5"/>
+      <c r="OS45" s="5"/>
+      <c r="OT45" s="5"/>
+      <c r="OU45" s="5"/>
+      <c r="OV45" s="5"/>
+      <c r="OW45" s="5"/>
+      <c r="OX45" s="5"/>
+      <c r="OY45" s="5"/>
+      <c r="OZ45" s="5"/>
+      <c r="PA45" s="5"/>
+      <c r="PB45" s="5"/>
+      <c r="PC45" s="5"/>
+      <c r="PD45" s="5"/>
+      <c r="PE45" s="5"/>
+      <c r="PF45" s="5"/>
+      <c r="PG45" s="5"/>
+      <c r="PH45" s="5"/>
+      <c r="PI45" s="5"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>161.03</v>
+      </c>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="5"/>
+      <c r="R46" s="5"/>
+      <c r="S46" s="5"/>
+      <c r="T46" s="5"/>
+      <c r="U46" s="5"/>
+      <c r="V46" s="5"/>
+      <c r="W46" s="5"/>
+      <c r="X46" s="5"/>
+      <c r="Y46" s="5"/>
+      <c r="Z46" s="5"/>
+      <c r="AA46" s="5"/>
+      <c r="AB46" s="5"/>
+      <c r="AC46" s="5"/>
+      <c r="AD46" s="5"/>
+      <c r="AE46" s="5"/>
+      <c r="AF46" s="5"/>
+      <c r="AG46" s="5"/>
+      <c r="AH46" s="5"/>
+      <c r="AI46" s="5"/>
+      <c r="AJ46" s="5"/>
+      <c r="AK46" s="5"/>
+      <c r="AL46" s="5"/>
+      <c r="AM46" s="5"/>
+      <c r="AN46" s="5"/>
+      <c r="AO46" s="5"/>
+      <c r="AP46" s="5"/>
+      <c r="AQ46" s="5"/>
+      <c r="AR46" s="5"/>
+      <c r="AS46" s="5"/>
+      <c r="AT46" s="5"/>
+      <c r="AU46" s="5"/>
+      <c r="AV46" s="5"/>
+      <c r="AW46" s="5"/>
+      <c r="AX46" s="5"/>
+      <c r="AY46" s="5"/>
+      <c r="AZ46" s="5"/>
+      <c r="BA46" s="5"/>
+      <c r="BB46" s="5"/>
+      <c r="BC46" s="5"/>
+      <c r="BD46" s="5"/>
+      <c r="BE46" s="5"/>
+      <c r="BF46" s="5"/>
+      <c r="BG46" s="5"/>
+      <c r="BH46" s="5"/>
+      <c r="BI46" s="5"/>
+      <c r="BJ46" s="5"/>
+      <c r="BK46" s="5"/>
+      <c r="BL46" s="5"/>
+      <c r="BM46" s="5"/>
+      <c r="BN46" s="5"/>
+      <c r="BO46" s="5"/>
+      <c r="BP46" s="5"/>
+      <c r="BQ46" s="5"/>
+      <c r="BR46" s="5"/>
+      <c r="BS46" s="5"/>
+      <c r="BT46" s="5"/>
+      <c r="BU46" s="5"/>
+      <c r="BV46" s="5"/>
+      <c r="BW46" s="5"/>
+      <c r="BX46" s="5"/>
+      <c r="BY46" s="5"/>
+      <c r="BZ46" s="5"/>
+      <c r="CA46" s="5"/>
+      <c r="CB46" s="5"/>
+      <c r="CC46" s="5"/>
+      <c r="CD46" s="5"/>
+      <c r="CE46" s="5"/>
+      <c r="CF46" s="5"/>
+      <c r="CG46" s="5"/>
+      <c r="CH46" s="5"/>
+      <c r="CI46" s="5"/>
+      <c r="CJ46" s="5"/>
+      <c r="CK46" s="5"/>
+      <c r="CL46" s="5"/>
+      <c r="CM46" s="5"/>
+      <c r="CN46" s="5"/>
+      <c r="CO46" s="5"/>
+      <c r="CP46" s="5"/>
+      <c r="CQ46" s="5"/>
+      <c r="CR46" s="5"/>
+      <c r="CS46" s="5"/>
+      <c r="CT46" s="5"/>
+      <c r="CU46" s="5"/>
+      <c r="CV46" s="5"/>
+      <c r="CW46" s="5"/>
+      <c r="CX46" s="5"/>
+      <c r="CY46" s="5"/>
+      <c r="CZ46" s="5"/>
+      <c r="DA46" s="5"/>
+      <c r="DB46" s="5"/>
+      <c r="DC46" s="5"/>
+      <c r="DD46" s="5"/>
+      <c r="DE46" s="5"/>
+      <c r="DF46" s="5"/>
+      <c r="DG46" s="5"/>
+      <c r="DH46" s="5"/>
+      <c r="DI46" s="5"/>
+      <c r="DJ46" s="5"/>
+      <c r="DK46" s="5"/>
+      <c r="DL46" s="5"/>
+      <c r="DM46" s="5"/>
+      <c r="DN46" s="5"/>
+      <c r="DO46" s="5"/>
+      <c r="DP46" s="5"/>
+      <c r="DQ46" s="5"/>
+      <c r="DR46" s="5"/>
+      <c r="DS46" s="5"/>
+      <c r="DT46" s="5"/>
+      <c r="DU46" s="5"/>
+      <c r="DV46" s="5"/>
+      <c r="DW46" s="5"/>
+      <c r="DX46" s="5"/>
+      <c r="DY46" s="5"/>
+      <c r="DZ46" s="5"/>
+      <c r="EA46" s="5"/>
+      <c r="EB46" s="5"/>
+      <c r="EC46" s="5"/>
+      <c r="ED46" s="5"/>
+      <c r="EE46" s="5"/>
+      <c r="EF46" s="5"/>
+      <c r="EG46" s="5"/>
+      <c r="EH46" s="5"/>
+      <c r="EI46" s="5"/>
+      <c r="EJ46" s="5"/>
+      <c r="EK46" s="5"/>
+      <c r="EL46" s="5"/>
+      <c r="EM46" s="5"/>
+      <c r="EN46" s="5"/>
+      <c r="EO46" s="5"/>
+      <c r="EP46" s="5"/>
+      <c r="EQ46" s="5"/>
+      <c r="ER46" s="5"/>
+      <c r="ES46" s="5"/>
+      <c r="ET46" s="5"/>
+      <c r="EU46" s="5"/>
+      <c r="EV46" s="5"/>
+      <c r="EW46" s="5"/>
+      <c r="EX46" s="5"/>
+      <c r="EY46" s="5"/>
+      <c r="EZ46" s="5"/>
+      <c r="FA46" s="5"/>
+      <c r="FB46" s="5"/>
+      <c r="FC46" s="5"/>
+      <c r="FD46" s="5"/>
+      <c r="FE46" s="5"/>
+      <c r="FF46" s="5"/>
+      <c r="FG46" s="5"/>
+      <c r="FH46" s="5"/>
+      <c r="FI46" s="5"/>
+      <c r="FJ46" s="5"/>
+      <c r="FK46" s="5"/>
+      <c r="FL46" s="5"/>
+      <c r="FM46" s="5"/>
+      <c r="FN46" s="5"/>
+      <c r="FO46" s="5"/>
+      <c r="FP46" s="5"/>
+      <c r="FQ46" s="5"/>
+      <c r="FR46" s="5"/>
+      <c r="FS46" s="5"/>
+      <c r="FT46" s="5"/>
+      <c r="FU46" s="5"/>
+      <c r="FV46" s="5"/>
+      <c r="FW46" s="5"/>
+      <c r="FX46" s="5"/>
+      <c r="FY46" s="5"/>
+      <c r="FZ46" s="5"/>
+      <c r="GA46" s="5"/>
+      <c r="GB46" s="5"/>
+      <c r="GC46" s="5"/>
+      <c r="GD46" s="5"/>
+      <c r="GE46" s="5"/>
+      <c r="GF46" s="5"/>
+      <c r="GG46" s="5"/>
+      <c r="GH46" s="5"/>
+      <c r="GI46" s="5"/>
+      <c r="GJ46" s="5"/>
+      <c r="GK46" s="5"/>
+      <c r="GL46" s="5"/>
+      <c r="GM46" s="5"/>
+      <c r="GN46" s="5"/>
+      <c r="GO46" s="5"/>
+      <c r="GP46" s="5"/>
+      <c r="GQ46" s="5"/>
+      <c r="GR46" s="5"/>
+      <c r="GS46" s="5"/>
+      <c r="GT46" s="5"/>
+      <c r="GU46" s="5"/>
+      <c r="GV46" s="5"/>
+      <c r="GW46" s="5"/>
+      <c r="GX46" s="5"/>
+      <c r="GY46" s="5"/>
+      <c r="GZ46" s="5"/>
+      <c r="HA46" s="5"/>
+      <c r="HB46" s="5"/>
+      <c r="HC46" s="5"/>
+      <c r="HD46" s="5"/>
+      <c r="HE46" s="5"/>
+      <c r="HF46" s="5"/>
+      <c r="HG46" s="5"/>
+      <c r="HH46" s="5"/>
+      <c r="HI46" s="5"/>
+      <c r="HJ46" s="5"/>
+      <c r="HK46" s="5"/>
+      <c r="HL46" s="5"/>
+      <c r="HM46" s="5"/>
+      <c r="HN46" s="5"/>
+      <c r="HO46" s="5"/>
+      <c r="HP46" s="5"/>
+      <c r="HQ46" s="5"/>
+      <c r="HR46" s="5"/>
+      <c r="HS46" s="5"/>
+      <c r="HT46" s="5"/>
+      <c r="HU46" s="5"/>
+      <c r="HV46" s="5"/>
+      <c r="HW46" s="5"/>
+      <c r="HX46" s="5"/>
+      <c r="HY46" s="5"/>
+      <c r="HZ46" s="5"/>
+      <c r="IA46" s="5"/>
+      <c r="IB46" s="5"/>
+      <c r="IC46" s="5"/>
+      <c r="ID46" s="5"/>
+      <c r="IE46" s="5"/>
+      <c r="IF46" s="5"/>
+      <c r="IG46" s="5"/>
+      <c r="IH46" s="5"/>
+      <c r="II46" s="5"/>
+      <c r="IJ46" s="5"/>
+      <c r="IK46" s="5"/>
+      <c r="IL46" s="5"/>
+      <c r="IM46" s="5"/>
+      <c r="IN46" s="5"/>
+      <c r="IO46" s="5"/>
+      <c r="IP46" s="5"/>
+      <c r="IQ46" s="5"/>
+      <c r="IR46" s="5"/>
+      <c r="IS46" s="5"/>
+      <c r="IT46" s="5"/>
+      <c r="IU46" s="5"/>
+      <c r="IV46" s="5"/>
+      <c r="IW46" s="5"/>
+      <c r="IX46" s="5"/>
+      <c r="IY46" s="5"/>
+      <c r="IZ46" s="5"/>
+      <c r="JA46" s="5"/>
+      <c r="JB46" s="5"/>
+      <c r="JC46" s="5"/>
+      <c r="JD46" s="5"/>
+      <c r="JE46" s="5"/>
+      <c r="JF46" s="5"/>
+      <c r="JG46" s="5"/>
+      <c r="JH46" s="5"/>
+      <c r="JI46" s="5"/>
+      <c r="JJ46" s="5"/>
+      <c r="JK46" s="5"/>
+      <c r="JL46" s="5"/>
+      <c r="JM46" s="5"/>
+      <c r="JN46" s="5"/>
+      <c r="JO46" s="5"/>
+      <c r="JP46" s="5"/>
+      <c r="JQ46" s="5"/>
+      <c r="JR46" s="5"/>
+      <c r="JS46" s="5"/>
+      <c r="JT46" s="5"/>
+      <c r="JU46" s="5"/>
+      <c r="JV46" s="5"/>
+      <c r="JW46" s="5"/>
+      <c r="JX46" s="5"/>
+      <c r="JY46" s="5"/>
+      <c r="JZ46" s="5"/>
+      <c r="KA46" s="5"/>
+      <c r="KB46" s="5"/>
+      <c r="KC46" s="5"/>
+      <c r="KD46" s="5"/>
+      <c r="KE46" s="5"/>
+      <c r="KF46" s="5"/>
+      <c r="KG46" s="5"/>
+      <c r="KH46" s="5"/>
+      <c r="KI46" s="5"/>
+      <c r="KJ46" s="5"/>
+      <c r="KK46" s="5"/>
+      <c r="KL46" s="5"/>
+      <c r="KM46" s="5"/>
+      <c r="KN46" s="5"/>
+      <c r="KO46" s="5"/>
+      <c r="KP46" s="5"/>
+      <c r="KQ46" s="5"/>
+      <c r="KR46" s="5"/>
+      <c r="KS46" s="5"/>
+      <c r="KT46" s="5"/>
+      <c r="KU46" s="5"/>
+      <c r="KV46" s="5"/>
+      <c r="KW46" s="5"/>
+      <c r="KX46" s="5"/>
+      <c r="KY46" s="5"/>
+      <c r="KZ46" s="5"/>
+      <c r="LA46" s="5"/>
+      <c r="LB46" s="5"/>
+      <c r="LC46" s="5"/>
+      <c r="LD46" s="5"/>
+      <c r="LE46" s="5"/>
+      <c r="LF46" s="5"/>
+      <c r="LG46" s="5"/>
+      <c r="LH46" s="5"/>
+      <c r="LI46" s="5"/>
+      <c r="LJ46" s="5"/>
+      <c r="LK46" s="5"/>
+      <c r="LL46" s="5"/>
+      <c r="LM46" s="5"/>
+      <c r="LN46" s="5"/>
+      <c r="LO46" s="5"/>
+      <c r="LP46" s="5"/>
+      <c r="LQ46" s="5"/>
+      <c r="LR46" s="5"/>
+      <c r="LS46" s="5"/>
+      <c r="LT46" s="5"/>
+      <c r="LU46" s="5"/>
+      <c r="LV46" s="5"/>
+      <c r="LW46" s="5"/>
+      <c r="LX46" s="5"/>
+      <c r="LY46" s="5"/>
+      <c r="LZ46" s="5"/>
+      <c r="MA46" s="5"/>
+      <c r="MB46" s="5"/>
+      <c r="MC46" s="5"/>
+      <c r="MD46" s="5"/>
+      <c r="ME46" s="5"/>
+      <c r="MF46" s="5"/>
+      <c r="MG46" s="5"/>
+      <c r="MH46" s="5"/>
+      <c r="MI46" s="5"/>
+      <c r="MJ46" s="5"/>
+      <c r="MK46" s="5"/>
+      <c r="ML46" s="5"/>
+      <c r="MM46" s="5"/>
+      <c r="MN46" s="5"/>
+      <c r="MO46" s="5"/>
+      <c r="MP46" s="5"/>
+      <c r="MQ46" s="5"/>
+      <c r="MR46" s="5"/>
+      <c r="MS46" s="5"/>
+      <c r="MT46" s="5"/>
+      <c r="MU46" s="5"/>
+      <c r="MV46" s="5"/>
+      <c r="MW46" s="5"/>
+      <c r="MX46" s="5"/>
+      <c r="MY46" s="5"/>
+      <c r="MZ46" s="5"/>
+      <c r="NA46" s="5"/>
+      <c r="NB46" s="5"/>
+      <c r="NC46" s="5"/>
+      <c r="ND46" s="5"/>
+      <c r="NE46" s="5"/>
+      <c r="NF46" s="5"/>
+      <c r="NG46" s="5"/>
+      <c r="NH46" s="5"/>
+      <c r="NI46" s="5"/>
+      <c r="NJ46" s="5"/>
+      <c r="NK46" s="5"/>
+      <c r="NL46" s="5"/>
+      <c r="NM46" s="5"/>
+      <c r="NN46" s="5"/>
+      <c r="NO46" s="5"/>
+      <c r="NP46" s="5"/>
+      <c r="NQ46" s="5"/>
+      <c r="NR46" s="5"/>
+      <c r="NS46" s="5"/>
+      <c r="NT46" s="5"/>
+      <c r="NU46" s="5"/>
+      <c r="NV46" s="5"/>
+      <c r="NW46" s="5"/>
+      <c r="NX46" s="5"/>
+      <c r="NY46" s="5"/>
+      <c r="NZ46" s="5"/>
+      <c r="OA46" s="5"/>
+      <c r="OB46" s="5"/>
+      <c r="OC46" s="5"/>
+      <c r="OD46" s="5"/>
+      <c r="OE46" s="5"/>
+      <c r="OF46" s="5"/>
+      <c r="OG46" s="5"/>
+      <c r="OH46" s="5"/>
+      <c r="OI46" s="5"/>
+      <c r="OJ46" s="5"/>
+      <c r="OK46" s="5"/>
+      <c r="OL46" s="5"/>
+      <c r="OM46" s="5"/>
+      <c r="ON46" s="5"/>
+      <c r="OO46" s="5"/>
+      <c r="OP46" s="5"/>
+      <c r="OQ46" s="5"/>
+      <c r="OR46" s="5"/>
+      <c r="OS46" s="5"/>
+      <c r="OT46" s="5"/>
+      <c r="OU46" s="5"/>
+      <c r="OV46" s="5"/>
+      <c r="OW46" s="5"/>
+      <c r="OX46" s="5"/>
+      <c r="OY46" s="5"/>
+      <c r="OZ46" s="5"/>
+      <c r="PA46" s="5"/>
+      <c r="PB46" s="5"/>
+      <c r="PC46" s="5"/>
+      <c r="PD46" s="5"/>
+      <c r="PE46" s="5"/>
+      <c r="PF46" s="5"/>
+      <c r="PG46" s="5"/>
+      <c r="PH46" s="5"/>
+      <c r="PI46" s="5"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="5"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="5"/>
+      <c r="Q47" s="5"/>
+      <c r="R47" s="5"/>
+      <c r="S47" s="5"/>
+      <c r="T47" s="5"/>
+      <c r="U47" s="5"/>
+      <c r="V47" s="5"/>
+      <c r="W47" s="5"/>
+      <c r="X47" s="5"/>
+      <c r="Y47" s="5"/>
+      <c r="Z47" s="5"/>
+      <c r="AA47" s="5"/>
+      <c r="AB47" s="5"/>
+      <c r="AC47" s="5"/>
+      <c r="AD47" s="5"/>
+      <c r="AE47" s="5"/>
+      <c r="AF47" s="5"/>
+      <c r="AG47" s="5"/>
+      <c r="AH47" s="5"/>
+      <c r="AI47" s="5"/>
+      <c r="AJ47" s="5"/>
+      <c r="AK47" s="5"/>
+      <c r="AL47" s="5"/>
+      <c r="AM47" s="5"/>
+      <c r="AN47" s="5"/>
+      <c r="AO47" s="5"/>
+      <c r="AP47" s="5"/>
+      <c r="AQ47" s="5"/>
+      <c r="AR47" s="5"/>
+      <c r="AS47" s="5"/>
+      <c r="AT47" s="5"/>
+      <c r="AU47" s="5"/>
+      <c r="AV47" s="5"/>
+      <c r="AW47" s="5"/>
+      <c r="AX47" s="5"/>
+      <c r="AY47" s="5"/>
+      <c r="AZ47" s="5"/>
+      <c r="BA47" s="5"/>
+      <c r="BB47" s="5"/>
+      <c r="BC47" s="5"/>
+      <c r="BD47" s="5"/>
+      <c r="BE47" s="5"/>
+      <c r="BF47" s="5"/>
+      <c r="BG47" s="5"/>
+      <c r="BH47" s="5"/>
+      <c r="BI47" s="5"/>
+      <c r="BJ47" s="5"/>
+      <c r="BK47" s="5"/>
+      <c r="BL47" s="5"/>
+      <c r="BM47" s="5"/>
+      <c r="BN47" s="5"/>
+      <c r="BO47" s="5"/>
+      <c r="BP47" s="5"/>
+      <c r="BQ47" s="5"/>
+      <c r="BR47" s="5"/>
+      <c r="BS47" s="5"/>
+      <c r="BT47" s="5"/>
+      <c r="BU47" s="5"/>
+      <c r="BV47" s="5"/>
+      <c r="BW47" s="5"/>
+      <c r="BX47" s="5"/>
+      <c r="BY47" s="5"/>
+      <c r="BZ47" s="5"/>
+      <c r="CA47" s="5"/>
+      <c r="CB47" s="5"/>
+      <c r="CC47" s="5"/>
+      <c r="CD47" s="5"/>
+      <c r="CE47" s="5"/>
+      <c r="CF47" s="5"/>
+      <c r="CG47" s="5"/>
+      <c r="CH47" s="5"/>
+      <c r="CI47" s="5"/>
+      <c r="CJ47" s="5"/>
+      <c r="CK47" s="5"/>
+      <c r="CL47" s="5"/>
+      <c r="CM47" s="5"/>
+      <c r="CN47" s="5"/>
+      <c r="CO47" s="5"/>
+      <c r="CP47" s="5"/>
+      <c r="CQ47" s="5"/>
+      <c r="CR47" s="5"/>
+      <c r="CS47" s="5"/>
+      <c r="CT47" s="5"/>
+      <c r="CU47" s="5"/>
+      <c r="CV47" s="5"/>
+      <c r="CW47" s="5"/>
+      <c r="CX47" s="5"/>
+      <c r="CY47" s="5"/>
+      <c r="CZ47" s="5"/>
+      <c r="DA47" s="5"/>
+      <c r="DB47" s="5"/>
+      <c r="DC47" s="5"/>
+      <c r="DD47" s="5"/>
+      <c r="DE47" s="5"/>
+      <c r="DF47" s="5"/>
+      <c r="DG47" s="5"/>
+      <c r="DH47" s="5"/>
+      <c r="DI47" s="5"/>
+      <c r="DJ47" s="5"/>
+      <c r="DK47" s="5"/>
+      <c r="DL47" s="5"/>
+      <c r="DM47" s="5"/>
+      <c r="DN47" s="5"/>
+      <c r="DO47" s="5"/>
+      <c r="DP47" s="5"/>
+      <c r="DQ47" s="5"/>
+      <c r="DR47" s="5"/>
+      <c r="DS47" s="5"/>
+      <c r="DT47" s="5"/>
+      <c r="DU47" s="5"/>
+      <c r="DV47" s="5"/>
+      <c r="DW47" s="5"/>
+      <c r="DX47" s="5"/>
+      <c r="DY47" s="5"/>
+      <c r="DZ47" s="5"/>
+      <c r="EA47" s="5"/>
+      <c r="EB47" s="5"/>
+      <c r="EC47" s="5"/>
+      <c r="ED47" s="5"/>
+      <c r="EE47" s="5"/>
+      <c r="EF47" s="5"/>
+      <c r="EG47" s="5"/>
+      <c r="EH47" s="5"/>
+      <c r="EI47" s="5"/>
+      <c r="EJ47" s="5"/>
+      <c r="EK47" s="5"/>
+      <c r="EL47" s="5"/>
+      <c r="EM47" s="5"/>
+      <c r="EN47" s="5"/>
+      <c r="EO47" s="5"/>
+      <c r="EP47" s="5"/>
+      <c r="EQ47" s="5"/>
+      <c r="ER47" s="5"/>
+      <c r="ES47" s="5"/>
+      <c r="ET47" s="5"/>
+      <c r="EU47" s="5"/>
+      <c r="EV47" s="5"/>
+      <c r="EW47" s="5"/>
+      <c r="EX47" s="5"/>
+      <c r="EY47" s="5"/>
+      <c r="EZ47" s="5"/>
+      <c r="FA47" s="5"/>
+      <c r="FB47" s="5"/>
+      <c r="FC47" s="5"/>
+      <c r="FD47" s="5"/>
+      <c r="FE47" s="5"/>
+      <c r="FF47" s="5"/>
+      <c r="FG47" s="5"/>
+      <c r="FH47" s="5"/>
+      <c r="FI47" s="5"/>
+      <c r="FJ47" s="5"/>
+      <c r="FK47" s="5"/>
+      <c r="FL47" s="5"/>
+      <c r="FM47" s="5"/>
+      <c r="FN47" s="5"/>
+      <c r="FO47" s="5"/>
+      <c r="FP47" s="5"/>
+      <c r="FQ47" s="5"/>
+      <c r="FR47" s="5"/>
+      <c r="FS47" s="5"/>
+      <c r="FT47" s="5"/>
+      <c r="FU47" s="5"/>
+      <c r="FV47" s="5"/>
+      <c r="FW47" s="5"/>
+      <c r="FX47" s="5"/>
+      <c r="FY47" s="5"/>
+      <c r="FZ47" s="5"/>
+      <c r="GA47" s="5"/>
+      <c r="GB47" s="5"/>
+      <c r="GC47" s="5"/>
+      <c r="GD47" s="5"/>
+      <c r="GE47" s="5"/>
+      <c r="GF47" s="5"/>
+      <c r="GG47" s="5"/>
+      <c r="GH47" s="5"/>
+      <c r="GI47" s="5"/>
+      <c r="GJ47" s="5"/>
+      <c r="GK47" s="5"/>
+      <c r="GL47" s="5"/>
+      <c r="GM47" s="5"/>
+      <c r="GN47" s="5"/>
+      <c r="GO47" s="5"/>
+      <c r="GP47" s="5"/>
+      <c r="GQ47" s="5"/>
+      <c r="GR47" s="5"/>
+      <c r="GS47" s="5"/>
+      <c r="GT47" s="5"/>
+      <c r="GU47" s="5"/>
+      <c r="GV47" s="5"/>
+      <c r="GW47" s="5"/>
+      <c r="GX47" s="5"/>
+      <c r="GY47" s="5"/>
+      <c r="GZ47" s="5"/>
+      <c r="HA47" s="5"/>
+      <c r="HB47" s="5"/>
+      <c r="HC47" s="5"/>
+      <c r="HD47" s="5"/>
+      <c r="HE47" s="5"/>
+      <c r="HF47" s="5"/>
+      <c r="HG47" s="5"/>
+      <c r="HH47" s="5"/>
+      <c r="HI47" s="5"/>
+      <c r="HJ47" s="5"/>
+      <c r="HK47" s="5"/>
+      <c r="HL47" s="5"/>
+      <c r="HM47" s="5"/>
+      <c r="HN47" s="5"/>
+      <c r="HO47" s="5"/>
+      <c r="HP47" s="5"/>
+      <c r="HQ47" s="5"/>
+      <c r="HR47" s="5"/>
+      <c r="HS47" s="5"/>
+      <c r="HT47" s="5"/>
+      <c r="HU47" s="5"/>
+      <c r="HV47" s="5"/>
+      <c r="HW47" s="5"/>
+      <c r="HX47" s="5"/>
+      <c r="HY47" s="5"/>
+      <c r="HZ47" s="5"/>
+      <c r="IA47" s="5"/>
+      <c r="IB47" s="5"/>
+      <c r="IC47" s="5"/>
+      <c r="ID47" s="5"/>
+      <c r="IE47" s="5"/>
+      <c r="IF47" s="5"/>
+      <c r="IG47" s="5"/>
+      <c r="IH47" s="5"/>
+      <c r="II47" s="5"/>
+      <c r="IJ47" s="5"/>
+      <c r="IK47" s="5"/>
+      <c r="IL47" s="5"/>
+      <c r="IM47" s="5"/>
+      <c r="IN47" s="5"/>
+      <c r="IO47" s="5"/>
+      <c r="IP47" s="5"/>
+      <c r="IQ47" s="5"/>
+      <c r="IR47" s="5"/>
+      <c r="IS47" s="5"/>
+      <c r="IT47" s="5"/>
+      <c r="IU47" s="5"/>
+      <c r="IV47" s="5"/>
+      <c r="IW47" s="5"/>
+      <c r="IX47" s="5"/>
+      <c r="IY47" s="5"/>
+      <c r="IZ47" s="5"/>
+      <c r="JA47" s="5"/>
+      <c r="JB47" s="5"/>
+      <c r="JC47" s="5"/>
+      <c r="JD47" s="5"/>
+      <c r="JE47" s="5"/>
+      <c r="JF47" s="5"/>
+      <c r="JG47" s="5"/>
+      <c r="JH47" s="5"/>
+      <c r="JI47" s="5"/>
+      <c r="JJ47" s="5"/>
+      <c r="JK47" s="5"/>
+      <c r="JL47" s="5"/>
+      <c r="JM47" s="5"/>
+      <c r="JN47" s="5"/>
+      <c r="JO47" s="5"/>
+      <c r="JP47" s="5"/>
+      <c r="JQ47" s="5"/>
+      <c r="JR47" s="5"/>
+      <c r="JS47" s="5"/>
+      <c r="JT47" s="5"/>
+      <c r="JU47" s="5"/>
+      <c r="JV47" s="5"/>
+      <c r="JW47" s="5"/>
+      <c r="JX47" s="5"/>
+      <c r="JY47" s="5"/>
+      <c r="JZ47" s="5"/>
+      <c r="KA47" s="5"/>
+      <c r="KB47" s="5"/>
+      <c r="KC47" s="5"/>
+      <c r="KD47" s="5"/>
+      <c r="KE47" s="5"/>
+      <c r="KF47" s="5"/>
+      <c r="KG47" s="5"/>
+      <c r="KH47" s="5"/>
+      <c r="KI47" s="5"/>
+      <c r="KJ47" s="5"/>
+      <c r="KK47" s="5"/>
+      <c r="KL47" s="5"/>
+      <c r="KM47" s="5"/>
+      <c r="KN47" s="5"/>
+      <c r="KO47" s="5"/>
+      <c r="KP47" s="5"/>
+      <c r="KQ47" s="5"/>
+      <c r="KR47" s="5"/>
+      <c r="KS47" s="5"/>
+      <c r="KT47" s="5"/>
+      <c r="KU47" s="5"/>
+      <c r="KV47" s="5"/>
+      <c r="KW47" s="5"/>
+      <c r="KX47" s="5"/>
+      <c r="KY47" s="5"/>
+      <c r="KZ47" s="5"/>
+      <c r="LA47" s="5"/>
+      <c r="LB47" s="5"/>
+      <c r="LC47" s="5"/>
+      <c r="LD47" s="5"/>
+      <c r="LE47" s="5"/>
+      <c r="LF47" s="5"/>
+      <c r="LG47" s="5"/>
+      <c r="LH47" s="5"/>
+      <c r="LI47" s="5"/>
+      <c r="LJ47" s="5"/>
+      <c r="LK47" s="5"/>
+      <c r="LL47" s="5"/>
+      <c r="LM47" s="5"/>
+      <c r="LN47" s="5"/>
+      <c r="LO47" s="5"/>
+      <c r="LP47" s="5"/>
+      <c r="LQ47" s="5"/>
+      <c r="LR47" s="5"/>
+      <c r="LS47" s="5"/>
+      <c r="LT47" s="5"/>
+      <c r="LU47" s="5"/>
+      <c r="LV47" s="5"/>
+      <c r="LW47" s="5"/>
+      <c r="LX47" s="5"/>
+      <c r="LY47" s="5"/>
+      <c r="LZ47" s="5"/>
+      <c r="MA47" s="5"/>
+      <c r="MB47" s="5"/>
+      <c r="MC47" s="5"/>
+      <c r="MD47" s="5"/>
+      <c r="ME47" s="5"/>
+      <c r="MF47" s="5"/>
+      <c r="MG47" s="5"/>
+      <c r="MH47" s="5"/>
+      <c r="MI47" s="5"/>
+      <c r="MJ47" s="5"/>
+      <c r="MK47" s="5"/>
+      <c r="ML47" s="5"/>
+      <c r="MM47" s="5"/>
+      <c r="MN47" s="5"/>
+      <c r="MO47" s="5"/>
+      <c r="MP47" s="5"/>
+      <c r="MQ47" s="5"/>
+      <c r="MR47" s="5"/>
+      <c r="MS47" s="5"/>
+      <c r="MT47" s="5"/>
+      <c r="MU47" s="5"/>
+      <c r="MV47" s="5"/>
+      <c r="MW47" s="5"/>
+      <c r="MX47" s="5"/>
+      <c r="MY47" s="5"/>
+      <c r="MZ47" s="5"/>
+      <c r="NA47" s="5"/>
+      <c r="NB47" s="5"/>
+      <c r="NC47" s="5"/>
+      <c r="ND47" s="5"/>
+      <c r="NE47" s="5"/>
+      <c r="NF47" s="5"/>
+      <c r="NG47" s="5"/>
+      <c r="NH47" s="5"/>
+      <c r="NI47" s="5"/>
+      <c r="NJ47" s="5"/>
+      <c r="NK47" s="5"/>
+      <c r="NL47" s="5"/>
+      <c r="NM47" s="5"/>
+      <c r="NN47" s="5"/>
+      <c r="NO47" s="5"/>
+      <c r="NP47" s="5"/>
+      <c r="NQ47" s="5"/>
+      <c r="NR47" s="5"/>
+      <c r="NS47" s="5"/>
+      <c r="NT47" s="5"/>
+      <c r="NU47" s="5"/>
+      <c r="NV47" s="5"/>
+      <c r="NW47" s="5"/>
+      <c r="NX47" s="5"/>
+      <c r="NY47" s="5"/>
+      <c r="NZ47" s="5"/>
+      <c r="OA47" s="5"/>
+      <c r="OB47" s="5"/>
+      <c r="OC47" s="5"/>
+      <c r="OD47" s="5"/>
+      <c r="OE47" s="5"/>
+      <c r="OF47" s="5"/>
+      <c r="OG47" s="5"/>
+      <c r="OH47" s="5"/>
+      <c r="OI47" s="5"/>
+      <c r="OJ47" s="5"/>
+      <c r="OK47" s="5"/>
+      <c r="OL47" s="5"/>
+      <c r="OM47" s="5"/>
+      <c r="ON47" s="5"/>
+      <c r="OO47" s="5"/>
+      <c r="OP47" s="5"/>
+      <c r="OQ47" s="5"/>
+      <c r="OR47" s="5"/>
+      <c r="OS47" s="5"/>
+      <c r="OT47" s="5"/>
+      <c r="OU47" s="5"/>
+      <c r="OV47" s="5"/>
+      <c r="OW47" s="5"/>
+      <c r="OX47" s="5"/>
+      <c r="OY47" s="5"/>
+      <c r="OZ47" s="5"/>
+      <c r="PA47" s="5"/>
+      <c r="PB47" s="5"/>
+      <c r="PC47" s="5"/>
+      <c r="PD47" s="5"/>
+      <c r="PE47" s="5"/>
+      <c r="PF47" s="5"/>
+      <c r="PG47" s="5"/>
+      <c r="PH47" s="5"/>
+      <c r="PI47" s="5"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="5"/>
+      <c r="Q48" s="5"/>
+      <c r="R48" s="5"/>
+      <c r="S48" s="5"/>
+      <c r="T48" s="5"/>
+      <c r="U48" s="5"/>
+      <c r="V48" s="5"/>
+      <c r="W48" s="5"/>
+      <c r="X48" s="5"/>
+      <c r="Y48" s="5"/>
+      <c r="Z48" s="5"/>
+      <c r="AA48" s="5"/>
+      <c r="AB48" s="5"/>
+      <c r="AC48" s="5"/>
+      <c r="AD48" s="5"/>
+      <c r="AE48" s="5"/>
+      <c r="AF48" s="5"/>
+      <c r="AG48" s="5"/>
+      <c r="AH48" s="5"/>
+      <c r="AI48" s="5"/>
+      <c r="AJ48" s="5"/>
+      <c r="AK48" s="5"/>
+      <c r="AL48" s="5"/>
+      <c r="AM48" s="5"/>
+      <c r="AN48" s="5"/>
+      <c r="AO48" s="5"/>
+      <c r="AP48" s="5"/>
+      <c r="AQ48" s="5"/>
+      <c r="AR48" s="5"/>
+      <c r="AS48" s="5"/>
+      <c r="AT48" s="5"/>
+      <c r="AU48" s="5"/>
+      <c r="AV48" s="5"/>
+      <c r="AW48" s="5"/>
+      <c r="AX48" s="5"/>
+      <c r="AY48" s="5"/>
+      <c r="AZ48" s="5"/>
+      <c r="BA48" s="5"/>
+      <c r="BB48" s="5"/>
+      <c r="BC48" s="5"/>
+      <c r="BD48" s="5"/>
+      <c r="BE48" s="5"/>
+      <c r="BF48" s="5"/>
+      <c r="BG48" s="5"/>
+      <c r="BH48" s="5"/>
+      <c r="BI48" s="5"/>
+      <c r="BJ48" s="5"/>
+      <c r="BK48" s="5"/>
+      <c r="BL48" s="5"/>
+      <c r="BM48" s="5"/>
+      <c r="BN48" s="5"/>
+      <c r="BO48" s="5"/>
+      <c r="BP48" s="5"/>
+      <c r="BQ48" s="5"/>
+      <c r="BR48" s="5"/>
+      <c r="BS48" s="5"/>
+      <c r="BT48" s="5"/>
+      <c r="BU48" s="5"/>
+      <c r="BV48" s="5"/>
+      <c r="BW48" s="5"/>
+      <c r="BX48" s="5"/>
+      <c r="BY48" s="5"/>
+      <c r="BZ48" s="5"/>
+      <c r="CA48" s="5"/>
+      <c r="CB48" s="5"/>
+      <c r="CC48" s="5"/>
+      <c r="CD48" s="5"/>
+      <c r="CE48" s="5"/>
+      <c r="CF48" s="5"/>
+      <c r="CG48" s="5"/>
+      <c r="CH48" s="5"/>
+      <c r="CI48" s="5"/>
+      <c r="CJ48" s="5"/>
+      <c r="CK48" s="5"/>
+      <c r="CL48" s="5"/>
+      <c r="CM48" s="5"/>
+      <c r="CN48" s="5"/>
+      <c r="CO48" s="5"/>
+      <c r="CP48" s="5"/>
+      <c r="CQ48" s="5"/>
+      <c r="CR48" s="5"/>
+      <c r="CS48" s="5"/>
+      <c r="CT48" s="5"/>
+      <c r="CU48" s="5"/>
+      <c r="CV48" s="5"/>
+      <c r="CW48" s="5"/>
+      <c r="CX48" s="5"/>
+      <c r="CY48" s="5"/>
+      <c r="CZ48" s="5"/>
+      <c r="DA48" s="5"/>
+      <c r="DB48" s="5"/>
+      <c r="DC48" s="5"/>
+      <c r="DD48" s="5"/>
+      <c r="DE48" s="5"/>
+      <c r="DF48" s="5"/>
+      <c r="DG48" s="5"/>
+      <c r="DH48" s="5"/>
+      <c r="DI48" s="5"/>
+      <c r="DJ48" s="5"/>
+      <c r="DK48" s="5"/>
+      <c r="DL48" s="5"/>
+      <c r="DM48" s="5"/>
+      <c r="DN48" s="5"/>
+      <c r="DO48" s="5"/>
+      <c r="DP48" s="5"/>
+      <c r="DQ48" s="5"/>
+      <c r="DR48" s="5"/>
+      <c r="DS48" s="5"/>
+      <c r="DT48" s="5"/>
+      <c r="DU48" s="5"/>
+      <c r="DV48" s="5"/>
+      <c r="DW48" s="5"/>
+      <c r="DX48" s="5"/>
+      <c r="DY48" s="5"/>
+      <c r="DZ48" s="5"/>
+      <c r="EA48" s="5"/>
+      <c r="EB48" s="5"/>
+      <c r="EC48" s="5"/>
+      <c r="ED48" s="5"/>
+      <c r="EE48" s="5"/>
+      <c r="EF48" s="5"/>
+      <c r="EG48" s="5"/>
+      <c r="EH48" s="5"/>
+      <c r="EI48" s="5"/>
+      <c r="EJ48" s="5"/>
+      <c r="EK48" s="5"/>
+      <c r="EL48" s="5"/>
+      <c r="EM48" s="5"/>
+      <c r="EN48" s="5"/>
+      <c r="EO48" s="5"/>
+      <c r="EP48" s="5"/>
+      <c r="EQ48" s="5"/>
+      <c r="ER48" s="5"/>
+      <c r="ES48" s="5"/>
+      <c r="ET48" s="5"/>
+      <c r="EU48" s="5"/>
+      <c r="EV48" s="5"/>
+      <c r="EW48" s="5"/>
+      <c r="EX48" s="5"/>
+      <c r="EY48" s="5"/>
+      <c r="EZ48" s="5"/>
+      <c r="FA48" s="5"/>
+      <c r="FB48" s="5"/>
+      <c r="FC48" s="5"/>
+      <c r="FD48" s="5"/>
+      <c r="FE48" s="5"/>
+      <c r="FF48" s="5"/>
+      <c r="FG48" s="5"/>
+      <c r="FH48" s="5"/>
+      <c r="FI48" s="5"/>
+      <c r="FJ48" s="5"/>
+      <c r="FK48" s="5"/>
+      <c r="FL48" s="5"/>
+      <c r="FM48" s="5"/>
+      <c r="FN48" s="5"/>
+      <c r="FO48" s="5"/>
+      <c r="FP48" s="5"/>
+      <c r="FQ48" s="5"/>
+      <c r="FR48" s="5"/>
+      <c r="FS48" s="5"/>
+      <c r="FT48" s="5"/>
+      <c r="FU48" s="5"/>
+      <c r="FV48" s="5"/>
+      <c r="FW48" s="5"/>
+      <c r="FX48" s="5"/>
+      <c r="FY48" s="5"/>
+      <c r="FZ48" s="5"/>
+      <c r="GA48" s="5"/>
+      <c r="GB48" s="5"/>
+      <c r="GC48" s="5"/>
+      <c r="GD48" s="5"/>
+      <c r="GE48" s="5"/>
+      <c r="GF48" s="5"/>
+      <c r="GG48" s="5"/>
+      <c r="GH48" s="5"/>
+      <c r="GI48" s="5"/>
+      <c r="GJ48" s="5"/>
+      <c r="GK48" s="5"/>
+      <c r="GL48" s="5"/>
+      <c r="GM48" s="5"/>
+      <c r="GN48" s="5"/>
+      <c r="GO48" s="5"/>
+      <c r="GP48" s="5"/>
+      <c r="GQ48" s="5"/>
+      <c r="GR48" s="5"/>
+      <c r="GS48" s="5"/>
+      <c r="GT48" s="5"/>
+      <c r="GU48" s="5"/>
+      <c r="GV48" s="5"/>
+      <c r="GW48" s="5"/>
+      <c r="GX48" s="5"/>
+      <c r="GY48" s="5"/>
+      <c r="GZ48" s="5"/>
+      <c r="HA48" s="5"/>
+      <c r="HB48" s="5"/>
+      <c r="HC48" s="5"/>
+      <c r="HD48" s="5"/>
+      <c r="HE48" s="5"/>
+      <c r="HF48" s="5"/>
+      <c r="HG48" s="5"/>
+      <c r="HH48" s="5"/>
+      <c r="HI48" s="5"/>
+      <c r="HJ48" s="5"/>
+      <c r="HK48" s="5"/>
+      <c r="HL48" s="5"/>
+      <c r="HM48" s="5"/>
+      <c r="HN48" s="5"/>
+      <c r="HO48" s="5"/>
+      <c r="HP48" s="5"/>
+      <c r="HQ48" s="5"/>
+      <c r="HR48" s="5"/>
+      <c r="HS48" s="5"/>
+      <c r="HT48" s="5"/>
+      <c r="HU48" s="5"/>
+      <c r="HV48" s="5"/>
+      <c r="HW48" s="5"/>
+      <c r="HX48" s="5"/>
+      <c r="HY48" s="5"/>
+      <c r="HZ48" s="5"/>
+      <c r="IA48" s="5"/>
+      <c r="IB48" s="5"/>
+      <c r="IC48" s="5"/>
+      <c r="ID48" s="5"/>
+      <c r="IE48" s="5"/>
+      <c r="IF48" s="5"/>
+      <c r="IG48" s="5"/>
+      <c r="IH48" s="5"/>
+      <c r="II48" s="5"/>
+      <c r="IJ48" s="5"/>
+      <c r="IK48" s="5"/>
+      <c r="IL48" s="5"/>
+      <c r="IM48" s="5"/>
+      <c r="IN48" s="5"/>
+      <c r="IO48" s="5"/>
+      <c r="IP48" s="5"/>
+      <c r="IQ48" s="5"/>
+      <c r="IR48" s="5"/>
+      <c r="IS48" s="5"/>
+      <c r="IT48" s="5"/>
+      <c r="IU48" s="5"/>
+      <c r="IV48" s="5"/>
+      <c r="IW48" s="5"/>
+      <c r="IX48" s="5"/>
+      <c r="IY48" s="5"/>
+      <c r="IZ48" s="5"/>
+      <c r="JA48" s="5"/>
+      <c r="JB48" s="5"/>
+      <c r="JC48" s="5"/>
+      <c r="JD48" s="5"/>
+      <c r="JE48" s="5"/>
+      <c r="JF48" s="5"/>
+      <c r="JG48" s="5"/>
+      <c r="JH48" s="5"/>
+      <c r="JI48" s="5"/>
+      <c r="JJ48" s="5"/>
+      <c r="JK48" s="5"/>
+      <c r="JL48" s="5"/>
+      <c r="JM48" s="5"/>
+      <c r="JN48" s="5"/>
+      <c r="JO48" s="5"/>
+      <c r="JP48" s="5"/>
+      <c r="JQ48" s="5"/>
+      <c r="JR48" s="5"/>
+      <c r="JS48" s="5"/>
+      <c r="JT48" s="5"/>
+      <c r="JU48" s="5"/>
+      <c r="JV48" s="5"/>
+      <c r="JW48" s="5"/>
+      <c r="JX48" s="5"/>
+      <c r="JY48" s="5"/>
+      <c r="JZ48" s="5"/>
+      <c r="KA48" s="5"/>
+      <c r="KB48" s="5"/>
+      <c r="KC48" s="5"/>
+      <c r="KD48" s="5"/>
+      <c r="KE48" s="5"/>
+      <c r="KF48" s="5"/>
+      <c r="KG48" s="5"/>
+      <c r="KH48" s="5"/>
+      <c r="KI48" s="5"/>
+      <c r="KJ48" s="5"/>
+      <c r="KK48" s="5"/>
+      <c r="KL48" s="5"/>
+      <c r="KM48" s="5"/>
+      <c r="KN48" s="5"/>
+      <c r="KO48" s="5"/>
+      <c r="KP48" s="5"/>
+      <c r="KQ48" s="5"/>
+      <c r="KR48" s="5"/>
+      <c r="KS48" s="5"/>
+      <c r="KT48" s="5"/>
+      <c r="KU48" s="5"/>
+      <c r="KV48" s="5"/>
+      <c r="KW48" s="5"/>
+      <c r="KX48" s="5"/>
+      <c r="KY48" s="5"/>
+      <c r="KZ48" s="5"/>
+      <c r="LA48" s="5"/>
+      <c r="LB48" s="5"/>
+      <c r="LC48" s="5"/>
+      <c r="LD48" s="5"/>
+      <c r="LE48" s="5"/>
+      <c r="LF48" s="5"/>
+      <c r="LG48" s="5"/>
+      <c r="LH48" s="5"/>
+      <c r="LI48" s="5"/>
+      <c r="LJ48" s="5"/>
+      <c r="LK48" s="5"/>
+      <c r="LL48" s="5"/>
+      <c r="LM48" s="5"/>
+      <c r="LN48" s="5"/>
+      <c r="LO48" s="5"/>
+      <c r="LP48" s="5"/>
+      <c r="LQ48" s="5"/>
+      <c r="LR48" s="5"/>
+      <c r="LS48" s="5"/>
+      <c r="LT48" s="5"/>
+      <c r="LU48" s="5"/>
+      <c r="LV48" s="5"/>
+      <c r="LW48" s="5"/>
+      <c r="LX48" s="5"/>
+      <c r="LY48" s="5"/>
+      <c r="LZ48" s="5"/>
+      <c r="MA48" s="5"/>
+      <c r="MB48" s="5"/>
+      <c r="MC48" s="5"/>
+      <c r="MD48" s="5"/>
+      <c r="ME48" s="5"/>
+      <c r="MF48" s="5"/>
+      <c r="MG48" s="5"/>
+      <c r="MH48" s="5"/>
+      <c r="MI48" s="5"/>
+      <c r="MJ48" s="5"/>
+      <c r="MK48" s="5"/>
+      <c r="ML48" s="5"/>
+      <c r="MM48" s="5"/>
+      <c r="MN48" s="5"/>
+      <c r="MO48" s="5"/>
+      <c r="MP48" s="5"/>
+      <c r="MQ48" s="5"/>
+      <c r="MR48" s="5"/>
+      <c r="MS48" s="5"/>
+      <c r="MT48" s="5"/>
+      <c r="MU48" s="5"/>
+      <c r="MV48" s="5"/>
+      <c r="MW48" s="5"/>
+      <c r="MX48" s="5"/>
+      <c r="MY48" s="5"/>
+      <c r="MZ48" s="5"/>
+      <c r="NA48" s="5"/>
+      <c r="NB48" s="5"/>
+      <c r="NC48" s="5"/>
+      <c r="ND48" s="5"/>
+      <c r="NE48" s="5"/>
+      <c r="NF48" s="5"/>
+      <c r="NG48" s="5"/>
+      <c r="NH48" s="5"/>
+      <c r="NI48" s="5"/>
+      <c r="NJ48" s="5"/>
+      <c r="NK48" s="5"/>
+      <c r="NL48" s="5"/>
+      <c r="NM48" s="5"/>
+      <c r="NN48" s="5"/>
+      <c r="NO48" s="5"/>
+      <c r="NP48" s="5"/>
+      <c r="NQ48" s="5"/>
+      <c r="NR48" s="5"/>
+      <c r="NS48" s="5"/>
+      <c r="NT48" s="5"/>
+      <c r="NU48" s="5"/>
+      <c r="NV48" s="5"/>
+      <c r="NW48" s="5"/>
+      <c r="NX48" s="5"/>
+      <c r="NY48" s="5"/>
+      <c r="NZ48" s="5"/>
+      <c r="OA48" s="5"/>
+      <c r="OB48" s="5"/>
+      <c r="OC48" s="5"/>
+      <c r="OD48" s="5"/>
+      <c r="OE48" s="5"/>
+      <c r="OF48" s="5"/>
+      <c r="OG48" s="5"/>
+      <c r="OH48" s="5"/>
+      <c r="OI48" s="5"/>
+      <c r="OJ48" s="5"/>
+      <c r="OK48" s="5"/>
+      <c r="OL48" s="5"/>
+      <c r="OM48" s="5"/>
+      <c r="ON48" s="5"/>
+      <c r="OO48" s="5"/>
+      <c r="OP48" s="5"/>
+      <c r="OQ48" s="5"/>
+      <c r="OR48" s="5"/>
+      <c r="OS48" s="5"/>
+      <c r="OT48" s="5"/>
+      <c r="OU48" s="5"/>
+      <c r="OV48" s="5"/>
+      <c r="OW48" s="5"/>
+      <c r="OX48" s="5"/>
+      <c r="OY48" s="5"/>
+      <c r="OZ48" s="5"/>
+      <c r="PA48" s="5"/>
+      <c r="PB48" s="5"/>
+      <c r="PC48" s="5"/>
+      <c r="PD48" s="5"/>
+      <c r="PE48" s="5"/>
+      <c r="PF48" s="5"/>
+      <c r="PG48" s="5"/>
+      <c r="PH48" s="5"/>
+      <c r="PI48" s="5"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="5"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="5"/>
+      <c r="Q49" s="5"/>
+      <c r="R49" s="5"/>
+      <c r="S49" s="5"/>
+      <c r="T49" s="5"/>
+      <c r="U49" s="5"/>
+      <c r="V49" s="5"/>
+      <c r="W49" s="5"/>
+      <c r="X49" s="5"/>
+      <c r="Y49" s="5"/>
+      <c r="Z49" s="5"/>
+      <c r="AA49" s="5"/>
+      <c r="AB49" s="5"/>
+      <c r="AC49" s="5"/>
+      <c r="AD49" s="5"/>
+      <c r="AE49" s="5"/>
+      <c r="AF49" s="5"/>
+      <c r="AG49" s="5"/>
+      <c r="AH49" s="5"/>
+      <c r="AI49" s="5"/>
+      <c r="AJ49" s="5"/>
+      <c r="AK49" s="5"/>
+      <c r="AL49" s="5"/>
+      <c r="AM49" s="5"/>
+      <c r="AN49" s="5"/>
+      <c r="AO49" s="5"/>
+      <c r="AP49" s="5"/>
+      <c r="AQ49" s="5"/>
+      <c r="AR49" s="5"/>
+      <c r="AS49" s="5"/>
+      <c r="AT49" s="5"/>
+      <c r="AU49" s="5"/>
+      <c r="AV49" s="5"/>
+      <c r="AW49" s="5"/>
+      <c r="AX49" s="5"/>
+      <c r="AY49" s="5"/>
+      <c r="AZ49" s="5"/>
+      <c r="BA49" s="5"/>
+      <c r="BB49" s="5"/>
+      <c r="BC49" s="5"/>
+      <c r="BD49" s="5"/>
+      <c r="BE49" s="5"/>
+      <c r="BF49" s="5"/>
+      <c r="BG49" s="5"/>
+      <c r="BH49" s="5"/>
+      <c r="BI49" s="5"/>
+      <c r="BJ49" s="5"/>
+      <c r="BK49" s="5"/>
+      <c r="BL49" s="5"/>
+      <c r="BM49" s="5"/>
+      <c r="BN49" s="5"/>
+      <c r="BO49" s="5"/>
+      <c r="BP49" s="5"/>
+      <c r="BQ49" s="5"/>
+      <c r="BR49" s="5"/>
+      <c r="BS49" s="5"/>
+      <c r="BT49" s="5"/>
+      <c r="BU49" s="5"/>
+      <c r="BV49" s="5"/>
+      <c r="BW49" s="5"/>
+      <c r="BX49" s="5"/>
+      <c r="BY49" s="5"/>
+      <c r="BZ49" s="5"/>
+      <c r="CA49" s="5"/>
+      <c r="CB49" s="5"/>
+      <c r="CC49" s="5"/>
+      <c r="CD49" s="5"/>
+      <c r="CE49" s="5"/>
+      <c r="CF49" s="5"/>
+      <c r="CG49" s="5"/>
+      <c r="CH49" s="5"/>
+      <c r="CI49" s="5"/>
+      <c r="CJ49" s="5"/>
+      <c r="CK49" s="5"/>
+      <c r="CL49" s="5"/>
+      <c r="CM49" s="5"/>
+      <c r="CN49" s="5"/>
+      <c r="CO49" s="5"/>
+      <c r="CP49" s="5"/>
+      <c r="CQ49" s="5"/>
+      <c r="CR49" s="5"/>
+      <c r="CS49" s="5"/>
+      <c r="CT49" s="5"/>
+      <c r="CU49" s="5"/>
+      <c r="CV49" s="5"/>
+      <c r="CW49" s="5"/>
+      <c r="CX49" s="5"/>
+      <c r="CY49" s="5"/>
+      <c r="CZ49" s="5"/>
+      <c r="DA49" s="5"/>
+      <c r="DB49" s="5"/>
+      <c r="DC49" s="5"/>
+      <c r="DD49" s="5"/>
+      <c r="DE49" s="5"/>
+      <c r="DF49" s="5"/>
+      <c r="DG49" s="5"/>
+      <c r="DH49" s="5"/>
+      <c r="DI49" s="5"/>
+      <c r="DJ49" s="5"/>
+      <c r="DK49" s="5"/>
+      <c r="DL49" s="5"/>
+      <c r="DM49" s="5"/>
+      <c r="DN49" s="5"/>
+      <c r="DO49" s="5"/>
+      <c r="DP49" s="5"/>
+      <c r="DQ49" s="5"/>
+      <c r="DR49" s="5"/>
+      <c r="DS49" s="5"/>
+      <c r="DT49" s="5"/>
+      <c r="DU49" s="5"/>
+      <c r="DV49" s="5"/>
+      <c r="DW49" s="5"/>
+      <c r="DX49" s="5"/>
+      <c r="DY49" s="5"/>
+      <c r="DZ49" s="5"/>
+      <c r="EA49" s="5"/>
+      <c r="EB49" s="5"/>
+      <c r="EC49" s="5"/>
+      <c r="ED49" s="5"/>
+      <c r="EE49" s="5"/>
+      <c r="EF49" s="5"/>
+      <c r="EG49" s="5"/>
+      <c r="EH49" s="5"/>
+      <c r="EI49" s="5"/>
+      <c r="EJ49" s="5"/>
+      <c r="EK49" s="5"/>
+      <c r="EL49" s="5"/>
+      <c r="EM49" s="5"/>
+      <c r="EN49" s="5"/>
+      <c r="EO49" s="5"/>
+      <c r="EP49" s="5"/>
+      <c r="EQ49" s="5"/>
+      <c r="ER49" s="5"/>
+      <c r="ES49" s="5"/>
+      <c r="ET49" s="5"/>
+      <c r="EU49" s="5"/>
+      <c r="EV49" s="5"/>
+      <c r="EW49" s="5"/>
+      <c r="EX49" s="5"/>
+      <c r="EY49" s="5"/>
+      <c r="EZ49" s="5"/>
+      <c r="FA49" s="5"/>
+      <c r="FB49" s="5"/>
+      <c r="FC49" s="5"/>
+      <c r="FD49" s="5"/>
+      <c r="FE49" s="5"/>
+      <c r="FF49" s="5"/>
+      <c r="FG49" s="5"/>
+      <c r="FH49" s="5"/>
+      <c r="FI49" s="5"/>
+      <c r="FJ49" s="5"/>
+      <c r="FK49" s="5"/>
+      <c r="FL49" s="5"/>
+      <c r="FM49" s="5"/>
+      <c r="FN49" s="5"/>
+      <c r="FO49" s="5"/>
+      <c r="FP49" s="5"/>
+      <c r="FQ49" s="5"/>
+      <c r="FR49" s="5"/>
+      <c r="FS49" s="5"/>
+      <c r="FT49" s="5"/>
+      <c r="FU49" s="5"/>
+      <c r="FV49" s="5"/>
+      <c r="FW49" s="5"/>
+      <c r="FX49" s="5"/>
+      <c r="FY49" s="5"/>
+      <c r="FZ49" s="5"/>
+      <c r="GA49" s="5"/>
+      <c r="GB49" s="5"/>
+      <c r="GC49" s="5"/>
+      <c r="GD49" s="5"/>
+      <c r="GE49" s="5"/>
+      <c r="GF49" s="5"/>
+      <c r="GG49" s="5"/>
+      <c r="GH49" s="5"/>
+      <c r="GI49" s="5"/>
+      <c r="GJ49" s="5"/>
+      <c r="GK49" s="5"/>
+      <c r="GL49" s="5"/>
+      <c r="GM49" s="5"/>
+      <c r="GN49" s="5"/>
+      <c r="GO49" s="5"/>
+      <c r="GP49" s="5"/>
+      <c r="GQ49" s="5"/>
+      <c r="GR49" s="5"/>
+      <c r="GS49" s="5"/>
+      <c r="GT49" s="5"/>
+      <c r="GU49" s="5"/>
+      <c r="GV49" s="5"/>
+      <c r="GW49" s="5"/>
+      <c r="GX49" s="5"/>
+      <c r="GY49" s="5"/>
+      <c r="GZ49" s="5"/>
+      <c r="HA49" s="5"/>
+      <c r="HB49" s="5"/>
+      <c r="HC49" s="5"/>
+      <c r="HD49" s="5"/>
+      <c r="HE49" s="5"/>
+      <c r="HF49" s="5"/>
+      <c r="HG49" s="5"/>
+      <c r="HH49" s="5"/>
+      <c r="HI49" s="5"/>
+      <c r="HJ49" s="5"/>
+      <c r="HK49" s="5"/>
+      <c r="HL49" s="5"/>
+      <c r="HM49" s="5"/>
+      <c r="HN49" s="5"/>
+      <c r="HO49" s="5"/>
+      <c r="HP49" s="5"/>
+      <c r="HQ49" s="5"/>
+      <c r="HR49" s="5"/>
+      <c r="HS49" s="5"/>
+      <c r="HT49" s="5"/>
+      <c r="HU49" s="5"/>
+      <c r="HV49" s="5"/>
+      <c r="HW49" s="5"/>
+      <c r="HX49" s="5"/>
+      <c r="HY49" s="5"/>
+      <c r="HZ49" s="5"/>
+      <c r="IA49" s="5"/>
+      <c r="IB49" s="5"/>
+      <c r="IC49" s="5"/>
+      <c r="ID49" s="5"/>
+      <c r="IE49" s="5"/>
+      <c r="IF49" s="5"/>
+      <c r="IG49" s="5"/>
+      <c r="IH49" s="5"/>
+      <c r="II49" s="5"/>
+      <c r="IJ49" s="5"/>
+      <c r="IK49" s="5"/>
+      <c r="IL49" s="5"/>
+      <c r="IM49" s="5"/>
+      <c r="IN49" s="5"/>
+      <c r="IO49" s="5"/>
+      <c r="IP49" s="5"/>
+      <c r="IQ49" s="5"/>
+      <c r="IR49" s="5"/>
+      <c r="IS49" s="5"/>
+      <c r="IT49" s="5"/>
+      <c r="IU49" s="5"/>
+      <c r="IV49" s="5"/>
+      <c r="IW49" s="5"/>
+      <c r="IX49" s="5"/>
+      <c r="IY49" s="5"/>
+      <c r="IZ49" s="5"/>
+      <c r="JA49" s="5"/>
+      <c r="JB49" s="5"/>
+      <c r="JC49" s="5"/>
+      <c r="JD49" s="5"/>
+      <c r="JE49" s="5"/>
+      <c r="JF49" s="5"/>
+      <c r="JG49" s="5"/>
+      <c r="JH49" s="5"/>
+      <c r="JI49" s="5"/>
+      <c r="JJ49" s="5"/>
+      <c r="JK49" s="5"/>
+      <c r="JL49" s="5"/>
+      <c r="JM49" s="5"/>
+      <c r="JN49" s="5"/>
+      <c r="JO49" s="5"/>
+      <c r="JP49" s="5"/>
+      <c r="JQ49" s="5"/>
+      <c r="JR49" s="5"/>
+      <c r="JS49" s="5"/>
+      <c r="JT49" s="5"/>
+      <c r="JU49" s="5"/>
+      <c r="JV49" s="5"/>
+      <c r="JW49" s="5"/>
+      <c r="JX49" s="5"/>
+      <c r="JY49" s="5"/>
+      <c r="JZ49" s="5"/>
+      <c r="KA49" s="5"/>
+      <c r="KB49" s="5"/>
+      <c r="KC49" s="5"/>
+      <c r="KD49" s="5"/>
+      <c r="KE49" s="5"/>
+      <c r="KF49" s="5"/>
+      <c r="KG49" s="5"/>
+      <c r="KH49" s="5"/>
+      <c r="KI49" s="5"/>
+      <c r="KJ49" s="5"/>
+      <c r="KK49" s="5"/>
+      <c r="KL49" s="5"/>
+      <c r="KM49" s="5"/>
+      <c r="KN49" s="5"/>
+      <c r="KO49" s="5"/>
+      <c r="KP49" s="5"/>
+      <c r="KQ49" s="5"/>
+      <c r="KR49" s="5"/>
+      <c r="KS49" s="5"/>
+      <c r="KT49" s="5"/>
+      <c r="KU49" s="5"/>
+      <c r="KV49" s="5"/>
+      <c r="KW49" s="5"/>
+      <c r="KX49" s="5"/>
+      <c r="KY49" s="5"/>
+      <c r="KZ49" s="5"/>
+      <c r="LA49" s="5"/>
+      <c r="LB49" s="5"/>
+      <c r="LC49" s="5"/>
+      <c r="LD49" s="5"/>
+      <c r="LE49" s="5"/>
+      <c r="LF49" s="5"/>
+      <c r="LG49" s="5"/>
+      <c r="LH49" s="5"/>
+      <c r="LI49" s="5"/>
+      <c r="LJ49" s="5"/>
+      <c r="LK49" s="5"/>
+      <c r="LL49" s="5"/>
+      <c r="LM49" s="5"/>
+      <c r="LN49" s="5"/>
+      <c r="LO49" s="5"/>
+      <c r="LP49" s="5"/>
+      <c r="LQ49" s="5"/>
+      <c r="LR49" s="5"/>
+      <c r="LS49" s="5"/>
+      <c r="LT49" s="5"/>
+      <c r="LU49" s="5"/>
+      <c r="LV49" s="5"/>
+      <c r="LW49" s="5"/>
+      <c r="LX49" s="5"/>
+      <c r="LY49" s="5"/>
+      <c r="LZ49" s="5"/>
+      <c r="MA49" s="5"/>
+      <c r="MB49" s="5"/>
+      <c r="MC49" s="5"/>
+      <c r="MD49" s="5"/>
+      <c r="ME49" s="5"/>
+      <c r="MF49" s="5"/>
+      <c r="MG49" s="5"/>
+      <c r="MH49" s="5"/>
+      <c r="MI49" s="5"/>
+      <c r="MJ49" s="5"/>
+      <c r="MK49" s="5"/>
+      <c r="ML49" s="5"/>
+      <c r="MM49" s="5"/>
+      <c r="MN49" s="5"/>
+      <c r="MO49" s="5"/>
+      <c r="MP49" s="5"/>
+      <c r="MQ49" s="5"/>
+      <c r="MR49" s="5"/>
+      <c r="MS49" s="5"/>
+      <c r="MT49" s="5"/>
+      <c r="MU49" s="5"/>
+      <c r="MV49" s="5"/>
+      <c r="MW49" s="5"/>
+      <c r="MX49" s="5"/>
+      <c r="MY49" s="5"/>
+      <c r="MZ49" s="5"/>
+      <c r="NA49" s="5"/>
+      <c r="NB49" s="5"/>
+      <c r="NC49" s="5"/>
+      <c r="ND49" s="5"/>
+      <c r="NE49" s="5"/>
+      <c r="NF49" s="5"/>
+      <c r="NG49" s="5"/>
+      <c r="NH49" s="5"/>
+      <c r="NI49" s="5"/>
+      <c r="NJ49" s="5"/>
+      <c r="NK49" s="5"/>
+      <c r="NL49" s="5"/>
+      <c r="NM49" s="5"/>
+      <c r="NN49" s="5"/>
+      <c r="NO49" s="5"/>
+      <c r="NP49" s="5"/>
+      <c r="NQ49" s="5"/>
+      <c r="NR49" s="5"/>
+      <c r="NS49" s="5"/>
+      <c r="NT49" s="5"/>
+      <c r="NU49" s="5"/>
+      <c r="NV49" s="5"/>
+      <c r="NW49" s="5"/>
+      <c r="NX49" s="5"/>
+      <c r="NY49" s="5"/>
+      <c r="NZ49" s="5"/>
+      <c r="OA49" s="5"/>
+      <c r="OB49" s="5"/>
+      <c r="OC49" s="5"/>
+      <c r="OD49" s="5"/>
+      <c r="OE49" s="5"/>
+      <c r="OF49" s="5"/>
+      <c r="OG49" s="5"/>
+      <c r="OH49" s="5"/>
+      <c r="OI49" s="5"/>
+      <c r="OJ49" s="5"/>
+      <c r="OK49" s="5"/>
+      <c r="OL49" s="5"/>
+      <c r="OM49" s="5"/>
+      <c r="ON49" s="5"/>
+      <c r="OO49" s="5"/>
+      <c r="OP49" s="5"/>
+      <c r="OQ49" s="5"/>
+      <c r="OR49" s="5"/>
+      <c r="OS49" s="5"/>
+      <c r="OT49" s="5"/>
+      <c r="OU49" s="5"/>
+      <c r="OV49" s="5"/>
+      <c r="OW49" s="5"/>
+      <c r="OX49" s="5"/>
+      <c r="OY49" s="5"/>
+      <c r="OZ49" s="5"/>
+      <c r="PA49" s="5"/>
+      <c r="PB49" s="5"/>
+      <c r="PC49" s="5"/>
+      <c r="PD49" s="5"/>
+      <c r="PE49" s="5"/>
+      <c r="PF49" s="5"/>
+      <c r="PG49" s="5"/>
+      <c r="PH49" s="5"/>
+      <c r="PI49" s="5"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>60.29</v>
+      </c>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="5"/>
+      <c r="Q50" s="5"/>
+      <c r="R50" s="5"/>
+      <c r="S50" s="5"/>
+      <c r="T50" s="5"/>
+      <c r="U50" s="5"/>
+      <c r="V50" s="5"/>
+      <c r="W50" s="5"/>
+      <c r="X50" s="5"/>
+      <c r="Y50" s="5"/>
+      <c r="Z50" s="5"/>
+      <c r="AA50" s="5"/>
+      <c r="AB50" s="5"/>
+      <c r="AC50" s="5"/>
+      <c r="AD50" s="5"/>
+      <c r="AE50" s="5"/>
+      <c r="AF50" s="5"/>
+      <c r="AG50" s="5"/>
+      <c r="AH50" s="5"/>
+      <c r="AI50" s="5"/>
+      <c r="AJ50" s="5"/>
+      <c r="AK50" s="5"/>
+      <c r="AL50" s="5"/>
+      <c r="AM50" s="5"/>
+      <c r="AN50" s="5"/>
+      <c r="AO50" s="5"/>
+      <c r="AP50" s="5"/>
+      <c r="AQ50" s="5"/>
+      <c r="AR50" s="5"/>
+      <c r="AS50" s="5"/>
+      <c r="AT50" s="5"/>
+      <c r="AU50" s="5"/>
+      <c r="AV50" s="5"/>
+      <c r="AW50" s="5"/>
+      <c r="AX50" s="5"/>
+      <c r="AY50" s="5"/>
+      <c r="AZ50" s="5"/>
+      <c r="BA50" s="5"/>
+      <c r="BB50" s="5"/>
+      <c r="BC50" s="5"/>
+      <c r="BD50" s="5"/>
+      <c r="BE50" s="5"/>
+      <c r="BF50" s="5"/>
+      <c r="BG50" s="5"/>
+      <c r="BH50" s="5"/>
+      <c r="BI50" s="5"/>
+      <c r="BJ50" s="5"/>
+      <c r="BK50" s="5"/>
+      <c r="BL50" s="5"/>
+      <c r="BM50" s="5"/>
+      <c r="BN50" s="5"/>
+      <c r="BO50" s="5"/>
+      <c r="BP50" s="5"/>
+      <c r="BQ50" s="5"/>
+      <c r="BR50" s="5"/>
+      <c r="BS50" s="5"/>
+      <c r="BT50" s="5"/>
+      <c r="BU50" s="5"/>
+      <c r="BV50" s="5"/>
+      <c r="BW50" s="5"/>
+      <c r="BX50" s="5"/>
+      <c r="BY50" s="5"/>
+      <c r="BZ50" s="5"/>
+      <c r="CA50" s="5"/>
+      <c r="CB50" s="5"/>
+      <c r="CC50" s="5"/>
+      <c r="CD50" s="5"/>
+      <c r="CE50" s="5"/>
+      <c r="CF50" s="5"/>
+      <c r="CG50" s="5"/>
+      <c r="CH50" s="5"/>
+      <c r="CI50" s="5"/>
+      <c r="CJ50" s="5"/>
+      <c r="CK50" s="5"/>
+      <c r="CL50" s="5"/>
+      <c r="CM50" s="5"/>
+      <c r="CN50" s="5"/>
+      <c r="CO50" s="5"/>
+      <c r="CP50" s="5"/>
+      <c r="CQ50" s="5"/>
+      <c r="CR50" s="5"/>
+      <c r="CS50" s="5"/>
+      <c r="CT50" s="5"/>
+      <c r="CU50" s="5"/>
+      <c r="CV50" s="5"/>
+      <c r="CW50" s="5"/>
+      <c r="CX50" s="5"/>
+      <c r="CY50" s="5"/>
+      <c r="CZ50" s="5"/>
+      <c r="DA50" s="5"/>
+      <c r="DB50" s="5"/>
+      <c r="DC50" s="5"/>
+      <c r="DD50" s="5"/>
+      <c r="DE50" s="5"/>
+      <c r="DF50" s="5"/>
+      <c r="DG50" s="5"/>
+      <c r="DH50" s="5"/>
+      <c r="DI50" s="5"/>
+      <c r="DJ50" s="5"/>
+      <c r="DK50" s="5"/>
+      <c r="DL50" s="5"/>
+      <c r="DM50" s="5"/>
+      <c r="DN50" s="5"/>
+      <c r="DO50" s="5"/>
+      <c r="DP50" s="5"/>
+      <c r="DQ50" s="5"/>
+      <c r="DR50" s="5"/>
+      <c r="DS50" s="5"/>
+      <c r="DT50" s="5"/>
+      <c r="DU50" s="5"/>
+      <c r="DV50" s="5"/>
+      <c r="DW50" s="5"/>
+      <c r="DX50" s="5"/>
+      <c r="DY50" s="5"/>
+      <c r="DZ50" s="5"/>
+      <c r="EA50" s="5"/>
+      <c r="EB50" s="5"/>
+      <c r="EC50" s="5"/>
+      <c r="ED50" s="5"/>
+      <c r="EE50" s="5"/>
+      <c r="EF50" s="5"/>
+      <c r="EG50" s="5"/>
+      <c r="EH50" s="5"/>
+      <c r="EI50" s="5"/>
+      <c r="EJ50" s="5"/>
+      <c r="EK50" s="5"/>
+      <c r="EL50" s="5"/>
+      <c r="EM50" s="5"/>
+      <c r="EN50" s="5"/>
+      <c r="EO50" s="5"/>
+      <c r="EP50" s="5"/>
+      <c r="EQ50" s="5"/>
+      <c r="ER50" s="5"/>
+      <c r="ES50" s="5"/>
+      <c r="ET50" s="5"/>
+      <c r="EU50" s="5"/>
+      <c r="EV50" s="5"/>
+      <c r="EW50" s="5"/>
+      <c r="EX50" s="5"/>
+      <c r="EY50" s="5"/>
+      <c r="EZ50" s="5"/>
+      <c r="FA50" s="5"/>
+      <c r="FB50" s="5"/>
+      <c r="FC50" s="5"/>
+      <c r="FD50" s="5"/>
+      <c r="FE50" s="5"/>
+      <c r="FF50" s="5"/>
+      <c r="FG50" s="5"/>
+      <c r="FH50" s="5"/>
+      <c r="FI50" s="5"/>
+      <c r="FJ50" s="5"/>
+      <c r="FK50" s="5"/>
+      <c r="FL50" s="5"/>
+      <c r="FM50" s="5"/>
+      <c r="FN50" s="5"/>
+      <c r="FO50" s="5"/>
+      <c r="FP50" s="5"/>
+      <c r="FQ50" s="5"/>
+      <c r="FR50" s="5"/>
+      <c r="FS50" s="5"/>
+      <c r="FT50" s="5"/>
+      <c r="FU50" s="5"/>
+      <c r="FV50" s="5"/>
+      <c r="FW50" s="5"/>
+      <c r="FX50" s="5"/>
+      <c r="FY50" s="5"/>
+      <c r="FZ50" s="5"/>
+      <c r="GA50" s="5"/>
+      <c r="GB50" s="5"/>
+      <c r="GC50" s="5"/>
+      <c r="GD50" s="5"/>
+      <c r="GE50" s="5"/>
+      <c r="GF50" s="5"/>
+      <c r="GG50" s="5"/>
+      <c r="GH50" s="5"/>
+      <c r="GI50" s="5"/>
+      <c r="GJ50" s="5"/>
+      <c r="GK50" s="5"/>
+      <c r="GL50" s="5"/>
+      <c r="GM50" s="5"/>
+      <c r="GN50" s="5"/>
+      <c r="GO50" s="5"/>
+      <c r="GP50" s="5"/>
+      <c r="GQ50" s="5"/>
+      <c r="GR50" s="5"/>
+      <c r="GS50" s="5"/>
+      <c r="GT50" s="5"/>
+      <c r="GU50" s="5"/>
+      <c r="GV50" s="5"/>
+      <c r="GW50" s="5"/>
+      <c r="GX50" s="5"/>
+      <c r="GY50" s="5"/>
+      <c r="GZ50" s="5"/>
+      <c r="HA50" s="5"/>
+      <c r="HB50" s="5"/>
+      <c r="HC50" s="5"/>
+      <c r="HD50" s="5"/>
+      <c r="HE50" s="5"/>
+      <c r="HF50" s="5"/>
+      <c r="HG50" s="5"/>
+      <c r="HH50" s="5"/>
+      <c r="HI50" s="5"/>
+      <c r="HJ50" s="5"/>
+      <c r="HK50" s="5"/>
+      <c r="HL50" s="5"/>
+      <c r="HM50" s="5"/>
+      <c r="HN50" s="5"/>
+      <c r="HO50" s="5"/>
+      <c r="HP50" s="5"/>
+      <c r="HQ50" s="5"/>
+      <c r="HR50" s="5"/>
+      <c r="HS50" s="5"/>
+      <c r="HT50" s="5"/>
+      <c r="HU50" s="5"/>
+      <c r="HV50" s="5"/>
+      <c r="HW50" s="5"/>
+      <c r="HX50" s="5"/>
+      <c r="HY50" s="5"/>
+      <c r="HZ50" s="5"/>
+      <c r="IA50" s="5"/>
+      <c r="IB50" s="5"/>
+      <c r="IC50" s="5"/>
+      <c r="ID50" s="5"/>
+      <c r="IE50" s="5"/>
+      <c r="IF50" s="5"/>
+      <c r="IG50" s="5"/>
+      <c r="IH50" s="5"/>
+      <c r="II50" s="5"/>
+      <c r="IJ50" s="5"/>
+      <c r="IK50" s="5"/>
+      <c r="IL50" s="5"/>
+      <c r="IM50" s="5"/>
+      <c r="IN50" s="5"/>
+      <c r="IO50" s="5"/>
+      <c r="IP50" s="5"/>
+      <c r="IQ50" s="5"/>
+      <c r="IR50" s="5"/>
+      <c r="IS50" s="5"/>
+      <c r="IT50" s="5"/>
+      <c r="IU50" s="5"/>
+      <c r="IV50" s="5"/>
+      <c r="IW50" s="5"/>
+      <c r="IX50" s="5"/>
+      <c r="IY50" s="5"/>
+      <c r="IZ50" s="5"/>
+      <c r="JA50" s="5"/>
+      <c r="JB50" s="5"/>
+      <c r="JC50" s="5"/>
+      <c r="JD50" s="5"/>
+      <c r="JE50" s="5"/>
+      <c r="JF50" s="5"/>
+      <c r="JG50" s="5"/>
+      <c r="JH50" s="5"/>
+      <c r="JI50" s="5"/>
+      <c r="JJ50" s="5"/>
+      <c r="JK50" s="5"/>
+      <c r="JL50" s="5"/>
+      <c r="JM50" s="5"/>
+      <c r="JN50" s="5"/>
+      <c r="JO50" s="5"/>
+      <c r="JP50" s="5"/>
+      <c r="JQ50" s="5"/>
+      <c r="JR50" s="5"/>
+      <c r="JS50" s="5"/>
+      <c r="JT50" s="5"/>
+      <c r="JU50" s="5"/>
+      <c r="JV50" s="5"/>
+      <c r="JW50" s="5"/>
+      <c r="JX50" s="5"/>
+      <c r="JY50" s="5"/>
+      <c r="JZ50" s="5"/>
+      <c r="KA50" s="5"/>
+      <c r="KB50" s="5"/>
+      <c r="KC50" s="5"/>
+      <c r="KD50" s="5"/>
+      <c r="KE50" s="5"/>
+      <c r="KF50" s="5"/>
+      <c r="KG50" s="5"/>
+      <c r="KH50" s="5"/>
+      <c r="KI50" s="5"/>
+      <c r="KJ50" s="5"/>
+      <c r="KK50" s="5"/>
+      <c r="KL50" s="5"/>
+      <c r="KM50" s="5"/>
+      <c r="KN50" s="5"/>
+      <c r="KO50" s="5"/>
+      <c r="KP50" s="5"/>
+      <c r="KQ50" s="5"/>
+      <c r="KR50" s="5"/>
+      <c r="KS50" s="5"/>
+      <c r="KT50" s="5"/>
+      <c r="KU50" s="5"/>
+      <c r="KV50" s="5"/>
+      <c r="KW50" s="5"/>
+      <c r="KX50" s="5"/>
+      <c r="KY50" s="5"/>
+      <c r="KZ50" s="5"/>
+      <c r="LA50" s="5"/>
+      <c r="LB50" s="5"/>
+      <c r="LC50" s="5"/>
+      <c r="LD50" s="5"/>
+      <c r="LE50" s="5"/>
+      <c r="LF50" s="5"/>
+      <c r="LG50" s="5"/>
+      <c r="LH50" s="5"/>
+      <c r="LI50" s="5"/>
+      <c r="LJ50" s="5"/>
+      <c r="LK50" s="5"/>
+      <c r="LL50" s="5"/>
+      <c r="LM50" s="5"/>
+      <c r="LN50" s="5"/>
+      <c r="LO50" s="5"/>
+      <c r="LP50" s="5"/>
+      <c r="LQ50" s="5"/>
+      <c r="LR50" s="5"/>
+      <c r="LS50" s="5"/>
+      <c r="LT50" s="5"/>
+      <c r="LU50" s="5"/>
+      <c r="LV50" s="5"/>
+      <c r="LW50" s="5"/>
+      <c r="LX50" s="5"/>
+      <c r="LY50" s="5"/>
+      <c r="LZ50" s="5"/>
+      <c r="MA50" s="5"/>
+      <c r="MB50" s="5"/>
+      <c r="MC50" s="5"/>
+      <c r="MD50" s="5"/>
+      <c r="ME50" s="5"/>
+      <c r="MF50" s="5"/>
+      <c r="MG50" s="5"/>
+      <c r="MH50" s="5"/>
+      <c r="MI50" s="5"/>
+      <c r="MJ50" s="5"/>
+      <c r="MK50" s="5"/>
+      <c r="ML50" s="5"/>
+      <c r="MM50" s="5"/>
+      <c r="MN50" s="5"/>
+      <c r="MO50" s="5"/>
+      <c r="MP50" s="5"/>
+      <c r="MQ50" s="5"/>
+      <c r="MR50" s="5"/>
+      <c r="MS50" s="5"/>
+      <c r="MT50" s="5"/>
+      <c r="MU50" s="5"/>
+      <c r="MV50" s="5"/>
+      <c r="MW50" s="5"/>
+      <c r="MX50" s="5"/>
+      <c r="MY50" s="5"/>
+      <c r="MZ50" s="5"/>
+      <c r="NA50" s="5"/>
+      <c r="NB50" s="5"/>
+      <c r="NC50" s="5"/>
+      <c r="ND50" s="5"/>
+      <c r="NE50" s="5"/>
+      <c r="NF50" s="5"/>
+      <c r="NG50" s="5"/>
+      <c r="NH50" s="5"/>
+      <c r="NI50" s="5"/>
+      <c r="NJ50" s="5"/>
+      <c r="NK50" s="5"/>
+      <c r="NL50" s="5"/>
+      <c r="NM50" s="5"/>
+      <c r="NN50" s="5"/>
+      <c r="NO50" s="5"/>
+      <c r="NP50" s="5"/>
+      <c r="NQ50" s="5"/>
+      <c r="NR50" s="5"/>
+      <c r="NS50" s="5"/>
+      <c r="NT50" s="5"/>
+      <c r="NU50" s="5"/>
+      <c r="NV50" s="5"/>
+      <c r="NW50" s="5"/>
+      <c r="NX50" s="5"/>
+      <c r="NY50" s="5"/>
+      <c r="NZ50" s="5"/>
+      <c r="OA50" s="5"/>
+      <c r="OB50" s="5"/>
+      <c r="OC50" s="5"/>
+      <c r="OD50" s="5"/>
+      <c r="OE50" s="5"/>
+      <c r="OF50" s="5"/>
+      <c r="OG50" s="5"/>
+      <c r="OH50" s="5"/>
+      <c r="OI50" s="5"/>
+      <c r="OJ50" s="5"/>
+      <c r="OK50" s="5"/>
+      <c r="OL50" s="5"/>
+      <c r="OM50" s="5"/>
+      <c r="ON50" s="5"/>
+      <c r="OO50" s="5"/>
+      <c r="OP50" s="5"/>
+      <c r="OQ50" s="5"/>
+      <c r="OR50" s="5"/>
+      <c r="OS50" s="5"/>
+      <c r="OT50" s="5"/>
+      <c r="OU50" s="5"/>
+      <c r="OV50" s="5"/>
+      <c r="OW50" s="5"/>
+      <c r="OX50" s="5"/>
+      <c r="OY50" s="5"/>
+      <c r="OZ50" s="5"/>
+      <c r="PA50" s="5"/>
+      <c r="PB50" s="5"/>
+      <c r="PC50" s="5"/>
+      <c r="PD50" s="5"/>
+      <c r="PE50" s="5"/>
+      <c r="PF50" s="5"/>
+      <c r="PG50" s="5"/>
+      <c r="PH50" s="5"/>
+      <c r="PI50" s="5"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="5"/>
+      <c r="Q51" s="5"/>
+      <c r="R51" s="5"/>
+      <c r="S51" s="5"/>
+      <c r="T51" s="5"/>
+      <c r="U51" s="5"/>
+      <c r="V51" s="5"/>
+      <c r="W51" s="5"/>
+      <c r="X51" s="5"/>
+      <c r="Y51" s="5"/>
+      <c r="Z51" s="5"/>
+      <c r="AA51" s="5"/>
+      <c r="AB51" s="5"/>
+      <c r="AC51" s="5"/>
+      <c r="AD51" s="5"/>
+      <c r="AE51" s="5"/>
+      <c r="AF51" s="5"/>
+      <c r="AG51" s="5"/>
+      <c r="AH51" s="5"/>
+      <c r="AI51" s="5"/>
+      <c r="AJ51" s="5"/>
+      <c r="AK51" s="5"/>
+      <c r="AL51" s="5"/>
+      <c r="AM51" s="5"/>
+      <c r="AN51" s="5"/>
+      <c r="AO51" s="5"/>
+      <c r="AP51" s="5"/>
+      <c r="AQ51" s="5"/>
+      <c r="AR51" s="5"/>
+      <c r="AS51" s="5"/>
+      <c r="AT51" s="5"/>
+      <c r="AU51" s="5"/>
+      <c r="AV51" s="5"/>
+      <c r="AW51" s="5"/>
+      <c r="AX51" s="5"/>
+      <c r="AY51" s="5"/>
+      <c r="AZ51" s="5"/>
+      <c r="BA51" s="5"/>
+      <c r="BB51" s="5"/>
+      <c r="BC51" s="5"/>
+      <c r="BD51" s="5"/>
+      <c r="BE51" s="5"/>
+      <c r="BF51" s="5"/>
+      <c r="BG51" s="5"/>
+      <c r="BH51" s="5"/>
+      <c r="BI51" s="5"/>
+      <c r="BJ51" s="5"/>
+      <c r="BK51" s="5"/>
+      <c r="BL51" s="5"/>
+      <c r="BM51" s="5"/>
+      <c r="BN51" s="5"/>
+      <c r="BO51" s="5"/>
+      <c r="BP51" s="5"/>
+      <c r="BQ51" s="5"/>
+      <c r="BR51" s="5"/>
+      <c r="BS51" s="5"/>
+      <c r="BT51" s="5"/>
+      <c r="BU51" s="5"/>
+      <c r="BV51" s="5"/>
+      <c r="BW51" s="5"/>
+      <c r="BX51" s="5"/>
+      <c r="BY51" s="5"/>
+      <c r="BZ51" s="5"/>
+      <c r="CA51" s="5"/>
+      <c r="CB51" s="5"/>
+      <c r="CC51" s="5"/>
+      <c r="CD51" s="5"/>
+      <c r="CE51" s="5"/>
+      <c r="CF51" s="5"/>
+      <c r="CG51" s="5"/>
+      <c r="CH51" s="5"/>
+      <c r="CI51" s="5"/>
+      <c r="CJ51" s="5"/>
+      <c r="CK51" s="5"/>
+      <c r="CL51" s="5"/>
+      <c r="CM51" s="5"/>
+      <c r="CN51" s="5"/>
+      <c r="CO51" s="5"/>
+      <c r="CP51" s="5"/>
+      <c r="CQ51" s="5"/>
+      <c r="CR51" s="5"/>
+      <c r="CS51" s="5"/>
+      <c r="CT51" s="5"/>
+      <c r="CU51" s="5"/>
+      <c r="CV51" s="5"/>
+      <c r="CW51" s="5"/>
+      <c r="CX51" s="5"/>
+      <c r="CY51" s="5"/>
+      <c r="CZ51" s="5"/>
+      <c r="DA51" s="5"/>
+      <c r="DB51" s="5"/>
+      <c r="DC51" s="5"/>
+      <c r="DD51" s="5"/>
+      <c r="DE51" s="5"/>
+      <c r="DF51" s="5"/>
+      <c r="DG51" s="5"/>
+      <c r="DH51" s="5"/>
+      <c r="DI51" s="5"/>
+      <c r="DJ51" s="5"/>
+      <c r="DK51" s="5"/>
+      <c r="DL51" s="5"/>
+      <c r="DM51" s="5"/>
+      <c r="DN51" s="5"/>
+      <c r="DO51" s="5"/>
+      <c r="DP51" s="5"/>
+      <c r="DQ51" s="5"/>
+      <c r="DR51" s="5"/>
+      <c r="DS51" s="5"/>
+      <c r="DT51" s="5"/>
+      <c r="DU51" s="5"/>
+      <c r="DV51" s="5"/>
+      <c r="DW51" s="5"/>
+      <c r="DX51" s="5"/>
+      <c r="DY51" s="5"/>
+      <c r="DZ51" s="5"/>
+      <c r="EA51" s="5"/>
+      <c r="EB51" s="5"/>
+      <c r="EC51" s="5"/>
+      <c r="ED51" s="5"/>
+      <c r="EE51" s="5"/>
+      <c r="EF51" s="5"/>
+      <c r="EG51" s="5"/>
+      <c r="EH51" s="5"/>
+      <c r="EI51" s="5"/>
+      <c r="EJ51" s="5"/>
+      <c r="EK51" s="5"/>
+      <c r="EL51" s="5"/>
+      <c r="EM51" s="5"/>
+      <c r="EN51" s="5"/>
+      <c r="EO51" s="5"/>
+      <c r="EP51" s="5"/>
+      <c r="EQ51" s="5"/>
+      <c r="ER51" s="5"/>
+      <c r="ES51" s="5"/>
+      <c r="ET51" s="5"/>
+      <c r="EU51" s="5"/>
+      <c r="EV51" s="5"/>
+      <c r="EW51" s="5"/>
+      <c r="EX51" s="5"/>
+      <c r="EY51" s="5"/>
+      <c r="EZ51" s="5"/>
+      <c r="FA51" s="5"/>
+      <c r="FB51" s="5"/>
+      <c r="FC51" s="5"/>
+      <c r="FD51" s="5"/>
+      <c r="FE51" s="5"/>
+      <c r="FF51" s="5"/>
+      <c r="FG51" s="5"/>
+      <c r="FH51" s="5"/>
+      <c r="FI51" s="5"/>
+      <c r="FJ51" s="5"/>
+      <c r="FK51" s="5"/>
+      <c r="FL51" s="5"/>
+      <c r="FM51" s="5"/>
+      <c r="FN51" s="5"/>
+      <c r="FO51" s="5"/>
+      <c r="FP51" s="5"/>
+      <c r="FQ51" s="5"/>
+      <c r="FR51" s="5"/>
+      <c r="FS51" s="5"/>
+      <c r="FT51" s="5"/>
+      <c r="FU51" s="5"/>
+      <c r="FV51" s="5"/>
+      <c r="FW51" s="5"/>
+      <c r="FX51" s="5"/>
+      <c r="FY51" s="5"/>
+      <c r="FZ51" s="5"/>
+      <c r="GA51" s="5"/>
+      <c r="GB51" s="5"/>
+      <c r="GC51" s="5"/>
+      <c r="GD51" s="5"/>
+      <c r="GE51" s="5"/>
+      <c r="GF51" s="5"/>
+      <c r="GG51" s="5"/>
+      <c r="GH51" s="5"/>
+      <c r="GI51" s="5"/>
+      <c r="GJ51" s="5"/>
+      <c r="GK51" s="5"/>
+      <c r="GL51" s="5"/>
+      <c r="GM51" s="5"/>
+      <c r="GN51" s="5"/>
+      <c r="GO51" s="5"/>
+      <c r="GP51" s="5"/>
+      <c r="GQ51" s="5"/>
+      <c r="GR51" s="5"/>
+      <c r="GS51" s="5"/>
+      <c r="GT51" s="5"/>
+      <c r="GU51" s="5"/>
+      <c r="GV51" s="5"/>
+      <c r="GW51" s="5"/>
+      <c r="GX51" s="5"/>
+      <c r="GY51" s="5"/>
+      <c r="GZ51" s="5"/>
+      <c r="HA51" s="5"/>
+      <c r="HB51" s="5"/>
+      <c r="HC51" s="5"/>
+      <c r="HD51" s="5"/>
+      <c r="HE51" s="5"/>
+      <c r="HF51" s="5"/>
+      <c r="HG51" s="5"/>
+      <c r="HH51" s="5"/>
+      <c r="HI51" s="5"/>
+      <c r="HJ51" s="5"/>
+      <c r="HK51" s="5"/>
+      <c r="HL51" s="5"/>
+      <c r="HM51" s="5"/>
+      <c r="HN51" s="5"/>
+      <c r="HO51" s="5"/>
+      <c r="HP51" s="5"/>
+      <c r="HQ51" s="5"/>
+      <c r="HR51" s="5"/>
+      <c r="HS51" s="5"/>
+      <c r="HT51" s="5"/>
+      <c r="HU51" s="5"/>
+      <c r="HV51" s="5"/>
+      <c r="HW51" s="5"/>
+      <c r="HX51" s="5"/>
+      <c r="HY51" s="5"/>
+      <c r="HZ51" s="5"/>
+      <c r="IA51" s="5"/>
+      <c r="IB51" s="5"/>
+      <c r="IC51" s="5"/>
+      <c r="ID51" s="5"/>
+      <c r="IE51" s="5"/>
+      <c r="IF51" s="5"/>
+      <c r="IG51" s="5"/>
+      <c r="IH51" s="5"/>
+      <c r="II51" s="5"/>
+      <c r="IJ51" s="5"/>
+      <c r="IK51" s="5"/>
+      <c r="IL51" s="5"/>
+      <c r="IM51" s="5"/>
+      <c r="IN51" s="5"/>
+      <c r="IO51" s="5"/>
+      <c r="IP51" s="5"/>
+      <c r="IQ51" s="5"/>
+      <c r="IR51" s="5"/>
+      <c r="IS51" s="5"/>
+      <c r="IT51" s="5"/>
+      <c r="IU51" s="5"/>
+      <c r="IV51" s="5"/>
+      <c r="IW51" s="5"/>
+      <c r="IX51" s="5"/>
+      <c r="IY51" s="5"/>
+      <c r="IZ51" s="5"/>
+      <c r="JA51" s="5"/>
+      <c r="JB51" s="5"/>
+      <c r="JC51" s="5"/>
+      <c r="JD51" s="5"/>
+      <c r="JE51" s="5"/>
+      <c r="JF51" s="5"/>
+      <c r="JG51" s="5"/>
+      <c r="JH51" s="5"/>
+      <c r="JI51" s="5"/>
+      <c r="JJ51" s="5"/>
+      <c r="JK51" s="5"/>
+      <c r="JL51" s="5"/>
+      <c r="JM51" s="5"/>
+      <c r="JN51" s="5"/>
+      <c r="JO51" s="5"/>
+      <c r="JP51" s="5"/>
+      <c r="JQ51" s="5"/>
+      <c r="JR51" s="5"/>
+      <c r="JS51" s="5"/>
+      <c r="JT51" s="5"/>
+      <c r="JU51" s="5"/>
+      <c r="JV51" s="5"/>
+      <c r="JW51" s="5"/>
+      <c r="JX51" s="5"/>
+      <c r="JY51" s="5"/>
+      <c r="JZ51" s="5"/>
+      <c r="KA51" s="5"/>
+      <c r="KB51" s="5"/>
+      <c r="KC51" s="5"/>
+      <c r="KD51" s="5"/>
+      <c r="KE51" s="5"/>
+      <c r="KF51" s="5"/>
+      <c r="KG51" s="5"/>
+      <c r="KH51" s="5"/>
+      <c r="KI51" s="5"/>
+      <c r="KJ51" s="5"/>
+      <c r="KK51" s="5"/>
+      <c r="KL51" s="5"/>
+      <c r="KM51" s="5"/>
+      <c r="KN51" s="5"/>
+      <c r="KO51" s="5"/>
+      <c r="KP51" s="5"/>
+      <c r="KQ51" s="5"/>
+      <c r="KR51" s="5"/>
+      <c r="KS51" s="5"/>
+      <c r="KT51" s="5"/>
+      <c r="KU51" s="5"/>
+      <c r="KV51" s="5"/>
+      <c r="KW51" s="5"/>
+      <c r="KX51" s="5"/>
+      <c r="KY51" s="5"/>
+      <c r="KZ51" s="5"/>
+      <c r="LA51" s="5"/>
+      <c r="LB51" s="5"/>
+      <c r="LC51" s="5"/>
+      <c r="LD51" s="5"/>
+      <c r="LE51" s="5"/>
+      <c r="LF51" s="5"/>
+      <c r="LG51" s="5"/>
+      <c r="LH51" s="5"/>
+      <c r="LI51" s="5"/>
+      <c r="LJ51" s="5"/>
+      <c r="LK51" s="5"/>
+      <c r="LL51" s="5"/>
+      <c r="LM51" s="5"/>
+      <c r="LN51" s="5"/>
+      <c r="LO51" s="5"/>
+      <c r="LP51" s="5"/>
+      <c r="LQ51" s="5"/>
+      <c r="LR51" s="5"/>
+      <c r="LS51" s="5"/>
+      <c r="LT51" s="5"/>
+      <c r="LU51" s="5"/>
+      <c r="LV51" s="5"/>
+      <c r="LW51" s="5"/>
+      <c r="LX51" s="5"/>
+      <c r="LY51" s="5"/>
+      <c r="LZ51" s="5"/>
+      <c r="MA51" s="5"/>
+      <c r="MB51" s="5"/>
+      <c r="MC51" s="5"/>
+      <c r="MD51" s="5"/>
+      <c r="ME51" s="5"/>
+      <c r="MF51" s="5"/>
+      <c r="MG51" s="5"/>
+      <c r="MH51" s="5"/>
+      <c r="MI51" s="5"/>
+      <c r="MJ51" s="5"/>
+      <c r="MK51" s="5"/>
+      <c r="ML51" s="5"/>
+      <c r="MM51" s="5"/>
+      <c r="MN51" s="5"/>
+      <c r="MO51" s="5"/>
+      <c r="MP51" s="5"/>
+      <c r="MQ51" s="5"/>
+      <c r="MR51" s="5"/>
+      <c r="MS51" s="5"/>
+      <c r="MT51" s="5"/>
+      <c r="MU51" s="5"/>
+      <c r="MV51" s="5"/>
+      <c r="MW51" s="5"/>
+      <c r="MX51" s="5"/>
+      <c r="MY51" s="5"/>
+      <c r="MZ51" s="5"/>
+      <c r="NA51" s="5"/>
+      <c r="NB51" s="5"/>
+      <c r="NC51" s="5"/>
+      <c r="ND51" s="5"/>
+      <c r="NE51" s="5"/>
+      <c r="NF51" s="5"/>
+      <c r="NG51" s="5"/>
+      <c r="NH51" s="5"/>
+      <c r="NI51" s="5"/>
+      <c r="NJ51" s="5"/>
+      <c r="NK51" s="5"/>
+      <c r="NL51" s="5"/>
+      <c r="NM51" s="5"/>
+      <c r="NN51" s="5"/>
+      <c r="NO51" s="5"/>
+      <c r="NP51" s="5"/>
+      <c r="NQ51" s="5"/>
+      <c r="NR51" s="5"/>
+      <c r="NS51" s="5"/>
+      <c r="NT51" s="5"/>
+      <c r="NU51" s="5"/>
+      <c r="NV51" s="5"/>
+      <c r="NW51" s="5"/>
+      <c r="NX51" s="5"/>
+      <c r="NY51" s="5"/>
+      <c r="NZ51" s="5"/>
+      <c r="OA51" s="5"/>
+      <c r="OB51" s="5"/>
+      <c r="OC51" s="5"/>
+      <c r="OD51" s="5"/>
+      <c r="OE51" s="5"/>
+      <c r="OF51" s="5"/>
+      <c r="OG51" s="5"/>
+      <c r="OH51" s="5"/>
+      <c r="OI51" s="5"/>
+      <c r="OJ51" s="5"/>
+      <c r="OK51" s="5"/>
+      <c r="OL51" s="5"/>
+      <c r="OM51" s="5"/>
+      <c r="ON51" s="5"/>
+      <c r="OO51" s="5"/>
+      <c r="OP51" s="5"/>
+      <c r="OQ51" s="5"/>
+      <c r="OR51" s="5"/>
+      <c r="OS51" s="5"/>
+      <c r="OT51" s="5"/>
+      <c r="OU51" s="5"/>
+      <c r="OV51" s="5"/>
+      <c r="OW51" s="5"/>
+      <c r="OX51" s="5"/>
+      <c r="OY51" s="5"/>
+      <c r="OZ51" s="5"/>
+      <c r="PA51" s="5"/>
+      <c r="PB51" s="5"/>
+      <c r="PC51" s="5"/>
+      <c r="PD51" s="5"/>
+      <c r="PE51" s="5"/>
+      <c r="PF51" s="5"/>
+      <c r="PG51" s="5"/>
+      <c r="PH51" s="5"/>
+      <c r="PI51" s="5"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>-0.431</v>
+      </c>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="5"/>
+      <c r="Q52" s="5"/>
+      <c r="R52" s="5"/>
+      <c r="S52" s="5"/>
+      <c r="T52" s="5"/>
+      <c r="U52" s="5"/>
+      <c r="V52" s="5"/>
+      <c r="W52" s="5"/>
+      <c r="X52" s="5"/>
+      <c r="Y52" s="5"/>
+      <c r="Z52" s="5"/>
+      <c r="AA52" s="5"/>
+      <c r="AB52" s="5"/>
+      <c r="AC52" s="5"/>
+      <c r="AD52" s="5"/>
+      <c r="AE52" s="5"/>
+      <c r="AF52" s="5"/>
+      <c r="AG52" s="5"/>
+      <c r="AH52" s="5"/>
+      <c r="AI52" s="5"/>
+      <c r="AJ52" s="5"/>
+      <c r="AK52" s="5"/>
+      <c r="AL52" s="5"/>
+      <c r="AM52" s="5"/>
+      <c r="AN52" s="5"/>
+      <c r="AO52" s="5"/>
+      <c r="AP52" s="5"/>
+      <c r="AQ52" s="5"/>
+      <c r="AR52" s="5"/>
+      <c r="AS52" s="5"/>
+      <c r="AT52" s="5"/>
+      <c r="AU52" s="5"/>
+      <c r="AV52" s="5"/>
+      <c r="AW52" s="5"/>
+      <c r="AX52" s="5"/>
+      <c r="AY52" s="5"/>
+      <c r="AZ52" s="5"/>
+      <c r="BA52" s="5"/>
+      <c r="BB52" s="5"/>
+      <c r="BC52" s="5"/>
+      <c r="BD52" s="5"/>
+      <c r="BE52" s="5"/>
+      <c r="BF52" s="5"/>
+      <c r="BG52" s="5"/>
+      <c r="BH52" s="5"/>
+      <c r="BI52" s="5"/>
+      <c r="BJ52" s="5"/>
+      <c r="BK52" s="5"/>
+      <c r="BL52" s="5"/>
+      <c r="BM52" s="5"/>
+      <c r="BN52" s="5"/>
+      <c r="BO52" s="5"/>
+      <c r="BP52" s="5"/>
+      <c r="BQ52" s="5"/>
+      <c r="BR52" s="5"/>
+      <c r="BS52" s="5"/>
+      <c r="BT52" s="5"/>
+      <c r="BU52" s="5"/>
+      <c r="BV52" s="5"/>
+      <c r="BW52" s="5"/>
+      <c r="BX52" s="5"/>
+      <c r="BY52" s="5"/>
+      <c r="BZ52" s="5"/>
+      <c r="CA52" s="5"/>
+      <c r="CB52" s="5"/>
+      <c r="CC52" s="5"/>
+      <c r="CD52" s="5"/>
+      <c r="CE52" s="5"/>
+      <c r="CF52" s="5"/>
+      <c r="CG52" s="5"/>
+      <c r="CH52" s="5"/>
+      <c r="CI52" s="5"/>
+      <c r="CJ52" s="5"/>
+      <c r="CK52" s="5"/>
+      <c r="CL52" s="5"/>
+      <c r="CM52" s="5"/>
+      <c r="CN52" s="5"/>
+      <c r="CO52" s="5"/>
+      <c r="CP52" s="5"/>
+      <c r="CQ52" s="5"/>
+      <c r="CR52" s="5"/>
+      <c r="CS52" s="5"/>
+      <c r="CT52" s="5"/>
+      <c r="CU52" s="5"/>
+      <c r="CV52" s="5"/>
+      <c r="CW52" s="5"/>
+      <c r="CX52" s="5"/>
+      <c r="CY52" s="5"/>
+      <c r="CZ52" s="5"/>
+      <c r="DA52" s="5"/>
+      <c r="DB52" s="5"/>
+      <c r="DC52" s="5"/>
+      <c r="DD52" s="5"/>
+      <c r="DE52" s="5"/>
+      <c r="DF52" s="5"/>
+      <c r="DG52" s="5"/>
+      <c r="DH52" s="5"/>
+      <c r="DI52" s="5"/>
+      <c r="DJ52" s="5"/>
+      <c r="DK52" s="5"/>
+      <c r="DL52" s="5"/>
+      <c r="DM52" s="5"/>
+      <c r="DN52" s="5"/>
+      <c r="DO52" s="5"/>
+      <c r="DP52" s="5"/>
+      <c r="DQ52" s="5"/>
+      <c r="DR52" s="5"/>
+      <c r="DS52" s="5"/>
+      <c r="DT52" s="5"/>
+      <c r="DU52" s="5"/>
+      <c r="DV52" s="5"/>
+      <c r="DW52" s="5"/>
+      <c r="DX52" s="5"/>
+      <c r="DY52" s="5"/>
+      <c r="DZ52" s="5"/>
+      <c r="EA52" s="5"/>
+      <c r="EB52" s="5"/>
+      <c r="EC52" s="5"/>
+      <c r="ED52" s="5"/>
+      <c r="EE52" s="5"/>
+      <c r="EF52" s="5"/>
+      <c r="EG52" s="5"/>
+      <c r="EH52" s="5"/>
+      <c r="EI52" s="5"/>
+      <c r="EJ52" s="5"/>
+      <c r="EK52" s="5"/>
+      <c r="EL52" s="5"/>
+      <c r="EM52" s="5"/>
+      <c r="EN52" s="5"/>
+      <c r="EO52" s="5"/>
+      <c r="EP52" s="5"/>
+      <c r="EQ52" s="5"/>
+      <c r="ER52" s="5"/>
+      <c r="ES52" s="5"/>
+      <c r="ET52" s="5"/>
+      <c r="EU52" s="5"/>
+      <c r="EV52" s="5"/>
+      <c r="EW52" s="5"/>
+      <c r="EX52" s="5"/>
+      <c r="EY52" s="5"/>
+      <c r="EZ52" s="5"/>
+      <c r="FA52" s="5"/>
+      <c r="FB52" s="5"/>
+      <c r="FC52" s="5"/>
+      <c r="FD52" s="5"/>
+      <c r="FE52" s="5"/>
+      <c r="FF52" s="5"/>
+      <c r="FG52" s="5"/>
+      <c r="FH52" s="5"/>
+      <c r="FI52" s="5"/>
+      <c r="FJ52" s="5"/>
+      <c r="FK52" s="5"/>
+      <c r="FL52" s="5"/>
+      <c r="FM52" s="5"/>
+      <c r="FN52" s="5"/>
+      <c r="FO52" s="5"/>
+      <c r="FP52" s="5"/>
+      <c r="FQ52" s="5"/>
+      <c r="FR52" s="5"/>
+      <c r="FS52" s="5"/>
+      <c r="FT52" s="5"/>
+      <c r="FU52" s="5"/>
+      <c r="FV52" s="5"/>
+      <c r="FW52" s="5"/>
+      <c r="FX52" s="5"/>
+      <c r="FY52" s="5"/>
+      <c r="FZ52" s="5"/>
+      <c r="GA52" s="5"/>
+      <c r="GB52" s="5"/>
+      <c r="GC52" s="5"/>
+      <c r="GD52" s="5"/>
+      <c r="GE52" s="5"/>
+      <c r="GF52" s="5"/>
+      <c r="GG52" s="5"/>
+      <c r="GH52" s="5"/>
+      <c r="GI52" s="5"/>
+      <c r="GJ52" s="5"/>
+      <c r="GK52" s="5"/>
+      <c r="GL52" s="5"/>
+      <c r="GM52" s="5"/>
+      <c r="GN52" s="5"/>
+      <c r="GO52" s="5"/>
+      <c r="GP52" s="5"/>
+      <c r="GQ52" s="5"/>
+      <c r="GR52" s="5"/>
+      <c r="GS52" s="5"/>
+      <c r="GT52" s="5"/>
+      <c r="GU52" s="5"/>
+      <c r="GV52" s="5"/>
+      <c r="GW52" s="5"/>
+      <c r="GX52" s="5"/>
+      <c r="GY52" s="5"/>
+      <c r="GZ52" s="5"/>
+      <c r="HA52" s="5"/>
+      <c r="HB52" s="5"/>
+      <c r="HC52" s="5"/>
+      <c r="HD52" s="5"/>
+      <c r="HE52" s="5"/>
+      <c r="HF52" s="5"/>
+      <c r="HG52" s="5"/>
+      <c r="HH52" s="5"/>
+      <c r="HI52" s="5"/>
+      <c r="HJ52" s="5"/>
+      <c r="HK52" s="5"/>
+      <c r="HL52" s="5"/>
+      <c r="HM52" s="5"/>
+      <c r="HN52" s="5"/>
+      <c r="HO52" s="5"/>
+      <c r="HP52" s="5"/>
+      <c r="HQ52" s="5"/>
+      <c r="HR52" s="5"/>
+      <c r="HS52" s="5"/>
+      <c r="HT52" s="5"/>
+      <c r="HU52" s="5"/>
+      <c r="HV52" s="5"/>
+      <c r="HW52" s="5"/>
+      <c r="HX52" s="5"/>
+      <c r="HY52" s="5"/>
+      <c r="HZ52" s="5"/>
+      <c r="IA52" s="5"/>
+      <c r="IB52" s="5"/>
+      <c r="IC52" s="5"/>
+      <c r="ID52" s="5"/>
+      <c r="IE52" s="5"/>
+      <c r="IF52" s="5"/>
+      <c r="IG52" s="5"/>
+      <c r="IH52" s="5"/>
+      <c r="II52" s="5"/>
+      <c r="IJ52" s="5"/>
+      <c r="IK52" s="5"/>
+      <c r="IL52" s="5"/>
+      <c r="IM52" s="5"/>
+      <c r="IN52" s="5"/>
+      <c r="IO52" s="5"/>
+      <c r="IP52" s="5"/>
+      <c r="IQ52" s="5"/>
+      <c r="IR52" s="5"/>
+      <c r="IS52" s="5"/>
+      <c r="IT52" s="5"/>
+      <c r="IU52" s="5"/>
+      <c r="IV52" s="5"/>
+      <c r="IW52" s="5"/>
+      <c r="IX52" s="5"/>
+      <c r="IY52" s="5"/>
+      <c r="IZ52" s="5"/>
+      <c r="JA52" s="5"/>
+      <c r="JB52" s="5"/>
+      <c r="JC52" s="5"/>
+      <c r="JD52" s="5"/>
+      <c r="JE52" s="5"/>
+      <c r="JF52" s="5"/>
+      <c r="JG52" s="5"/>
+      <c r="JH52" s="5"/>
+      <c r="JI52" s="5"/>
+      <c r="JJ52" s="5"/>
+      <c r="JK52" s="5"/>
+      <c r="JL52" s="5"/>
+      <c r="JM52" s="5"/>
+      <c r="JN52" s="5"/>
+      <c r="JO52" s="5"/>
+      <c r="JP52" s="5"/>
+      <c r="JQ52" s="5"/>
+      <c r="JR52" s="5"/>
+      <c r="JS52" s="5"/>
+      <c r="JT52" s="5"/>
+      <c r="JU52" s="5"/>
+      <c r="JV52" s="5"/>
+      <c r="JW52" s="5"/>
+      <c r="JX52" s="5"/>
+      <c r="JY52" s="5"/>
+      <c r="JZ52" s="5"/>
+      <c r="KA52" s="5"/>
+      <c r="KB52" s="5"/>
+      <c r="KC52" s="5"/>
+      <c r="KD52" s="5"/>
+      <c r="KE52" s="5"/>
+      <c r="KF52" s="5"/>
+      <c r="KG52" s="5"/>
+      <c r="KH52" s="5"/>
+      <c r="KI52" s="5"/>
+      <c r="KJ52" s="5"/>
+      <c r="KK52" s="5"/>
+      <c r="KL52" s="5"/>
+      <c r="KM52" s="5"/>
+      <c r="KN52" s="5"/>
+      <c r="KO52" s="5"/>
+      <c r="KP52" s="5"/>
+      <c r="KQ52" s="5"/>
+      <c r="KR52" s="5"/>
+      <c r="KS52" s="5"/>
+      <c r="KT52" s="5"/>
+      <c r="KU52" s="5"/>
+      <c r="KV52" s="5"/>
+      <c r="KW52" s="5"/>
+      <c r="KX52" s="5"/>
+      <c r="KY52" s="5"/>
+      <c r="KZ52" s="5"/>
+      <c r="LA52" s="5"/>
+      <c r="LB52" s="5"/>
+      <c r="LC52" s="5"/>
+      <c r="LD52" s="5"/>
+      <c r="LE52" s="5"/>
+      <c r="LF52" s="5"/>
+      <c r="LG52" s="5"/>
+      <c r="LH52" s="5"/>
+      <c r="LI52" s="5"/>
+      <c r="LJ52" s="5"/>
+      <c r="LK52" s="5"/>
+      <c r="LL52" s="5"/>
+      <c r="LM52" s="5"/>
+      <c r="LN52" s="5"/>
+      <c r="LO52" s="5"/>
+      <c r="LP52" s="5"/>
+      <c r="LQ52" s="5"/>
+      <c r="LR52" s="5"/>
+      <c r="LS52" s="5"/>
+      <c r="LT52" s="5"/>
+      <c r="LU52" s="5"/>
+      <c r="LV52" s="5"/>
+      <c r="LW52" s="5"/>
+      <c r="LX52" s="5"/>
+      <c r="LY52" s="5"/>
+      <c r="LZ52" s="5"/>
+      <c r="MA52" s="5"/>
+      <c r="MB52" s="5"/>
+      <c r="MC52" s="5"/>
+      <c r="MD52" s="5"/>
+      <c r="ME52" s="5"/>
+      <c r="MF52" s="5"/>
+      <c r="MG52" s="5"/>
+      <c r="MH52" s="5"/>
+      <c r="MI52" s="5"/>
+      <c r="MJ52" s="5"/>
+      <c r="MK52" s="5"/>
+      <c r="ML52" s="5"/>
+      <c r="MM52" s="5"/>
+      <c r="MN52" s="5"/>
+      <c r="MO52" s="5"/>
+      <c r="MP52" s="5"/>
+      <c r="MQ52" s="5"/>
+      <c r="MR52" s="5"/>
+      <c r="MS52" s="5"/>
+      <c r="MT52" s="5"/>
+      <c r="MU52" s="5"/>
+      <c r="MV52" s="5"/>
+      <c r="MW52" s="5"/>
+      <c r="MX52" s="5"/>
+      <c r="MY52" s="5"/>
+      <c r="MZ52" s="5"/>
+      <c r="NA52" s="5"/>
+      <c r="NB52" s="5"/>
+      <c r="NC52" s="5"/>
+      <c r="ND52" s="5"/>
+      <c r="NE52" s="5"/>
+      <c r="NF52" s="5"/>
+      <c r="NG52" s="5"/>
+      <c r="NH52" s="5"/>
+      <c r="NI52" s="5"/>
+      <c r="NJ52" s="5"/>
+      <c r="NK52" s="5"/>
+      <c r="NL52" s="5"/>
+      <c r="NM52" s="5"/>
+      <c r="NN52" s="5"/>
+      <c r="NO52" s="5"/>
+      <c r="NP52" s="5"/>
+      <c r="NQ52" s="5"/>
+      <c r="NR52" s="5"/>
+      <c r="NS52" s="5"/>
+      <c r="NT52" s="5"/>
+      <c r="NU52" s="5"/>
+      <c r="NV52" s="5"/>
+      <c r="NW52" s="5"/>
+      <c r="NX52" s="5"/>
+      <c r="NY52" s="5"/>
+      <c r="NZ52" s="5"/>
+      <c r="OA52" s="5"/>
+      <c r="OB52" s="5"/>
+      <c r="OC52" s="5"/>
+      <c r="OD52" s="5"/>
+      <c r="OE52" s="5"/>
+      <c r="OF52" s="5"/>
+      <c r="OG52" s="5"/>
+      <c r="OH52" s="5"/>
+      <c r="OI52" s="5"/>
+      <c r="OJ52" s="5"/>
+      <c r="OK52" s="5"/>
+      <c r="OL52" s="5"/>
+      <c r="OM52" s="5"/>
+      <c r="ON52" s="5"/>
+      <c r="OO52" s="5"/>
+      <c r="OP52" s="5"/>
+      <c r="OQ52" s="5"/>
+      <c r="OR52" s="5"/>
+      <c r="OS52" s="5"/>
+      <c r="OT52" s="5"/>
+      <c r="OU52" s="5"/>
+      <c r="OV52" s="5"/>
+      <c r="OW52" s="5"/>
+      <c r="OX52" s="5"/>
+      <c r="OY52" s="5"/>
+      <c r="OZ52" s="5"/>
+      <c r="PA52" s="5"/>
+      <c r="PB52" s="5"/>
+      <c r="PC52" s="5"/>
+      <c r="PD52" s="5"/>
+      <c r="PE52" s="5"/>
+      <c r="PF52" s="5"/>
+      <c r="PG52" s="5"/>
+      <c r="PH52" s="5"/>
+      <c r="PI52" s="5"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="5"/>
+      <c r="Q53" s="5"/>
+      <c r="R53" s="5"/>
+      <c r="S53" s="5"/>
+      <c r="T53" s="5"/>
+      <c r="U53" s="5"/>
+      <c r="V53" s="5"/>
+      <c r="W53" s="5"/>
+      <c r="X53" s="5"/>
+      <c r="Y53" s="5"/>
+      <c r="Z53" s="5"/>
+      <c r="AA53" s="5"/>
+      <c r="AB53" s="5"/>
+      <c r="AC53" s="5"/>
+      <c r="AD53" s="5"/>
+      <c r="AE53" s="5"/>
+      <c r="AF53" s="5"/>
+      <c r="AG53" s="5"/>
+      <c r="AH53" s="5"/>
+      <c r="AI53" s="5"/>
+      <c r="AJ53" s="5"/>
+      <c r="AK53" s="5"/>
+      <c r="AL53" s="5"/>
+      <c r="AM53" s="5"/>
+      <c r="AN53" s="5"/>
+      <c r="AO53" s="5"/>
+      <c r="AP53" s="5"/>
+      <c r="AQ53" s="5"/>
+      <c r="AR53" s="5"/>
+      <c r="AS53" s="5"/>
+      <c r="AT53" s="5"/>
+      <c r="AU53" s="5"/>
+      <c r="AV53" s="5"/>
+      <c r="AW53" s="5"/>
+      <c r="AX53" s="5"/>
+      <c r="AY53" s="5"/>
+      <c r="AZ53" s="5"/>
+      <c r="BA53" s="5"/>
+      <c r="BB53" s="5"/>
+      <c r="BC53" s="5"/>
+      <c r="BD53" s="5"/>
+      <c r="BE53" s="5"/>
+      <c r="BF53" s="5"/>
+      <c r="BG53" s="5"/>
+      <c r="BH53" s="5"/>
+      <c r="BI53" s="5"/>
+      <c r="BJ53" s="5"/>
+      <c r="BK53" s="5"/>
+      <c r="BL53" s="5"/>
+      <c r="BM53" s="5"/>
+      <c r="BN53" s="5"/>
+      <c r="BO53" s="5"/>
+      <c r="BP53" s="5"/>
+      <c r="BQ53" s="5"/>
+      <c r="BR53" s="5"/>
+      <c r="BS53" s="5"/>
+      <c r="BT53" s="5"/>
+      <c r="BU53" s="5"/>
+      <c r="BV53" s="5"/>
+      <c r="BW53" s="5"/>
+      <c r="BX53" s="5"/>
+      <c r="BY53" s="5"/>
+      <c r="BZ53" s="5"/>
+      <c r="CA53" s="5"/>
+      <c r="CB53" s="5"/>
+      <c r="CC53" s="5"/>
+      <c r="CD53" s="5"/>
+      <c r="CE53" s="5"/>
+      <c r="CF53" s="5"/>
+      <c r="CG53" s="5"/>
+      <c r="CH53" s="5"/>
+      <c r="CI53" s="5"/>
+      <c r="CJ53" s="5"/>
+      <c r="CK53" s="5"/>
+      <c r="CL53" s="5"/>
+      <c r="CM53" s="5"/>
+      <c r="CN53" s="5"/>
+      <c r="CO53" s="5"/>
+      <c r="CP53" s="5"/>
+      <c r="CQ53" s="5"/>
+      <c r="CR53" s="5"/>
+      <c r="CS53" s="5"/>
+      <c r="CT53" s="5"/>
+      <c r="CU53" s="5"/>
+      <c r="CV53" s="5"/>
+      <c r="CW53" s="5"/>
+      <c r="CX53" s="5"/>
+      <c r="CY53" s="5"/>
+      <c r="CZ53" s="5"/>
+      <c r="DA53" s="5"/>
+      <c r="DB53" s="5"/>
+      <c r="DC53" s="5"/>
+      <c r="DD53" s="5"/>
+      <c r="DE53" s="5"/>
+      <c r="DF53" s="5"/>
+      <c r="DG53" s="5"/>
+      <c r="DH53" s="5"/>
+      <c r="DI53" s="5"/>
+      <c r="DJ53" s="5"/>
+      <c r="DK53" s="5"/>
+      <c r="DL53" s="5"/>
+      <c r="DM53" s="5"/>
+      <c r="DN53" s="5"/>
+      <c r="DO53" s="5"/>
+      <c r="DP53" s="5"/>
+      <c r="DQ53" s="5"/>
+      <c r="DR53" s="5"/>
+      <c r="DS53" s="5"/>
+      <c r="DT53" s="5"/>
+      <c r="DU53" s="5"/>
+      <c r="DV53" s="5"/>
+      <c r="DW53" s="5"/>
+      <c r="DX53" s="5"/>
+      <c r="DY53" s="5"/>
+      <c r="DZ53" s="5"/>
+      <c r="EA53" s="5"/>
+      <c r="EB53" s="5"/>
+      <c r="EC53" s="5"/>
+      <c r="ED53" s="5"/>
+      <c r="EE53" s="5"/>
+      <c r="EF53" s="5"/>
+      <c r="EG53" s="5"/>
+      <c r="EH53" s="5"/>
+      <c r="EI53" s="5"/>
+      <c r="EJ53" s="5"/>
+      <c r="EK53" s="5"/>
+      <c r="EL53" s="5"/>
+      <c r="EM53" s="5"/>
+      <c r="EN53" s="5"/>
+      <c r="EO53" s="5"/>
+      <c r="EP53" s="5"/>
+      <c r="EQ53" s="5"/>
+      <c r="ER53" s="5"/>
+      <c r="ES53" s="5"/>
+      <c r="ET53" s="5"/>
+      <c r="EU53" s="5"/>
+      <c r="EV53" s="5"/>
+      <c r="EW53" s="5"/>
+      <c r="EX53" s="5"/>
+      <c r="EY53" s="5"/>
+      <c r="EZ53" s="5"/>
+      <c r="FA53" s="5"/>
+      <c r="FB53" s="5"/>
+      <c r="FC53" s="5"/>
+      <c r="FD53" s="5"/>
+      <c r="FE53" s="5"/>
+      <c r="FF53" s="5"/>
+      <c r="FG53" s="5"/>
+      <c r="FH53" s="5"/>
+      <c r="FI53" s="5"/>
+      <c r="FJ53" s="5"/>
+      <c r="FK53" s="5"/>
+      <c r="FL53" s="5"/>
+      <c r="FM53" s="5"/>
+      <c r="FN53" s="5"/>
+      <c r="FO53" s="5"/>
+      <c r="FP53" s="5"/>
+      <c r="FQ53" s="5"/>
+      <c r="FR53" s="5"/>
+      <c r="FS53" s="5"/>
+      <c r="FT53" s="5"/>
+      <c r="FU53" s="5"/>
+      <c r="FV53" s="5"/>
+      <c r="FW53" s="5"/>
+      <c r="FX53" s="5"/>
+      <c r="FY53" s="5"/>
+      <c r="FZ53" s="5"/>
+      <c r="GA53" s="5"/>
+      <c r="GB53" s="5"/>
+      <c r="GC53" s="5"/>
+      <c r="GD53" s="5"/>
+      <c r="GE53" s="5"/>
+      <c r="GF53" s="5"/>
+      <c r="GG53" s="5"/>
+      <c r="GH53" s="5"/>
+      <c r="GI53" s="5"/>
+      <c r="GJ53" s="5"/>
+      <c r="GK53" s="5"/>
+      <c r="GL53" s="5"/>
+      <c r="GM53" s="5"/>
+      <c r="GN53" s="5"/>
+      <c r="GO53" s="5"/>
+      <c r="GP53" s="5"/>
+      <c r="GQ53" s="5"/>
+      <c r="GR53" s="5"/>
+      <c r="GS53" s="5"/>
+      <c r="GT53" s="5"/>
+      <c r="GU53" s="5"/>
+      <c r="GV53" s="5"/>
+      <c r="GW53" s="5"/>
+      <c r="GX53" s="5"/>
+      <c r="GY53" s="5"/>
+      <c r="GZ53" s="5"/>
+      <c r="HA53" s="5"/>
+      <c r="HB53" s="5"/>
+      <c r="HC53" s="5"/>
+      <c r="HD53" s="5"/>
+      <c r="HE53" s="5"/>
+      <c r="HF53" s="5"/>
+      <c r="HG53" s="5"/>
+      <c r="HH53" s="5"/>
+      <c r="HI53" s="5"/>
+      <c r="HJ53" s="5"/>
+      <c r="HK53" s="5"/>
+      <c r="HL53" s="5"/>
+      <c r="HM53" s="5"/>
+      <c r="HN53" s="5"/>
+      <c r="HO53" s="5"/>
+      <c r="HP53" s="5"/>
+      <c r="HQ53" s="5"/>
+      <c r="HR53" s="5"/>
+      <c r="HS53" s="5"/>
+      <c r="HT53" s="5"/>
+      <c r="HU53" s="5"/>
+      <c r="HV53" s="5"/>
+      <c r="HW53" s="5"/>
+      <c r="HX53" s="5"/>
+      <c r="HY53" s="5"/>
+      <c r="HZ53" s="5"/>
+      <c r="IA53" s="5"/>
+      <c r="IB53" s="5"/>
+      <c r="IC53" s="5"/>
+      <c r="ID53" s="5"/>
+      <c r="IE53" s="5"/>
+      <c r="IF53" s="5"/>
+      <c r="IG53" s="5"/>
+      <c r="IH53" s="5"/>
+      <c r="II53" s="5"/>
+      <c r="IJ53" s="5"/>
+      <c r="IK53" s="5"/>
+      <c r="IL53" s="5"/>
+      <c r="IM53" s="5"/>
+      <c r="IN53" s="5"/>
+      <c r="IO53" s="5"/>
+      <c r="IP53" s="5"/>
+      <c r="IQ53" s="5"/>
+      <c r="IR53" s="5"/>
+      <c r="IS53" s="5"/>
+      <c r="IT53" s="5"/>
+      <c r="IU53" s="5"/>
+      <c r="IV53" s="5"/>
+      <c r="IW53" s="5"/>
+      <c r="IX53" s="5"/>
+      <c r="IY53" s="5"/>
+      <c r="IZ53" s="5"/>
+      <c r="JA53" s="5"/>
+      <c r="JB53" s="5"/>
+      <c r="JC53" s="5"/>
+      <c r="JD53" s="5"/>
+      <c r="JE53" s="5"/>
+      <c r="JF53" s="5"/>
+      <c r="JG53" s="5"/>
+      <c r="JH53" s="5"/>
+      <c r="JI53" s="5"/>
+      <c r="JJ53" s="5"/>
+      <c r="JK53" s="5"/>
+      <c r="JL53" s="5"/>
+      <c r="JM53" s="5"/>
+      <c r="JN53" s="5"/>
+      <c r="JO53" s="5"/>
+      <c r="JP53" s="5"/>
+      <c r="JQ53" s="5"/>
+      <c r="JR53" s="5"/>
+      <c r="JS53" s="5"/>
+      <c r="JT53" s="5"/>
+      <c r="JU53" s="5"/>
+      <c r="JV53" s="5"/>
+      <c r="JW53" s="5"/>
+      <c r="JX53" s="5"/>
+      <c r="JY53" s="5"/>
+      <c r="JZ53" s="5"/>
+      <c r="KA53" s="5"/>
+      <c r="KB53" s="5"/>
+      <c r="KC53" s="5"/>
+      <c r="KD53" s="5"/>
+      <c r="KE53" s="5"/>
+      <c r="KF53" s="5"/>
+      <c r="KG53" s="5"/>
+      <c r="KH53" s="5"/>
+      <c r="KI53" s="5"/>
+      <c r="KJ53" s="5"/>
+      <c r="KK53" s="5"/>
+      <c r="KL53" s="5"/>
+      <c r="KM53" s="5"/>
+      <c r="KN53" s="5"/>
+      <c r="KO53" s="5"/>
+      <c r="KP53" s="5"/>
+      <c r="KQ53" s="5"/>
+      <c r="KR53" s="5"/>
+      <c r="KS53" s="5"/>
+      <c r="KT53" s="5"/>
+      <c r="KU53" s="5"/>
+      <c r="KV53" s="5"/>
+      <c r="KW53" s="5"/>
+      <c r="KX53" s="5"/>
+      <c r="KY53" s="5"/>
+      <c r="KZ53" s="5"/>
+      <c r="LA53" s="5"/>
+      <c r="LB53" s="5"/>
+      <c r="LC53" s="5"/>
+      <c r="LD53" s="5"/>
+      <c r="LE53" s="5"/>
+      <c r="LF53" s="5"/>
+      <c r="LG53" s="5"/>
+      <c r="LH53" s="5"/>
+      <c r="LI53" s="5"/>
+      <c r="LJ53" s="5"/>
+      <c r="LK53" s="5"/>
+      <c r="LL53" s="5"/>
+      <c r="LM53" s="5"/>
+      <c r="LN53" s="5"/>
+      <c r="LO53" s="5"/>
+      <c r="LP53" s="5"/>
+      <c r="LQ53" s="5"/>
+      <c r="LR53" s="5"/>
+      <c r="LS53" s="5"/>
+      <c r="LT53" s="5"/>
+      <c r="LU53" s="5"/>
+      <c r="LV53" s="5"/>
+      <c r="LW53" s="5"/>
+      <c r="LX53" s="5"/>
+      <c r="LY53" s="5"/>
+      <c r="LZ53" s="5"/>
+      <c r="MA53" s="5"/>
+      <c r="MB53" s="5"/>
+      <c r="MC53" s="5"/>
+      <c r="MD53" s="5"/>
+      <c r="ME53" s="5"/>
+      <c r="MF53" s="5"/>
+      <c r="MG53" s="5"/>
+      <c r="MH53" s="5"/>
+      <c r="MI53" s="5"/>
+      <c r="MJ53" s="5"/>
+      <c r="MK53" s="5"/>
+      <c r="ML53" s="5"/>
+      <c r="MM53" s="5"/>
+      <c r="MN53" s="5"/>
+      <c r="MO53" s="5"/>
+      <c r="MP53" s="5"/>
+      <c r="MQ53" s="5"/>
+      <c r="MR53" s="5"/>
+      <c r="MS53" s="5"/>
+      <c r="MT53" s="5"/>
+      <c r="MU53" s="5"/>
+      <c r="MV53" s="5"/>
+      <c r="MW53" s="5"/>
+      <c r="MX53" s="5"/>
+      <c r="MY53" s="5"/>
+      <c r="MZ53" s="5"/>
+      <c r="NA53" s="5"/>
+      <c r="NB53" s="5"/>
+      <c r="NC53" s="5"/>
+      <c r="ND53" s="5"/>
+      <c r="NE53" s="5"/>
+      <c r="NF53" s="5"/>
+      <c r="NG53" s="5"/>
+      <c r="NH53" s="5"/>
+      <c r="NI53" s="5"/>
+      <c r="NJ53" s="5"/>
+      <c r="NK53" s="5"/>
+      <c r="NL53" s="5"/>
+      <c r="NM53" s="5"/>
+      <c r="NN53" s="5"/>
+      <c r="NO53" s="5"/>
+      <c r="NP53" s="5"/>
+      <c r="NQ53" s="5"/>
+      <c r="NR53" s="5"/>
+      <c r="NS53" s="5"/>
+      <c r="NT53" s="5"/>
+      <c r="NU53" s="5"/>
+      <c r="NV53" s="5"/>
+      <c r="NW53" s="5"/>
+      <c r="NX53" s="5"/>
+      <c r="NY53" s="5"/>
+      <c r="NZ53" s="5"/>
+      <c r="OA53" s="5"/>
+      <c r="OB53" s="5"/>
+      <c r="OC53" s="5"/>
+      <c r="OD53" s="5"/>
+      <c r="OE53" s="5"/>
+      <c r="OF53" s="5"/>
+      <c r="OG53" s="5"/>
+      <c r="OH53" s="5"/>
+      <c r="OI53" s="5"/>
+      <c r="OJ53" s="5"/>
+      <c r="OK53" s="5"/>
+      <c r="OL53" s="5"/>
+      <c r="OM53" s="5"/>
+      <c r="ON53" s="5"/>
+      <c r="OO53" s="5"/>
+      <c r="OP53" s="5"/>
+      <c r="OQ53" s="5"/>
+      <c r="OR53" s="5"/>
+      <c r="OS53" s="5"/>
+      <c r="OT53" s="5"/>
+      <c r="OU53" s="5"/>
+      <c r="OV53" s="5"/>
+      <c r="OW53" s="5"/>
+      <c r="OX53" s="5"/>
+      <c r="OY53" s="5"/>
+      <c r="OZ53" s="5"/>
+      <c r="PA53" s="5"/>
+      <c r="PB53" s="5"/>
+      <c r="PC53" s="5"/>
+      <c r="PD53" s="5"/>
+      <c r="PE53" s="5"/>
+      <c r="PF53" s="5"/>
+      <c r="PG53" s="5"/>
+      <c r="PH53" s="5"/>
+      <c r="PI53" s="5"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="5"/>
+      <c r="Q54" s="5"/>
+      <c r="R54" s="5"/>
+      <c r="S54" s="5"/>
+      <c r="T54" s="5"/>
+      <c r="U54" s="5"/>
+      <c r="V54" s="5"/>
+      <c r="W54" s="5"/>
+      <c r="X54" s="5"/>
+      <c r="Y54" s="5"/>
+      <c r="Z54" s="5"/>
+      <c r="AA54" s="5"/>
+      <c r="AB54" s="5"/>
+      <c r="AC54" s="5"/>
+      <c r="AD54" s="5"/>
+      <c r="AE54" s="5"/>
+      <c r="AF54" s="5"/>
+      <c r="AG54" s="5"/>
+      <c r="AH54" s="5"/>
+      <c r="AI54" s="5"/>
+      <c r="AJ54" s="5"/>
+      <c r="AK54" s="5"/>
+      <c r="AL54" s="5"/>
+      <c r="AM54" s="5"/>
+      <c r="AN54" s="5"/>
+      <c r="AO54" s="5"/>
+      <c r="AP54" s="5"/>
+      <c r="AQ54" s="5"/>
+      <c r="AR54" s="5"/>
+      <c r="AS54" s="5"/>
+      <c r="AT54" s="5"/>
+      <c r="AU54" s="5"/>
+      <c r="AV54" s="5"/>
+      <c r="AW54" s="5"/>
+      <c r="AX54" s="5"/>
+      <c r="AY54" s="5"/>
+      <c r="AZ54" s="5"/>
+      <c r="BA54" s="5"/>
+      <c r="BB54" s="5"/>
+      <c r="BC54" s="5"/>
+      <c r="BD54" s="5"/>
+      <c r="BE54" s="5"/>
+      <c r="BF54" s="5"/>
+      <c r="BG54" s="5"/>
+      <c r="BH54" s="5"/>
+      <c r="BI54" s="5"/>
+      <c r="BJ54" s="5"/>
+      <c r="BK54" s="5"/>
+      <c r="BL54" s="5"/>
+      <c r="BM54" s="5"/>
+      <c r="BN54" s="5"/>
+      <c r="BO54" s="5"/>
+      <c r="BP54" s="5"/>
+      <c r="BQ54" s="5"/>
+      <c r="BR54" s="5"/>
+      <c r="BS54" s="5"/>
+      <c r="BT54" s="5"/>
+      <c r="BU54" s="5"/>
+      <c r="BV54" s="5"/>
+      <c r="BW54" s="5"/>
+      <c r="BX54" s="5"/>
+      <c r="BY54" s="5"/>
+      <c r="BZ54" s="5"/>
+      <c r="CA54" s="5"/>
+      <c r="CB54" s="5"/>
+      <c r="CC54" s="5"/>
+      <c r="CD54" s="5"/>
+      <c r="CE54" s="5"/>
+      <c r="CF54" s="5"/>
+      <c r="CG54" s="5"/>
+      <c r="CH54" s="5"/>
+      <c r="CI54" s="5"/>
+      <c r="CJ54" s="5"/>
+      <c r="CK54" s="5"/>
+      <c r="CL54" s="5"/>
+      <c r="CM54" s="5"/>
+      <c r="CN54" s="5"/>
+      <c r="CO54" s="5"/>
+      <c r="CP54" s="5"/>
+      <c r="CQ54" s="5"/>
+      <c r="CR54" s="5"/>
+      <c r="CS54" s="5"/>
+      <c r="CT54" s="5"/>
+      <c r="CU54" s="5"/>
+      <c r="CV54" s="5"/>
+      <c r="CW54" s="5"/>
+      <c r="CX54" s="5"/>
+      <c r="CY54" s="5"/>
+      <c r="CZ54" s="5"/>
+      <c r="DA54" s="5"/>
+      <c r="DB54" s="5"/>
+      <c r="DC54" s="5"/>
+      <c r="DD54" s="5"/>
+      <c r="DE54" s="5"/>
+      <c r="DF54" s="5"/>
+      <c r="DG54" s="5"/>
+      <c r="DH54" s="5"/>
+      <c r="DI54" s="5"/>
+      <c r="DJ54" s="5"/>
+      <c r="DK54" s="5"/>
+      <c r="DL54" s="5"/>
+      <c r="DM54" s="5"/>
+      <c r="DN54" s="5"/>
+      <c r="DO54" s="5"/>
+      <c r="DP54" s="5"/>
+      <c r="DQ54" s="5"/>
+      <c r="DR54" s="5"/>
+      <c r="DS54" s="5"/>
+      <c r="DT54" s="5"/>
+      <c r="DU54" s="5"/>
+      <c r="DV54" s="5"/>
+      <c r="DW54" s="5"/>
+      <c r="DX54" s="5"/>
+      <c r="DY54" s="5"/>
+      <c r="DZ54" s="5"/>
+      <c r="EA54" s="5"/>
+      <c r="EB54" s="5"/>
+      <c r="EC54" s="5"/>
+      <c r="ED54" s="5"/>
+      <c r="EE54" s="5"/>
+      <c r="EF54" s="5"/>
+      <c r="EG54" s="5"/>
+      <c r="EH54" s="5"/>
+      <c r="EI54" s="5"/>
+      <c r="EJ54" s="5"/>
+      <c r="EK54" s="5"/>
+      <c r="EL54" s="5"/>
+      <c r="EM54" s="5"/>
+      <c r="EN54" s="5"/>
+      <c r="EO54" s="5"/>
+      <c r="EP54" s="5"/>
+      <c r="EQ54" s="5"/>
+      <c r="ER54" s="5"/>
+      <c r="ES54" s="5"/>
+      <c r="ET54" s="5"/>
+      <c r="EU54" s="5"/>
+      <c r="EV54" s="5"/>
+      <c r="EW54" s="5"/>
+      <c r="EX54" s="5"/>
+      <c r="EY54" s="5"/>
+      <c r="EZ54" s="5"/>
+      <c r="FA54" s="5"/>
+      <c r="FB54" s="5"/>
+      <c r="FC54" s="5"/>
+      <c r="FD54" s="5"/>
+      <c r="FE54" s="5"/>
+      <c r="FF54" s="5"/>
+      <c r="FG54" s="5"/>
+      <c r="FH54" s="5"/>
+      <c r="FI54" s="5"/>
+      <c r="FJ54" s="5"/>
+      <c r="FK54" s="5"/>
+      <c r="FL54" s="5"/>
+      <c r="FM54" s="5"/>
+      <c r="FN54" s="5"/>
+      <c r="FO54" s="5"/>
+      <c r="FP54" s="5"/>
+      <c r="FQ54" s="5"/>
+      <c r="FR54" s="5"/>
+      <c r="FS54" s="5"/>
+      <c r="FT54" s="5"/>
+      <c r="FU54" s="5"/>
+      <c r="FV54" s="5"/>
+      <c r="FW54" s="5"/>
+      <c r="FX54" s="5"/>
+      <c r="FY54" s="5"/>
+      <c r="FZ54" s="5"/>
+      <c r="GA54" s="5"/>
+      <c r="GB54" s="5"/>
+      <c r="GC54" s="5"/>
+      <c r="GD54" s="5"/>
+      <c r="GE54" s="5"/>
+      <c r="GF54" s="5"/>
+      <c r="GG54" s="5"/>
+      <c r="GH54" s="5"/>
+      <c r="GI54" s="5"/>
+      <c r="GJ54" s="5"/>
+      <c r="GK54" s="5"/>
+      <c r="GL54" s="5"/>
+      <c r="GM54" s="5"/>
+      <c r="GN54" s="5"/>
+      <c r="GO54" s="5"/>
+      <c r="GP54" s="5"/>
+      <c r="GQ54" s="5"/>
+      <c r="GR54" s="5"/>
+      <c r="GS54" s="5"/>
+      <c r="GT54" s="5"/>
+      <c r="GU54" s="5"/>
+      <c r="GV54" s="5"/>
+      <c r="GW54" s="5"/>
+      <c r="GX54" s="5"/>
+      <c r="GY54" s="5"/>
+      <c r="GZ54" s="5"/>
+      <c r="HA54" s="5"/>
+      <c r="HB54" s="5"/>
+      <c r="HC54" s="5"/>
+      <c r="HD54" s="5"/>
+      <c r="HE54" s="5"/>
+      <c r="HF54" s="5"/>
+      <c r="HG54" s="5"/>
+      <c r="HH54" s="5"/>
+      <c r="HI54" s="5"/>
+      <c r="HJ54" s="5"/>
+      <c r="HK54" s="5"/>
+      <c r="HL54" s="5"/>
+      <c r="HM54" s="5"/>
+      <c r="HN54" s="5"/>
+      <c r="HO54" s="5"/>
+      <c r="HP54" s="5"/>
+      <c r="HQ54" s="5"/>
+      <c r="HR54" s="5"/>
+      <c r="HS54" s="5"/>
+      <c r="HT54" s="5"/>
+      <c r="HU54" s="5"/>
+      <c r="HV54" s="5"/>
+      <c r="HW54" s="5"/>
+      <c r="HX54" s="5"/>
+      <c r="HY54" s="5"/>
+      <c r="HZ54" s="5"/>
+      <c r="IA54" s="5"/>
+      <c r="IB54" s="5"/>
+      <c r="IC54" s="5"/>
+      <c r="ID54" s="5"/>
+      <c r="IE54" s="5"/>
+      <c r="IF54" s="5"/>
+      <c r="IG54" s="5"/>
+      <c r="IH54" s="5"/>
+      <c r="II54" s="5"/>
+      <c r="IJ54" s="5"/>
+      <c r="IK54" s="5"/>
+      <c r="IL54" s="5"/>
+      <c r="IM54" s="5"/>
+      <c r="IN54" s="5"/>
+      <c r="IO54" s="5"/>
+      <c r="IP54" s="5"/>
+      <c r="IQ54" s="5"/>
+      <c r="IR54" s="5"/>
+      <c r="IS54" s="5"/>
+      <c r="IT54" s="5"/>
+      <c r="IU54" s="5"/>
+      <c r="IV54" s="5"/>
+      <c r="IW54" s="5"/>
+      <c r="IX54" s="5"/>
+      <c r="IY54" s="5"/>
+      <c r="IZ54" s="5"/>
+      <c r="JA54" s="5"/>
+      <c r="JB54" s="5"/>
+      <c r="JC54" s="5"/>
+      <c r="JD54" s="5"/>
+      <c r="JE54" s="5"/>
+      <c r="JF54" s="5"/>
+      <c r="JG54" s="5"/>
+      <c r="JH54" s="5"/>
+      <c r="JI54" s="5"/>
+      <c r="JJ54" s="5"/>
+      <c r="JK54" s="5"/>
+      <c r="JL54" s="5"/>
+      <c r="JM54" s="5"/>
+      <c r="JN54" s="5"/>
+      <c r="JO54" s="5"/>
+      <c r="JP54" s="5"/>
+      <c r="JQ54" s="5"/>
+      <c r="JR54" s="5"/>
+      <c r="JS54" s="5"/>
+      <c r="JT54" s="5"/>
+      <c r="JU54" s="5"/>
+      <c r="JV54" s="5"/>
+      <c r="JW54" s="5"/>
+      <c r="JX54" s="5"/>
+      <c r="JY54" s="5"/>
+      <c r="JZ54" s="5"/>
+      <c r="KA54" s="5"/>
+      <c r="KB54" s="5"/>
+      <c r="KC54" s="5"/>
+      <c r="KD54" s="5"/>
+      <c r="KE54" s="5"/>
+      <c r="KF54" s="5"/>
+      <c r="KG54" s="5"/>
+      <c r="KH54" s="5"/>
+      <c r="KI54" s="5"/>
+      <c r="KJ54" s="5"/>
+      <c r="KK54" s="5"/>
+      <c r="KL54" s="5"/>
+      <c r="KM54" s="5"/>
+      <c r="KN54" s="5"/>
+      <c r="KO54" s="5"/>
+      <c r="KP54" s="5"/>
+      <c r="KQ54" s="5"/>
+      <c r="KR54" s="5"/>
+      <c r="KS54" s="5"/>
+      <c r="KT54" s="5"/>
+      <c r="KU54" s="5"/>
+      <c r="KV54" s="5"/>
+      <c r="KW54" s="5"/>
+      <c r="KX54" s="5"/>
+      <c r="KY54" s="5"/>
+      <c r="KZ54" s="5"/>
+      <c r="LA54" s="5"/>
+      <c r="LB54" s="5"/>
+      <c r="LC54" s="5"/>
+      <c r="LD54" s="5"/>
+      <c r="LE54" s="5"/>
+      <c r="LF54" s="5"/>
+      <c r="LG54" s="5"/>
+      <c r="LH54" s="5"/>
+      <c r="LI54" s="5"/>
+      <c r="LJ54" s="5"/>
+      <c r="LK54" s="5"/>
+      <c r="LL54" s="5"/>
+      <c r="LM54" s="5"/>
+      <c r="LN54" s="5"/>
+      <c r="LO54" s="5"/>
+      <c r="LP54" s="5"/>
+      <c r="LQ54" s="5"/>
+      <c r="LR54" s="5"/>
+      <c r="LS54" s="5"/>
+      <c r="LT54" s="5"/>
+      <c r="LU54" s="5"/>
+      <c r="LV54" s="5"/>
+      <c r="LW54" s="5"/>
+      <c r="LX54" s="5"/>
+      <c r="LY54" s="5"/>
+      <c r="LZ54" s="5"/>
+      <c r="MA54" s="5"/>
+      <c r="MB54" s="5"/>
+      <c r="MC54" s="5"/>
+      <c r="MD54" s="5"/>
+      <c r="ME54" s="5"/>
+      <c r="MF54" s="5"/>
+      <c r="MG54" s="5"/>
+      <c r="MH54" s="5"/>
+      <c r="MI54" s="5"/>
+      <c r="MJ54" s="5"/>
+      <c r="MK54" s="5"/>
+      <c r="ML54" s="5"/>
+      <c r="MM54" s="5"/>
+      <c r="MN54" s="5"/>
+      <c r="MO54" s="5"/>
+      <c r="MP54" s="5"/>
+      <c r="MQ54" s="5"/>
+      <c r="MR54" s="5"/>
+      <c r="MS54" s="5"/>
+      <c r="MT54" s="5"/>
+      <c r="MU54" s="5"/>
+      <c r="MV54" s="5"/>
+      <c r="MW54" s="5"/>
+      <c r="MX54" s="5"/>
+      <c r="MY54" s="5"/>
+      <c r="MZ54" s="5"/>
+      <c r="NA54" s="5"/>
+      <c r="NB54" s="5"/>
+      <c r="NC54" s="5"/>
+      <c r="ND54" s="5"/>
+      <c r="NE54" s="5"/>
+      <c r="NF54" s="5"/>
+      <c r="NG54" s="5"/>
+      <c r="NH54" s="5"/>
+      <c r="NI54" s="5"/>
+      <c r="NJ54" s="5"/>
+      <c r="NK54" s="5"/>
+      <c r="NL54" s="5"/>
+      <c r="NM54" s="5"/>
+      <c r="NN54" s="5"/>
+      <c r="NO54" s="5"/>
+      <c r="NP54" s="5"/>
+      <c r="NQ54" s="5"/>
+      <c r="NR54" s="5"/>
+      <c r="NS54" s="5"/>
+      <c r="NT54" s="5"/>
+      <c r="NU54" s="5"/>
+      <c r="NV54" s="5"/>
+      <c r="NW54" s="5"/>
+      <c r="NX54" s="5"/>
+      <c r="NY54" s="5"/>
+      <c r="NZ54" s="5"/>
+      <c r="OA54" s="5"/>
+      <c r="OB54" s="5"/>
+      <c r="OC54" s="5"/>
+      <c r="OD54" s="5"/>
+      <c r="OE54" s="5"/>
+      <c r="OF54" s="5"/>
+      <c r="OG54" s="5"/>
+      <c r="OH54" s="5"/>
+      <c r="OI54" s="5"/>
+      <c r="OJ54" s="5"/>
+      <c r="OK54" s="5"/>
+      <c r="OL54" s="5"/>
+      <c r="OM54" s="5"/>
+      <c r="ON54" s="5"/>
+      <c r="OO54" s="5"/>
+      <c r="OP54" s="5"/>
+      <c r="OQ54" s="5"/>
+      <c r="OR54" s="5"/>
+      <c r="OS54" s="5"/>
+      <c r="OT54" s="5"/>
+      <c r="OU54" s="5"/>
+      <c r="OV54" s="5"/>
+      <c r="OW54" s="5"/>
+      <c r="OX54" s="5"/>
+      <c r="OY54" s="5"/>
+      <c r="OZ54" s="5"/>
+      <c r="PA54" s="5"/>
+      <c r="PB54" s="5"/>
+      <c r="PC54" s="5"/>
+      <c r="PD54" s="5"/>
+      <c r="PE54" s="5"/>
+      <c r="PF54" s="5"/>
+      <c r="PG54" s="5"/>
+      <c r="PH54" s="5"/>
+      <c r="PI54" s="5"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="5"/>
+      <c r="Q55" s="5"/>
+      <c r="R55" s="5"/>
+      <c r="S55" s="5"/>
+      <c r="T55" s="5"/>
+      <c r="U55" s="5"/>
+      <c r="V55" s="5"/>
+      <c r="W55" s="5"/>
+      <c r="X55" s="5"/>
+      <c r="Y55" s="5"/>
+      <c r="Z55" s="5"/>
+      <c r="AA55" s="5"/>
+      <c r="AB55" s="5"/>
+      <c r="AC55" s="5"/>
+      <c r="AD55" s="5"/>
+      <c r="AE55" s="5"/>
+      <c r="AF55" s="5"/>
+      <c r="AG55" s="5"/>
+      <c r="AH55" s="5"/>
+      <c r="AI55" s="5"/>
+      <c r="AJ55" s="5"/>
+      <c r="AK55" s="5"/>
+      <c r="AL55" s="5"/>
+      <c r="AM55" s="5"/>
+      <c r="AN55" s="5"/>
+      <c r="AO55" s="5"/>
+      <c r="AP55" s="5"/>
+      <c r="AQ55" s="5"/>
+      <c r="AR55" s="5"/>
+      <c r="AS55" s="5"/>
+      <c r="AT55" s="5"/>
+      <c r="AU55" s="5"/>
+      <c r="AV55" s="5"/>
+      <c r="AW55" s="5"/>
+      <c r="AX55" s="5"/>
+      <c r="AY55" s="5"/>
+      <c r="AZ55" s="5"/>
+      <c r="BA55" s="5"/>
+      <c r="BB55" s="5"/>
+      <c r="BC55" s="5"/>
+      <c r="BD55" s="5"/>
+      <c r="BE55" s="5"/>
+      <c r="BF55" s="5"/>
+      <c r="BG55" s="5"/>
+      <c r="BH55" s="5"/>
+      <c r="BI55" s="5"/>
+      <c r="BJ55" s="5"/>
+      <c r="BK55" s="5"/>
+      <c r="BL55" s="5"/>
+      <c r="BM55" s="5"/>
+      <c r="BN55" s="5"/>
+      <c r="BO55" s="5"/>
+      <c r="BP55" s="5"/>
+      <c r="BQ55" s="5"/>
+      <c r="BR55" s="5"/>
+      <c r="BS55" s="5"/>
+      <c r="BT55" s="5"/>
+      <c r="BU55" s="5"/>
+      <c r="BV55" s="5"/>
+      <c r="BW55" s="5"/>
+      <c r="BX55" s="5"/>
+      <c r="BY55" s="5"/>
+      <c r="BZ55" s="5"/>
+      <c r="CA55" s="5"/>
+      <c r="CB55" s="5"/>
+      <c r="CC55" s="5"/>
+      <c r="CD55" s="5"/>
+      <c r="CE55" s="5"/>
+      <c r="CF55" s="5"/>
+      <c r="CG55" s="5"/>
+      <c r="CH55" s="5"/>
+      <c r="CI55" s="5"/>
+      <c r="CJ55" s="5"/>
+      <c r="CK55" s="5"/>
+      <c r="CL55" s="5"/>
+      <c r="CM55" s="5"/>
+      <c r="CN55" s="5"/>
+      <c r="CO55" s="5"/>
+      <c r="CP55" s="5"/>
+      <c r="CQ55" s="5"/>
+      <c r="CR55" s="5"/>
+      <c r="CS55" s="5"/>
+      <c r="CT55" s="5"/>
+      <c r="CU55" s="5"/>
+      <c r="CV55" s="5"/>
+      <c r="CW55" s="5"/>
+      <c r="CX55" s="5"/>
+      <c r="CY55" s="5"/>
+      <c r="CZ55" s="5"/>
+      <c r="DA55" s="5"/>
+      <c r="DB55" s="5"/>
+      <c r="DC55" s="5"/>
+      <c r="DD55" s="5"/>
+      <c r="DE55" s="5"/>
+      <c r="DF55" s="5"/>
+      <c r="DG55" s="5"/>
+      <c r="DH55" s="5"/>
+      <c r="DI55" s="5"/>
+      <c r="DJ55" s="5"/>
+      <c r="DK55" s="5"/>
+      <c r="DL55" s="5"/>
+      <c r="DM55" s="5"/>
+      <c r="DN55" s="5"/>
+      <c r="DO55" s="5"/>
+      <c r="DP55" s="5"/>
+      <c r="DQ55" s="5"/>
+      <c r="DR55" s="5"/>
+      <c r="DS55" s="5"/>
+      <c r="DT55" s="5"/>
+      <c r="DU55" s="5"/>
+      <c r="DV55" s="5"/>
+      <c r="DW55" s="5"/>
+      <c r="DX55" s="5"/>
+      <c r="DY55" s="5"/>
+      <c r="DZ55" s="5"/>
+      <c r="EA55" s="5"/>
+      <c r="EB55" s="5"/>
+      <c r="EC55" s="5"/>
+      <c r="ED55" s="5"/>
+      <c r="EE55" s="5"/>
+      <c r="EF55" s="5"/>
+      <c r="EG55" s="5"/>
+      <c r="EH55" s="5"/>
+      <c r="EI55" s="5"/>
+      <c r="EJ55" s="5"/>
+      <c r="EK55" s="5"/>
+      <c r="EL55" s="5"/>
+      <c r="EM55" s="5"/>
+      <c r="EN55" s="5"/>
+      <c r="EO55" s="5"/>
+      <c r="EP55" s="5"/>
+      <c r="EQ55" s="5"/>
+      <c r="ER55" s="5"/>
+      <c r="ES55" s="5"/>
+      <c r="ET55" s="5"/>
+      <c r="EU55" s="5"/>
+      <c r="EV55" s="5"/>
+      <c r="EW55" s="5"/>
+      <c r="EX55" s="5"/>
+      <c r="EY55" s="5"/>
+      <c r="EZ55" s="5"/>
+      <c r="FA55" s="5"/>
+      <c r="FB55" s="5"/>
+      <c r="FC55" s="5"/>
+      <c r="FD55" s="5"/>
+      <c r="FE55" s="5"/>
+      <c r="FF55" s="5"/>
+      <c r="FG55" s="5"/>
+      <c r="FH55" s="5"/>
+      <c r="FI55" s="5"/>
+      <c r="FJ55" s="5"/>
+      <c r="FK55" s="5"/>
+      <c r="FL55" s="5"/>
+      <c r="FM55" s="5"/>
+      <c r="FN55" s="5"/>
+      <c r="FO55" s="5"/>
+      <c r="FP55" s="5"/>
+      <c r="FQ55" s="5"/>
+      <c r="FR55" s="5"/>
+      <c r="FS55" s="5"/>
+      <c r="FT55" s="5"/>
+      <c r="FU55" s="5"/>
+      <c r="FV55" s="5"/>
+      <c r="FW55" s="5"/>
+      <c r="FX55" s="5"/>
+      <c r="FY55" s="5"/>
+      <c r="FZ55" s="5"/>
+      <c r="GA55" s="5"/>
+      <c r="GB55" s="5"/>
+      <c r="GC55" s="5"/>
+      <c r="GD55" s="5"/>
+      <c r="GE55" s="5"/>
+      <c r="GF55" s="5"/>
+      <c r="GG55" s="5"/>
+      <c r="GH55" s="5"/>
+      <c r="GI55" s="5"/>
+      <c r="GJ55" s="5"/>
+      <c r="GK55" s="5"/>
+      <c r="GL55" s="5"/>
+      <c r="GM55" s="5"/>
+      <c r="GN55" s="5"/>
+      <c r="GO55" s="5"/>
+      <c r="GP55" s="5"/>
+      <c r="GQ55" s="5"/>
+      <c r="GR55" s="5"/>
+      <c r="GS55" s="5"/>
+      <c r="GT55" s="5"/>
+      <c r="GU55" s="5"/>
+      <c r="GV55" s="5"/>
+      <c r="GW55" s="5"/>
+      <c r="GX55" s="5"/>
+      <c r="GY55" s="5"/>
+      <c r="GZ55" s="5"/>
+      <c r="HA55" s="5"/>
+      <c r="HB55" s="5"/>
+      <c r="HC55" s="5"/>
+      <c r="HD55" s="5"/>
+      <c r="HE55" s="5"/>
+      <c r="HF55" s="5"/>
+      <c r="HG55" s="5"/>
+      <c r="HH55" s="5"/>
+      <c r="HI55" s="5"/>
+      <c r="HJ55" s="5"/>
+      <c r="HK55" s="5"/>
+      <c r="HL55" s="5"/>
+      <c r="HM55" s="5"/>
+      <c r="HN55" s="5"/>
+      <c r="HO55" s="5"/>
+      <c r="HP55" s="5"/>
+      <c r="HQ55" s="5"/>
+      <c r="HR55" s="5"/>
+      <c r="HS55" s="5"/>
+      <c r="HT55" s="5"/>
+      <c r="HU55" s="5"/>
+      <c r="HV55" s="5"/>
+      <c r="HW55" s="5"/>
+      <c r="HX55" s="5"/>
+      <c r="HY55" s="5"/>
+      <c r="HZ55" s="5"/>
+      <c r="IA55" s="5"/>
+      <c r="IB55" s="5"/>
+      <c r="IC55" s="5"/>
+      <c r="ID55" s="5"/>
+      <c r="IE55" s="5"/>
+      <c r="IF55" s="5"/>
+      <c r="IG55" s="5"/>
+      <c r="IH55" s="5"/>
+      <c r="II55" s="5"/>
+      <c r="IJ55" s="5"/>
+      <c r="IK55" s="5"/>
+      <c r="IL55" s="5"/>
+      <c r="IM55" s="5"/>
+      <c r="IN55" s="5"/>
+      <c r="IO55" s="5"/>
+      <c r="IP55" s="5"/>
+      <c r="IQ55" s="5"/>
+      <c r="IR55" s="5"/>
+      <c r="IS55" s="5"/>
+      <c r="IT55" s="5"/>
+      <c r="IU55" s="5"/>
+      <c r="IV55" s="5"/>
+      <c r="IW55" s="5"/>
+      <c r="IX55" s="5"/>
+      <c r="IY55" s="5"/>
+      <c r="IZ55" s="5"/>
+      <c r="JA55" s="5"/>
+      <c r="JB55" s="5"/>
+      <c r="JC55" s="5"/>
+      <c r="JD55" s="5"/>
+      <c r="JE55" s="5"/>
+      <c r="JF55" s="5"/>
+      <c r="JG55" s="5"/>
+      <c r="JH55" s="5"/>
+      <c r="JI55" s="5"/>
+      <c r="JJ55" s="5"/>
+      <c r="JK55" s="5"/>
+      <c r="JL55" s="5"/>
+      <c r="JM55" s="5"/>
+      <c r="JN55" s="5"/>
+      <c r="JO55" s="5"/>
+      <c r="JP55" s="5"/>
+      <c r="JQ55" s="5"/>
+      <c r="JR55" s="5"/>
+      <c r="JS55" s="5"/>
+      <c r="JT55" s="5"/>
+      <c r="JU55" s="5"/>
+      <c r="JV55" s="5"/>
+      <c r="JW55" s="5"/>
+      <c r="JX55" s="5"/>
+      <c r="JY55" s="5"/>
+      <c r="JZ55" s="5"/>
+      <c r="KA55" s="5"/>
+      <c r="KB55" s="5"/>
+      <c r="KC55" s="5"/>
+      <c r="KD55" s="5"/>
+      <c r="KE55" s="5"/>
+      <c r="KF55" s="5"/>
+      <c r="KG55" s="5"/>
+      <c r="KH55" s="5"/>
+      <c r="KI55" s="5"/>
+      <c r="KJ55" s="5"/>
+      <c r="KK55" s="5"/>
+      <c r="KL55" s="5"/>
+      <c r="KM55" s="5"/>
+      <c r="KN55" s="5"/>
+      <c r="KO55" s="5"/>
+      <c r="KP55" s="5"/>
+      <c r="KQ55" s="5"/>
+      <c r="KR55" s="5"/>
+      <c r="KS55" s="5"/>
+      <c r="KT55" s="5"/>
+      <c r="KU55" s="5"/>
+      <c r="KV55" s="5"/>
+      <c r="KW55" s="5"/>
+      <c r="KX55" s="5"/>
+      <c r="KY55" s="5"/>
+      <c r="KZ55" s="5"/>
+      <c r="LA55" s="5"/>
+      <c r="LB55" s="5"/>
+      <c r="LC55" s="5"/>
+      <c r="LD55" s="5"/>
+      <c r="LE55" s="5"/>
+      <c r="LF55" s="5"/>
+      <c r="LG55" s="5"/>
+      <c r="LH55" s="5"/>
+      <c r="LI55" s="5"/>
+      <c r="LJ55" s="5"/>
+      <c r="LK55" s="5"/>
+      <c r="LL55" s="5"/>
+      <c r="LM55" s="5"/>
+      <c r="LN55" s="5"/>
+      <c r="LO55" s="5"/>
+      <c r="LP55" s="5"/>
+      <c r="LQ55" s="5"/>
+      <c r="LR55" s="5"/>
+      <c r="LS55" s="5"/>
+      <c r="LT55" s="5"/>
+      <c r="LU55" s="5"/>
+      <c r="LV55" s="5"/>
+      <c r="LW55" s="5"/>
+      <c r="LX55" s="5"/>
+      <c r="LY55" s="5"/>
+      <c r="LZ55" s="5"/>
+      <c r="MA55" s="5"/>
+      <c r="MB55" s="5"/>
+      <c r="MC55" s="5"/>
+      <c r="MD55" s="5"/>
+      <c r="ME55" s="5"/>
+      <c r="MF55" s="5"/>
+      <c r="MG55" s="5"/>
+      <c r="MH55" s="5"/>
+      <c r="MI55" s="5"/>
+      <c r="MJ55" s="5"/>
+      <c r="MK55" s="5"/>
+      <c r="ML55" s="5"/>
+      <c r="MM55" s="5"/>
+      <c r="MN55" s="5"/>
+      <c r="MO55" s="5"/>
+      <c r="MP55" s="5"/>
+      <c r="MQ55" s="5"/>
+      <c r="MR55" s="5"/>
+      <c r="MS55" s="5"/>
+      <c r="MT55" s="5"/>
+      <c r="MU55" s="5"/>
+      <c r="MV55" s="5"/>
+      <c r="MW55" s="5"/>
+      <c r="MX55" s="5"/>
+      <c r="MY55" s="5"/>
+      <c r="MZ55" s="5"/>
+      <c r="NA55" s="5"/>
+      <c r="NB55" s="5"/>
+      <c r="NC55" s="5"/>
+      <c r="ND55" s="5"/>
+      <c r="NE55" s="5"/>
+      <c r="NF55" s="5"/>
+      <c r="NG55" s="5"/>
+      <c r="NH55" s="5"/>
+      <c r="NI55" s="5"/>
+      <c r="NJ55" s="5"/>
+      <c r="NK55" s="5"/>
+      <c r="NL55" s="5"/>
+      <c r="NM55" s="5"/>
+      <c r="NN55" s="5"/>
+      <c r="NO55" s="5"/>
+      <c r="NP55" s="5"/>
+      <c r="NQ55" s="5"/>
+      <c r="NR55" s="5"/>
+      <c r="NS55" s="5"/>
+      <c r="NT55" s="5"/>
+      <c r="NU55" s="5"/>
+      <c r="NV55" s="5"/>
+      <c r="NW55" s="5"/>
+      <c r="NX55" s="5"/>
+      <c r="NY55" s="5"/>
+      <c r="NZ55" s="5"/>
+      <c r="OA55" s="5"/>
+      <c r="OB55" s="5"/>
+      <c r="OC55" s="5"/>
+      <c r="OD55" s="5"/>
+      <c r="OE55" s="5"/>
+      <c r="OF55" s="5"/>
+      <c r="OG55" s="5"/>
+      <c r="OH55" s="5"/>
+      <c r="OI55" s="5"/>
+      <c r="OJ55" s="5"/>
+      <c r="OK55" s="5"/>
+      <c r="OL55" s="5"/>
+      <c r="OM55" s="5"/>
+      <c r="ON55" s="5"/>
+      <c r="OO55" s="5"/>
+      <c r="OP55" s="5"/>
+      <c r="OQ55" s="5"/>
+      <c r="OR55" s="5"/>
+      <c r="OS55" s="5"/>
+      <c r="OT55" s="5"/>
+      <c r="OU55" s="5"/>
+      <c r="OV55" s="5"/>
+      <c r="OW55" s="5"/>
+      <c r="OX55" s="5"/>
+      <c r="OY55" s="5"/>
+      <c r="OZ55" s="5"/>
+      <c r="PA55" s="5"/>
+      <c r="PB55" s="5"/>
+      <c r="PC55" s="5"/>
+      <c r="PD55" s="5"/>
+      <c r="PE55" s="5"/>
+      <c r="PF55" s="5"/>
+      <c r="PG55" s="5"/>
+      <c r="PH55" s="5"/>
+      <c r="PI55" s="5"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="5"/>
+      <c r="K56" s="5"/>
+      <c r="L56" s="5"/>
+      <c r="M56" s="5"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="5"/>
+      <c r="P56" s="5"/>
+      <c r="Q56" s="5"/>
+      <c r="R56" s="5"/>
+      <c r="S56" s="5"/>
+      <c r="T56" s="5"/>
+      <c r="U56" s="5"/>
+      <c r="V56" s="5"/>
+      <c r="W56" s="5"/>
+      <c r="X56" s="5"/>
+      <c r="Y56" s="5"/>
+      <c r="Z56" s="5"/>
+      <c r="AA56" s="5"/>
+      <c r="AB56" s="5"/>
+      <c r="AC56" s="5"/>
+      <c r="AD56" s="5"/>
+      <c r="AE56" s="5"/>
+      <c r="AF56" s="5"/>
+      <c r="AG56" s="5"/>
+      <c r="AH56" s="5"/>
+      <c r="AI56" s="5"/>
+      <c r="AJ56" s="5"/>
+      <c r="AK56" s="5"/>
+      <c r="AL56" s="5"/>
+      <c r="AM56" s="5"/>
+      <c r="AN56" s="5"/>
+      <c r="AO56" s="5"/>
+      <c r="AP56" s="5"/>
+      <c r="AQ56" s="5"/>
+      <c r="AR56" s="5"/>
+      <c r="AS56" s="5"/>
+      <c r="AT56" s="5"/>
+      <c r="AU56" s="5"/>
+      <c r="AV56" s="5"/>
+      <c r="AW56" s="5"/>
+      <c r="AX56" s="5"/>
+      <c r="AY56" s="5"/>
+      <c r="AZ56" s="5"/>
+      <c r="BA56" s="5"/>
+      <c r="BB56" s="5"/>
+      <c r="BC56" s="5"/>
+      <c r="BD56" s="5"/>
+      <c r="BE56" s="5"/>
+      <c r="BF56" s="5"/>
+      <c r="BG56" s="5"/>
+      <c r="BH56" s="5"/>
+      <c r="BI56" s="5"/>
+      <c r="BJ56" s="5"/>
+      <c r="BK56" s="5"/>
+      <c r="BL56" s="5"/>
+      <c r="BM56" s="5"/>
+      <c r="BN56" s="5"/>
+      <c r="BO56" s="5"/>
+      <c r="BP56" s="5"/>
+      <c r="BQ56" s="5"/>
+      <c r="BR56" s="5"/>
+      <c r="BS56" s="5"/>
+      <c r="BT56" s="5"/>
+      <c r="BU56" s="5"/>
+      <c r="BV56" s="5"/>
+      <c r="BW56" s="5"/>
+      <c r="BX56" s="5"/>
+      <c r="BY56" s="5"/>
+      <c r="BZ56" s="5"/>
+      <c r="CA56" s="5"/>
+      <c r="CB56" s="5"/>
+      <c r="CC56" s="5"/>
+      <c r="CD56" s="5"/>
+      <c r="CE56" s="5"/>
+      <c r="CF56" s="5"/>
+      <c r="CG56" s="5"/>
+      <c r="CH56" s="5"/>
+      <c r="CI56" s="5"/>
+      <c r="CJ56" s="5"/>
+      <c r="CK56" s="5"/>
+      <c r="CL56" s="5"/>
+      <c r="CM56" s="5"/>
+      <c r="CN56" s="5"/>
+      <c r="CO56" s="5"/>
+      <c r="CP56" s="5"/>
+      <c r="CQ56" s="5"/>
+      <c r="CR56" s="5"/>
+      <c r="CS56" s="5"/>
+      <c r="CT56" s="5"/>
+      <c r="CU56" s="5"/>
+      <c r="CV56" s="5"/>
+      <c r="CW56" s="5"/>
+      <c r="CX56" s="5"/>
+      <c r="CY56" s="5"/>
+      <c r="CZ56" s="5"/>
+      <c r="DA56" s="5"/>
+      <c r="DB56" s="5"/>
+      <c r="DC56" s="5"/>
+      <c r="DD56" s="5"/>
+      <c r="DE56" s="5"/>
+      <c r="DF56" s="5"/>
+      <c r="DG56" s="5"/>
+      <c r="DH56" s="5"/>
+      <c r="DI56" s="5"/>
+      <c r="DJ56" s="5"/>
+      <c r="DK56" s="5"/>
+      <c r="DL56" s="5"/>
+      <c r="DM56" s="5"/>
+      <c r="DN56" s="5"/>
+      <c r="DO56" s="5"/>
+      <c r="DP56" s="5"/>
+      <c r="DQ56" s="5"/>
+      <c r="DR56" s="5"/>
+      <c r="DS56" s="5"/>
+      <c r="DT56" s="5"/>
+      <c r="DU56" s="5"/>
+      <c r="DV56" s="5"/>
+      <c r="DW56" s="5"/>
+      <c r="DX56" s="5"/>
+      <c r="DY56" s="5"/>
+      <c r="DZ56" s="5"/>
+      <c r="EA56" s="5"/>
+      <c r="EB56" s="5"/>
+      <c r="EC56" s="5"/>
+      <c r="ED56" s="5"/>
+      <c r="EE56" s="5"/>
+      <c r="EF56" s="5"/>
+      <c r="EG56" s="5"/>
+      <c r="EH56" s="5"/>
+      <c r="EI56" s="5"/>
+      <c r="EJ56" s="5"/>
+      <c r="EK56" s="5"/>
+      <c r="EL56" s="5"/>
+      <c r="EM56" s="5"/>
+      <c r="EN56" s="5"/>
+      <c r="EO56" s="5"/>
+      <c r="EP56" s="5"/>
+      <c r="EQ56" s="5"/>
+      <c r="ER56" s="5"/>
+      <c r="ES56" s="5"/>
+      <c r="ET56" s="5"/>
+      <c r="EU56" s="5"/>
+      <c r="EV56" s="5"/>
+      <c r="EW56" s="5"/>
+      <c r="EX56" s="5"/>
+      <c r="EY56" s="5"/>
+      <c r="EZ56" s="5"/>
+      <c r="FA56" s="5"/>
+      <c r="FB56" s="5"/>
+      <c r="FC56" s="5"/>
+      <c r="FD56" s="5"/>
+      <c r="FE56" s="5"/>
+      <c r="FF56" s="5"/>
+      <c r="FG56" s="5"/>
+      <c r="FH56" s="5"/>
+      <c r="FI56" s="5"/>
+      <c r="FJ56" s="5"/>
+      <c r="FK56" s="5"/>
+      <c r="FL56" s="5"/>
+      <c r="FM56" s="5"/>
+      <c r="FN56" s="5"/>
+      <c r="FO56" s="5"/>
+      <c r="FP56" s="5"/>
+      <c r="FQ56" s="5"/>
+      <c r="FR56" s="5"/>
+      <c r="FS56" s="5"/>
+      <c r="FT56" s="5"/>
+      <c r="FU56" s="5"/>
+      <c r="FV56" s="5"/>
+      <c r="FW56" s="5"/>
+      <c r="FX56" s="5"/>
+      <c r="FY56" s="5"/>
+      <c r="FZ56" s="5"/>
+      <c r="GA56" s="5"/>
+      <c r="GB56" s="5"/>
+      <c r="GC56" s="5"/>
+      <c r="GD56" s="5"/>
+      <c r="GE56" s="5"/>
+      <c r="GF56" s="5"/>
+      <c r="GG56" s="5"/>
+      <c r="GH56" s="5"/>
+      <c r="GI56" s="5"/>
+      <c r="GJ56" s="5"/>
+      <c r="GK56" s="5"/>
+      <c r="GL56" s="5"/>
+      <c r="GM56" s="5"/>
+      <c r="GN56" s="5"/>
+      <c r="GO56" s="5"/>
+      <c r="GP56" s="5"/>
+      <c r="GQ56" s="5"/>
+      <c r="GR56" s="5"/>
+      <c r="GS56" s="5"/>
+      <c r="GT56" s="5"/>
+      <c r="GU56" s="5"/>
+      <c r="GV56" s="5"/>
+      <c r="GW56" s="5"/>
+      <c r="GX56" s="5"/>
+      <c r="GY56" s="5"/>
+      <c r="GZ56" s="5"/>
+      <c r="HA56" s="5"/>
+      <c r="HB56" s="5"/>
+      <c r="HC56" s="5"/>
+      <c r="HD56" s="5"/>
+      <c r="HE56" s="5"/>
+      <c r="HF56" s="5"/>
+      <c r="HG56" s="5"/>
+      <c r="HH56" s="5"/>
+      <c r="HI56" s="5"/>
+      <c r="HJ56" s="5"/>
+      <c r="HK56" s="5"/>
+      <c r="HL56" s="5"/>
+      <c r="HM56" s="5"/>
+      <c r="HN56" s="5"/>
+      <c r="HO56" s="5"/>
+      <c r="HP56" s="5"/>
+      <c r="HQ56" s="5"/>
+      <c r="HR56" s="5"/>
+      <c r="HS56" s="5"/>
+      <c r="HT56" s="5"/>
+      <c r="HU56" s="5"/>
+      <c r="HV56" s="5"/>
+      <c r="HW56" s="5"/>
+      <c r="HX56" s="5"/>
+      <c r="HY56" s="5"/>
+      <c r="HZ56" s="5"/>
+      <c r="IA56" s="5"/>
+      <c r="IB56" s="5"/>
+      <c r="IC56" s="5"/>
+      <c r="ID56" s="5"/>
+      <c r="IE56" s="5"/>
+      <c r="IF56" s="5"/>
+      <c r="IG56" s="5"/>
+      <c r="IH56" s="5"/>
+      <c r="II56" s="5"/>
+      <c r="IJ56" s="5"/>
+      <c r="IK56" s="5"/>
+      <c r="IL56" s="5"/>
+      <c r="IM56" s="5"/>
+      <c r="IN56" s="5"/>
+      <c r="IO56" s="5"/>
+      <c r="IP56" s="5"/>
+      <c r="IQ56" s="5"/>
+      <c r="IR56" s="5"/>
+      <c r="IS56" s="5"/>
+      <c r="IT56" s="5"/>
+      <c r="IU56" s="5"/>
+      <c r="IV56" s="5"/>
+      <c r="IW56" s="5"/>
+      <c r="IX56" s="5"/>
+      <c r="IY56" s="5"/>
+      <c r="IZ56" s="5"/>
+      <c r="JA56" s="5"/>
+      <c r="JB56" s="5"/>
+      <c r="JC56" s="5"/>
+      <c r="JD56" s="5"/>
+      <c r="JE56" s="5"/>
+      <c r="JF56" s="5"/>
+      <c r="JG56" s="5"/>
+      <c r="JH56" s="5"/>
+      <c r="JI56" s="5"/>
+      <c r="JJ56" s="5"/>
+      <c r="JK56" s="5"/>
+      <c r="JL56" s="5"/>
+      <c r="JM56" s="5"/>
+      <c r="JN56" s="5"/>
+      <c r="JO56" s="5"/>
+      <c r="JP56" s="5"/>
+      <c r="JQ56" s="5"/>
+      <c r="JR56" s="5"/>
+      <c r="JS56" s="5"/>
+      <c r="JT56" s="5"/>
+      <c r="JU56" s="5"/>
+      <c r="JV56" s="5"/>
+      <c r="JW56" s="5"/>
+      <c r="JX56" s="5"/>
+      <c r="JY56" s="5"/>
+      <c r="JZ56" s="5"/>
+      <c r="KA56" s="5"/>
+      <c r="KB56" s="5"/>
+      <c r="KC56" s="5"/>
+      <c r="KD56" s="5"/>
+      <c r="KE56" s="5"/>
+      <c r="KF56" s="5"/>
+      <c r="KG56" s="5"/>
+      <c r="KH56" s="5"/>
+      <c r="KI56" s="5"/>
+      <c r="KJ56" s="5"/>
+      <c r="KK56" s="5"/>
+      <c r="KL56" s="5"/>
+      <c r="KM56" s="5"/>
+      <c r="KN56" s="5"/>
+      <c r="KO56" s="5"/>
+      <c r="KP56" s="5"/>
+      <c r="KQ56" s="5"/>
+      <c r="KR56" s="5"/>
+      <c r="KS56" s="5"/>
+      <c r="KT56" s="5"/>
+      <c r="KU56" s="5"/>
+      <c r="KV56" s="5"/>
+      <c r="KW56" s="5"/>
+      <c r="KX56" s="5"/>
+      <c r="KY56" s="5"/>
+      <c r="KZ56" s="5"/>
+      <c r="LA56" s="5"/>
+      <c r="LB56" s="5"/>
+      <c r="LC56" s="5"/>
+      <c r="LD56" s="5"/>
+      <c r="LE56" s="5"/>
+      <c r="LF56" s="5"/>
+      <c r="LG56" s="5"/>
+      <c r="LH56" s="5"/>
+      <c r="LI56" s="5"/>
+      <c r="LJ56" s="5"/>
+      <c r="LK56" s="5"/>
+      <c r="LL56" s="5"/>
+      <c r="LM56" s="5"/>
+      <c r="LN56" s="5"/>
+      <c r="LO56" s="5"/>
+      <c r="LP56" s="5"/>
+      <c r="LQ56" s="5"/>
+      <c r="LR56" s="5"/>
+      <c r="LS56" s="5"/>
+      <c r="LT56" s="5"/>
+      <c r="LU56" s="5"/>
+      <c r="LV56" s="5"/>
+      <c r="LW56" s="5"/>
+      <c r="LX56" s="5"/>
+      <c r="LY56" s="5"/>
+      <c r="LZ56" s="5"/>
+      <c r="MA56" s="5"/>
+      <c r="MB56" s="5"/>
+      <c r="MC56" s="5"/>
+      <c r="MD56" s="5"/>
+      <c r="ME56" s="5"/>
+      <c r="MF56" s="5"/>
+      <c r="MG56" s="5"/>
+      <c r="MH56" s="5"/>
+      <c r="MI56" s="5"/>
+      <c r="MJ56" s="5"/>
+      <c r="MK56" s="5"/>
+      <c r="ML56" s="5"/>
+      <c r="MM56" s="5"/>
+      <c r="MN56" s="5"/>
+      <c r="MO56" s="5"/>
+      <c r="MP56" s="5"/>
+      <c r="MQ56" s="5"/>
+      <c r="MR56" s="5"/>
+      <c r="MS56" s="5"/>
+      <c r="MT56" s="5"/>
+      <c r="MU56" s="5"/>
+      <c r="MV56" s="5"/>
+      <c r="MW56" s="5"/>
+      <c r="MX56" s="5"/>
+      <c r="MY56" s="5"/>
+      <c r="MZ56" s="5"/>
+      <c r="NA56" s="5"/>
+      <c r="NB56" s="5"/>
+      <c r="NC56" s="5"/>
+      <c r="ND56" s="5"/>
+      <c r="NE56" s="5"/>
+      <c r="NF56" s="5"/>
+      <c r="NG56" s="5"/>
+      <c r="NH56" s="5"/>
+      <c r="NI56" s="5"/>
+      <c r="NJ56" s="5"/>
+      <c r="NK56" s="5"/>
+      <c r="NL56" s="5"/>
+      <c r="NM56" s="5"/>
+      <c r="NN56" s="5"/>
+      <c r="NO56" s="5"/>
+      <c r="NP56" s="5"/>
+      <c r="NQ56" s="5"/>
+      <c r="NR56" s="5"/>
+      <c r="NS56" s="5"/>
+      <c r="NT56" s="5"/>
+      <c r="NU56" s="5"/>
+      <c r="NV56" s="5"/>
+      <c r="NW56" s="5"/>
+      <c r="NX56" s="5"/>
+      <c r="NY56" s="5"/>
+      <c r="NZ56" s="5"/>
+      <c r="OA56" s="5"/>
+      <c r="OB56" s="5"/>
+      <c r="OC56" s="5"/>
+      <c r="OD56" s="5"/>
+      <c r="OE56" s="5"/>
+      <c r="OF56" s="5"/>
+      <c r="OG56" s="5"/>
+      <c r="OH56" s="5"/>
+      <c r="OI56" s="5"/>
+      <c r="OJ56" s="5"/>
+      <c r="OK56" s="5"/>
+      <c r="OL56" s="5"/>
+      <c r="OM56" s="5"/>
+      <c r="ON56" s="5"/>
+      <c r="OO56" s="5"/>
+      <c r="OP56" s="5"/>
+      <c r="OQ56" s="5"/>
+      <c r="OR56" s="5"/>
+      <c r="OS56" s="5"/>
+      <c r="OT56" s="5"/>
+      <c r="OU56" s="5"/>
+      <c r="OV56" s="5"/>
+      <c r="OW56" s="5"/>
+      <c r="OX56" s="5"/>
+      <c r="OY56" s="5"/>
+      <c r="OZ56" s="5"/>
+      <c r="PA56" s="5"/>
+      <c r="PB56" s="5"/>
+      <c r="PC56" s="5"/>
+      <c r="PD56" s="5"/>
+      <c r="PE56" s="5"/>
+      <c r="PF56" s="5"/>
+      <c r="PG56" s="5"/>
+      <c r="PH56" s="5"/>
+      <c r="PI56" s="5"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="5"/>
+      <c r="K57" s="5"/>
+      <c r="L57" s="5"/>
+      <c r="M57" s="5"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="5"/>
+      <c r="P57" s="5"/>
+      <c r="Q57" s="5"/>
+      <c r="R57" s="5"/>
+      <c r="S57" s="5"/>
+      <c r="T57" s="5"/>
+      <c r="U57" s="5"/>
+      <c r="V57" s="5"/>
+      <c r="W57" s="5"/>
+      <c r="X57" s="5"/>
+      <c r="Y57" s="5"/>
+      <c r="Z57" s="5"/>
+      <c r="AA57" s="5"/>
+      <c r="AB57" s="5"/>
+      <c r="AC57" s="5"/>
+      <c r="AD57" s="5"/>
+      <c r="AE57" s="5"/>
+      <c r="AF57" s="5"/>
+      <c r="AG57" s="5"/>
+      <c r="AH57" s="5"/>
+      <c r="AI57" s="5"/>
+      <c r="AJ57" s="5"/>
+      <c r="AK57" s="5"/>
+      <c r="AL57" s="5"/>
+      <c r="AM57" s="5"/>
+      <c r="AN57" s="5"/>
+      <c r="AO57" s="5"/>
+      <c r="AP57" s="5"/>
+      <c r="AQ57" s="5"/>
+      <c r="AR57" s="5"/>
+      <c r="AS57" s="5"/>
+      <c r="AT57" s="5"/>
+      <c r="AU57" s="5"/>
+      <c r="AV57" s="5"/>
+      <c r="AW57" s="5"/>
+      <c r="AX57" s="5"/>
+      <c r="AY57" s="5"/>
+      <c r="AZ57" s="5"/>
+      <c r="BA57" s="5"/>
+      <c r="BB57" s="5"/>
+      <c r="BC57" s="5"/>
+      <c r="BD57" s="5"/>
+      <c r="BE57" s="5"/>
+      <c r="BF57" s="5"/>
+      <c r="BG57" s="5"/>
+      <c r="BH57" s="5"/>
+      <c r="BI57" s="5"/>
+      <c r="BJ57" s="5"/>
+      <c r="BK57" s="5"/>
+      <c r="BL57" s="5"/>
+      <c r="BM57" s="5"/>
+      <c r="BN57" s="5"/>
+      <c r="BO57" s="5"/>
+      <c r="BP57" s="5"/>
+      <c r="BQ57" s="5"/>
+      <c r="BR57" s="5"/>
+      <c r="BS57" s="5"/>
+      <c r="BT57" s="5"/>
+      <c r="BU57" s="5"/>
+      <c r="BV57" s="5"/>
+      <c r="BW57" s="5"/>
+      <c r="BX57" s="5"/>
+      <c r="BY57" s="5"/>
+      <c r="BZ57" s="5"/>
+      <c r="CA57" s="5"/>
+      <c r="CB57" s="5"/>
+      <c r="CC57" s="5"/>
+      <c r="CD57" s="5"/>
+      <c r="CE57" s="5"/>
+      <c r="CF57" s="5"/>
+      <c r="CG57" s="5"/>
+      <c r="CH57" s="5"/>
+      <c r="CI57" s="5"/>
+      <c r="CJ57" s="5"/>
+      <c r="CK57" s="5"/>
+      <c r="CL57" s="5"/>
+      <c r="CM57" s="5"/>
+      <c r="CN57" s="5"/>
+      <c r="CO57" s="5"/>
+      <c r="CP57" s="5"/>
+      <c r="CQ57" s="5"/>
+      <c r="CR57" s="5"/>
+      <c r="CS57" s="5"/>
+      <c r="CT57" s="5"/>
+      <c r="CU57" s="5"/>
+      <c r="CV57" s="5"/>
+      <c r="CW57" s="5"/>
+      <c r="CX57" s="5"/>
+      <c r="CY57" s="5"/>
+      <c r="CZ57" s="5"/>
+      <c r="DA57" s="5"/>
+      <c r="DB57" s="5"/>
+      <c r="DC57" s="5"/>
+      <c r="DD57" s="5"/>
+      <c r="DE57" s="5"/>
+      <c r="DF57" s="5"/>
+      <c r="DG57" s="5"/>
+      <c r="DH57" s="5"/>
+      <c r="DI57" s="5"/>
+      <c r="DJ57" s="5"/>
+      <c r="DK57" s="5"/>
+      <c r="DL57" s="5"/>
+      <c r="DM57" s="5"/>
+      <c r="DN57" s="5"/>
+      <c r="DO57" s="5"/>
+      <c r="DP57" s="5"/>
+      <c r="DQ57" s="5"/>
+      <c r="DR57" s="5"/>
+      <c r="DS57" s="5"/>
+      <c r="DT57" s="5"/>
+      <c r="DU57" s="5"/>
+      <c r="DV57" s="5"/>
+      <c r="DW57" s="5"/>
+      <c r="DX57" s="5"/>
+      <c r="DY57" s="5"/>
+      <c r="DZ57" s="5"/>
+      <c r="EA57" s="5"/>
+      <c r="EB57" s="5"/>
+      <c r="EC57" s="5"/>
+      <c r="ED57" s="5"/>
+      <c r="EE57" s="5"/>
+      <c r="EF57" s="5"/>
+      <c r="EG57" s="5"/>
+      <c r="EH57" s="5"/>
+      <c r="EI57" s="5"/>
+      <c r="EJ57" s="5"/>
+      <c r="EK57" s="5"/>
+      <c r="EL57" s="5"/>
+      <c r="EM57" s="5"/>
+      <c r="EN57" s="5"/>
+      <c r="EO57" s="5"/>
+      <c r="EP57" s="5"/>
+      <c r="EQ57" s="5"/>
+      <c r="ER57" s="5"/>
+      <c r="ES57" s="5"/>
+      <c r="ET57" s="5"/>
+      <c r="EU57" s="5"/>
+      <c r="EV57" s="5"/>
+      <c r="EW57" s="5"/>
+      <c r="EX57" s="5"/>
+      <c r="EY57" s="5"/>
+      <c r="EZ57" s="5"/>
+      <c r="FA57" s="5"/>
+      <c r="FB57" s="5"/>
+      <c r="FC57" s="5"/>
+      <c r="FD57" s="5"/>
+      <c r="FE57" s="5"/>
+      <c r="FF57" s="5"/>
+      <c r="FG57" s="5"/>
+      <c r="FH57" s="5"/>
+      <c r="FI57" s="5"/>
+      <c r="FJ57" s="5"/>
+      <c r="FK57" s="5"/>
+      <c r="FL57" s="5"/>
+      <c r="FM57" s="5"/>
+      <c r="FN57" s="5"/>
+      <c r="FO57" s="5"/>
+      <c r="FP57" s="5"/>
+      <c r="FQ57" s="5"/>
+      <c r="FR57" s="5"/>
+      <c r="FS57" s="5"/>
+      <c r="FT57" s="5"/>
+      <c r="FU57" s="5"/>
+      <c r="FV57" s="5"/>
+      <c r="FW57" s="5"/>
+      <c r="FX57" s="5"/>
+      <c r="FY57" s="5"/>
+      <c r="FZ57" s="5"/>
+      <c r="GA57" s="5"/>
+      <c r="GB57" s="5"/>
+      <c r="GC57" s="5"/>
+      <c r="GD57" s="5"/>
+      <c r="GE57" s="5"/>
+      <c r="GF57" s="5"/>
+      <c r="GG57" s="5"/>
+      <c r="GH57" s="5"/>
+      <c r="GI57" s="5"/>
+      <c r="GJ57" s="5"/>
+      <c r="GK57" s="5"/>
+      <c r="GL57" s="5"/>
+      <c r="GM57" s="5"/>
+      <c r="GN57" s="5"/>
+      <c r="GO57" s="5"/>
+      <c r="GP57" s="5"/>
+      <c r="GQ57" s="5"/>
+      <c r="GR57" s="5"/>
+      <c r="GS57" s="5"/>
+      <c r="GT57" s="5"/>
+      <c r="GU57" s="5"/>
+      <c r="GV57" s="5"/>
+      <c r="GW57" s="5"/>
+      <c r="GX57" s="5"/>
+      <c r="GY57" s="5"/>
+      <c r="GZ57" s="5"/>
+      <c r="HA57" s="5"/>
+      <c r="HB57" s="5"/>
+      <c r="HC57" s="5"/>
+      <c r="HD57" s="5"/>
+      <c r="HE57" s="5"/>
+      <c r="HF57" s="5"/>
+      <c r="HG57" s="5"/>
+      <c r="HH57" s="5"/>
+      <c r="HI57" s="5"/>
+      <c r="HJ57" s="5"/>
+      <c r="HK57" s="5"/>
+      <c r="HL57" s="5"/>
+      <c r="HM57" s="5"/>
+      <c r="HN57" s="5"/>
+      <c r="HO57" s="5"/>
+      <c r="HP57" s="5"/>
+      <c r="HQ57" s="5"/>
+      <c r="HR57" s="5"/>
+      <c r="HS57" s="5"/>
+      <c r="HT57" s="5"/>
+      <c r="HU57" s="5"/>
+      <c r="HV57" s="5"/>
+      <c r="HW57" s="5"/>
+      <c r="HX57" s="5"/>
+      <c r="HY57" s="5"/>
+      <c r="HZ57" s="5"/>
+      <c r="IA57" s="5"/>
+      <c r="IB57" s="5"/>
+      <c r="IC57" s="5"/>
+      <c r="ID57" s="5"/>
+      <c r="IE57" s="5"/>
+      <c r="IF57" s="5"/>
+      <c r="IG57" s="5"/>
+      <c r="IH57" s="5"/>
+      <c r="II57" s="5"/>
+      <c r="IJ57" s="5"/>
+      <c r="IK57" s="5"/>
+      <c r="IL57" s="5"/>
+      <c r="IM57" s="5"/>
+      <c r="IN57" s="5"/>
+      <c r="IO57" s="5"/>
+      <c r="IP57" s="5"/>
+      <c r="IQ57" s="5"/>
+      <c r="IR57" s="5"/>
+      <c r="IS57" s="5"/>
+      <c r="IT57" s="5"/>
+      <c r="IU57" s="5"/>
+      <c r="IV57" s="5"/>
+      <c r="IW57" s="5"/>
+      <c r="IX57" s="5"/>
+      <c r="IY57" s="5"/>
+      <c r="IZ57" s="5"/>
+      <c r="JA57" s="5"/>
+      <c r="JB57" s="5"/>
+      <c r="JC57" s="5"/>
+      <c r="JD57" s="5"/>
+      <c r="JE57" s="5"/>
+      <c r="JF57" s="5"/>
+      <c r="JG57" s="5"/>
+      <c r="JH57" s="5"/>
+      <c r="JI57" s="5"/>
+      <c r="JJ57" s="5"/>
+      <c r="JK57" s="5"/>
+      <c r="JL57" s="5"/>
+      <c r="JM57" s="5"/>
+      <c r="JN57" s="5"/>
+      <c r="JO57" s="5"/>
+      <c r="JP57" s="5"/>
+      <c r="JQ57" s="5"/>
+      <c r="JR57" s="5"/>
+      <c r="JS57" s="5"/>
+      <c r="JT57" s="5"/>
+      <c r="JU57" s="5"/>
+      <c r="JV57" s="5"/>
+      <c r="JW57" s="5"/>
+      <c r="JX57" s="5"/>
+      <c r="JY57" s="5"/>
+      <c r="JZ57" s="5"/>
+      <c r="KA57" s="5"/>
+      <c r="KB57" s="5"/>
+      <c r="KC57" s="5"/>
+      <c r="KD57" s="5"/>
+      <c r="KE57" s="5"/>
+      <c r="KF57" s="5"/>
+      <c r="KG57" s="5"/>
+      <c r="KH57" s="5"/>
+      <c r="KI57" s="5"/>
+      <c r="KJ57" s="5"/>
+      <c r="KK57" s="5"/>
+      <c r="KL57" s="5"/>
+      <c r="KM57" s="5"/>
+      <c r="KN57" s="5"/>
+      <c r="KO57" s="5"/>
+      <c r="KP57" s="5"/>
+      <c r="KQ57" s="5"/>
+      <c r="KR57" s="5"/>
+      <c r="KS57" s="5"/>
+      <c r="KT57" s="5"/>
+      <c r="KU57" s="5"/>
+      <c r="KV57" s="5"/>
+      <c r="KW57" s="5"/>
+      <c r="KX57" s="5"/>
+      <c r="KY57" s="5"/>
+      <c r="KZ57" s="5"/>
+      <c r="LA57" s="5"/>
+      <c r="LB57" s="5"/>
+      <c r="LC57" s="5"/>
+      <c r="LD57" s="5"/>
+      <c r="LE57" s="5"/>
+      <c r="LF57" s="5"/>
+      <c r="LG57" s="5"/>
+      <c r="LH57" s="5"/>
+      <c r="LI57" s="5"/>
+      <c r="LJ57" s="5"/>
+      <c r="LK57" s="5"/>
+      <c r="LL57" s="5"/>
+      <c r="LM57" s="5"/>
+      <c r="LN57" s="5"/>
+      <c r="LO57" s="5"/>
+      <c r="LP57" s="5"/>
+      <c r="LQ57" s="5"/>
+      <c r="LR57" s="5"/>
+      <c r="LS57" s="5"/>
+      <c r="LT57" s="5"/>
+      <c r="LU57" s="5"/>
+      <c r="LV57" s="5"/>
+      <c r="LW57" s="5"/>
+      <c r="LX57" s="5"/>
+      <c r="LY57" s="5"/>
+      <c r="LZ57" s="5"/>
+      <c r="MA57" s="5"/>
+      <c r="MB57" s="5"/>
+      <c r="MC57" s="5"/>
+      <c r="MD57" s="5"/>
+      <c r="ME57" s="5"/>
+      <c r="MF57" s="5"/>
+      <c r="MG57" s="5"/>
+      <c r="MH57" s="5"/>
+      <c r="MI57" s="5"/>
+      <c r="MJ57" s="5"/>
+      <c r="MK57" s="5"/>
+      <c r="ML57" s="5"/>
+      <c r="MM57" s="5"/>
+      <c r="MN57" s="5"/>
+      <c r="MO57" s="5"/>
+      <c r="MP57" s="5"/>
+      <c r="MQ57" s="5"/>
+      <c r="MR57" s="5"/>
+      <c r="MS57" s="5"/>
+      <c r="MT57" s="5"/>
+      <c r="MU57" s="5"/>
+      <c r="MV57" s="5"/>
+      <c r="MW57" s="5"/>
+      <c r="MX57" s="5"/>
+      <c r="MY57" s="5"/>
+      <c r="MZ57" s="5"/>
+      <c r="NA57" s="5"/>
+      <c r="NB57" s="5"/>
+      <c r="NC57" s="5"/>
+      <c r="ND57" s="5"/>
+      <c r="NE57" s="5"/>
+      <c r="NF57" s="5"/>
+      <c r="NG57" s="5"/>
+      <c r="NH57" s="5"/>
+      <c r="NI57" s="5"/>
+      <c r="NJ57" s="5"/>
+      <c r="NK57" s="5"/>
+      <c r="NL57" s="5"/>
+      <c r="NM57" s="5"/>
+      <c r="NN57" s="5"/>
+      <c r="NO57" s="5"/>
+      <c r="NP57" s="5"/>
+      <c r="NQ57" s="5"/>
+      <c r="NR57" s="5"/>
+      <c r="NS57" s="5"/>
+      <c r="NT57" s="5"/>
+      <c r="NU57" s="5"/>
+      <c r="NV57" s="5"/>
+      <c r="NW57" s="5"/>
+      <c r="NX57" s="5"/>
+      <c r="NY57" s="5"/>
+      <c r="NZ57" s="5"/>
+      <c r="OA57" s="5"/>
+      <c r="OB57" s="5"/>
+      <c r="OC57" s="5"/>
+      <c r="OD57" s="5"/>
+      <c r="OE57" s="5"/>
+      <c r="OF57" s="5"/>
+      <c r="OG57" s="5"/>
+      <c r="OH57" s="5"/>
+      <c r="OI57" s="5"/>
+      <c r="OJ57" s="5"/>
+      <c r="OK57" s="5"/>
+      <c r="OL57" s="5"/>
+      <c r="OM57" s="5"/>
+      <c r="ON57" s="5"/>
+      <c r="OO57" s="5"/>
+      <c r="OP57" s="5"/>
+      <c r="OQ57" s="5"/>
+      <c r="OR57" s="5"/>
+      <c r="OS57" s="5"/>
+      <c r="OT57" s="5"/>
+      <c r="OU57" s="5"/>
+      <c r="OV57" s="5"/>
+      <c r="OW57" s="5"/>
+      <c r="OX57" s="5"/>
+      <c r="OY57" s="5"/>
+      <c r="OZ57" s="5"/>
+      <c r="PA57" s="5"/>
+      <c r="PB57" s="5"/>
+      <c r="PC57" s="5"/>
+      <c r="PD57" s="5"/>
+      <c r="PE57" s="5"/>
+      <c r="PF57" s="5"/>
+      <c r="PG57" s="5"/>
+      <c r="PH57" s="5"/>
+      <c r="PI57" s="5"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5"/>
+      <c r="J58" s="5"/>
+      <c r="K58" s="5"/>
+      <c r="L58" s="5"/>
+      <c r="M58" s="5"/>
+      <c r="N58" s="5"/>
+      <c r="O58" s="5"/>
+      <c r="P58" s="5"/>
+      <c r="Q58" s="5"/>
+      <c r="R58" s="5"/>
+      <c r="S58" s="5"/>
+      <c r="T58" s="5"/>
+      <c r="U58" s="5"/>
+      <c r="V58" s="5"/>
+      <c r="W58" s="5"/>
+      <c r="X58" s="5"/>
+      <c r="Y58" s="5"/>
+      <c r="Z58" s="5"/>
+      <c r="AA58" s="5"/>
+      <c r="AB58" s="5"/>
+      <c r="AC58" s="5"/>
+      <c r="AD58" s="5"/>
+      <c r="AE58" s="5"/>
+      <c r="AF58" s="5"/>
+      <c r="AG58" s="5"/>
+      <c r="AH58" s="5"/>
+      <c r="AI58" s="5"/>
+      <c r="AJ58" s="5"/>
+      <c r="AK58" s="5"/>
+      <c r="AL58" s="5"/>
+      <c r="AM58" s="5"/>
+      <c r="AN58" s="5"/>
+      <c r="AO58" s="5"/>
+      <c r="AP58" s="5"/>
+      <c r="AQ58" s="5"/>
+      <c r="AR58" s="5"/>
+      <c r="AS58" s="5"/>
+      <c r="AT58" s="5"/>
+      <c r="AU58" s="5"/>
+      <c r="AV58" s="5"/>
+      <c r="AW58" s="5"/>
+      <c r="AX58" s="5"/>
+      <c r="AY58" s="5"/>
+      <c r="AZ58" s="5"/>
+      <c r="BA58" s="5"/>
+      <c r="BB58" s="5"/>
+      <c r="BC58" s="5"/>
+      <c r="BD58" s="5"/>
+      <c r="BE58" s="5"/>
+      <c r="BF58" s="5"/>
+      <c r="BG58" s="5"/>
+      <c r="BH58" s="5"/>
+      <c r="BI58" s="5"/>
+      <c r="BJ58" s="5"/>
+      <c r="BK58" s="5"/>
+      <c r="BL58" s="5"/>
+      <c r="BM58" s="5"/>
+      <c r="BN58" s="5"/>
+      <c r="BO58" s="5"/>
+      <c r="BP58" s="5"/>
+      <c r="BQ58" s="5"/>
+      <c r="BR58" s="5"/>
+      <c r="BS58" s="5"/>
+      <c r="BT58" s="5"/>
+      <c r="BU58" s="5"/>
+      <c r="BV58" s="5"/>
+      <c r="BW58" s="5"/>
+      <c r="BX58" s="5"/>
+      <c r="BY58" s="5"/>
+      <c r="BZ58" s="5"/>
+      <c r="CA58" s="5"/>
+      <c r="CB58" s="5"/>
+      <c r="CC58" s="5"/>
+      <c r="CD58" s="5"/>
+      <c r="CE58" s="5"/>
+      <c r="CF58" s="5"/>
+      <c r="CG58" s="5"/>
+      <c r="CH58" s="5"/>
+      <c r="CI58" s="5"/>
+      <c r="CJ58" s="5"/>
+      <c r="CK58" s="5"/>
+      <c r="CL58" s="5"/>
+      <c r="CM58" s="5"/>
+      <c r="CN58" s="5"/>
+      <c r="CO58" s="5"/>
+      <c r="CP58" s="5"/>
+      <c r="CQ58" s="5"/>
+      <c r="CR58" s="5"/>
+      <c r="CS58" s="5"/>
+      <c r="CT58" s="5"/>
+      <c r="CU58" s="5"/>
+      <c r="CV58" s="5"/>
+      <c r="CW58" s="5"/>
+      <c r="CX58" s="5"/>
+      <c r="CY58" s="5"/>
+      <c r="CZ58" s="5"/>
+      <c r="DA58" s="5"/>
+      <c r="DB58" s="5"/>
+      <c r="DC58" s="5"/>
+      <c r="DD58" s="5"/>
+      <c r="DE58" s="5"/>
+      <c r="DF58" s="5"/>
+      <c r="DG58" s="5"/>
+      <c r="DH58" s="5"/>
+      <c r="DI58" s="5"/>
+      <c r="DJ58" s="5"/>
+      <c r="DK58" s="5"/>
+      <c r="DL58" s="5"/>
+      <c r="DM58" s="5"/>
+      <c r="DN58" s="5"/>
+      <c r="DO58" s="5"/>
+      <c r="DP58" s="5"/>
+      <c r="DQ58" s="5"/>
+      <c r="DR58" s="5"/>
+      <c r="DS58" s="5"/>
+      <c r="DT58" s="5"/>
+      <c r="DU58" s="5"/>
+      <c r="DV58" s="5"/>
+      <c r="DW58" s="5"/>
+      <c r="DX58" s="5"/>
+      <c r="DY58" s="5"/>
+      <c r="DZ58" s="5"/>
+      <c r="EA58" s="5"/>
+      <c r="EB58" s="5"/>
+      <c r="EC58" s="5"/>
+      <c r="ED58" s="5"/>
+      <c r="EE58" s="5"/>
+      <c r="EF58" s="5"/>
+      <c r="EG58" s="5"/>
+      <c r="EH58" s="5"/>
+      <c r="EI58" s="5"/>
+      <c r="EJ58" s="5"/>
+      <c r="EK58" s="5"/>
+      <c r="EL58" s="5"/>
+      <c r="EM58" s="5"/>
+      <c r="EN58" s="5"/>
+      <c r="EO58" s="5"/>
+      <c r="EP58" s="5"/>
+      <c r="EQ58" s="5"/>
+      <c r="ER58" s="5"/>
+      <c r="ES58" s="5"/>
+      <c r="ET58" s="5"/>
+      <c r="EU58" s="5"/>
+      <c r="EV58" s="5"/>
+      <c r="EW58" s="5"/>
+      <c r="EX58" s="5"/>
+      <c r="EY58" s="5"/>
+      <c r="EZ58" s="5"/>
+      <c r="FA58" s="5"/>
+      <c r="FB58" s="5"/>
+      <c r="FC58" s="5"/>
+      <c r="FD58" s="5"/>
+      <c r="FE58" s="5"/>
+      <c r="FF58" s="5"/>
+      <c r="FG58" s="5"/>
+      <c r="FH58" s="5"/>
+      <c r="FI58" s="5"/>
+      <c r="FJ58" s="5"/>
+      <c r="FK58" s="5"/>
+      <c r="FL58" s="5"/>
+      <c r="FM58" s="5"/>
+      <c r="FN58" s="5"/>
+      <c r="FO58" s="5"/>
+      <c r="FP58" s="5"/>
+      <c r="FQ58" s="5"/>
+      <c r="FR58" s="5"/>
+      <c r="FS58" s="5"/>
+      <c r="FT58" s="5"/>
+      <c r="FU58" s="5"/>
+      <c r="FV58" s="5"/>
+      <c r="FW58" s="5"/>
+      <c r="FX58" s="5"/>
+      <c r="FY58" s="5"/>
+      <c r="FZ58" s="5"/>
+      <c r="GA58" s="5"/>
+      <c r="GB58" s="5"/>
+      <c r="GC58" s="5"/>
+      <c r="GD58" s="5"/>
+      <c r="GE58" s="5"/>
+      <c r="GF58" s="5"/>
+      <c r="GG58" s="5"/>
+      <c r="GH58" s="5"/>
+      <c r="GI58" s="5"/>
+      <c r="GJ58" s="5"/>
+      <c r="GK58" s="5"/>
+      <c r="GL58" s="5"/>
+      <c r="GM58" s="5"/>
+      <c r="GN58" s="5"/>
+      <c r="GO58" s="5"/>
+      <c r="GP58" s="5"/>
+      <c r="GQ58" s="5"/>
+      <c r="GR58" s="5"/>
+      <c r="GS58" s="5"/>
+      <c r="GT58" s="5"/>
+      <c r="GU58" s="5"/>
+      <c r="GV58" s="5"/>
+      <c r="GW58" s="5"/>
+      <c r="GX58" s="5"/>
+      <c r="GY58" s="5"/>
+      <c r="GZ58" s="5"/>
+      <c r="HA58" s="5"/>
+      <c r="HB58" s="5"/>
+      <c r="HC58" s="5"/>
+      <c r="HD58" s="5"/>
+      <c r="HE58" s="5"/>
+      <c r="HF58" s="5"/>
+      <c r="HG58" s="5"/>
+      <c r="HH58" s="5"/>
+      <c r="HI58" s="5"/>
+      <c r="HJ58" s="5"/>
+      <c r="HK58" s="5"/>
+      <c r="HL58" s="5"/>
+      <c r="HM58" s="5"/>
+      <c r="HN58" s="5"/>
+      <c r="HO58" s="5"/>
+      <c r="HP58" s="5"/>
+      <c r="HQ58" s="5"/>
+      <c r="HR58" s="5"/>
+      <c r="HS58" s="5"/>
+      <c r="HT58" s="5"/>
+      <c r="HU58" s="5"/>
+      <c r="HV58" s="5"/>
+      <c r="HW58" s="5"/>
+      <c r="HX58" s="5"/>
+      <c r="HY58" s="5"/>
+      <c r="HZ58" s="5"/>
+      <c r="IA58" s="5"/>
+      <c r="IB58" s="5"/>
+      <c r="IC58" s="5"/>
+      <c r="ID58" s="5"/>
+      <c r="IE58" s="5"/>
+      <c r="IF58" s="5"/>
+      <c r="IG58" s="5"/>
+      <c r="IH58" s="5"/>
+      <c r="II58" s="5"/>
+      <c r="IJ58" s="5"/>
+      <c r="IK58" s="5"/>
+      <c r="IL58" s="5"/>
+      <c r="IM58" s="5"/>
+      <c r="IN58" s="5"/>
+      <c r="IO58" s="5"/>
+      <c r="IP58" s="5"/>
+      <c r="IQ58" s="5"/>
+      <c r="IR58" s="5"/>
+      <c r="IS58" s="5"/>
+      <c r="IT58" s="5"/>
+      <c r="IU58" s="5"/>
+      <c r="IV58" s="5"/>
+      <c r="IW58" s="5"/>
+      <c r="IX58" s="5"/>
+      <c r="IY58" s="5"/>
+      <c r="IZ58" s="5"/>
+      <c r="JA58" s="5"/>
+      <c r="JB58" s="5"/>
+      <c r="JC58" s="5"/>
+      <c r="JD58" s="5"/>
+      <c r="JE58" s="5"/>
+      <c r="JF58" s="5"/>
+      <c r="JG58" s="5"/>
+      <c r="JH58" s="5"/>
+      <c r="JI58" s="5"/>
+      <c r="JJ58" s="5"/>
+      <c r="JK58" s="5"/>
+      <c r="JL58" s="5"/>
+      <c r="JM58" s="5"/>
+      <c r="JN58" s="5"/>
+      <c r="JO58" s="5"/>
+      <c r="JP58" s="5"/>
+      <c r="JQ58" s="5"/>
+      <c r="JR58" s="5"/>
+      <c r="JS58" s="5"/>
+      <c r="JT58" s="5"/>
+      <c r="JU58" s="5"/>
+      <c r="JV58" s="5"/>
+      <c r="JW58" s="5"/>
+      <c r="JX58" s="5"/>
+      <c r="JY58" s="5"/>
+      <c r="JZ58" s="5"/>
+      <c r="KA58" s="5"/>
+      <c r="KB58" s="5"/>
+      <c r="KC58" s="5"/>
+      <c r="KD58" s="5"/>
+      <c r="KE58" s="5"/>
+      <c r="KF58" s="5"/>
+      <c r="KG58" s="5"/>
+      <c r="KH58" s="5"/>
+      <c r="KI58" s="5"/>
+      <c r="KJ58" s="5"/>
+      <c r="KK58" s="5"/>
+      <c r="KL58" s="5"/>
+      <c r="KM58" s="5"/>
+      <c r="KN58" s="5"/>
+      <c r="KO58" s="5"/>
+      <c r="KP58" s="5"/>
+      <c r="KQ58" s="5"/>
+      <c r="KR58" s="5"/>
+      <c r="KS58" s="5"/>
+      <c r="KT58" s="5"/>
+      <c r="KU58" s="5"/>
+      <c r="KV58" s="5"/>
+      <c r="KW58" s="5"/>
+      <c r="KX58" s="5"/>
+      <c r="KY58" s="5"/>
+      <c r="KZ58" s="5"/>
+      <c r="LA58" s="5"/>
+      <c r="LB58" s="5"/>
+      <c r="LC58" s="5"/>
+      <c r="LD58" s="5"/>
+      <c r="LE58" s="5"/>
+      <c r="LF58" s="5"/>
+      <c r="LG58" s="5"/>
+      <c r="LH58" s="5"/>
+      <c r="LI58" s="5"/>
+      <c r="LJ58" s="5"/>
+      <c r="LK58" s="5"/>
+      <c r="LL58" s="5"/>
+      <c r="LM58" s="5"/>
+      <c r="LN58" s="5"/>
+      <c r="LO58" s="5"/>
+      <c r="LP58" s="5"/>
+      <c r="LQ58" s="5"/>
+      <c r="LR58" s="5"/>
+      <c r="LS58" s="5"/>
+      <c r="LT58" s="5"/>
+      <c r="LU58" s="5"/>
+      <c r="LV58" s="5"/>
+      <c r="LW58" s="5"/>
+      <c r="LX58" s="5"/>
+      <c r="LY58" s="5"/>
+      <c r="LZ58" s="5"/>
+      <c r="MA58" s="5"/>
+      <c r="MB58" s="5"/>
+      <c r="MC58" s="5"/>
+      <c r="MD58" s="5"/>
+      <c r="ME58" s="5"/>
+      <c r="MF58" s="5"/>
+      <c r="MG58" s="5"/>
+      <c r="MH58" s="5"/>
+      <c r="MI58" s="5"/>
+      <c r="MJ58" s="5"/>
+      <c r="MK58" s="5"/>
+      <c r="ML58" s="5"/>
+      <c r="MM58" s="5"/>
+      <c r="MN58" s="5"/>
+      <c r="MO58" s="5"/>
+      <c r="MP58" s="5"/>
+      <c r="MQ58" s="5"/>
+      <c r="MR58" s="5"/>
+      <c r="MS58" s="5"/>
+      <c r="MT58" s="5"/>
+      <c r="MU58" s="5"/>
+      <c r="MV58" s="5"/>
+      <c r="MW58" s="5"/>
+      <c r="MX58" s="5"/>
+      <c r="MY58" s="5"/>
+      <c r="MZ58" s="5"/>
+      <c r="NA58" s="5"/>
+      <c r="NB58" s="5"/>
+      <c r="NC58" s="5"/>
+      <c r="ND58" s="5"/>
+      <c r="NE58" s="5"/>
+      <c r="NF58" s="5"/>
+      <c r="NG58" s="5"/>
+      <c r="NH58" s="5"/>
+      <c r="NI58" s="5"/>
+      <c r="NJ58" s="5"/>
+      <c r="NK58" s="5"/>
+      <c r="NL58" s="5"/>
+      <c r="NM58" s="5"/>
+      <c r="NN58" s="5"/>
+      <c r="NO58" s="5"/>
+      <c r="NP58" s="5"/>
+      <c r="NQ58" s="5"/>
+      <c r="NR58" s="5"/>
+      <c r="NS58" s="5"/>
+      <c r="NT58" s="5"/>
+      <c r="NU58" s="5"/>
+      <c r="NV58" s="5"/>
+      <c r="NW58" s="5"/>
+      <c r="NX58" s="5"/>
+      <c r="NY58" s="5"/>
+      <c r="NZ58" s="5"/>
+      <c r="OA58" s="5"/>
+      <c r="OB58" s="5"/>
+      <c r="OC58" s="5"/>
+      <c r="OD58" s="5"/>
+      <c r="OE58" s="5"/>
+      <c r="OF58" s="5"/>
+      <c r="OG58" s="5"/>
+      <c r="OH58" s="5"/>
+      <c r="OI58" s="5"/>
+      <c r="OJ58" s="5"/>
+      <c r="OK58" s="5"/>
+      <c r="OL58" s="5"/>
+      <c r="OM58" s="5"/>
+      <c r="ON58" s="5"/>
+      <c r="OO58" s="5"/>
+      <c r="OP58" s="5"/>
+      <c r="OQ58" s="5"/>
+      <c r="OR58" s="5"/>
+      <c r="OS58" s="5"/>
+      <c r="OT58" s="5"/>
+      <c r="OU58" s="5"/>
+      <c r="OV58" s="5"/>
+      <c r="OW58" s="5"/>
+      <c r="OX58" s="5"/>
+      <c r="OY58" s="5"/>
+      <c r="OZ58" s="5"/>
+      <c r="PA58" s="5"/>
+      <c r="PB58" s="5"/>
+      <c r="PC58" s="5"/>
+      <c r="PD58" s="5"/>
+      <c r="PE58" s="5"/>
+      <c r="PF58" s="5"/>
+      <c r="PG58" s="5"/>
+      <c r="PH58" s="5"/>
+      <c r="PI58" s="5"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5"/>
+      <c r="J59" s="5"/>
+      <c r="K59" s="5"/>
+      <c r="L59" s="5"/>
+      <c r="M59" s="5"/>
+      <c r="N59" s="5"/>
+      <c r="O59" s="5"/>
+      <c r="P59" s="5"/>
+      <c r="Q59" s="5"/>
+      <c r="R59" s="5"/>
+      <c r="S59" s="5"/>
+      <c r="T59" s="5"/>
+      <c r="U59" s="5"/>
+      <c r="V59" s="5"/>
+      <c r="W59" s="5"/>
+      <c r="X59" s="5"/>
+      <c r="Y59" s="5"/>
+      <c r="Z59" s="5"/>
+      <c r="AA59" s="5"/>
+      <c r="AB59" s="5"/>
+      <c r="AC59" s="5"/>
+      <c r="AD59" s="5"/>
+      <c r="AE59" s="5"/>
+      <c r="AF59" s="5"/>
+      <c r="AG59" s="5"/>
+      <c r="AH59" s="5"/>
+      <c r="AI59" s="5"/>
+      <c r="AJ59" s="5"/>
+      <c r="AK59" s="5"/>
+      <c r="AL59" s="5"/>
+      <c r="AM59" s="5"/>
+      <c r="AN59" s="5"/>
+      <c r="AO59" s="5"/>
+      <c r="AP59" s="5"/>
+      <c r="AQ59" s="5"/>
+      <c r="AR59" s="5"/>
+      <c r="AS59" s="5"/>
+      <c r="AT59" s="5"/>
+      <c r="AU59" s="5"/>
+      <c r="AV59" s="5"/>
+      <c r="AW59" s="5"/>
+      <c r="AX59" s="5"/>
+      <c r="AY59" s="5"/>
+      <c r="AZ59" s="5"/>
+      <c r="BA59" s="5"/>
+      <c r="BB59" s="5"/>
+      <c r="BC59" s="5"/>
+      <c r="BD59" s="5"/>
+      <c r="BE59" s="5"/>
+      <c r="BF59" s="5"/>
+      <c r="BG59" s="5"/>
+      <c r="BH59" s="5"/>
+      <c r="BI59" s="5"/>
+      <c r="BJ59" s="5"/>
+      <c r="BK59" s="5"/>
+      <c r="BL59" s="5"/>
+      <c r="BM59" s="5"/>
+      <c r="BN59" s="5"/>
+      <c r="BO59" s="5"/>
+      <c r="BP59" s="5"/>
+      <c r="BQ59" s="5"/>
+      <c r="BR59" s="5"/>
+      <c r="BS59" s="5"/>
+      <c r="BT59" s="5"/>
+      <c r="BU59" s="5"/>
+      <c r="BV59" s="5"/>
+      <c r="BW59" s="5"/>
+      <c r="BX59" s="5"/>
+      <c r="BY59" s="5"/>
+      <c r="BZ59" s="5"/>
+      <c r="CA59" s="5"/>
+      <c r="CB59" s="5"/>
+      <c r="CC59" s="5"/>
+      <c r="CD59" s="5"/>
+      <c r="CE59" s="5"/>
+      <c r="CF59" s="5"/>
+      <c r="CG59" s="5"/>
+      <c r="CH59" s="5"/>
+      <c r="CI59" s="5"/>
+      <c r="CJ59" s="5"/>
+      <c r="CK59" s="5"/>
+      <c r="CL59" s="5"/>
+      <c r="CM59" s="5"/>
+      <c r="CN59" s="5"/>
+      <c r="CO59" s="5"/>
+      <c r="CP59" s="5"/>
+      <c r="CQ59" s="5"/>
+      <c r="CR59" s="5"/>
+      <c r="CS59" s="5"/>
+      <c r="CT59" s="5"/>
+      <c r="CU59" s="5"/>
+      <c r="CV59" s="5"/>
+      <c r="CW59" s="5"/>
+      <c r="CX59" s="5"/>
+      <c r="CY59" s="5"/>
+      <c r="CZ59" s="5"/>
+      <c r="DA59" s="5"/>
+      <c r="DB59" s="5"/>
+      <c r="DC59" s="5"/>
+      <c r="DD59" s="5"/>
+      <c r="DE59" s="5"/>
+      <c r="DF59" s="5"/>
+      <c r="DG59" s="5"/>
+      <c r="DH59" s="5"/>
+      <c r="DI59" s="5"/>
+      <c r="DJ59" s="5"/>
+      <c r="DK59" s="5"/>
+      <c r="DL59" s="5"/>
+      <c r="DM59" s="5"/>
+      <c r="DN59" s="5"/>
+      <c r="DO59" s="5"/>
+      <c r="DP59" s="5"/>
+      <c r="DQ59" s="5"/>
+      <c r="DR59" s="5"/>
+      <c r="DS59" s="5"/>
+      <c r="DT59" s="5"/>
+      <c r="DU59" s="5"/>
+      <c r="DV59" s="5"/>
+      <c r="DW59" s="5"/>
+      <c r="DX59" s="5"/>
+      <c r="DY59" s="5"/>
+      <c r="DZ59" s="5"/>
+      <c r="EA59" s="5"/>
+      <c r="EB59" s="5"/>
+      <c r="EC59" s="5"/>
+      <c r="ED59" s="5"/>
+      <c r="EE59" s="5"/>
+      <c r="EF59" s="5"/>
+      <c r="EG59" s="5"/>
+      <c r="EH59" s="5"/>
+      <c r="EI59" s="5"/>
+      <c r="EJ59" s="5"/>
+      <c r="EK59" s="5"/>
+      <c r="EL59" s="5"/>
+      <c r="EM59" s="5"/>
+      <c r="EN59" s="5"/>
+      <c r="EO59" s="5"/>
+      <c r="EP59" s="5"/>
+      <c r="EQ59" s="5"/>
+      <c r="ER59" s="5"/>
+      <c r="ES59" s="5"/>
+      <c r="ET59" s="5"/>
+      <c r="EU59" s="5"/>
+      <c r="EV59" s="5"/>
+      <c r="EW59" s="5"/>
+      <c r="EX59" s="5"/>
+      <c r="EY59" s="5"/>
+      <c r="EZ59" s="5"/>
+      <c r="FA59" s="5"/>
+      <c r="FB59" s="5"/>
+      <c r="FC59" s="5"/>
+      <c r="FD59" s="5"/>
+      <c r="FE59" s="5"/>
+      <c r="FF59" s="5"/>
+      <c r="FG59" s="5"/>
+      <c r="FH59" s="5"/>
+      <c r="FI59" s="5"/>
+      <c r="FJ59" s="5"/>
+      <c r="FK59" s="5"/>
+      <c r="FL59" s="5"/>
+      <c r="FM59" s="5"/>
+      <c r="FN59" s="5"/>
+      <c r="FO59" s="5"/>
+      <c r="FP59" s="5"/>
+      <c r="FQ59" s="5"/>
+      <c r="FR59" s="5"/>
+      <c r="FS59" s="5"/>
+      <c r="FT59" s="5"/>
+      <c r="FU59" s="5"/>
+      <c r="FV59" s="5"/>
+      <c r="FW59" s="5"/>
+      <c r="FX59" s="5"/>
+      <c r="FY59" s="5"/>
+      <c r="FZ59" s="5"/>
+      <c r="GA59" s="5"/>
+      <c r="GB59" s="5"/>
+      <c r="GC59" s="5"/>
+      <c r="GD59" s="5"/>
+      <c r="GE59" s="5"/>
+      <c r="GF59" s="5"/>
+      <c r="GG59" s="5"/>
+      <c r="GH59" s="5"/>
+      <c r="GI59" s="5"/>
+      <c r="GJ59" s="5"/>
+      <c r="GK59" s="5"/>
+      <c r="GL59" s="5"/>
+      <c r="GM59" s="5"/>
+      <c r="GN59" s="5"/>
+      <c r="GO59" s="5"/>
+      <c r="GP59" s="5"/>
+      <c r="GQ59" s="5"/>
+      <c r="GR59" s="5"/>
+      <c r="GS59" s="5"/>
+      <c r="GT59" s="5"/>
+      <c r="GU59" s="5"/>
+      <c r="GV59" s="5"/>
+      <c r="GW59" s="5"/>
+      <c r="GX59" s="5"/>
+      <c r="GY59" s="5"/>
+      <c r="GZ59" s="5"/>
+      <c r="HA59" s="5"/>
+      <c r="HB59" s="5"/>
+      <c r="HC59" s="5"/>
+      <c r="HD59" s="5"/>
+      <c r="HE59" s="5"/>
+      <c r="HF59" s="5"/>
+      <c r="HG59" s="5"/>
+      <c r="HH59" s="5"/>
+      <c r="HI59" s="5"/>
+      <c r="HJ59" s="5"/>
+      <c r="HK59" s="5"/>
+      <c r="HL59" s="5"/>
+      <c r="HM59" s="5"/>
+      <c r="HN59" s="5"/>
+      <c r="HO59" s="5"/>
+      <c r="HP59" s="5"/>
+      <c r="HQ59" s="5"/>
+      <c r="HR59" s="5"/>
+      <c r="HS59" s="5"/>
+      <c r="HT59" s="5"/>
+      <c r="HU59" s="5"/>
+      <c r="HV59" s="5"/>
+      <c r="HW59" s="5"/>
+      <c r="HX59" s="5"/>
+      <c r="HY59" s="5"/>
+      <c r="HZ59" s="5"/>
+      <c r="IA59" s="5"/>
+      <c r="IB59" s="5"/>
+      <c r="IC59" s="5"/>
+      <c r="ID59" s="5"/>
+      <c r="IE59" s="5"/>
+      <c r="IF59" s="5"/>
+      <c r="IG59" s="5"/>
+      <c r="IH59" s="5"/>
+      <c r="II59" s="5"/>
+      <c r="IJ59" s="5"/>
+      <c r="IK59" s="5"/>
+      <c r="IL59" s="5"/>
+      <c r="IM59" s="5"/>
+      <c r="IN59" s="5"/>
+      <c r="IO59" s="5"/>
+      <c r="IP59" s="5"/>
+      <c r="IQ59" s="5"/>
+      <c r="IR59" s="5"/>
+      <c r="IS59" s="5"/>
+      <c r="IT59" s="5"/>
+      <c r="IU59" s="5"/>
+      <c r="IV59" s="5"/>
+      <c r="IW59" s="5"/>
+      <c r="IX59" s="5"/>
+      <c r="IY59" s="5"/>
+      <c r="IZ59" s="5"/>
+      <c r="JA59" s="5"/>
+      <c r="JB59" s="5"/>
+      <c r="JC59" s="5"/>
+      <c r="JD59" s="5"/>
+      <c r="JE59" s="5"/>
+      <c r="JF59" s="5"/>
+      <c r="JG59" s="5"/>
+      <c r="JH59" s="5"/>
+      <c r="JI59" s="5"/>
+      <c r="JJ59" s="5"/>
+      <c r="JK59" s="5"/>
+      <c r="JL59" s="5"/>
+      <c r="JM59" s="5"/>
+      <c r="JN59" s="5"/>
+      <c r="JO59" s="5"/>
+      <c r="JP59" s="5"/>
+      <c r="JQ59" s="5"/>
+      <c r="JR59" s="5"/>
+      <c r="JS59" s="5"/>
+      <c r="JT59" s="5"/>
+      <c r="JU59" s="5"/>
+      <c r="JV59" s="5"/>
+      <c r="JW59" s="5"/>
+      <c r="JX59" s="5"/>
+      <c r="JY59" s="5"/>
+      <c r="JZ59" s="5"/>
+      <c r="KA59" s="5"/>
+      <c r="KB59" s="5"/>
+      <c r="KC59" s="5"/>
+      <c r="KD59" s="5"/>
+      <c r="KE59" s="5"/>
+      <c r="KF59" s="5"/>
+      <c r="KG59" s="5"/>
+      <c r="KH59" s="5"/>
+      <c r="KI59" s="5"/>
+      <c r="KJ59" s="5"/>
+      <c r="KK59" s="5"/>
+      <c r="KL59" s="5"/>
+      <c r="KM59" s="5"/>
+      <c r="KN59" s="5"/>
+      <c r="KO59" s="5"/>
+      <c r="KP59" s="5"/>
+      <c r="KQ59" s="5"/>
+      <c r="KR59" s="5"/>
+      <c r="KS59" s="5"/>
+      <c r="KT59" s="5"/>
+      <c r="KU59" s="5"/>
+      <c r="KV59" s="5"/>
+      <c r="KW59" s="5"/>
+      <c r="KX59" s="5"/>
+      <c r="KY59" s="5"/>
+      <c r="KZ59" s="5"/>
+      <c r="LA59" s="5"/>
+      <c r="LB59" s="5"/>
+      <c r="LC59" s="5"/>
+      <c r="LD59" s="5"/>
+      <c r="LE59" s="5"/>
+      <c r="LF59" s="5"/>
+      <c r="LG59" s="5"/>
+      <c r="LH59" s="5"/>
+      <c r="LI59" s="5"/>
+      <c r="LJ59" s="5"/>
+      <c r="LK59" s="5"/>
+      <c r="LL59" s="5"/>
+      <c r="LM59" s="5"/>
+      <c r="LN59" s="5"/>
+      <c r="LO59" s="5"/>
+      <c r="LP59" s="5"/>
+      <c r="LQ59" s="5"/>
+      <c r="LR59" s="5"/>
+      <c r="LS59" s="5"/>
+      <c r="LT59" s="5"/>
+      <c r="LU59" s="5"/>
+      <c r="LV59" s="5"/>
+      <c r="LW59" s="5"/>
+      <c r="LX59" s="5"/>
+      <c r="LY59" s="5"/>
+      <c r="LZ59" s="5"/>
+      <c r="MA59" s="5"/>
+      <c r="MB59" s="5"/>
+      <c r="MC59" s="5"/>
+      <c r="MD59" s="5"/>
+      <c r="ME59" s="5"/>
+      <c r="MF59" s="5"/>
+      <c r="MG59" s="5"/>
+      <c r="MH59" s="5"/>
+      <c r="MI59" s="5"/>
+      <c r="MJ59" s="5"/>
+      <c r="MK59" s="5"/>
+      <c r="ML59" s="5"/>
+      <c r="MM59" s="5"/>
+      <c r="MN59" s="5"/>
+      <c r="MO59" s="5"/>
+      <c r="MP59" s="5"/>
+      <c r="MQ59" s="5"/>
+      <c r="MR59" s="5"/>
+      <c r="MS59" s="5"/>
+      <c r="MT59" s="5"/>
+      <c r="MU59" s="5"/>
+      <c r="MV59" s="5"/>
+      <c r="MW59" s="5"/>
+      <c r="MX59" s="5"/>
+      <c r="MY59" s="5"/>
+      <c r="MZ59" s="5"/>
+      <c r="NA59" s="5"/>
+      <c r="NB59" s="5"/>
+      <c r="NC59" s="5"/>
+      <c r="ND59" s="5"/>
+      <c r="NE59" s="5"/>
+      <c r="NF59" s="5"/>
+      <c r="NG59" s="5"/>
+      <c r="NH59" s="5"/>
+      <c r="NI59" s="5"/>
+      <c r="NJ59" s="5"/>
+      <c r="NK59" s="5"/>
+      <c r="NL59" s="5"/>
+      <c r="NM59" s="5"/>
+      <c r="NN59" s="5"/>
+      <c r="NO59" s="5"/>
+      <c r="NP59" s="5"/>
+      <c r="NQ59" s="5"/>
+      <c r="NR59" s="5"/>
+      <c r="NS59" s="5"/>
+      <c r="NT59" s="5"/>
+      <c r="NU59" s="5"/>
+      <c r="NV59" s="5"/>
+      <c r="NW59" s="5"/>
+      <c r="NX59" s="5"/>
+      <c r="NY59" s="5"/>
+      <c r="NZ59" s="5"/>
+      <c r="OA59" s="5"/>
+      <c r="OB59" s="5"/>
+      <c r="OC59" s="5"/>
+      <c r="OD59" s="5"/>
+      <c r="OE59" s="5"/>
+      <c r="OF59" s="5"/>
+      <c r="OG59" s="5"/>
+      <c r="OH59" s="5"/>
+      <c r="OI59" s="5"/>
+      <c r="OJ59" s="5"/>
+      <c r="OK59" s="5"/>
+      <c r="OL59" s="5"/>
+      <c r="OM59" s="5"/>
+      <c r="ON59" s="5"/>
+      <c r="OO59" s="5"/>
+      <c r="OP59" s="5"/>
+      <c r="OQ59" s="5"/>
+      <c r="OR59" s="5"/>
+      <c r="OS59" s="5"/>
+      <c r="OT59" s="5"/>
+      <c r="OU59" s="5"/>
+      <c r="OV59" s="5"/>
+      <c r="OW59" s="5"/>
+      <c r="OX59" s="5"/>
+      <c r="OY59" s="5"/>
+      <c r="OZ59" s="5"/>
+      <c r="PA59" s="5"/>
+      <c r="PB59" s="5"/>
+      <c r="PC59" s="5"/>
+      <c r="PD59" s="5"/>
+      <c r="PE59" s="5"/>
+      <c r="PF59" s="5"/>
+      <c r="PG59" s="5"/>
+      <c r="PH59" s="5"/>
+      <c r="PI59" s="5"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="5"/>
+      <c r="J60" s="5"/>
+      <c r="K60" s="5"/>
+      <c r="L60" s="5"/>
+      <c r="M60" s="5"/>
+      <c r="N60" s="5"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="5"/>
+      <c r="Q60" s="5"/>
+      <c r="R60" s="5"/>
+      <c r="S60" s="5"/>
+      <c r="T60" s="5"/>
+      <c r="U60" s="5"/>
+      <c r="V60" s="5"/>
+      <c r="W60" s="5"/>
+      <c r="X60" s="5"/>
+      <c r="Y60" s="5"/>
+      <c r="Z60" s="5"/>
+      <c r="AA60" s="5"/>
+      <c r="AB60" s="5"/>
+      <c r="AC60" s="5"/>
+      <c r="AD60" s="5"/>
+      <c r="AE60" s="5"/>
+      <c r="AF60" s="5"/>
+      <c r="AG60" s="5"/>
+      <c r="AH60" s="5"/>
+      <c r="AI60" s="5"/>
+      <c r="AJ60" s="5"/>
+      <c r="AK60" s="5"/>
+      <c r="AL60" s="5"/>
+      <c r="AM60" s="5"/>
+      <c r="AN60" s="5"/>
+      <c r="AO60" s="5"/>
+      <c r="AP60" s="5"/>
+      <c r="AQ60" s="5"/>
+      <c r="AR60" s="5"/>
+      <c r="AS60" s="5"/>
+      <c r="AT60" s="5"/>
+      <c r="AU60" s="5"/>
+      <c r="AV60" s="5"/>
+      <c r="AW60" s="5"/>
+      <c r="AX60" s="5"/>
+      <c r="AY60" s="5"/>
+      <c r="AZ60" s="5"/>
+      <c r="BA60" s="5"/>
+      <c r="BB60" s="5"/>
+      <c r="BC60" s="5"/>
+      <c r="BD60" s="5"/>
+      <c r="BE60" s="5"/>
+      <c r="BF60" s="5"/>
+      <c r="BG60" s="5"/>
+      <c r="BH60" s="5"/>
+      <c r="BI60" s="5"/>
+      <c r="BJ60" s="5"/>
+      <c r="BK60" s="5"/>
+      <c r="BL60" s="5"/>
+      <c r="BM60" s="5"/>
+      <c r="BN60" s="5"/>
+      <c r="BO60" s="5"/>
+      <c r="BP60" s="5"/>
+      <c r="BQ60" s="5"/>
+      <c r="BR60" s="5"/>
+      <c r="BS60" s="5"/>
+      <c r="BT60" s="5"/>
+      <c r="BU60" s="5"/>
+      <c r="BV60" s="5"/>
+      <c r="BW60" s="5"/>
+      <c r="BX60" s="5"/>
+      <c r="BY60" s="5"/>
+      <c r="BZ60" s="5"/>
+      <c r="CA60" s="5"/>
+      <c r="CB60" s="5"/>
+      <c r="CC60" s="5"/>
+      <c r="CD60" s="5"/>
+      <c r="CE60" s="5"/>
+      <c r="CF60" s="5"/>
+      <c r="CG60" s="5"/>
+      <c r="CH60" s="5"/>
+      <c r="CI60" s="5"/>
+      <c r="CJ60" s="5"/>
+      <c r="CK60" s="5"/>
+      <c r="CL60" s="5"/>
+      <c r="CM60" s="5"/>
+      <c r="CN60" s="5"/>
+      <c r="CO60" s="5"/>
+      <c r="CP60" s="5"/>
+      <c r="CQ60" s="5"/>
+      <c r="CR60" s="5"/>
+      <c r="CS60" s="5"/>
+      <c r="CT60" s="5"/>
+      <c r="CU60" s="5"/>
+      <c r="CV60" s="5"/>
+      <c r="CW60" s="5"/>
+      <c r="CX60" s="5"/>
+      <c r="CY60" s="5"/>
+      <c r="CZ60" s="5"/>
+      <c r="DA60" s="5"/>
+      <c r="DB60" s="5"/>
+      <c r="DC60" s="5"/>
+      <c r="DD60" s="5"/>
+      <c r="DE60" s="5"/>
+      <c r="DF60" s="5"/>
+      <c r="DG60" s="5"/>
+      <c r="DH60" s="5"/>
+      <c r="DI60" s="5"/>
+      <c r="DJ60" s="5"/>
+      <c r="DK60" s="5"/>
+      <c r="DL60" s="5"/>
+      <c r="DM60" s="5"/>
+      <c r="DN60" s="5"/>
+      <c r="DO60" s="5"/>
+      <c r="DP60" s="5"/>
+      <c r="DQ60" s="5"/>
+      <c r="DR60" s="5"/>
+      <c r="DS60" s="5"/>
+      <c r="DT60" s="5"/>
+      <c r="DU60" s="5"/>
+      <c r="DV60" s="5"/>
+      <c r="DW60" s="5"/>
+      <c r="DX60" s="5"/>
+      <c r="DY60" s="5"/>
+      <c r="DZ60" s="5"/>
+      <c r="EA60" s="5"/>
+      <c r="EB60" s="5"/>
+      <c r="EC60" s="5"/>
+      <c r="ED60" s="5"/>
+      <c r="EE60" s="5"/>
+      <c r="EF60" s="5"/>
+      <c r="EG60" s="5"/>
+      <c r="EH60" s="5"/>
+      <c r="EI60" s="5"/>
+      <c r="EJ60" s="5"/>
+      <c r="EK60" s="5"/>
+      <c r="EL60" s="5"/>
+      <c r="EM60" s="5"/>
+      <c r="EN60" s="5"/>
+      <c r="EO60" s="5"/>
+      <c r="EP60" s="5"/>
+      <c r="EQ60" s="5"/>
+      <c r="ER60" s="5"/>
+      <c r="ES60" s="5"/>
+      <c r="ET60" s="5"/>
+      <c r="EU60" s="5"/>
+      <c r="EV60" s="5"/>
+      <c r="EW60" s="5"/>
+      <c r="EX60" s="5"/>
+      <c r="EY60" s="5"/>
+      <c r="EZ60" s="5"/>
+      <c r="FA60" s="5"/>
+      <c r="FB60" s="5"/>
+      <c r="FC60" s="5"/>
+      <c r="FD60" s="5"/>
+      <c r="FE60" s="5"/>
+      <c r="FF60" s="5"/>
+      <c r="FG60" s="5"/>
+      <c r="FH60" s="5"/>
+      <c r="FI60" s="5"/>
+      <c r="FJ60" s="5"/>
+      <c r="FK60" s="5"/>
+      <c r="FL60" s="5"/>
+      <c r="FM60" s="5"/>
+      <c r="FN60" s="5"/>
+      <c r="FO60" s="5"/>
+      <c r="FP60" s="5"/>
+      <c r="FQ60" s="5"/>
+      <c r="FR60" s="5"/>
+      <c r="FS60" s="5"/>
+      <c r="FT60" s="5"/>
+      <c r="FU60" s="5"/>
+      <c r="FV60" s="5"/>
+      <c r="FW60" s="5"/>
+      <c r="FX60" s="5"/>
+      <c r="FY60" s="5"/>
+      <c r="FZ60" s="5"/>
+      <c r="GA60" s="5"/>
+      <c r="GB60" s="5"/>
+      <c r="GC60" s="5"/>
+      <c r="GD60" s="5"/>
+      <c r="GE60" s="5"/>
+      <c r="GF60" s="5"/>
+      <c r="GG60" s="5"/>
+      <c r="GH60" s="5"/>
+      <c r="GI60" s="5"/>
+      <c r="GJ60" s="5"/>
+      <c r="GK60" s="5"/>
+      <c r="GL60" s="5"/>
+      <c r="GM60" s="5"/>
+      <c r="GN60" s="5"/>
+      <c r="GO60" s="5"/>
+      <c r="GP60" s="5"/>
+      <c r="GQ60" s="5"/>
+      <c r="GR60" s="5"/>
+      <c r="GS60" s="5"/>
+      <c r="GT60" s="5"/>
+      <c r="GU60" s="5"/>
+      <c r="GV60" s="5"/>
+      <c r="GW60" s="5"/>
+      <c r="GX60" s="5"/>
+      <c r="GY60" s="5"/>
+      <c r="GZ60" s="5"/>
+      <c r="HA60" s="5"/>
+      <c r="HB60" s="5"/>
+      <c r="HC60" s="5"/>
+      <c r="HD60" s="5"/>
+      <c r="HE60" s="5"/>
+      <c r="HF60" s="5"/>
+      <c r="HG60" s="5"/>
+      <c r="HH60" s="5"/>
+      <c r="HI60" s="5"/>
+      <c r="HJ60" s="5"/>
+      <c r="HK60" s="5"/>
+      <c r="HL60" s="5"/>
+      <c r="HM60" s="5"/>
+      <c r="HN60" s="5"/>
+      <c r="HO60" s="5"/>
+      <c r="HP60" s="5"/>
+      <c r="HQ60" s="5"/>
+      <c r="HR60" s="5"/>
+      <c r="HS60" s="5"/>
+      <c r="HT60" s="5"/>
+      <c r="HU60" s="5"/>
+      <c r="HV60" s="5"/>
+      <c r="HW60" s="5"/>
+      <c r="HX60" s="5"/>
+      <c r="HY60" s="5"/>
+      <c r="HZ60" s="5"/>
+      <c r="IA60" s="5"/>
+      <c r="IB60" s="5"/>
+      <c r="IC60" s="5"/>
+      <c r="ID60" s="5"/>
+      <c r="IE60" s="5"/>
+      <c r="IF60" s="5"/>
+      <c r="IG60" s="5"/>
+      <c r="IH60" s="5"/>
+      <c r="II60" s="5"/>
+      <c r="IJ60" s="5"/>
+      <c r="IK60" s="5"/>
+      <c r="IL60" s="5"/>
+      <c r="IM60" s="5"/>
+      <c r="IN60" s="5"/>
+      <c r="IO60" s="5"/>
+      <c r="IP60" s="5"/>
+      <c r="IQ60" s="5"/>
+      <c r="IR60" s="5"/>
+      <c r="IS60" s="5"/>
+      <c r="IT60" s="5"/>
+      <c r="IU60" s="5"/>
+      <c r="IV60" s="5"/>
+      <c r="IW60" s="5"/>
+      <c r="IX60" s="5"/>
+      <c r="IY60" s="5"/>
+      <c r="IZ60" s="5"/>
+      <c r="JA60" s="5"/>
+      <c r="JB60" s="5"/>
+      <c r="JC60" s="5"/>
+      <c r="JD60" s="5"/>
+      <c r="JE60" s="5"/>
+      <c r="JF60" s="5"/>
+      <c r="JG60" s="5"/>
+      <c r="JH60" s="5"/>
+      <c r="JI60" s="5"/>
+      <c r="JJ60" s="5"/>
+      <c r="JK60" s="5"/>
+      <c r="JL60" s="5"/>
+      <c r="JM60" s="5"/>
+      <c r="JN60" s="5"/>
+      <c r="JO60" s="5"/>
+      <c r="JP60" s="5"/>
+      <c r="JQ60" s="5"/>
+      <c r="JR60" s="5"/>
+      <c r="JS60" s="5"/>
+      <c r="JT60" s="5"/>
+      <c r="JU60" s="5"/>
+      <c r="JV60" s="5"/>
+      <c r="JW60" s="5"/>
+      <c r="JX60" s="5"/>
+      <c r="JY60" s="5"/>
+      <c r="JZ60" s="5"/>
+      <c r="KA60" s="5"/>
+      <c r="KB60" s="5"/>
+      <c r="KC60" s="5"/>
+      <c r="KD60" s="5"/>
+      <c r="KE60" s="5"/>
+      <c r="KF60" s="5"/>
+      <c r="KG60" s="5"/>
+      <c r="KH60" s="5"/>
+      <c r="KI60" s="5"/>
+      <c r="KJ60" s="5"/>
+      <c r="KK60" s="5"/>
+      <c r="KL60" s="5"/>
+      <c r="KM60" s="5"/>
+      <c r="KN60" s="5"/>
+      <c r="KO60" s="5"/>
+      <c r="KP60" s="5"/>
+      <c r="KQ60" s="5"/>
+      <c r="KR60" s="5"/>
+      <c r="KS60" s="5"/>
+      <c r="KT60" s="5"/>
+      <c r="KU60" s="5"/>
+      <c r="KV60" s="5"/>
+      <c r="KW60" s="5"/>
+      <c r="KX60" s="5"/>
+      <c r="KY60" s="5"/>
+      <c r="KZ60" s="5"/>
+      <c r="LA60" s="5"/>
+      <c r="LB60" s="5"/>
+      <c r="LC60" s="5"/>
+      <c r="LD60" s="5"/>
+      <c r="LE60" s="5"/>
+      <c r="LF60" s="5"/>
+      <c r="LG60" s="5"/>
+      <c r="LH60" s="5"/>
+      <c r="LI60" s="5"/>
+      <c r="LJ60" s="5"/>
+      <c r="LK60" s="5"/>
+      <c r="LL60" s="5"/>
+      <c r="LM60" s="5"/>
+      <c r="LN60" s="5"/>
+      <c r="LO60" s="5"/>
+      <c r="LP60" s="5"/>
+      <c r="LQ60" s="5"/>
+      <c r="LR60" s="5"/>
+      <c r="LS60" s="5"/>
+      <c r="LT60" s="5"/>
+      <c r="LU60" s="5"/>
+      <c r="LV60" s="5"/>
+      <c r="LW60" s="5"/>
+      <c r="LX60" s="5"/>
+      <c r="LY60" s="5"/>
+      <c r="LZ60" s="5"/>
+      <c r="MA60" s="5"/>
+      <c r="MB60" s="5"/>
+      <c r="MC60" s="5"/>
+      <c r="MD60" s="5"/>
+      <c r="ME60" s="5"/>
+      <c r="MF60" s="5"/>
+      <c r="MG60" s="5"/>
+      <c r="MH60" s="5"/>
+      <c r="MI60" s="5"/>
+      <c r="MJ60" s="5"/>
+      <c r="MK60" s="5"/>
+      <c r="ML60" s="5"/>
+      <c r="MM60" s="5"/>
+      <c r="MN60" s="5"/>
+      <c r="MO60" s="5"/>
+      <c r="MP60" s="5"/>
+      <c r="MQ60" s="5"/>
+      <c r="MR60" s="5"/>
+      <c r="MS60" s="5"/>
+      <c r="MT60" s="5"/>
+      <c r="MU60" s="5"/>
+      <c r="MV60" s="5"/>
+      <c r="MW60" s="5"/>
+      <c r="MX60" s="5"/>
+      <c r="MY60" s="5"/>
+      <c r="MZ60" s="5"/>
+      <c r="NA60" s="5"/>
+      <c r="NB60" s="5"/>
+      <c r="NC60" s="5"/>
+      <c r="ND60" s="5"/>
+      <c r="NE60" s="5"/>
+      <c r="NF60" s="5"/>
+      <c r="NG60" s="5"/>
+      <c r="NH60" s="5"/>
+      <c r="NI60" s="5"/>
+      <c r="NJ60" s="5"/>
+      <c r="NK60" s="5"/>
+      <c r="NL60" s="5"/>
+      <c r="NM60" s="5"/>
+      <c r="NN60" s="5"/>
+      <c r="NO60" s="5"/>
+      <c r="NP60" s="5"/>
+      <c r="NQ60" s="5"/>
+      <c r="NR60" s="5"/>
+      <c r="NS60" s="5"/>
+      <c r="NT60" s="5"/>
+      <c r="NU60" s="5"/>
+      <c r="NV60" s="5"/>
+      <c r="NW60" s="5"/>
+      <c r="NX60" s="5"/>
+      <c r="NY60" s="5"/>
+      <c r="NZ60" s="5"/>
+      <c r="OA60" s="5"/>
+      <c r="OB60" s="5"/>
+      <c r="OC60" s="5"/>
+      <c r="OD60" s="5"/>
+      <c r="OE60" s="5"/>
+      <c r="OF60" s="5"/>
+      <c r="OG60" s="5"/>
+      <c r="OH60" s="5"/>
+      <c r="OI60" s="5"/>
+      <c r="OJ60" s="5"/>
+      <c r="OK60" s="5"/>
+      <c r="OL60" s="5"/>
+      <c r="OM60" s="5"/>
+      <c r="ON60" s="5"/>
+      <c r="OO60" s="5"/>
+      <c r="OP60" s="5"/>
+      <c r="OQ60" s="5"/>
+      <c r="OR60" s="5"/>
+      <c r="OS60" s="5"/>
+      <c r="OT60" s="5"/>
+      <c r="OU60" s="5"/>
+      <c r="OV60" s="5"/>
+      <c r="OW60" s="5"/>
+      <c r="OX60" s="5"/>
+      <c r="OY60" s="5"/>
+      <c r="OZ60" s="5"/>
+      <c r="PA60" s="5"/>
+      <c r="PB60" s="5"/>
+      <c r="PC60" s="5"/>
+      <c r="PD60" s="5"/>
+      <c r="PE60" s="5"/>
+      <c r="PF60" s="5"/>
+      <c r="PG60" s="5"/>
+      <c r="PH60" s="5"/>
+      <c r="PI60" s="5"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:PI1"/>

--- a/Part2_PlatformBenchmarks_Results.xlsx
+++ b/Part2_PlatformBenchmarks_Results.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="505">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 2: Platform Benchmarks</t>
   </si>
@@ -1457,6 +1457,12 @@
   </si>
   <si>
     <t xml:space="preserve">Balance (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bridge Killer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Round trip latency (μs)</t>
   </si>
   <si>
     <t xml:space="preserve">LED Matrix</t>
@@ -1922,7 +1928,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:PI60"/>
+  <dimension ref="A1:PI62"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.31"/>
@@ -3682,7 +3688,9 @@
       <c r="AH4" s="5"/>
       <c r="AI4" s="5"/>
       <c r="AJ4" s="5"/>
-      <c r="AK4" s="5"/>
+      <c r="AK4" s="5" t="n">
+        <v>3.43</v>
+      </c>
       <c r="AL4" s="5"/>
       <c r="AM4" s="5"/>
       <c r="AN4" s="5"/>
@@ -4117,7 +4125,9 @@
       <c r="AH5" s="5"/>
       <c r="AI5" s="5"/>
       <c r="AJ5" s="5"/>
-      <c r="AK5" s="5"/>
+      <c r="AK5" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL5" s="5"/>
       <c r="AM5" s="5"/>
       <c r="AN5" s="5"/>
@@ -4552,7 +4562,9 @@
       <c r="AH6" s="5"/>
       <c r="AI6" s="5"/>
       <c r="AJ6" s="5"/>
-      <c r="AK6" s="5"/>
+      <c r="AK6" s="5" t="n">
+        <v>4.54</v>
+      </c>
       <c r="AL6" s="5"/>
       <c r="AM6" s="5"/>
       <c r="AN6" s="5"/>
@@ -4987,7 +4999,9 @@
       <c r="AH7" s="5"/>
       <c r="AI7" s="5"/>
       <c r="AJ7" s="5"/>
-      <c r="AK7" s="5"/>
+      <c r="AK7" s="5" t="n">
+        <v>6.18</v>
+      </c>
       <c r="AL7" s="5"/>
       <c r="AM7" s="5"/>
       <c r="AN7" s="5"/>
@@ -5422,7 +5436,9 @@
       <c r="AH8" s="5"/>
       <c r="AI8" s="5"/>
       <c r="AJ8" s="5"/>
-      <c r="AK8" s="5"/>
+      <c r="AK8" s="5" t="n">
+        <v>5.89</v>
+      </c>
       <c r="AL8" s="5"/>
       <c r="AM8" s="5"/>
       <c r="AN8" s="5"/>
@@ -5857,7 +5873,9 @@
       <c r="AH9" s="5"/>
       <c r="AI9" s="5"/>
       <c r="AJ9" s="5"/>
-      <c r="AK9" s="5"/>
+      <c r="AK9" s="5" t="n">
+        <v>2.87</v>
+      </c>
       <c r="AL9" s="5"/>
       <c r="AM9" s="5"/>
       <c r="AN9" s="5"/>
@@ -6292,7 +6310,9 @@
       <c r="AH10" s="5"/>
       <c r="AI10" s="5"/>
       <c r="AJ10" s="5"/>
-      <c r="AK10" s="5"/>
+      <c r="AK10" s="5" t="n">
+        <v>5.04</v>
+      </c>
       <c r="AL10" s="5"/>
       <c r="AM10" s="5"/>
       <c r="AN10" s="5"/>
@@ -6727,7 +6747,9 @@
       <c r="AH11" s="5"/>
       <c r="AI11" s="5"/>
       <c r="AJ11" s="5"/>
-      <c r="AK11" s="5"/>
+      <c r="AK11" s="5" t="n">
+        <v>5.48</v>
+      </c>
       <c r="AL11" s="5"/>
       <c r="AM11" s="5"/>
       <c r="AN11" s="5"/>
@@ -7162,7 +7184,9 @@
       <c r="AH12" s="5"/>
       <c r="AI12" s="5"/>
       <c r="AJ12" s="5"/>
-      <c r="AK12" s="5"/>
+      <c r="AK12" s="5" t="n">
+        <v>5.01</v>
+      </c>
       <c r="AL12" s="5"/>
       <c r="AM12" s="5"/>
       <c r="AN12" s="5"/>
@@ -7597,7 +7621,9 @@
       <c r="AH13" s="5"/>
       <c r="AI13" s="5"/>
       <c r="AJ13" s="5"/>
-      <c r="AK13" s="5"/>
+      <c r="AK13" s="5" t="n">
+        <v>5.94</v>
+      </c>
       <c r="AL13" s="5"/>
       <c r="AM13" s="5"/>
       <c r="AN13" s="5"/>
@@ -8032,7 +8058,9 @@
       <c r="AH14" s="5"/>
       <c r="AI14" s="5"/>
       <c r="AJ14" s="5"/>
-      <c r="AK14" s="5"/>
+      <c r="AK14" s="5" t="n">
+        <v>35.18</v>
+      </c>
       <c r="AL14" s="5"/>
       <c r="AM14" s="5"/>
       <c r="AN14" s="5"/>
@@ -8467,7 +8495,9 @@
       <c r="AH15" s="5"/>
       <c r="AI15" s="5"/>
       <c r="AJ15" s="5"/>
-      <c r="AK15" s="5"/>
+      <c r="AK15" s="5" t="n">
+        <v>20.64</v>
+      </c>
       <c r="AL15" s="5"/>
       <c r="AM15" s="5"/>
       <c r="AN15" s="5"/>
@@ -8902,7 +8932,9 @@
       <c r="AH16" s="5"/>
       <c r="AI16" s="5"/>
       <c r="AJ16" s="5"/>
-      <c r="AK16" s="5"/>
+      <c r="AK16" s="5" t="n">
+        <v>11.52</v>
+      </c>
       <c r="AL16" s="5"/>
       <c r="AM16" s="5"/>
       <c r="AN16" s="5"/>
@@ -9337,7 +9369,9 @@
       <c r="AH17" s="5"/>
       <c r="AI17" s="5"/>
       <c r="AJ17" s="5"/>
-      <c r="AK17" s="5"/>
+      <c r="AK17" s="5" t="n">
+        <v>55.81</v>
+      </c>
       <c r="AL17" s="5"/>
       <c r="AM17" s="5"/>
       <c r="AN17" s="5"/>
@@ -9772,7 +9806,9 @@
       <c r="AH18" s="5"/>
       <c r="AI18" s="5"/>
       <c r="AJ18" s="5"/>
-      <c r="AK18" s="5"/>
+      <c r="AK18" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="AL18" s="5"/>
       <c r="AM18" s="5"/>
       <c r="AN18" s="5"/>
@@ -10207,7 +10243,9 @@
       <c r="AH19" s="5"/>
       <c r="AI19" s="5"/>
       <c r="AJ19" s="5"/>
-      <c r="AK19" s="5"/>
+      <c r="AK19" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="AL19" s="5"/>
       <c r="AM19" s="5"/>
       <c r="AN19" s="5"/>
@@ -10642,7 +10680,9 @@
       <c r="AH20" s="5"/>
       <c r="AI20" s="5"/>
       <c r="AJ20" s="5"/>
-      <c r="AK20" s="5"/>
+      <c r="AK20" s="5" t="n">
+        <v>16</v>
+      </c>
       <c r="AL20" s="5"/>
       <c r="AM20" s="5"/>
       <c r="AN20" s="5"/>
@@ -11077,7 +11117,9 @@
       <c r="AH21" s="5"/>
       <c r="AI21" s="5"/>
       <c r="AJ21" s="5"/>
-      <c r="AK21" s="5"/>
+      <c r="AK21" s="5" t="n">
+        <v>0.002</v>
+      </c>
       <c r="AL21" s="5"/>
       <c r="AM21" s="5"/>
       <c r="AN21" s="5"/>
@@ -11512,7 +11554,9 @@
       <c r="AH22" s="5"/>
       <c r="AI22" s="5"/>
       <c r="AJ22" s="5"/>
-      <c r="AK22" s="5"/>
+      <c r="AK22" s="5" t="n">
+        <v>2.1</v>
+      </c>
       <c r="AL22" s="5"/>
       <c r="AM22" s="5"/>
       <c r="AN22" s="5"/>
@@ -11947,7 +11991,9 @@
       <c r="AH23" s="5"/>
       <c r="AI23" s="5"/>
       <c r="AJ23" s="5"/>
-      <c r="AK23" s="5"/>
+      <c r="AK23" s="5" t="n">
+        <v>19</v>
+      </c>
       <c r="AL23" s="5"/>
       <c r="AM23" s="5"/>
       <c r="AN23" s="5"/>
@@ -12382,7 +12428,9 @@
       <c r="AH24" s="5"/>
       <c r="AI24" s="5"/>
       <c r="AJ24" s="5"/>
-      <c r="AK24" s="5"/>
+      <c r="AK24" s="5" t="n">
+        <v>49</v>
+      </c>
       <c r="AL24" s="5"/>
       <c r="AM24" s="5"/>
       <c r="AN24" s="5"/>
@@ -12817,7 +12865,9 @@
       <c r="AH25" s="5"/>
       <c r="AI25" s="5"/>
       <c r="AJ25" s="5"/>
-      <c r="AK25" s="5"/>
+      <c r="AK25" s="5" t="n">
+        <v>4.71</v>
+      </c>
       <c r="AL25" s="5"/>
       <c r="AM25" s="5"/>
       <c r="AN25" s="5"/>
@@ -13252,7 +13302,9 @@
       <c r="AH26" s="5"/>
       <c r="AI26" s="5"/>
       <c r="AJ26" s="5"/>
-      <c r="AK26" s="5"/>
+      <c r="AK26" s="5" t="n">
+        <v>7.36</v>
+      </c>
       <c r="AL26" s="5"/>
       <c r="AM26" s="5"/>
       <c r="AN26" s="5"/>
@@ -13687,7 +13739,9 @@
       <c r="AH27" s="5"/>
       <c r="AI27" s="5"/>
       <c r="AJ27" s="5"/>
-      <c r="AK27" s="5"/>
+      <c r="AK27" s="5" t="n">
+        <v>16.16</v>
+      </c>
       <c r="AL27" s="5"/>
       <c r="AM27" s="5"/>
       <c r="AN27" s="5"/>
@@ -14122,7 +14176,9 @@
       <c r="AH28" s="5"/>
       <c r="AI28" s="5"/>
       <c r="AJ28" s="5"/>
-      <c r="AK28" s="5"/>
+      <c r="AK28" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL28" s="5"/>
       <c r="AM28" s="5"/>
       <c r="AN28" s="5"/>
@@ -14557,7 +14613,9 @@
       <c r="AH29" s="5"/>
       <c r="AI29" s="5"/>
       <c r="AJ29" s="5"/>
-      <c r="AK29" s="5"/>
+      <c r="AK29" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL29" s="5"/>
       <c r="AM29" s="5"/>
       <c r="AN29" s="5"/>
@@ -14992,7 +15050,9 @@
       <c r="AH30" s="5"/>
       <c r="AI30" s="5"/>
       <c r="AJ30" s="5"/>
-      <c r="AK30" s="5"/>
+      <c r="AK30" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL30" s="5"/>
       <c r="AM30" s="5"/>
       <c r="AN30" s="5"/>
@@ -15427,7 +15487,9 @@
       <c r="AH31" s="5"/>
       <c r="AI31" s="5"/>
       <c r="AJ31" s="5"/>
-      <c r="AK31" s="5"/>
+      <c r="AK31" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL31" s="5"/>
       <c r="AM31" s="5"/>
       <c r="AN31" s="5"/>
@@ -15862,7 +15924,9 @@
       <c r="AH32" s="5"/>
       <c r="AI32" s="5"/>
       <c r="AJ32" s="5"/>
-      <c r="AK32" s="5"/>
+      <c r="AK32" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL32" s="5"/>
       <c r="AM32" s="5"/>
       <c r="AN32" s="5"/>
@@ -16297,7 +16361,9 @@
       <c r="AH33" s="5"/>
       <c r="AI33" s="5"/>
       <c r="AJ33" s="5"/>
-      <c r="AK33" s="5"/>
+      <c r="AK33" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL33" s="5"/>
       <c r="AM33" s="5"/>
       <c r="AN33" s="5"/>
@@ -16732,7 +16798,9 @@
       <c r="AH34" s="5"/>
       <c r="AI34" s="5"/>
       <c r="AJ34" s="5"/>
-      <c r="AK34" s="5"/>
+      <c r="AK34" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL34" s="5"/>
       <c r="AM34" s="5"/>
       <c r="AN34" s="5"/>
@@ -17167,7 +17235,9 @@
       <c r="AH35" s="5"/>
       <c r="AI35" s="5"/>
       <c r="AJ35" s="5"/>
-      <c r="AK35" s="5"/>
+      <c r="AK35" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL35" s="5"/>
       <c r="AM35" s="5"/>
       <c r="AN35" s="5"/>
@@ -17602,7 +17672,9 @@
       <c r="AH36" s="5"/>
       <c r="AI36" s="5"/>
       <c r="AJ36" s="5"/>
-      <c r="AK36" s="5"/>
+      <c r="AK36" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL36" s="5"/>
       <c r="AM36" s="5"/>
       <c r="AN36" s="5"/>
@@ -18037,7 +18109,9 @@
       <c r="AH37" s="5"/>
       <c r="AI37" s="5"/>
       <c r="AJ37" s="5"/>
-      <c r="AK37" s="5"/>
+      <c r="AK37" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL37" s="5"/>
       <c r="AM37" s="5"/>
       <c r="AN37" s="5"/>
@@ -18472,7 +18546,9 @@
       <c r="AH38" s="5"/>
       <c r="AI38" s="5"/>
       <c r="AJ38" s="5"/>
-      <c r="AK38" s="5"/>
+      <c r="AK38" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL38" s="5"/>
       <c r="AM38" s="5"/>
       <c r="AN38" s="5"/>
@@ -18907,7 +18983,9 @@
       <c r="AH39" s="5"/>
       <c r="AI39" s="5"/>
       <c r="AJ39" s="5"/>
-      <c r="AK39" s="5"/>
+      <c r="AK39" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL39" s="5"/>
       <c r="AM39" s="5"/>
       <c r="AN39" s="5"/>
@@ -19342,7 +19420,9 @@
       <c r="AH40" s="5"/>
       <c r="AI40" s="5"/>
       <c r="AJ40" s="5"/>
-      <c r="AK40" s="5"/>
+      <c r="AK40" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL40" s="5"/>
       <c r="AM40" s="5"/>
       <c r="AN40" s="5"/>
@@ -19777,7 +19857,9 @@
       <c r="AH41" s="5"/>
       <c r="AI41" s="5"/>
       <c r="AJ41" s="5"/>
-      <c r="AK41" s="5"/>
+      <c r="AK41" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL41" s="5"/>
       <c r="AM41" s="5"/>
       <c r="AN41" s="5"/>
@@ -20212,7 +20294,9 @@
       <c r="AH42" s="5"/>
       <c r="AI42" s="5"/>
       <c r="AJ42" s="5"/>
-      <c r="AK42" s="5"/>
+      <c r="AK42" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL42" s="5"/>
       <c r="AM42" s="5"/>
       <c r="AN42" s="5"/>
@@ -20647,7 +20731,9 @@
       <c r="AH43" s="5"/>
       <c r="AI43" s="5"/>
       <c r="AJ43" s="5"/>
-      <c r="AK43" s="5"/>
+      <c r="AK43" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL43" s="5"/>
       <c r="AM43" s="5"/>
       <c r="AN43" s="5"/>
@@ -21082,7 +21168,9 @@
       <c r="AH44" s="5"/>
       <c r="AI44" s="5"/>
       <c r="AJ44" s="5"/>
-      <c r="AK44" s="5"/>
+      <c r="AK44" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL44" s="5"/>
       <c r="AM44" s="5"/>
       <c r="AN44" s="5"/>
@@ -21517,7 +21605,9 @@
       <c r="AH45" s="5"/>
       <c r="AI45" s="5"/>
       <c r="AJ45" s="5"/>
-      <c r="AK45" s="5"/>
+      <c r="AK45" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL45" s="5"/>
       <c r="AM45" s="5"/>
       <c r="AN45" s="5"/>
@@ -21917,8 +22007,8 @@
       <c r="C46" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="D46" s="5" t="n">
-        <v>161.03</v>
+      <c r="D46" s="5" t="s">
+        <v>429</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
@@ -21952,7 +22042,9 @@
       <c r="AH46" s="5"/>
       <c r="AI46" s="5"/>
       <c r="AJ46" s="5"/>
-      <c r="AK46" s="5"/>
+      <c r="AK46" s="5" t="n">
+        <v>22324</v>
+      </c>
       <c r="AL46" s="5"/>
       <c r="AM46" s="5"/>
       <c r="AN46" s="5"/>
@@ -22347,13 +22439,13 @@
         <v>479</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>481</v>
+        <v>442</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="D47" s="5" t="n">
-        <v>26.5</v>
+      <c r="D47" s="5" t="s">
+        <v>429</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
@@ -22387,7 +22479,9 @@
       <c r="AH47" s="5"/>
       <c r="AI47" s="5"/>
       <c r="AJ47" s="5"/>
-      <c r="AK47" s="5"/>
+      <c r="AK47" s="5" t="n">
+        <v>1892.4</v>
+      </c>
       <c r="AL47" s="5"/>
       <c r="AM47" s="5"/>
       <c r="AN47" s="5"/>
@@ -22779,16 +22873,16 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="B48" s="5" t="s">
         <v>482</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>483</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>429</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>101.85</v>
+        <v>161.03</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
@@ -22822,7 +22916,9 @@
       <c r="AH48" s="5"/>
       <c r="AI48" s="5"/>
       <c r="AJ48" s="5"/>
-      <c r="AK48" s="5"/>
+      <c r="AK48" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL48" s="5"/>
       <c r="AM48" s="5"/>
       <c r="AN48" s="5"/>
@@ -23214,16 +23310,16 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>429</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>103.1</v>
+        <v>26.5</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
@@ -23257,7 +23353,9 @@
       <c r="AH49" s="5"/>
       <c r="AI49" s="5"/>
       <c r="AJ49" s="5"/>
-      <c r="AK49" s="5"/>
+      <c r="AK49" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL49" s="5"/>
       <c r="AM49" s="5"/>
       <c r="AN49" s="5"/>
@@ -23649,16 +23747,16 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="B50" s="5" t="s">
         <v>485</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>486</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>429</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>60.29</v>
+        <v>101.85</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
@@ -23692,7 +23790,9 @@
       <c r="AH50" s="5"/>
       <c r="AI50" s="5"/>
       <c r="AJ50" s="5"/>
-      <c r="AK50" s="5"/>
+      <c r="AK50" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL50" s="5"/>
       <c r="AM50" s="5"/>
       <c r="AN50" s="5"/>
@@ -24084,16 +24184,16 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>429</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>5.49</v>
+        <v>103.1</v>
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
@@ -24127,7 +24227,9 @@
       <c r="AH51" s="5"/>
       <c r="AI51" s="5"/>
       <c r="AJ51" s="5"/>
-      <c r="AK51" s="5"/>
+      <c r="AK51" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL51" s="5"/>
       <c r="AM51" s="5"/>
       <c r="AN51" s="5"/>
@@ -24519,7 +24621,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>488</v>
@@ -24528,7 +24630,7 @@
         <v>429</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>-0.431</v>
+        <v>60.29</v>
       </c>
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
@@ -24562,7 +24664,9 @@
       <c r="AH52" s="5"/>
       <c r="AI52" s="5"/>
       <c r="AJ52" s="5"/>
-      <c r="AK52" s="5"/>
+      <c r="AK52" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL52" s="5"/>
       <c r="AM52" s="5"/>
       <c r="AN52" s="5"/>
@@ -24954,16 +25058,16 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="B53" s="5" t="s">
         <v>489</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>490</v>
       </c>
       <c r="C53" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="D53" s="5" t="s">
-        <v>429</v>
+      <c r="D53" s="5" t="n">
+        <v>5.49</v>
       </c>
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
@@ -24997,7 +25101,9 @@
       <c r="AH53" s="5"/>
       <c r="AI53" s="5"/>
       <c r="AJ53" s="5"/>
-      <c r="AK53" s="5"/>
+      <c r="AK53" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL53" s="5"/>
       <c r="AM53" s="5"/>
       <c r="AN53" s="5"/>
@@ -25389,16 +25495,16 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C54" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="D54" s="5" t="s">
-        <v>429</v>
+      <c r="D54" s="5" t="n">
+        <v>-0.431</v>
       </c>
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
@@ -25432,7 +25538,9 @@
       <c r="AH54" s="5"/>
       <c r="AI54" s="5"/>
       <c r="AJ54" s="5"/>
-      <c r="AK54" s="5"/>
+      <c r="AK54" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL54" s="5"/>
       <c r="AM54" s="5"/>
       <c r="AN54" s="5"/>
@@ -25824,10 +25932,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>429</v>
@@ -25867,7 +25975,9 @@
       <c r="AH55" s="5"/>
       <c r="AI55" s="5"/>
       <c r="AJ55" s="5"/>
-      <c r="AK55" s="5"/>
+      <c r="AK55" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL55" s="5"/>
       <c r="AM55" s="5"/>
       <c r="AN55" s="5"/>
@@ -26262,7 +26372,7 @@
         <v>493</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>429</v>
@@ -26302,7 +26412,9 @@
       <c r="AH56" s="5"/>
       <c r="AI56" s="5"/>
       <c r="AJ56" s="5"/>
-      <c r="AK56" s="5"/>
+      <c r="AK56" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL56" s="5"/>
       <c r="AM56" s="5"/>
       <c r="AN56" s="5"/>
@@ -26694,10 +26806,10 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>496</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>497</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>429</v>
@@ -26737,7 +26849,9 @@
       <c r="AH57" s="5"/>
       <c r="AI57" s="5"/>
       <c r="AJ57" s="5"/>
-      <c r="AK57" s="5"/>
+      <c r="AK57" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL57" s="5"/>
       <c r="AM57" s="5"/>
       <c r="AN57" s="5"/>
@@ -27129,13 +27243,13 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>499</v>
-      </c>
-      <c r="C58" s="5" t="n">
-        <v>56</v>
+        <v>497</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>429</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>429</v>
@@ -27172,7 +27286,9 @@
       <c r="AH58" s="5"/>
       <c r="AI58" s="5"/>
       <c r="AJ58" s="5"/>
-      <c r="AK58" s="5"/>
+      <c r="AK58" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL58" s="5"/>
       <c r="AM58" s="5"/>
       <c r="AN58" s="5"/>
@@ -27567,13 +27683,13 @@
         <v>498</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="D59" s="5" t="n">
-        <v>86</v>
+      <c r="D59" s="5" t="s">
+        <v>429</v>
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
@@ -27607,7 +27723,9 @@
       <c r="AH59" s="5"/>
       <c r="AI59" s="5"/>
       <c r="AJ59" s="5"/>
-      <c r="AK59" s="5"/>
+      <c r="AK59" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="AL59" s="5"/>
       <c r="AM59" s="5"/>
       <c r="AN59" s="5"/>
@@ -27999,13 +28117,13 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>501</v>
       </c>
-      <c r="B60" s="5" t="s">
-        <v>502</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>429</v>
+      <c r="C60" s="5" t="n">
+        <v>56</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>429</v>
@@ -28042,7 +28160,9 @@
       <c r="AH60" s="5"/>
       <c r="AI60" s="5"/>
       <c r="AJ60" s="5"/>
-      <c r="AK60" s="5"/>
+      <c r="AK60" s="5" t="n">
+        <v>660</v>
+      </c>
       <c r="AL60" s="5"/>
       <c r="AM60" s="5"/>
       <c r="AN60" s="5"/>
@@ -28432,6 +28552,880 @@
       <c r="PH60" s="5"/>
       <c r="PI60" s="5"/>
     </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5"/>
+      <c r="K61" s="5"/>
+      <c r="L61" s="5"/>
+      <c r="M61" s="5"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="5"/>
+      <c r="Q61" s="5"/>
+      <c r="R61" s="5"/>
+      <c r="S61" s="5"/>
+      <c r="T61" s="5"/>
+      <c r="U61" s="5"/>
+      <c r="V61" s="5"/>
+      <c r="W61" s="5"/>
+      <c r="X61" s="5"/>
+      <c r="Y61" s="5"/>
+      <c r="Z61" s="5"/>
+      <c r="AA61" s="5"/>
+      <c r="AB61" s="5"/>
+      <c r="AC61" s="5"/>
+      <c r="AD61" s="5"/>
+      <c r="AE61" s="5"/>
+      <c r="AF61" s="5"/>
+      <c r="AG61" s="5"/>
+      <c r="AH61" s="5"/>
+      <c r="AI61" s="5"/>
+      <c r="AJ61" s="5"/>
+      <c r="AK61" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="AL61" s="5"/>
+      <c r="AM61" s="5"/>
+      <c r="AN61" s="5"/>
+      <c r="AO61" s="5"/>
+      <c r="AP61" s="5"/>
+      <c r="AQ61" s="5"/>
+      <c r="AR61" s="5"/>
+      <c r="AS61" s="5"/>
+      <c r="AT61" s="5"/>
+      <c r="AU61" s="5"/>
+      <c r="AV61" s="5"/>
+      <c r="AW61" s="5"/>
+      <c r="AX61" s="5"/>
+      <c r="AY61" s="5"/>
+      <c r="AZ61" s="5"/>
+      <c r="BA61" s="5"/>
+      <c r="BB61" s="5"/>
+      <c r="BC61" s="5"/>
+      <c r="BD61" s="5"/>
+      <c r="BE61" s="5"/>
+      <c r="BF61" s="5"/>
+      <c r="BG61" s="5"/>
+      <c r="BH61" s="5"/>
+      <c r="BI61" s="5"/>
+      <c r="BJ61" s="5"/>
+      <c r="BK61" s="5"/>
+      <c r="BL61" s="5"/>
+      <c r="BM61" s="5"/>
+      <c r="BN61" s="5"/>
+      <c r="BO61" s="5"/>
+      <c r="BP61" s="5"/>
+      <c r="BQ61" s="5"/>
+      <c r="BR61" s="5"/>
+      <c r="BS61" s="5"/>
+      <c r="BT61" s="5"/>
+      <c r="BU61" s="5"/>
+      <c r="BV61" s="5"/>
+      <c r="BW61" s="5"/>
+      <c r="BX61" s="5"/>
+      <c r="BY61" s="5"/>
+      <c r="BZ61" s="5"/>
+      <c r="CA61" s="5"/>
+      <c r="CB61" s="5"/>
+      <c r="CC61" s="5"/>
+      <c r="CD61" s="5"/>
+      <c r="CE61" s="5"/>
+      <c r="CF61" s="5"/>
+      <c r="CG61" s="5"/>
+      <c r="CH61" s="5"/>
+      <c r="CI61" s="5"/>
+      <c r="CJ61" s="5"/>
+      <c r="CK61" s="5"/>
+      <c r="CL61" s="5"/>
+      <c r="CM61" s="5"/>
+      <c r="CN61" s="5"/>
+      <c r="CO61" s="5"/>
+      <c r="CP61" s="5"/>
+      <c r="CQ61" s="5"/>
+      <c r="CR61" s="5"/>
+      <c r="CS61" s="5"/>
+      <c r="CT61" s="5"/>
+      <c r="CU61" s="5"/>
+      <c r="CV61" s="5"/>
+      <c r="CW61" s="5"/>
+      <c r="CX61" s="5"/>
+      <c r="CY61" s="5"/>
+      <c r="CZ61" s="5"/>
+      <c r="DA61" s="5"/>
+      <c r="DB61" s="5"/>
+      <c r="DC61" s="5"/>
+      <c r="DD61" s="5"/>
+      <c r="DE61" s="5"/>
+      <c r="DF61" s="5"/>
+      <c r="DG61" s="5"/>
+      <c r="DH61" s="5"/>
+      <c r="DI61" s="5"/>
+      <c r="DJ61" s="5"/>
+      <c r="DK61" s="5"/>
+      <c r="DL61" s="5"/>
+      <c r="DM61" s="5"/>
+      <c r="DN61" s="5"/>
+      <c r="DO61" s="5"/>
+      <c r="DP61" s="5"/>
+      <c r="DQ61" s="5"/>
+      <c r="DR61" s="5"/>
+      <c r="DS61" s="5"/>
+      <c r="DT61" s="5"/>
+      <c r="DU61" s="5"/>
+      <c r="DV61" s="5"/>
+      <c r="DW61" s="5"/>
+      <c r="DX61" s="5"/>
+      <c r="DY61" s="5"/>
+      <c r="DZ61" s="5"/>
+      <c r="EA61" s="5"/>
+      <c r="EB61" s="5"/>
+      <c r="EC61" s="5"/>
+      <c r="ED61" s="5"/>
+      <c r="EE61" s="5"/>
+      <c r="EF61" s="5"/>
+      <c r="EG61" s="5"/>
+      <c r="EH61" s="5"/>
+      <c r="EI61" s="5"/>
+      <c r="EJ61" s="5"/>
+      <c r="EK61" s="5"/>
+      <c r="EL61" s="5"/>
+      <c r="EM61" s="5"/>
+      <c r="EN61" s="5"/>
+      <c r="EO61" s="5"/>
+      <c r="EP61" s="5"/>
+      <c r="EQ61" s="5"/>
+      <c r="ER61" s="5"/>
+      <c r="ES61" s="5"/>
+      <c r="ET61" s="5"/>
+      <c r="EU61" s="5"/>
+      <c r="EV61" s="5"/>
+      <c r="EW61" s="5"/>
+      <c r="EX61" s="5"/>
+      <c r="EY61" s="5"/>
+      <c r="EZ61" s="5"/>
+      <c r="FA61" s="5"/>
+      <c r="FB61" s="5"/>
+      <c r="FC61" s="5"/>
+      <c r="FD61" s="5"/>
+      <c r="FE61" s="5"/>
+      <c r="FF61" s="5"/>
+      <c r="FG61" s="5"/>
+      <c r="FH61" s="5"/>
+      <c r="FI61" s="5"/>
+      <c r="FJ61" s="5"/>
+      <c r="FK61" s="5"/>
+      <c r="FL61" s="5"/>
+      <c r="FM61" s="5"/>
+      <c r="FN61" s="5"/>
+      <c r="FO61" s="5"/>
+      <c r="FP61" s="5"/>
+      <c r="FQ61" s="5"/>
+      <c r="FR61" s="5"/>
+      <c r="FS61" s="5"/>
+      <c r="FT61" s="5"/>
+      <c r="FU61" s="5"/>
+      <c r="FV61" s="5"/>
+      <c r="FW61" s="5"/>
+      <c r="FX61" s="5"/>
+      <c r="FY61" s="5"/>
+      <c r="FZ61" s="5"/>
+      <c r="GA61" s="5"/>
+      <c r="GB61" s="5"/>
+      <c r="GC61" s="5"/>
+      <c r="GD61" s="5"/>
+      <c r="GE61" s="5"/>
+      <c r="GF61" s="5"/>
+      <c r="GG61" s="5"/>
+      <c r="GH61" s="5"/>
+      <c r="GI61" s="5"/>
+      <c r="GJ61" s="5"/>
+      <c r="GK61" s="5"/>
+      <c r="GL61" s="5"/>
+      <c r="GM61" s="5"/>
+      <c r="GN61" s="5"/>
+      <c r="GO61" s="5"/>
+      <c r="GP61" s="5"/>
+      <c r="GQ61" s="5"/>
+      <c r="GR61" s="5"/>
+      <c r="GS61" s="5"/>
+      <c r="GT61" s="5"/>
+      <c r="GU61" s="5"/>
+      <c r="GV61" s="5"/>
+      <c r="GW61" s="5"/>
+      <c r="GX61" s="5"/>
+      <c r="GY61" s="5"/>
+      <c r="GZ61" s="5"/>
+      <c r="HA61" s="5"/>
+      <c r="HB61" s="5"/>
+      <c r="HC61" s="5"/>
+      <c r="HD61" s="5"/>
+      <c r="HE61" s="5"/>
+      <c r="HF61" s="5"/>
+      <c r="HG61" s="5"/>
+      <c r="HH61" s="5"/>
+      <c r="HI61" s="5"/>
+      <c r="HJ61" s="5"/>
+      <c r="HK61" s="5"/>
+      <c r="HL61" s="5"/>
+      <c r="HM61" s="5"/>
+      <c r="HN61" s="5"/>
+      <c r="HO61" s="5"/>
+      <c r="HP61" s="5"/>
+      <c r="HQ61" s="5"/>
+      <c r="HR61" s="5"/>
+      <c r="HS61" s="5"/>
+      <c r="HT61" s="5"/>
+      <c r="HU61" s="5"/>
+      <c r="HV61" s="5"/>
+      <c r="HW61" s="5"/>
+      <c r="HX61" s="5"/>
+      <c r="HY61" s="5"/>
+      <c r="HZ61" s="5"/>
+      <c r="IA61" s="5"/>
+      <c r="IB61" s="5"/>
+      <c r="IC61" s="5"/>
+      <c r="ID61" s="5"/>
+      <c r="IE61" s="5"/>
+      <c r="IF61" s="5"/>
+      <c r="IG61" s="5"/>
+      <c r="IH61" s="5"/>
+      <c r="II61" s="5"/>
+      <c r="IJ61" s="5"/>
+      <c r="IK61" s="5"/>
+      <c r="IL61" s="5"/>
+      <c r="IM61" s="5"/>
+      <c r="IN61" s="5"/>
+      <c r="IO61" s="5"/>
+      <c r="IP61" s="5"/>
+      <c r="IQ61" s="5"/>
+      <c r="IR61" s="5"/>
+      <c r="IS61" s="5"/>
+      <c r="IT61" s="5"/>
+      <c r="IU61" s="5"/>
+      <c r="IV61" s="5"/>
+      <c r="IW61" s="5"/>
+      <c r="IX61" s="5"/>
+      <c r="IY61" s="5"/>
+      <c r="IZ61" s="5"/>
+      <c r="JA61" s="5"/>
+      <c r="JB61" s="5"/>
+      <c r="JC61" s="5"/>
+      <c r="JD61" s="5"/>
+      <c r="JE61" s="5"/>
+      <c r="JF61" s="5"/>
+      <c r="JG61" s="5"/>
+      <c r="JH61" s="5"/>
+      <c r="JI61" s="5"/>
+      <c r="JJ61" s="5"/>
+      <c r="JK61" s="5"/>
+      <c r="JL61" s="5"/>
+      <c r="JM61" s="5"/>
+      <c r="JN61" s="5"/>
+      <c r="JO61" s="5"/>
+      <c r="JP61" s="5"/>
+      <c r="JQ61" s="5"/>
+      <c r="JR61" s="5"/>
+      <c r="JS61" s="5"/>
+      <c r="JT61" s="5"/>
+      <c r="JU61" s="5"/>
+      <c r="JV61" s="5"/>
+      <c r="JW61" s="5"/>
+      <c r="JX61" s="5"/>
+      <c r="JY61" s="5"/>
+      <c r="JZ61" s="5"/>
+      <c r="KA61" s="5"/>
+      <c r="KB61" s="5"/>
+      <c r="KC61" s="5"/>
+      <c r="KD61" s="5"/>
+      <c r="KE61" s="5"/>
+      <c r="KF61" s="5"/>
+      <c r="KG61" s="5"/>
+      <c r="KH61" s="5"/>
+      <c r="KI61" s="5"/>
+      <c r="KJ61" s="5"/>
+      <c r="KK61" s="5"/>
+      <c r="KL61" s="5"/>
+      <c r="KM61" s="5"/>
+      <c r="KN61" s="5"/>
+      <c r="KO61" s="5"/>
+      <c r="KP61" s="5"/>
+      <c r="KQ61" s="5"/>
+      <c r="KR61" s="5"/>
+      <c r="KS61" s="5"/>
+      <c r="KT61" s="5"/>
+      <c r="KU61" s="5"/>
+      <c r="KV61" s="5"/>
+      <c r="KW61" s="5"/>
+      <c r="KX61" s="5"/>
+      <c r="KY61" s="5"/>
+      <c r="KZ61" s="5"/>
+      <c r="LA61" s="5"/>
+      <c r="LB61" s="5"/>
+      <c r="LC61" s="5"/>
+      <c r="LD61" s="5"/>
+      <c r="LE61" s="5"/>
+      <c r="LF61" s="5"/>
+      <c r="LG61" s="5"/>
+      <c r="LH61" s="5"/>
+      <c r="LI61" s="5"/>
+      <c r="LJ61" s="5"/>
+      <c r="LK61" s="5"/>
+      <c r="LL61" s="5"/>
+      <c r="LM61" s="5"/>
+      <c r="LN61" s="5"/>
+      <c r="LO61" s="5"/>
+      <c r="LP61" s="5"/>
+      <c r="LQ61" s="5"/>
+      <c r="LR61" s="5"/>
+      <c r="LS61" s="5"/>
+      <c r="LT61" s="5"/>
+      <c r="LU61" s="5"/>
+      <c r="LV61" s="5"/>
+      <c r="LW61" s="5"/>
+      <c r="LX61" s="5"/>
+      <c r="LY61" s="5"/>
+      <c r="LZ61" s="5"/>
+      <c r="MA61" s="5"/>
+      <c r="MB61" s="5"/>
+      <c r="MC61" s="5"/>
+      <c r="MD61" s="5"/>
+      <c r="ME61" s="5"/>
+      <c r="MF61" s="5"/>
+      <c r="MG61" s="5"/>
+      <c r="MH61" s="5"/>
+      <c r="MI61" s="5"/>
+      <c r="MJ61" s="5"/>
+      <c r="MK61" s="5"/>
+      <c r="ML61" s="5"/>
+      <c r="MM61" s="5"/>
+      <c r="MN61" s="5"/>
+      <c r="MO61" s="5"/>
+      <c r="MP61" s="5"/>
+      <c r="MQ61" s="5"/>
+      <c r="MR61" s="5"/>
+      <c r="MS61" s="5"/>
+      <c r="MT61" s="5"/>
+      <c r="MU61" s="5"/>
+      <c r="MV61" s="5"/>
+      <c r="MW61" s="5"/>
+      <c r="MX61" s="5"/>
+      <c r="MY61" s="5"/>
+      <c r="MZ61" s="5"/>
+      <c r="NA61" s="5"/>
+      <c r="NB61" s="5"/>
+      <c r="NC61" s="5"/>
+      <c r="ND61" s="5"/>
+      <c r="NE61" s="5"/>
+      <c r="NF61" s="5"/>
+      <c r="NG61" s="5"/>
+      <c r="NH61" s="5"/>
+      <c r="NI61" s="5"/>
+      <c r="NJ61" s="5"/>
+      <c r="NK61" s="5"/>
+      <c r="NL61" s="5"/>
+      <c r="NM61" s="5"/>
+      <c r="NN61" s="5"/>
+      <c r="NO61" s="5"/>
+      <c r="NP61" s="5"/>
+      <c r="NQ61" s="5"/>
+      <c r="NR61" s="5"/>
+      <c r="NS61" s="5"/>
+      <c r="NT61" s="5"/>
+      <c r="NU61" s="5"/>
+      <c r="NV61" s="5"/>
+      <c r="NW61" s="5"/>
+      <c r="NX61" s="5"/>
+      <c r="NY61" s="5"/>
+      <c r="NZ61" s="5"/>
+      <c r="OA61" s="5"/>
+      <c r="OB61" s="5"/>
+      <c r="OC61" s="5"/>
+      <c r="OD61" s="5"/>
+      <c r="OE61" s="5"/>
+      <c r="OF61" s="5"/>
+      <c r="OG61" s="5"/>
+      <c r="OH61" s="5"/>
+      <c r="OI61" s="5"/>
+      <c r="OJ61" s="5"/>
+      <c r="OK61" s="5"/>
+      <c r="OL61" s="5"/>
+      <c r="OM61" s="5"/>
+      <c r="ON61" s="5"/>
+      <c r="OO61" s="5"/>
+      <c r="OP61" s="5"/>
+      <c r="OQ61" s="5"/>
+      <c r="OR61" s="5"/>
+      <c r="OS61" s="5"/>
+      <c r="OT61" s="5"/>
+      <c r="OU61" s="5"/>
+      <c r="OV61" s="5"/>
+      <c r="OW61" s="5"/>
+      <c r="OX61" s="5"/>
+      <c r="OY61" s="5"/>
+      <c r="OZ61" s="5"/>
+      <c r="PA61" s="5"/>
+      <c r="PB61" s="5"/>
+      <c r="PC61" s="5"/>
+      <c r="PD61" s="5"/>
+      <c r="PE61" s="5"/>
+      <c r="PF61" s="5"/>
+      <c r="PG61" s="5"/>
+      <c r="PH61" s="5"/>
+      <c r="PI61" s="5"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="5"/>
+      <c r="K62" s="5"/>
+      <c r="L62" s="5"/>
+      <c r="M62" s="5"/>
+      <c r="N62" s="5"/>
+      <c r="O62" s="5"/>
+      <c r="P62" s="5"/>
+      <c r="Q62" s="5"/>
+      <c r="R62" s="5"/>
+      <c r="S62" s="5"/>
+      <c r="T62" s="5"/>
+      <c r="U62" s="5"/>
+      <c r="V62" s="5"/>
+      <c r="W62" s="5"/>
+      <c r="X62" s="5"/>
+      <c r="Y62" s="5"/>
+      <c r="Z62" s="5"/>
+      <c r="AA62" s="5"/>
+      <c r="AB62" s="5"/>
+      <c r="AC62" s="5"/>
+      <c r="AD62" s="5"/>
+      <c r="AE62" s="5"/>
+      <c r="AF62" s="5"/>
+      <c r="AG62" s="5"/>
+      <c r="AH62" s="5"/>
+      <c r="AI62" s="5"/>
+      <c r="AJ62" s="5"/>
+      <c r="AK62" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="AL62" s="5"/>
+      <c r="AM62" s="5"/>
+      <c r="AN62" s="5"/>
+      <c r="AO62" s="5"/>
+      <c r="AP62" s="5"/>
+      <c r="AQ62" s="5"/>
+      <c r="AR62" s="5"/>
+      <c r="AS62" s="5"/>
+      <c r="AT62" s="5"/>
+      <c r="AU62" s="5"/>
+      <c r="AV62" s="5"/>
+      <c r="AW62" s="5"/>
+      <c r="AX62" s="5"/>
+      <c r="AY62" s="5"/>
+      <c r="AZ62" s="5"/>
+      <c r="BA62" s="5"/>
+      <c r="BB62" s="5"/>
+      <c r="BC62" s="5"/>
+      <c r="BD62" s="5"/>
+      <c r="BE62" s="5"/>
+      <c r="BF62" s="5"/>
+      <c r="BG62" s="5"/>
+      <c r="BH62" s="5"/>
+      <c r="BI62" s="5"/>
+      <c r="BJ62" s="5"/>
+      <c r="BK62" s="5"/>
+      <c r="BL62" s="5"/>
+      <c r="BM62" s="5"/>
+      <c r="BN62" s="5"/>
+      <c r="BO62" s="5"/>
+      <c r="BP62" s="5"/>
+      <c r="BQ62" s="5"/>
+      <c r="BR62" s="5"/>
+      <c r="BS62" s="5"/>
+      <c r="BT62" s="5"/>
+      <c r="BU62" s="5"/>
+      <c r="BV62" s="5"/>
+      <c r="BW62" s="5"/>
+      <c r="BX62" s="5"/>
+      <c r="BY62" s="5"/>
+      <c r="BZ62" s="5"/>
+      <c r="CA62" s="5"/>
+      <c r="CB62" s="5"/>
+      <c r="CC62" s="5"/>
+      <c r="CD62" s="5"/>
+      <c r="CE62" s="5"/>
+      <c r="CF62" s="5"/>
+      <c r="CG62" s="5"/>
+      <c r="CH62" s="5"/>
+      <c r="CI62" s="5"/>
+      <c r="CJ62" s="5"/>
+      <c r="CK62" s="5"/>
+      <c r="CL62" s="5"/>
+      <c r="CM62" s="5"/>
+      <c r="CN62" s="5"/>
+      <c r="CO62" s="5"/>
+      <c r="CP62" s="5"/>
+      <c r="CQ62" s="5"/>
+      <c r="CR62" s="5"/>
+      <c r="CS62" s="5"/>
+      <c r="CT62" s="5"/>
+      <c r="CU62" s="5"/>
+      <c r="CV62" s="5"/>
+      <c r="CW62" s="5"/>
+      <c r="CX62" s="5"/>
+      <c r="CY62" s="5"/>
+      <c r="CZ62" s="5"/>
+      <c r="DA62" s="5"/>
+      <c r="DB62" s="5"/>
+      <c r="DC62" s="5"/>
+      <c r="DD62" s="5"/>
+      <c r="DE62" s="5"/>
+      <c r="DF62" s="5"/>
+      <c r="DG62" s="5"/>
+      <c r="DH62" s="5"/>
+      <c r="DI62" s="5"/>
+      <c r="DJ62" s="5"/>
+      <c r="DK62" s="5"/>
+      <c r="DL62" s="5"/>
+      <c r="DM62" s="5"/>
+      <c r="DN62" s="5"/>
+      <c r="DO62" s="5"/>
+      <c r="DP62" s="5"/>
+      <c r="DQ62" s="5"/>
+      <c r="DR62" s="5"/>
+      <c r="DS62" s="5"/>
+      <c r="DT62" s="5"/>
+      <c r="DU62" s="5"/>
+      <c r="DV62" s="5"/>
+      <c r="DW62" s="5"/>
+      <c r="DX62" s="5"/>
+      <c r="DY62" s="5"/>
+      <c r="DZ62" s="5"/>
+      <c r="EA62" s="5"/>
+      <c r="EB62" s="5"/>
+      <c r="EC62" s="5"/>
+      <c r="ED62" s="5"/>
+      <c r="EE62" s="5"/>
+      <c r="EF62" s="5"/>
+      <c r="EG62" s="5"/>
+      <c r="EH62" s="5"/>
+      <c r="EI62" s="5"/>
+      <c r="EJ62" s="5"/>
+      <c r="EK62" s="5"/>
+      <c r="EL62" s="5"/>
+      <c r="EM62" s="5"/>
+      <c r="EN62" s="5"/>
+      <c r="EO62" s="5"/>
+      <c r="EP62" s="5"/>
+      <c r="EQ62" s="5"/>
+      <c r="ER62" s="5"/>
+      <c r="ES62" s="5"/>
+      <c r="ET62" s="5"/>
+      <c r="EU62" s="5"/>
+      <c r="EV62" s="5"/>
+      <c r="EW62" s="5"/>
+      <c r="EX62" s="5"/>
+      <c r="EY62" s="5"/>
+      <c r="EZ62" s="5"/>
+      <c r="FA62" s="5"/>
+      <c r="FB62" s="5"/>
+      <c r="FC62" s="5"/>
+      <c r="FD62" s="5"/>
+      <c r="FE62" s="5"/>
+      <c r="FF62" s="5"/>
+      <c r="FG62" s="5"/>
+      <c r="FH62" s="5"/>
+      <c r="FI62" s="5"/>
+      <c r="FJ62" s="5"/>
+      <c r="FK62" s="5"/>
+      <c r="FL62" s="5"/>
+      <c r="FM62" s="5"/>
+      <c r="FN62" s="5"/>
+      <c r="FO62" s="5"/>
+      <c r="FP62" s="5"/>
+      <c r="FQ62" s="5"/>
+      <c r="FR62" s="5"/>
+      <c r="FS62" s="5"/>
+      <c r="FT62" s="5"/>
+      <c r="FU62" s="5"/>
+      <c r="FV62" s="5"/>
+      <c r="FW62" s="5"/>
+      <c r="FX62" s="5"/>
+      <c r="FY62" s="5"/>
+      <c r="FZ62" s="5"/>
+      <c r="GA62" s="5"/>
+      <c r="GB62" s="5"/>
+      <c r="GC62" s="5"/>
+      <c r="GD62" s="5"/>
+      <c r="GE62" s="5"/>
+      <c r="GF62" s="5"/>
+      <c r="GG62" s="5"/>
+      <c r="GH62" s="5"/>
+      <c r="GI62" s="5"/>
+      <c r="GJ62" s="5"/>
+      <c r="GK62" s="5"/>
+      <c r="GL62" s="5"/>
+      <c r="GM62" s="5"/>
+      <c r="GN62" s="5"/>
+      <c r="GO62" s="5"/>
+      <c r="GP62" s="5"/>
+      <c r="GQ62" s="5"/>
+      <c r="GR62" s="5"/>
+      <c r="GS62" s="5"/>
+      <c r="GT62" s="5"/>
+      <c r="GU62" s="5"/>
+      <c r="GV62" s="5"/>
+      <c r="GW62" s="5"/>
+      <c r="GX62" s="5"/>
+      <c r="GY62" s="5"/>
+      <c r="GZ62" s="5"/>
+      <c r="HA62" s="5"/>
+      <c r="HB62" s="5"/>
+      <c r="HC62" s="5"/>
+      <c r="HD62" s="5"/>
+      <c r="HE62" s="5"/>
+      <c r="HF62" s="5"/>
+      <c r="HG62" s="5"/>
+      <c r="HH62" s="5"/>
+      <c r="HI62" s="5"/>
+      <c r="HJ62" s="5"/>
+      <c r="HK62" s="5"/>
+      <c r="HL62" s="5"/>
+      <c r="HM62" s="5"/>
+      <c r="HN62" s="5"/>
+      <c r="HO62" s="5"/>
+      <c r="HP62" s="5"/>
+      <c r="HQ62" s="5"/>
+      <c r="HR62" s="5"/>
+      <c r="HS62" s="5"/>
+      <c r="HT62" s="5"/>
+      <c r="HU62" s="5"/>
+      <c r="HV62" s="5"/>
+      <c r="HW62" s="5"/>
+      <c r="HX62" s="5"/>
+      <c r="HY62" s="5"/>
+      <c r="HZ62" s="5"/>
+      <c r="IA62" s="5"/>
+      <c r="IB62" s="5"/>
+      <c r="IC62" s="5"/>
+      <c r="ID62" s="5"/>
+      <c r="IE62" s="5"/>
+      <c r="IF62" s="5"/>
+      <c r="IG62" s="5"/>
+      <c r="IH62" s="5"/>
+      <c r="II62" s="5"/>
+      <c r="IJ62" s="5"/>
+      <c r="IK62" s="5"/>
+      <c r="IL62" s="5"/>
+      <c r="IM62" s="5"/>
+      <c r="IN62" s="5"/>
+      <c r="IO62" s="5"/>
+      <c r="IP62" s="5"/>
+      <c r="IQ62" s="5"/>
+      <c r="IR62" s="5"/>
+      <c r="IS62" s="5"/>
+      <c r="IT62" s="5"/>
+      <c r="IU62" s="5"/>
+      <c r="IV62" s="5"/>
+      <c r="IW62" s="5"/>
+      <c r="IX62" s="5"/>
+      <c r="IY62" s="5"/>
+      <c r="IZ62" s="5"/>
+      <c r="JA62" s="5"/>
+      <c r="JB62" s="5"/>
+      <c r="JC62" s="5"/>
+      <c r="JD62" s="5"/>
+      <c r="JE62" s="5"/>
+      <c r="JF62" s="5"/>
+      <c r="JG62" s="5"/>
+      <c r="JH62" s="5"/>
+      <c r="JI62" s="5"/>
+      <c r="JJ62" s="5"/>
+      <c r="JK62" s="5"/>
+      <c r="JL62" s="5"/>
+      <c r="JM62" s="5"/>
+      <c r="JN62" s="5"/>
+      <c r="JO62" s="5"/>
+      <c r="JP62" s="5"/>
+      <c r="JQ62" s="5"/>
+      <c r="JR62" s="5"/>
+      <c r="JS62" s="5"/>
+      <c r="JT62" s="5"/>
+      <c r="JU62" s="5"/>
+      <c r="JV62" s="5"/>
+      <c r="JW62" s="5"/>
+      <c r="JX62" s="5"/>
+      <c r="JY62" s="5"/>
+      <c r="JZ62" s="5"/>
+      <c r="KA62" s="5"/>
+      <c r="KB62" s="5"/>
+      <c r="KC62" s="5"/>
+      <c r="KD62" s="5"/>
+      <c r="KE62" s="5"/>
+      <c r="KF62" s="5"/>
+      <c r="KG62" s="5"/>
+      <c r="KH62" s="5"/>
+      <c r="KI62" s="5"/>
+      <c r="KJ62" s="5"/>
+      <c r="KK62" s="5"/>
+      <c r="KL62" s="5"/>
+      <c r="KM62" s="5"/>
+      <c r="KN62" s="5"/>
+      <c r="KO62" s="5"/>
+      <c r="KP62" s="5"/>
+      <c r="KQ62" s="5"/>
+      <c r="KR62" s="5"/>
+      <c r="KS62" s="5"/>
+      <c r="KT62" s="5"/>
+      <c r="KU62" s="5"/>
+      <c r="KV62" s="5"/>
+      <c r="KW62" s="5"/>
+      <c r="KX62" s="5"/>
+      <c r="KY62" s="5"/>
+      <c r="KZ62" s="5"/>
+      <c r="LA62" s="5"/>
+      <c r="LB62" s="5"/>
+      <c r="LC62" s="5"/>
+      <c r="LD62" s="5"/>
+      <c r="LE62" s="5"/>
+      <c r="LF62" s="5"/>
+      <c r="LG62" s="5"/>
+      <c r="LH62" s="5"/>
+      <c r="LI62" s="5"/>
+      <c r="LJ62" s="5"/>
+      <c r="LK62" s="5"/>
+      <c r="LL62" s="5"/>
+      <c r="LM62" s="5"/>
+      <c r="LN62" s="5"/>
+      <c r="LO62" s="5"/>
+      <c r="LP62" s="5"/>
+      <c r="LQ62" s="5"/>
+      <c r="LR62" s="5"/>
+      <c r="LS62" s="5"/>
+      <c r="LT62" s="5"/>
+      <c r="LU62" s="5"/>
+      <c r="LV62" s="5"/>
+      <c r="LW62" s="5"/>
+      <c r="LX62" s="5"/>
+      <c r="LY62" s="5"/>
+      <c r="LZ62" s="5"/>
+      <c r="MA62" s="5"/>
+      <c r="MB62" s="5"/>
+      <c r="MC62" s="5"/>
+      <c r="MD62" s="5"/>
+      <c r="ME62" s="5"/>
+      <c r="MF62" s="5"/>
+      <c r="MG62" s="5"/>
+      <c r="MH62" s="5"/>
+      <c r="MI62" s="5"/>
+      <c r="MJ62" s="5"/>
+      <c r="MK62" s="5"/>
+      <c r="ML62" s="5"/>
+      <c r="MM62" s="5"/>
+      <c r="MN62" s="5"/>
+      <c r="MO62" s="5"/>
+      <c r="MP62" s="5"/>
+      <c r="MQ62" s="5"/>
+      <c r="MR62" s="5"/>
+      <c r="MS62" s="5"/>
+      <c r="MT62" s="5"/>
+      <c r="MU62" s="5"/>
+      <c r="MV62" s="5"/>
+      <c r="MW62" s="5"/>
+      <c r="MX62" s="5"/>
+      <c r="MY62" s="5"/>
+      <c r="MZ62" s="5"/>
+      <c r="NA62" s="5"/>
+      <c r="NB62" s="5"/>
+      <c r="NC62" s="5"/>
+      <c r="ND62" s="5"/>
+      <c r="NE62" s="5"/>
+      <c r="NF62" s="5"/>
+      <c r="NG62" s="5"/>
+      <c r="NH62" s="5"/>
+      <c r="NI62" s="5"/>
+      <c r="NJ62" s="5"/>
+      <c r="NK62" s="5"/>
+      <c r="NL62" s="5"/>
+      <c r="NM62" s="5"/>
+      <c r="NN62" s="5"/>
+      <c r="NO62" s="5"/>
+      <c r="NP62" s="5"/>
+      <c r="NQ62" s="5"/>
+      <c r="NR62" s="5"/>
+      <c r="NS62" s="5"/>
+      <c r="NT62" s="5"/>
+      <c r="NU62" s="5"/>
+      <c r="NV62" s="5"/>
+      <c r="NW62" s="5"/>
+      <c r="NX62" s="5"/>
+      <c r="NY62" s="5"/>
+      <c r="NZ62" s="5"/>
+      <c r="OA62" s="5"/>
+      <c r="OB62" s="5"/>
+      <c r="OC62" s="5"/>
+      <c r="OD62" s="5"/>
+      <c r="OE62" s="5"/>
+      <c r="OF62" s="5"/>
+      <c r="OG62" s="5"/>
+      <c r="OH62" s="5"/>
+      <c r="OI62" s="5"/>
+      <c r="OJ62" s="5"/>
+      <c r="OK62" s="5"/>
+      <c r="OL62" s="5"/>
+      <c r="OM62" s="5"/>
+      <c r="ON62" s="5"/>
+      <c r="OO62" s="5"/>
+      <c r="OP62" s="5"/>
+      <c r="OQ62" s="5"/>
+      <c r="OR62" s="5"/>
+      <c r="OS62" s="5"/>
+      <c r="OT62" s="5"/>
+      <c r="OU62" s="5"/>
+      <c r="OV62" s="5"/>
+      <c r="OW62" s="5"/>
+      <c r="OX62" s="5"/>
+      <c r="OY62" s="5"/>
+      <c r="OZ62" s="5"/>
+      <c r="PA62" s="5"/>
+      <c r="PB62" s="5"/>
+      <c r="PC62" s="5"/>
+      <c r="PD62" s="5"/>
+      <c r="PE62" s="5"/>
+      <c r="PF62" s="5"/>
+      <c r="PG62" s="5"/>
+      <c r="PH62" s="5"/>
+      <c r="PI62" s="5"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:PI1"/>

--- a/Part2_PlatformBenchmarks_Results.xlsx
+++ b/Part2_PlatformBenchmarks_Results.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="506">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 2: Platform Benchmarks</t>
   </si>
@@ -1445,6 +1445,9 @@
   </si>
   <si>
     <t xml:space="preserve">Hardware RNG (bytes/sec)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hardware RNG (values/ms)</t>
   </si>
   <si>
     <t xml:space="preserve">Multi-Core</t>
@@ -1928,7 +1931,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:PI62"/>
+  <dimension ref="A1:PI63"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.31"/>
@@ -3660,7 +3663,9 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
+      <c r="I4" s="5" t="n">
+        <v>4768.53</v>
+      </c>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
@@ -4097,7 +4102,9 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
+      <c r="I5" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
@@ -4534,7 +4541,9 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
+      <c r="I6" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
@@ -4971,7 +4980,9 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
+      <c r="I7" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
@@ -5408,7 +5419,9 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
+      <c r="I8" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
@@ -5845,7 +5858,9 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
+      <c r="I9" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
@@ -6282,7 +6297,9 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
+      <c r="I10" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
@@ -6719,7 +6736,9 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
+      <c r="I11" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
@@ -7156,7 +7175,9 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
+      <c r="I12" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
@@ -7593,7 +7614,9 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
+      <c r="I13" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
@@ -8030,7 +8053,9 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
+      <c r="I14" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
@@ -8467,7 +8492,9 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
+      <c r="I15" s="5" t="n">
+        <v>0.33</v>
+      </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
@@ -8904,7 +8931,9 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
+      <c r="I16" s="5" t="n">
+        <v>11.52</v>
+      </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
@@ -9341,7 +9370,9 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
+      <c r="I17" s="5" t="n">
+        <v>3505.11</v>
+      </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
@@ -9778,7 +9809,9 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
+      <c r="I18" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
@@ -10215,7 +10248,9 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
+      <c r="I19" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
@@ -10652,7 +10687,9 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
+      <c r="I20" s="5" t="n">
+        <v>75</v>
+      </c>
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
@@ -11089,7 +11126,9 @@
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
+      <c r="I21" s="5" t="n">
+        <v>0.094</v>
+      </c>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
@@ -11526,7 +11565,9 @@
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
+      <c r="I22" s="5" t="n">
+        <v>168.3</v>
+      </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
@@ -11963,7 +12004,9 @@
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
+      <c r="I23" s="5" t="n">
+        <v>62</v>
+      </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
@@ -12400,7 +12443,9 @@
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
+      <c r="I24" s="5" t="n">
+        <v>57</v>
+      </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
@@ -12837,7 +12882,9 @@
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
+      <c r="I25" s="5" t="n">
+        <v>0.2</v>
+      </c>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
@@ -13274,7 +13321,9 @@
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
+      <c r="I26" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
@@ -13711,7 +13760,9 @@
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
+      <c r="I27" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
@@ -14148,7 +14199,9 @@
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
+      <c r="I28" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
@@ -14585,7 +14638,9 @@
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
+      <c r="I29" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
       <c r="L29" s="5"/>
@@ -15022,7 +15077,9 @@
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
+      <c r="I30" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
       <c r="L30" s="5"/>
@@ -15459,7 +15516,9 @@
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
+      <c r="I31" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
       <c r="L31" s="5"/>
@@ -15896,7 +15955,9 @@
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
+      <c r="I32" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
       <c r="L32" s="5"/>
@@ -16333,7 +16394,9 @@
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
+      <c r="I33" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
       <c r="L33" s="5"/>
@@ -16770,7 +16833,9 @@
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
+      <c r="I34" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
@@ -17207,7 +17272,9 @@
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
+      <c r="I35" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
       <c r="L35" s="5"/>
@@ -17644,7 +17711,9 @@
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
+      <c r="I36" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
       <c r="L36" s="5"/>
@@ -18081,7 +18150,9 @@
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
+      <c r="I37" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
@@ -18518,7 +18589,9 @@
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
+      <c r="I38" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
@@ -18955,7 +19028,9 @@
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
+      <c r="I39" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
       <c r="L39" s="5"/>
@@ -19392,7 +19467,9 @@
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
+      <c r="I40" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
@@ -19829,7 +19906,9 @@
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
+      <c r="I41" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
       <c r="L41" s="5"/>
@@ -20266,7 +20345,9 @@
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
+      <c r="I42" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
       <c r="L42" s="5"/>
@@ -20688,10 +20769,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>475</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>476</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>429</v>
@@ -20703,7 +20784,9 @@
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
+      <c r="I43" s="5" t="n">
+        <v>8.21</v>
+      </c>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
@@ -21125,7 +21208,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>477</v>
@@ -21140,7 +21223,9 @@
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
+      <c r="I44" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
@@ -21562,7 +21647,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>478</v>
@@ -21577,7 +21662,9 @@
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
+      <c r="I45" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
@@ -21999,10 +22086,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>479</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>480</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>429</v>
@@ -22014,7 +22101,9 @@
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
+      <c r="I46" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
@@ -22042,8 +22131,8 @@
       <c r="AH46" s="5"/>
       <c r="AI46" s="5"/>
       <c r="AJ46" s="5"/>
-      <c r="AK46" s="5" t="n">
-        <v>22324</v>
+      <c r="AK46" s="5" t="s">
+        <v>429</v>
       </c>
       <c r="AL46" s="5"/>
       <c r="AM46" s="5"/>
@@ -22436,10 +22525,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>442</v>
+        <v>481</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>429</v>
@@ -22451,7 +22540,9 @@
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
-      <c r="I47" s="5"/>
+      <c r="I47" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
@@ -22480,7 +22571,7 @@
       <c r="AI47" s="5"/>
       <c r="AJ47" s="5"/>
       <c r="AK47" s="5" t="n">
-        <v>1892.4</v>
+        <v>22324</v>
       </c>
       <c r="AL47" s="5"/>
       <c r="AM47" s="5"/>
@@ -22873,22 +22964,24 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>482</v>
+        <v>442</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="D48" s="5" t="n">
-        <v>161.03</v>
+      <c r="D48" s="5" t="s">
+        <v>429</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
-      <c r="I48" s="5"/>
+      <c r="I48" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
@@ -22916,8 +23009,8 @@
       <c r="AH48" s="5"/>
       <c r="AI48" s="5"/>
       <c r="AJ48" s="5"/>
-      <c r="AK48" s="5" t="s">
-        <v>429</v>
+      <c r="AK48" s="5" t="n">
+        <v>1892.4</v>
       </c>
       <c r="AL48" s="5"/>
       <c r="AM48" s="5"/>
@@ -23310,7 +23403,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>483</v>
@@ -23319,13 +23412,15 @@
         <v>429</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>26.5</v>
+        <v>161.03</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
-      <c r="I49" s="5"/>
+      <c r="I49" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J49" s="5"/>
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
@@ -23747,22 +23842,24 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="B50" s="5" t="s">
         <v>484</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>485</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>429</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>101.85</v>
+        <v>26.5</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
-      <c r="I50" s="5"/>
+      <c r="I50" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J50" s="5"/>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
@@ -24184,7 +24281,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>486</v>
@@ -24193,13 +24290,15 @@
         <v>429</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>103.1</v>
+        <v>101.85</v>
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
+      <c r="I51" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
@@ -24621,22 +24720,24 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="B52" s="5" t="s">
         <v>487</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>488</v>
       </c>
       <c r="C52" s="5" t="s">
         <v>429</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>60.29</v>
+        <v>103.1</v>
       </c>
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
-      <c r="I52" s="5"/>
+      <c r="I52" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J52" s="5"/>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
@@ -25058,7 +25159,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>489</v>
@@ -25067,13 +25168,15 @@
         <v>429</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>5.49</v>
+        <v>60.29</v>
       </c>
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
-      <c r="I53" s="5"/>
+      <c r="I53" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
@@ -25495,7 +25598,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>490</v>
@@ -25504,13 +25607,15 @@
         <v>429</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>-0.431</v>
+        <v>5.49</v>
       </c>
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
-      <c r="I54" s="5"/>
+      <c r="I54" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J54" s="5"/>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
@@ -25932,22 +26037,24 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="B55" s="5" t="s">
         <v>491</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>492</v>
       </c>
       <c r="C55" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="D55" s="5" t="s">
-        <v>429</v>
+      <c r="D55" s="5" t="n">
+        <v>-0.431</v>
       </c>
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
-      <c r="I55" s="5"/>
+      <c r="I55" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
@@ -26369,10 +26476,10 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="B56" s="5" t="s">
         <v>493</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>494</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>429</v>
@@ -26384,7 +26491,9 @@
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
-      <c r="I56" s="5"/>
+      <c r="I56" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J56" s="5"/>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
@@ -26806,10 +26915,10 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>495</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>496</v>
       </c>
       <c r="C57" s="5" t="s">
         <v>429</v>
@@ -26821,7 +26930,9 @@
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
-      <c r="I57" s="5"/>
+      <c r="I57" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
@@ -27243,7 +27354,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>497</v>
@@ -27258,7 +27369,9 @@
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
-      <c r="I58" s="5"/>
+      <c r="I58" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J58" s="5"/>
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
@@ -27680,10 +27793,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>498</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>499</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>429</v>
@@ -27695,7 +27808,9 @@
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
-      <c r="I59" s="5"/>
+      <c r="I59" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J59" s="5"/>
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
@@ -28117,13 +28232,13 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>500</v>
       </c>
-      <c r="B60" s="5" t="s">
-        <v>501</v>
-      </c>
-      <c r="C60" s="5" t="n">
-        <v>56</v>
+      <c r="C60" s="5" t="s">
+        <v>429</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>429</v>
@@ -28132,7 +28247,9 @@
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
-      <c r="I60" s="5"/>
+      <c r="I60" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J60" s="5"/>
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
@@ -28160,8 +28277,8 @@
       <c r="AH60" s="5"/>
       <c r="AI60" s="5"/>
       <c r="AJ60" s="5"/>
-      <c r="AK60" s="5" t="n">
-        <v>660</v>
+      <c r="AK60" s="5" t="s">
+        <v>429</v>
       </c>
       <c r="AL60" s="5"/>
       <c r="AM60" s="5"/>
@@ -28554,22 +28671,24 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="C61" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="D61" s="5" t="s">
         <v>429</v>
-      </c>
-      <c r="D61" s="5" t="n">
-        <v>86</v>
       </c>
       <c r="E61" s="5"/>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
-      <c r="I61" s="5"/>
+      <c r="I61" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J61" s="5"/>
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
@@ -28597,8 +28716,8 @@
       <c r="AH61" s="5"/>
       <c r="AI61" s="5"/>
       <c r="AJ61" s="5"/>
-      <c r="AK61" s="5" t="s">
-        <v>429</v>
+      <c r="AK61" s="5" t="n">
+        <v>660</v>
       </c>
       <c r="AL61" s="5"/>
       <c r="AM61" s="5"/>
@@ -28991,22 +29110,24 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="B62" s="5" t="s">
         <v>503</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>504</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="D62" s="5" t="s">
-        <v>429</v>
+      <c r="D62" s="5" t="n">
+        <v>86</v>
       </c>
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
-      <c r="I62" s="5"/>
+      <c r="I62" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="J62" s="5"/>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
@@ -29426,6 +29547,445 @@
       <c r="PH62" s="5"/>
       <c r="PI62" s="5"/>
     </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="5"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="5"/>
+      <c r="O63" s="5"/>
+      <c r="P63" s="5"/>
+      <c r="Q63" s="5"/>
+      <c r="R63" s="5"/>
+      <c r="S63" s="5"/>
+      <c r="T63" s="5"/>
+      <c r="U63" s="5"/>
+      <c r="V63" s="5"/>
+      <c r="W63" s="5"/>
+      <c r="X63" s="5"/>
+      <c r="Y63" s="5"/>
+      <c r="Z63" s="5"/>
+      <c r="AA63" s="5"/>
+      <c r="AB63" s="5"/>
+      <c r="AC63" s="5"/>
+      <c r="AD63" s="5"/>
+      <c r="AE63" s="5"/>
+      <c r="AF63" s="5"/>
+      <c r="AG63" s="5"/>
+      <c r="AH63" s="5"/>
+      <c r="AI63" s="5"/>
+      <c r="AJ63" s="5"/>
+      <c r="AK63" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="AL63" s="5"/>
+      <c r="AM63" s="5"/>
+      <c r="AN63" s="5"/>
+      <c r="AO63" s="5"/>
+      <c r="AP63" s="5"/>
+      <c r="AQ63" s="5"/>
+      <c r="AR63" s="5"/>
+      <c r="AS63" s="5"/>
+      <c r="AT63" s="5"/>
+      <c r="AU63" s="5"/>
+      <c r="AV63" s="5"/>
+      <c r="AW63" s="5"/>
+      <c r="AX63" s="5"/>
+      <c r="AY63" s="5"/>
+      <c r="AZ63" s="5"/>
+      <c r="BA63" s="5"/>
+      <c r="BB63" s="5"/>
+      <c r="BC63" s="5"/>
+      <c r="BD63" s="5"/>
+      <c r="BE63" s="5"/>
+      <c r="BF63" s="5"/>
+      <c r="BG63" s="5"/>
+      <c r="BH63" s="5"/>
+      <c r="BI63" s="5"/>
+      <c r="BJ63" s="5"/>
+      <c r="BK63" s="5"/>
+      <c r="BL63" s="5"/>
+      <c r="BM63" s="5"/>
+      <c r="BN63" s="5"/>
+      <c r="BO63" s="5"/>
+      <c r="BP63" s="5"/>
+      <c r="BQ63" s="5"/>
+      <c r="BR63" s="5"/>
+      <c r="BS63" s="5"/>
+      <c r="BT63" s="5"/>
+      <c r="BU63" s="5"/>
+      <c r="BV63" s="5"/>
+      <c r="BW63" s="5"/>
+      <c r="BX63" s="5"/>
+      <c r="BY63" s="5"/>
+      <c r="BZ63" s="5"/>
+      <c r="CA63" s="5"/>
+      <c r="CB63" s="5"/>
+      <c r="CC63" s="5"/>
+      <c r="CD63" s="5"/>
+      <c r="CE63" s="5"/>
+      <c r="CF63" s="5"/>
+      <c r="CG63" s="5"/>
+      <c r="CH63" s="5"/>
+      <c r="CI63" s="5"/>
+      <c r="CJ63" s="5"/>
+      <c r="CK63" s="5"/>
+      <c r="CL63" s="5"/>
+      <c r="CM63" s="5"/>
+      <c r="CN63" s="5"/>
+      <c r="CO63" s="5"/>
+      <c r="CP63" s="5"/>
+      <c r="CQ63" s="5"/>
+      <c r="CR63" s="5"/>
+      <c r="CS63" s="5"/>
+      <c r="CT63" s="5"/>
+      <c r="CU63" s="5"/>
+      <c r="CV63" s="5"/>
+      <c r="CW63" s="5"/>
+      <c r="CX63" s="5"/>
+      <c r="CY63" s="5"/>
+      <c r="CZ63" s="5"/>
+      <c r="DA63" s="5"/>
+      <c r="DB63" s="5"/>
+      <c r="DC63" s="5"/>
+      <c r="DD63" s="5"/>
+      <c r="DE63" s="5"/>
+      <c r="DF63" s="5"/>
+      <c r="DG63" s="5"/>
+      <c r="DH63" s="5"/>
+      <c r="DI63" s="5"/>
+      <c r="DJ63" s="5"/>
+      <c r="DK63" s="5"/>
+      <c r="DL63" s="5"/>
+      <c r="DM63" s="5"/>
+      <c r="DN63" s="5"/>
+      <c r="DO63" s="5"/>
+      <c r="DP63" s="5"/>
+      <c r="DQ63" s="5"/>
+      <c r="DR63" s="5"/>
+      <c r="DS63" s="5"/>
+      <c r="DT63" s="5"/>
+      <c r="DU63" s="5"/>
+      <c r="DV63" s="5"/>
+      <c r="DW63" s="5"/>
+      <c r="DX63" s="5"/>
+      <c r="DY63" s="5"/>
+      <c r="DZ63" s="5"/>
+      <c r="EA63" s="5"/>
+      <c r="EB63" s="5"/>
+      <c r="EC63" s="5"/>
+      <c r="ED63" s="5"/>
+      <c r="EE63" s="5"/>
+      <c r="EF63" s="5"/>
+      <c r="EG63" s="5"/>
+      <c r="EH63" s="5"/>
+      <c r="EI63" s="5"/>
+      <c r="EJ63" s="5"/>
+      <c r="EK63" s="5"/>
+      <c r="EL63" s="5"/>
+      <c r="EM63" s="5"/>
+      <c r="EN63" s="5"/>
+      <c r="EO63" s="5"/>
+      <c r="EP63" s="5"/>
+      <c r="EQ63" s="5"/>
+      <c r="ER63" s="5"/>
+      <c r="ES63" s="5"/>
+      <c r="ET63" s="5"/>
+      <c r="EU63" s="5"/>
+      <c r="EV63" s="5"/>
+      <c r="EW63" s="5"/>
+      <c r="EX63" s="5"/>
+      <c r="EY63" s="5"/>
+      <c r="EZ63" s="5"/>
+      <c r="FA63" s="5"/>
+      <c r="FB63" s="5"/>
+      <c r="FC63" s="5"/>
+      <c r="FD63" s="5"/>
+      <c r="FE63" s="5"/>
+      <c r="FF63" s="5"/>
+      <c r="FG63" s="5"/>
+      <c r="FH63" s="5"/>
+      <c r="FI63" s="5"/>
+      <c r="FJ63" s="5"/>
+      <c r="FK63" s="5"/>
+      <c r="FL63" s="5"/>
+      <c r="FM63" s="5"/>
+      <c r="FN63" s="5"/>
+      <c r="FO63" s="5"/>
+      <c r="FP63" s="5"/>
+      <c r="FQ63" s="5"/>
+      <c r="FR63" s="5"/>
+      <c r="FS63" s="5"/>
+      <c r="FT63" s="5"/>
+      <c r="FU63" s="5"/>
+      <c r="FV63" s="5"/>
+      <c r="FW63" s="5"/>
+      <c r="FX63" s="5"/>
+      <c r="FY63" s="5"/>
+      <c r="FZ63" s="5"/>
+      <c r="GA63" s="5"/>
+      <c r="GB63" s="5"/>
+      <c r="GC63" s="5"/>
+      <c r="GD63" s="5"/>
+      <c r="GE63" s="5"/>
+      <c r="GF63" s="5"/>
+      <c r="GG63" s="5"/>
+      <c r="GH63" s="5"/>
+      <c r="GI63" s="5"/>
+      <c r="GJ63" s="5"/>
+      <c r="GK63" s="5"/>
+      <c r="GL63" s="5"/>
+      <c r="GM63" s="5"/>
+      <c r="GN63" s="5"/>
+      <c r="GO63" s="5"/>
+      <c r="GP63" s="5"/>
+      <c r="GQ63" s="5"/>
+      <c r="GR63" s="5"/>
+      <c r="GS63" s="5"/>
+      <c r="GT63" s="5"/>
+      <c r="GU63" s="5"/>
+      <c r="GV63" s="5"/>
+      <c r="GW63" s="5"/>
+      <c r="GX63" s="5"/>
+      <c r="GY63" s="5"/>
+      <c r="GZ63" s="5"/>
+      <c r="HA63" s="5"/>
+      <c r="HB63" s="5"/>
+      <c r="HC63" s="5"/>
+      <c r="HD63" s="5"/>
+      <c r="HE63" s="5"/>
+      <c r="HF63" s="5"/>
+      <c r="HG63" s="5"/>
+      <c r="HH63" s="5"/>
+      <c r="HI63" s="5"/>
+      <c r="HJ63" s="5"/>
+      <c r="HK63" s="5"/>
+      <c r="HL63" s="5"/>
+      <c r="HM63" s="5"/>
+      <c r="HN63" s="5"/>
+      <c r="HO63" s="5"/>
+      <c r="HP63" s="5"/>
+      <c r="HQ63" s="5"/>
+      <c r="HR63" s="5"/>
+      <c r="HS63" s="5"/>
+      <c r="HT63" s="5"/>
+      <c r="HU63" s="5"/>
+      <c r="HV63" s="5"/>
+      <c r="HW63" s="5"/>
+      <c r="HX63" s="5"/>
+      <c r="HY63" s="5"/>
+      <c r="HZ63" s="5"/>
+      <c r="IA63" s="5"/>
+      <c r="IB63" s="5"/>
+      <c r="IC63" s="5"/>
+      <c r="ID63" s="5"/>
+      <c r="IE63" s="5"/>
+      <c r="IF63" s="5"/>
+      <c r="IG63" s="5"/>
+      <c r="IH63" s="5"/>
+      <c r="II63" s="5"/>
+      <c r="IJ63" s="5"/>
+      <c r="IK63" s="5"/>
+      <c r="IL63" s="5"/>
+      <c r="IM63" s="5"/>
+      <c r="IN63" s="5"/>
+      <c r="IO63" s="5"/>
+      <c r="IP63" s="5"/>
+      <c r="IQ63" s="5"/>
+      <c r="IR63" s="5"/>
+      <c r="IS63" s="5"/>
+      <c r="IT63" s="5"/>
+      <c r="IU63" s="5"/>
+      <c r="IV63" s="5"/>
+      <c r="IW63" s="5"/>
+      <c r="IX63" s="5"/>
+      <c r="IY63" s="5"/>
+      <c r="IZ63" s="5"/>
+      <c r="JA63" s="5"/>
+      <c r="JB63" s="5"/>
+      <c r="JC63" s="5"/>
+      <c r="JD63" s="5"/>
+      <c r="JE63" s="5"/>
+      <c r="JF63" s="5"/>
+      <c r="JG63" s="5"/>
+      <c r="JH63" s="5"/>
+      <c r="JI63" s="5"/>
+      <c r="JJ63" s="5"/>
+      <c r="JK63" s="5"/>
+      <c r="JL63" s="5"/>
+      <c r="JM63" s="5"/>
+      <c r="JN63" s="5"/>
+      <c r="JO63" s="5"/>
+      <c r="JP63" s="5"/>
+      <c r="JQ63" s="5"/>
+      <c r="JR63" s="5"/>
+      <c r="JS63" s="5"/>
+      <c r="JT63" s="5"/>
+      <c r="JU63" s="5"/>
+      <c r="JV63" s="5"/>
+      <c r="JW63" s="5"/>
+      <c r="JX63" s="5"/>
+      <c r="JY63" s="5"/>
+      <c r="JZ63" s="5"/>
+      <c r="KA63" s="5"/>
+      <c r="KB63" s="5"/>
+      <c r="KC63" s="5"/>
+      <c r="KD63" s="5"/>
+      <c r="KE63" s="5"/>
+      <c r="KF63" s="5"/>
+      <c r="KG63" s="5"/>
+      <c r="KH63" s="5"/>
+      <c r="KI63" s="5"/>
+      <c r="KJ63" s="5"/>
+      <c r="KK63" s="5"/>
+      <c r="KL63" s="5"/>
+      <c r="KM63" s="5"/>
+      <c r="KN63" s="5"/>
+      <c r="KO63" s="5"/>
+      <c r="KP63" s="5"/>
+      <c r="KQ63" s="5"/>
+      <c r="KR63" s="5"/>
+      <c r="KS63" s="5"/>
+      <c r="KT63" s="5"/>
+      <c r="KU63" s="5"/>
+      <c r="KV63" s="5"/>
+      <c r="KW63" s="5"/>
+      <c r="KX63" s="5"/>
+      <c r="KY63" s="5"/>
+      <c r="KZ63" s="5"/>
+      <c r="LA63" s="5"/>
+      <c r="LB63" s="5"/>
+      <c r="LC63" s="5"/>
+      <c r="LD63" s="5"/>
+      <c r="LE63" s="5"/>
+      <c r="LF63" s="5"/>
+      <c r="LG63" s="5"/>
+      <c r="LH63" s="5"/>
+      <c r="LI63" s="5"/>
+      <c r="LJ63" s="5"/>
+      <c r="LK63" s="5"/>
+      <c r="LL63" s="5"/>
+      <c r="LM63" s="5"/>
+      <c r="LN63" s="5"/>
+      <c r="LO63" s="5"/>
+      <c r="LP63" s="5"/>
+      <c r="LQ63" s="5"/>
+      <c r="LR63" s="5"/>
+      <c r="LS63" s="5"/>
+      <c r="LT63" s="5"/>
+      <c r="LU63" s="5"/>
+      <c r="LV63" s="5"/>
+      <c r="LW63" s="5"/>
+      <c r="LX63" s="5"/>
+      <c r="LY63" s="5"/>
+      <c r="LZ63" s="5"/>
+      <c r="MA63" s="5"/>
+      <c r="MB63" s="5"/>
+      <c r="MC63" s="5"/>
+      <c r="MD63" s="5"/>
+      <c r="ME63" s="5"/>
+      <c r="MF63" s="5"/>
+      <c r="MG63" s="5"/>
+      <c r="MH63" s="5"/>
+      <c r="MI63" s="5"/>
+      <c r="MJ63" s="5"/>
+      <c r="MK63" s="5"/>
+      <c r="ML63" s="5"/>
+      <c r="MM63" s="5"/>
+      <c r="MN63" s="5"/>
+      <c r="MO63" s="5"/>
+      <c r="MP63" s="5"/>
+      <c r="MQ63" s="5"/>
+      <c r="MR63" s="5"/>
+      <c r="MS63" s="5"/>
+      <c r="MT63" s="5"/>
+      <c r="MU63" s="5"/>
+      <c r="MV63" s="5"/>
+      <c r="MW63" s="5"/>
+      <c r="MX63" s="5"/>
+      <c r="MY63" s="5"/>
+      <c r="MZ63" s="5"/>
+      <c r="NA63" s="5"/>
+      <c r="NB63" s="5"/>
+      <c r="NC63" s="5"/>
+      <c r="ND63" s="5"/>
+      <c r="NE63" s="5"/>
+      <c r="NF63" s="5"/>
+      <c r="NG63" s="5"/>
+      <c r="NH63" s="5"/>
+      <c r="NI63" s="5"/>
+      <c r="NJ63" s="5"/>
+      <c r="NK63" s="5"/>
+      <c r="NL63" s="5"/>
+      <c r="NM63" s="5"/>
+      <c r="NN63" s="5"/>
+      <c r="NO63" s="5"/>
+      <c r="NP63" s="5"/>
+      <c r="NQ63" s="5"/>
+      <c r="NR63" s="5"/>
+      <c r="NS63" s="5"/>
+      <c r="NT63" s="5"/>
+      <c r="NU63" s="5"/>
+      <c r="NV63" s="5"/>
+      <c r="NW63" s="5"/>
+      <c r="NX63" s="5"/>
+      <c r="NY63" s="5"/>
+      <c r="NZ63" s="5"/>
+      <c r="OA63" s="5"/>
+      <c r="OB63" s="5"/>
+      <c r="OC63" s="5"/>
+      <c r="OD63" s="5"/>
+      <c r="OE63" s="5"/>
+      <c r="OF63" s="5"/>
+      <c r="OG63" s="5"/>
+      <c r="OH63" s="5"/>
+      <c r="OI63" s="5"/>
+      <c r="OJ63" s="5"/>
+      <c r="OK63" s="5"/>
+      <c r="OL63" s="5"/>
+      <c r="OM63" s="5"/>
+      <c r="ON63" s="5"/>
+      <c r="OO63" s="5"/>
+      <c r="OP63" s="5"/>
+      <c r="OQ63" s="5"/>
+      <c r="OR63" s="5"/>
+      <c r="OS63" s="5"/>
+      <c r="OT63" s="5"/>
+      <c r="OU63" s="5"/>
+      <c r="OV63" s="5"/>
+      <c r="OW63" s="5"/>
+      <c r="OX63" s="5"/>
+      <c r="OY63" s="5"/>
+      <c r="OZ63" s="5"/>
+      <c r="PA63" s="5"/>
+      <c r="PB63" s="5"/>
+      <c r="PC63" s="5"/>
+      <c r="PD63" s="5"/>
+      <c r="PE63" s="5"/>
+      <c r="PF63" s="5"/>
+      <c r="PG63" s="5"/>
+      <c r="PH63" s="5"/>
+      <c r="PI63" s="5"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:PI1"/>

--- a/Part2_PlatformBenchmarks_Results.xlsx
+++ b/Part2_PlatformBenchmarks_Results.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="506">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 2: Platform Benchmarks</t>
   </si>
@@ -3660,7 +3660,9 @@
         <v>75.81</v>
       </c>
       <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="F4" s="5" t="n">
+        <v>3.45</v>
+      </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5" t="n">
@@ -4099,7 +4101,9 @@
         <v>429</v>
       </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+      <c r="F5" s="5" t="n">
+        <v>0.41</v>
+      </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5" t="s">
@@ -4538,7 +4542,9 @@
         <v>36.86</v>
       </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="F6" s="5" t="n">
+        <v>4.48</v>
+      </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5" t="s">
@@ -4977,7 +4983,9 @@
         <v>37.79</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="F7" s="5" t="n">
+        <v>6.24</v>
+      </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
@@ -5416,7 +5424,9 @@
         <v>37.71</v>
       </c>
       <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="F8" s="5" t="n">
+        <v>5.94</v>
+      </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
       <c r="I8" s="5" t="s">
@@ -5855,7 +5865,9 @@
         <v>17.41</v>
       </c>
       <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
+      <c r="F9" s="5" t="n">
+        <v>2.89</v>
+      </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
       <c r="I9" s="5" t="s">
@@ -6294,7 +6306,9 @@
         <v>173.91</v>
       </c>
       <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
+      <c r="F10" s="5" t="n">
+        <v>5.08</v>
+      </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5" t="s">
@@ -6733,7 +6747,9 @@
         <v>199.2</v>
       </c>
       <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
+      <c r="F11" s="5" t="n">
+        <v>5.52</v>
+      </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5" t="s">
@@ -7172,7 +7188,9 @@
         <v>205.76</v>
       </c>
       <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="F12" s="5" t="n">
+        <v>5.05</v>
+      </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5" t="s">
@@ -7611,7 +7629,9 @@
         <v>214.59</v>
       </c>
       <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
+      <c r="F13" s="5" t="n">
+        <v>5.99</v>
+      </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5" t="s">
@@ -8050,7 +8070,9 @@
         <v>210.97</v>
       </c>
       <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="F14" s="5" t="n">
+        <v>35.47</v>
+      </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
       <c r="I14" s="5" t="s">
@@ -8489,7 +8511,9 @@
         <v>11.56</v>
       </c>
       <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
+      <c r="F15" s="5" t="n">
+        <v>17.77</v>
+      </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5" t="n">
@@ -8928,7 +8952,9 @@
         <v>11.52</v>
       </c>
       <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
+      <c r="F16" s="5" t="n">
+        <v>11.52</v>
+      </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5" t="n">
@@ -9367,7 +9393,9 @@
         <v>99.63</v>
       </c>
       <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
+      <c r="F17" s="5" t="n">
+        <v>64.83</v>
+      </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5" t="n">
@@ -9806,7 +9834,9 @@
         <v>0</v>
       </c>
       <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+      <c r="F18" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5" t="n">
@@ -10245,7 +10275,9 @@
         <v>2</v>
       </c>
       <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
+      <c r="F19" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5" t="n">
@@ -10684,7 +10716,9 @@
         <v>51</v>
       </c>
       <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
+      <c r="F20" s="5" t="n">
+        <v>108</v>
+      </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
       <c r="I20" s="5" t="n">
@@ -11123,7 +11157,9 @@
         <v>0.006</v>
       </c>
       <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
+      <c r="F21" s="5" t="n">
+        <v>0.003</v>
+      </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
       <c r="I21" s="5" t="n">
@@ -11562,7 +11598,9 @@
         <v>0.5</v>
       </c>
       <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
+      <c r="F22" s="5" t="n">
+        <v>1.9</v>
+      </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5" t="n">
@@ -12001,7 +12039,9 @@
         <v>325</v>
       </c>
       <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
+      <c r="F23" s="5" t="n">
+        <v>14</v>
+      </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
       <c r="I23" s="5" t="n">
@@ -12440,7 +12480,9 @@
         <v>56</v>
       </c>
       <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
+      <c r="F24" s="5" t="n">
+        <v>45</v>
+      </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
       <c r="I24" s="5" t="n">
@@ -12879,7 +12921,9 @@
         <v>0.61</v>
       </c>
       <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
+      <c r="F25" s="5" t="n">
+        <v>5.67</v>
+      </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
       <c r="I25" s="5" t="n">
@@ -13318,7 +13362,9 @@
         <v>0.99</v>
       </c>
       <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
+      <c r="F26" s="5" t="n">
+        <v>7.38</v>
+      </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
       <c r="I26" s="5" t="s">
@@ -13757,7 +13803,9 @@
         <v>0.99</v>
       </c>
       <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
+      <c r="F27" s="5" t="n">
+        <v>16.85</v>
+      </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
       <c r="I27" s="5" t="s">
@@ -14196,7 +14244,9 @@
         <v>2</v>
       </c>
       <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
+      <c r="F28" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5" t="s">
@@ -14635,7 +14685,9 @@
         <v>429</v>
       </c>
       <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
+      <c r="F29" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
       <c r="I29" s="5" t="s">
@@ -15074,7 +15126,9 @@
         <v>6</v>
       </c>
       <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
+      <c r="F30" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5" t="s">
@@ -15513,7 +15567,9 @@
         <v>5068.28</v>
       </c>
       <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
+      <c r="F31" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
       <c r="I31" s="5" t="s">
@@ -15952,7 +16008,9 @@
         <v>5.155</v>
       </c>
       <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
+      <c r="F32" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5" t="s">
@@ -16391,7 +16449,9 @@
         <v>128000000</v>
       </c>
       <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
+      <c r="F33" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5" t="s">
@@ -16830,7 +16890,9 @@
         <v>5.16</v>
       </c>
       <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
+      <c r="F34" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5" t="s">
@@ -17269,7 +17331,9 @@
         <v>429</v>
       </c>
       <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
+      <c r="F35" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
       <c r="I35" s="5" t="s">
@@ -17708,7 +17772,9 @@
         <v>429</v>
       </c>
       <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
+      <c r="F36" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="5" t="s">
@@ -18147,7 +18213,9 @@
         <v>429</v>
       </c>
       <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
+      <c r="F37" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5" t="s">
@@ -18586,7 +18654,9 @@
         <v>429</v>
       </c>
       <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
+      <c r="F38" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
       <c r="I38" s="5" t="s">
@@ -19025,7 +19095,9 @@
         <v>429</v>
       </c>
       <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
+      <c r="F39" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5" t="s">
@@ -19464,7 +19536,9 @@
         <v>429</v>
       </c>
       <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
+      <c r="F40" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5" t="s">
@@ -19903,7 +19977,9 @@
         <v>429</v>
       </c>
       <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
+      <c r="F41" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="5" t="s">
@@ -20342,7 +20418,9 @@
         <v>9142.04</v>
       </c>
       <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
+      <c r="F42" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5" t="s">
@@ -20781,7 +20859,9 @@
         <v>429</v>
       </c>
       <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
+      <c r="F43" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5" t="n">
@@ -21220,7 +21300,9 @@
         <v>429</v>
       </c>
       <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
+      <c r="F44" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5" t="s">
@@ -21659,7 +21741,9 @@
         <v>429</v>
       </c>
       <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
+      <c r="F45" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5" t="s">
@@ -22098,7 +22182,9 @@
         <v>429</v>
       </c>
       <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
+      <c r="F46" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5" t="s">
@@ -22537,7 +22623,9 @@
         <v>429</v>
       </c>
       <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
+      <c r="F47" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5" t="s">
@@ -22976,7 +23064,9 @@
         <v>429</v>
       </c>
       <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
+      <c r="F48" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5" t="s">
@@ -23415,7 +23505,9 @@
         <v>161.03</v>
       </c>
       <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
+      <c r="F49" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5" t="s">
@@ -23854,7 +23946,9 @@
         <v>26.5</v>
       </c>
       <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
+      <c r="F50" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5" t="s">
@@ -24293,7 +24387,9 @@
         <v>101.85</v>
       </c>
       <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
+      <c r="F51" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5" t="s">
@@ -24732,7 +24828,9 @@
         <v>103.1</v>
       </c>
       <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
+      <c r="F52" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5" t="s">
@@ -25171,7 +25269,9 @@
         <v>60.29</v>
       </c>
       <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
+      <c r="F53" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="5" t="s">
@@ -25610,7 +25710,9 @@
         <v>5.49</v>
       </c>
       <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
+      <c r="F54" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5" t="s">
@@ -26049,7 +26151,9 @@
         <v>-0.431</v>
       </c>
       <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
+      <c r="F55" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="5" t="s">
@@ -26488,7 +26592,9 @@
         <v>429</v>
       </c>
       <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
+      <c r="F56" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="5" t="s">
@@ -26927,7 +27033,9 @@
         <v>429</v>
       </c>
       <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
+      <c r="F57" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="5" t="s">
@@ -27366,7 +27474,9 @@
         <v>429</v>
       </c>
       <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
+      <c r="F58" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="5" t="s">
@@ -27805,7 +27915,9 @@
         <v>429</v>
       </c>
       <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
+      <c r="F59" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5" t="s">
@@ -28244,7 +28356,9 @@
         <v>429</v>
       </c>
       <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
+      <c r="F60" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5" t="s">
@@ -28683,7 +28797,9 @@
         <v>429</v>
       </c>
       <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
+      <c r="F61" s="5" t="n">
+        <v>520</v>
+      </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5" t="s">
@@ -29122,7 +29238,9 @@
         <v>86</v>
       </c>
       <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
+      <c r="F62" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5" t="s">
@@ -29561,7 +29679,9 @@
         <v>429</v>
       </c>
       <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
+      <c r="F63" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="5" t="s">

--- a/Part2_PlatformBenchmarks_Results.xlsx
+++ b/Part2_PlatformBenchmarks_Results.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="506">
   <si>
     <t xml:space="preserve">Arduino Benchmark Suite – Part 2: Platform Benchmarks</t>
   </si>
@@ -4082,7 +4082,9 @@
       <c r="PC4" s="5"/>
       <c r="PD4" s="5"/>
       <c r="PE4" s="5"/>
-      <c r="PF4" s="5"/>
+      <c r="PF4" s="5" t="n">
+        <v>3.45</v>
+      </c>
       <c r="PG4" s="5"/>
       <c r="PH4" s="5"/>
       <c r="PI4" s="5"/>
@@ -4523,7 +4525,9 @@
       <c r="PC5" s="5"/>
       <c r="PD5" s="5"/>
       <c r="PE5" s="5"/>
-      <c r="PF5" s="5"/>
+      <c r="PF5" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="PG5" s="5"/>
       <c r="PH5" s="5"/>
       <c r="PI5" s="5"/>
@@ -4964,7 +4968,9 @@
       <c r="PC6" s="5"/>
       <c r="PD6" s="5"/>
       <c r="PE6" s="5"/>
-      <c r="PF6" s="5"/>
+      <c r="PF6" s="5" t="n">
+        <v>4.48</v>
+      </c>
       <c r="PG6" s="5"/>
       <c r="PH6" s="5"/>
       <c r="PI6" s="5"/>
@@ -5405,7 +5411,9 @@
       <c r="PC7" s="5"/>
       <c r="PD7" s="5"/>
       <c r="PE7" s="5"/>
-      <c r="PF7" s="5"/>
+      <c r="PF7" s="5" t="n">
+        <v>6.24</v>
+      </c>
       <c r="PG7" s="5"/>
       <c r="PH7" s="5"/>
       <c r="PI7" s="5"/>
@@ -5846,7 +5854,9 @@
       <c r="PC8" s="5"/>
       <c r="PD8" s="5"/>
       <c r="PE8" s="5"/>
-      <c r="PF8" s="5"/>
+      <c r="PF8" s="5" t="n">
+        <v>5.94</v>
+      </c>
       <c r="PG8" s="5"/>
       <c r="PH8" s="5"/>
       <c r="PI8" s="5"/>
@@ -6287,7 +6297,9 @@
       <c r="PC9" s="5"/>
       <c r="PD9" s="5"/>
       <c r="PE9" s="5"/>
-      <c r="PF9" s="5"/>
+      <c r="PF9" s="5" t="n">
+        <v>2.89</v>
+      </c>
       <c r="PG9" s="5"/>
       <c r="PH9" s="5"/>
       <c r="PI9" s="5"/>
@@ -6728,7 +6740,9 @@
       <c r="PC10" s="5"/>
       <c r="PD10" s="5"/>
       <c r="PE10" s="5"/>
-      <c r="PF10" s="5"/>
+      <c r="PF10" s="5" t="n">
+        <v>5.08</v>
+      </c>
       <c r="PG10" s="5"/>
       <c r="PH10" s="5"/>
       <c r="PI10" s="5"/>
@@ -7169,7 +7183,9 @@
       <c r="PC11" s="5"/>
       <c r="PD11" s="5"/>
       <c r="PE11" s="5"/>
-      <c r="PF11" s="5"/>
+      <c r="PF11" s="5" t="n">
+        <v>5.52</v>
+      </c>
       <c r="PG11" s="5"/>
       <c r="PH11" s="5"/>
       <c r="PI11" s="5"/>
@@ -7610,7 +7626,9 @@
       <c r="PC12" s="5"/>
       <c r="PD12" s="5"/>
       <c r="PE12" s="5"/>
-      <c r="PF12" s="5"/>
+      <c r="PF12" s="5" t="n">
+        <v>5.06</v>
+      </c>
       <c r="PG12" s="5"/>
       <c r="PH12" s="5"/>
       <c r="PI12" s="5"/>
@@ -8051,7 +8069,9 @@
       <c r="PC13" s="5"/>
       <c r="PD13" s="5"/>
       <c r="PE13" s="5"/>
-      <c r="PF13" s="5"/>
+      <c r="PF13" s="5" t="n">
+        <v>5.99</v>
+      </c>
       <c r="PG13" s="5"/>
       <c r="PH13" s="5"/>
       <c r="PI13" s="5"/>
@@ -8492,7 +8512,9 @@
       <c r="PC14" s="5"/>
       <c r="PD14" s="5"/>
       <c r="PE14" s="5"/>
-      <c r="PF14" s="5"/>
+      <c r="PF14" s="5" t="n">
+        <v>35.47</v>
+      </c>
       <c r="PG14" s="5"/>
       <c r="PH14" s="5"/>
       <c r="PI14" s="5"/>
@@ -8933,7 +8955,9 @@
       <c r="PC15" s="5"/>
       <c r="PD15" s="5"/>
       <c r="PE15" s="5"/>
-      <c r="PF15" s="5"/>
+      <c r="PF15" s="5" t="n">
+        <v>17.76</v>
+      </c>
       <c r="PG15" s="5"/>
       <c r="PH15" s="5"/>
       <c r="PI15" s="5"/>
@@ -9374,7 +9398,9 @@
       <c r="PC16" s="5"/>
       <c r="PD16" s="5"/>
       <c r="PE16" s="5"/>
-      <c r="PF16" s="5"/>
+      <c r="PF16" s="5" t="n">
+        <v>11.52</v>
+      </c>
       <c r="PG16" s="5"/>
       <c r="PH16" s="5"/>
       <c r="PI16" s="5"/>
@@ -9815,7 +9841,9 @@
       <c r="PC17" s="5"/>
       <c r="PD17" s="5"/>
       <c r="PE17" s="5"/>
-      <c r="PF17" s="5"/>
+      <c r="PF17" s="5" t="n">
+        <v>64.85</v>
+      </c>
       <c r="PG17" s="5"/>
       <c r="PH17" s="5"/>
       <c r="PI17" s="5"/>
@@ -10256,7 +10284,9 @@
       <c r="PC18" s="5"/>
       <c r="PD18" s="5"/>
       <c r="PE18" s="5"/>
-      <c r="PF18" s="5"/>
+      <c r="PF18" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="PG18" s="5"/>
       <c r="PH18" s="5"/>
       <c r="PI18" s="5"/>
@@ -10697,7 +10727,9 @@
       <c r="PC19" s="5"/>
       <c r="PD19" s="5"/>
       <c r="PE19" s="5"/>
-      <c r="PF19" s="5"/>
+      <c r="PF19" s="5" t="n">
+        <v>4</v>
+      </c>
       <c r="PG19" s="5"/>
       <c r="PH19" s="5"/>
       <c r="PI19" s="5"/>
@@ -11138,7 +11170,9 @@
       <c r="PC20" s="5"/>
       <c r="PD20" s="5"/>
       <c r="PE20" s="5"/>
-      <c r="PF20" s="5"/>
+      <c r="PF20" s="5" t="n">
+        <v>108</v>
+      </c>
       <c r="PG20" s="5"/>
       <c r="PH20" s="5"/>
       <c r="PI20" s="5"/>
@@ -11579,7 +11613,9 @@
       <c r="PC21" s="5"/>
       <c r="PD21" s="5"/>
       <c r="PE21" s="5"/>
-      <c r="PF21" s="5"/>
+      <c r="PF21" s="5" t="n">
+        <v>0.003</v>
+      </c>
       <c r="PG21" s="5"/>
       <c r="PH21" s="5"/>
       <c r="PI21" s="5"/>
@@ -12020,7 +12056,9 @@
       <c r="PC22" s="5"/>
       <c r="PD22" s="5"/>
       <c r="PE22" s="5"/>
-      <c r="PF22" s="5"/>
+      <c r="PF22" s="5" t="n">
+        <v>1.7</v>
+      </c>
       <c r="PG22" s="5"/>
       <c r="PH22" s="5"/>
       <c r="PI22" s="5"/>
@@ -12461,7 +12499,9 @@
       <c r="PC23" s="5"/>
       <c r="PD23" s="5"/>
       <c r="PE23" s="5"/>
-      <c r="PF23" s="5"/>
+      <c r="PF23" s="5" t="n">
+        <v>14</v>
+      </c>
       <c r="PG23" s="5"/>
       <c r="PH23" s="5"/>
       <c r="PI23" s="5"/>
@@ -12902,7 +12942,9 @@
       <c r="PC24" s="5"/>
       <c r="PD24" s="5"/>
       <c r="PE24" s="5"/>
-      <c r="PF24" s="5"/>
+      <c r="PF24" s="5" t="n">
+        <v>45</v>
+      </c>
       <c r="PG24" s="5"/>
       <c r="PH24" s="5"/>
       <c r="PI24" s="5"/>
@@ -13343,7 +13385,9 @@
       <c r="PC25" s="5"/>
       <c r="PD25" s="5"/>
       <c r="PE25" s="5"/>
-      <c r="PF25" s="5"/>
+      <c r="PF25" s="5" t="n">
+        <v>5.67</v>
+      </c>
       <c r="PG25" s="5"/>
       <c r="PH25" s="5"/>
       <c r="PI25" s="5"/>
@@ -13784,7 +13828,9 @@
       <c r="PC26" s="5"/>
       <c r="PD26" s="5"/>
       <c r="PE26" s="5"/>
-      <c r="PF26" s="5"/>
+      <c r="PF26" s="5" t="n">
+        <v>7.39</v>
+      </c>
       <c r="PG26" s="5"/>
       <c r="PH26" s="5"/>
       <c r="PI26" s="5"/>
@@ -14225,7 +14271,9 @@
       <c r="PC27" s="5"/>
       <c r="PD27" s="5"/>
       <c r="PE27" s="5"/>
-      <c r="PF27" s="5"/>
+      <c r="PF27" s="5" t="n">
+        <v>17.49</v>
+      </c>
       <c r="PG27" s="5"/>
       <c r="PH27" s="5"/>
       <c r="PI27" s="5"/>
@@ -14666,7 +14714,9 @@
       <c r="PC28" s="5"/>
       <c r="PD28" s="5"/>
       <c r="PE28" s="5"/>
-      <c r="PF28" s="5"/>
+      <c r="PF28" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG28" s="5"/>
       <c r="PH28" s="5"/>
       <c r="PI28" s="5"/>
@@ -15107,7 +15157,9 @@
       <c r="PC29" s="5"/>
       <c r="PD29" s="5"/>
       <c r="PE29" s="5"/>
-      <c r="PF29" s="5"/>
+      <c r="PF29" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG29" s="5"/>
       <c r="PH29" s="5"/>
       <c r="PI29" s="5"/>
@@ -15548,7 +15600,9 @@
       <c r="PC30" s="5"/>
       <c r="PD30" s="5"/>
       <c r="PE30" s="5"/>
-      <c r="PF30" s="5"/>
+      <c r="PF30" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG30" s="5"/>
       <c r="PH30" s="5"/>
       <c r="PI30" s="5"/>
@@ -15989,7 +16043,9 @@
       <c r="PC31" s="5"/>
       <c r="PD31" s="5"/>
       <c r="PE31" s="5"/>
-      <c r="PF31" s="5"/>
+      <c r="PF31" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG31" s="5"/>
       <c r="PH31" s="5"/>
       <c r="PI31" s="5"/>
@@ -16430,7 +16486,9 @@
       <c r="PC32" s="5"/>
       <c r="PD32" s="5"/>
       <c r="PE32" s="5"/>
-      <c r="PF32" s="5"/>
+      <c r="PF32" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG32" s="5"/>
       <c r="PH32" s="5"/>
       <c r="PI32" s="5"/>
@@ -16871,7 +16929,9 @@
       <c r="PC33" s="5"/>
       <c r="PD33" s="5"/>
       <c r="PE33" s="5"/>
-      <c r="PF33" s="5"/>
+      <c r="PF33" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG33" s="5"/>
       <c r="PH33" s="5"/>
       <c r="PI33" s="5"/>
@@ -17312,7 +17372,9 @@
       <c r="PC34" s="5"/>
       <c r="PD34" s="5"/>
       <c r="PE34" s="5"/>
-      <c r="PF34" s="5"/>
+      <c r="PF34" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG34" s="5"/>
       <c r="PH34" s="5"/>
       <c r="PI34" s="5"/>
@@ -17753,7 +17815,9 @@
       <c r="PC35" s="5"/>
       <c r="PD35" s="5"/>
       <c r="PE35" s="5"/>
-      <c r="PF35" s="5"/>
+      <c r="PF35" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG35" s="5"/>
       <c r="PH35" s="5"/>
       <c r="PI35" s="5"/>
@@ -18194,7 +18258,9 @@
       <c r="PC36" s="5"/>
       <c r="PD36" s="5"/>
       <c r="PE36" s="5"/>
-      <c r="PF36" s="5"/>
+      <c r="PF36" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG36" s="5"/>
       <c r="PH36" s="5"/>
       <c r="PI36" s="5"/>
@@ -18635,7 +18701,9 @@
       <c r="PC37" s="5"/>
       <c r="PD37" s="5"/>
       <c r="PE37" s="5"/>
-      <c r="PF37" s="5"/>
+      <c r="PF37" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG37" s="5"/>
       <c r="PH37" s="5"/>
       <c r="PI37" s="5"/>
@@ -19076,7 +19144,9 @@
       <c r="PC38" s="5"/>
       <c r="PD38" s="5"/>
       <c r="PE38" s="5"/>
-      <c r="PF38" s="5"/>
+      <c r="PF38" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG38" s="5"/>
       <c r="PH38" s="5"/>
       <c r="PI38" s="5"/>
@@ -19517,7 +19587,9 @@
       <c r="PC39" s="5"/>
       <c r="PD39" s="5"/>
       <c r="PE39" s="5"/>
-      <c r="PF39" s="5"/>
+      <c r="PF39" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG39" s="5"/>
       <c r="PH39" s="5"/>
       <c r="PI39" s="5"/>
@@ -19958,7 +20030,9 @@
       <c r="PC40" s="5"/>
       <c r="PD40" s="5"/>
       <c r="PE40" s="5"/>
-      <c r="PF40" s="5"/>
+      <c r="PF40" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG40" s="5"/>
       <c r="PH40" s="5"/>
       <c r="PI40" s="5"/>
@@ -20399,7 +20473,9 @@
       <c r="PC41" s="5"/>
       <c r="PD41" s="5"/>
       <c r="PE41" s="5"/>
-      <c r="PF41" s="5"/>
+      <c r="PF41" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG41" s="5"/>
       <c r="PH41" s="5"/>
       <c r="PI41" s="5"/>
@@ -20840,7 +20916,9 @@
       <c r="PC42" s="5"/>
       <c r="PD42" s="5"/>
       <c r="PE42" s="5"/>
-      <c r="PF42" s="5"/>
+      <c r="PF42" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG42" s="5"/>
       <c r="PH42" s="5"/>
       <c r="PI42" s="5"/>
@@ -21281,7 +21359,9 @@
       <c r="PC43" s="5"/>
       <c r="PD43" s="5"/>
       <c r="PE43" s="5"/>
-      <c r="PF43" s="5"/>
+      <c r="PF43" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG43" s="5"/>
       <c r="PH43" s="5"/>
       <c r="PI43" s="5"/>
@@ -21722,7 +21802,9 @@
       <c r="PC44" s="5"/>
       <c r="PD44" s="5"/>
       <c r="PE44" s="5"/>
-      <c r="PF44" s="5"/>
+      <c r="PF44" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG44" s="5"/>
       <c r="PH44" s="5"/>
       <c r="PI44" s="5"/>
@@ -22163,7 +22245,9 @@
       <c r="PC45" s="5"/>
       <c r="PD45" s="5"/>
       <c r="PE45" s="5"/>
-      <c r="PF45" s="5"/>
+      <c r="PF45" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG45" s="5"/>
       <c r="PH45" s="5"/>
       <c r="PI45" s="5"/>
@@ -22604,7 +22688,9 @@
       <c r="PC46" s="5"/>
       <c r="PD46" s="5"/>
       <c r="PE46" s="5"/>
-      <c r="PF46" s="5"/>
+      <c r="PF46" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG46" s="5"/>
       <c r="PH46" s="5"/>
       <c r="PI46" s="5"/>
@@ -23045,7 +23131,9 @@
       <c r="PC47" s="5"/>
       <c r="PD47" s="5"/>
       <c r="PE47" s="5"/>
-      <c r="PF47" s="5"/>
+      <c r="PF47" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG47" s="5"/>
       <c r="PH47" s="5"/>
       <c r="PI47" s="5"/>
@@ -23486,7 +23574,9 @@
       <c r="PC48" s="5"/>
       <c r="PD48" s="5"/>
       <c r="PE48" s="5"/>
-      <c r="PF48" s="5"/>
+      <c r="PF48" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG48" s="5"/>
       <c r="PH48" s="5"/>
       <c r="PI48" s="5"/>
@@ -23927,7 +24017,9 @@
       <c r="PC49" s="5"/>
       <c r="PD49" s="5"/>
       <c r="PE49" s="5"/>
-      <c r="PF49" s="5"/>
+      <c r="PF49" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG49" s="5"/>
       <c r="PH49" s="5"/>
       <c r="PI49" s="5"/>
@@ -24368,7 +24460,9 @@
       <c r="PC50" s="5"/>
       <c r="PD50" s="5"/>
       <c r="PE50" s="5"/>
-      <c r="PF50" s="5"/>
+      <c r="PF50" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG50" s="5"/>
       <c r="PH50" s="5"/>
       <c r="PI50" s="5"/>
@@ -24809,7 +24903,9 @@
       <c r="PC51" s="5"/>
       <c r="PD51" s="5"/>
       <c r="PE51" s="5"/>
-      <c r="PF51" s="5"/>
+      <c r="PF51" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG51" s="5"/>
       <c r="PH51" s="5"/>
       <c r="PI51" s="5"/>
@@ -25250,7 +25346,9 @@
       <c r="PC52" s="5"/>
       <c r="PD52" s="5"/>
       <c r="PE52" s="5"/>
-      <c r="PF52" s="5"/>
+      <c r="PF52" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG52" s="5"/>
       <c r="PH52" s="5"/>
       <c r="PI52" s="5"/>
@@ -25691,7 +25789,9 @@
       <c r="PC53" s="5"/>
       <c r="PD53" s="5"/>
       <c r="PE53" s="5"/>
-      <c r="PF53" s="5"/>
+      <c r="PF53" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG53" s="5"/>
       <c r="PH53" s="5"/>
       <c r="PI53" s="5"/>
@@ -26132,7 +26232,9 @@
       <c r="PC54" s="5"/>
       <c r="PD54" s="5"/>
       <c r="PE54" s="5"/>
-      <c r="PF54" s="5"/>
+      <c r="PF54" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG54" s="5"/>
       <c r="PH54" s="5"/>
       <c r="PI54" s="5"/>
@@ -26573,7 +26675,9 @@
       <c r="PC55" s="5"/>
       <c r="PD55" s="5"/>
       <c r="PE55" s="5"/>
-      <c r="PF55" s="5"/>
+      <c r="PF55" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG55" s="5"/>
       <c r="PH55" s="5"/>
       <c r="PI55" s="5"/>
@@ -27014,7 +27118,9 @@
       <c r="PC56" s="5"/>
       <c r="PD56" s="5"/>
       <c r="PE56" s="5"/>
-      <c r="PF56" s="5"/>
+      <c r="PF56" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG56" s="5"/>
       <c r="PH56" s="5"/>
       <c r="PI56" s="5"/>
@@ -27455,7 +27561,9 @@
       <c r="PC57" s="5"/>
       <c r="PD57" s="5"/>
       <c r="PE57" s="5"/>
-      <c r="PF57" s="5"/>
+      <c r="PF57" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG57" s="5"/>
       <c r="PH57" s="5"/>
       <c r="PI57" s="5"/>
@@ -27896,7 +28004,9 @@
       <c r="PC58" s="5"/>
       <c r="PD58" s="5"/>
       <c r="PE58" s="5"/>
-      <c r="PF58" s="5"/>
+      <c r="PF58" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG58" s="5"/>
       <c r="PH58" s="5"/>
       <c r="PI58" s="5"/>
@@ -28337,7 +28447,9 @@
       <c r="PC59" s="5"/>
       <c r="PD59" s="5"/>
       <c r="PE59" s="5"/>
-      <c r="PF59" s="5"/>
+      <c r="PF59" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG59" s="5"/>
       <c r="PH59" s="5"/>
       <c r="PI59" s="5"/>
@@ -28778,7 +28890,9 @@
       <c r="PC60" s="5"/>
       <c r="PD60" s="5"/>
       <c r="PE60" s="5"/>
-      <c r="PF60" s="5"/>
+      <c r="PF60" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG60" s="5"/>
       <c r="PH60" s="5"/>
       <c r="PI60" s="5"/>
@@ -29219,7 +29333,9 @@
       <c r="PC61" s="5"/>
       <c r="PD61" s="5"/>
       <c r="PE61" s="5"/>
-      <c r="PF61" s="5"/>
+      <c r="PF61" s="5" t="n">
+        <v>484</v>
+      </c>
       <c r="PG61" s="5"/>
       <c r="PH61" s="5"/>
       <c r="PI61" s="5"/>
@@ -29660,7 +29776,9 @@
       <c r="PC62" s="5"/>
       <c r="PD62" s="5"/>
       <c r="PE62" s="5"/>
-      <c r="PF62" s="5"/>
+      <c r="PF62" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG62" s="5"/>
       <c r="PH62" s="5"/>
       <c r="PI62" s="5"/>
@@ -30101,7 +30219,9 @@
       <c r="PC63" s="5"/>
       <c r="PD63" s="5"/>
       <c r="PE63" s="5"/>
-      <c r="PF63" s="5"/>
+      <c r="PF63" s="5" t="s">
+        <v>429</v>
+      </c>
       <c r="PG63" s="5"/>
       <c r="PH63" s="5"/>
       <c r="PI63" s="5"/>
